--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">알바천국!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">풍년순대국밥!$A$1:$J$26</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="735">
   <si>
     <t>guild_name</t>
   </si>
@@ -300,7 +300,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 1221억 9952만</t>
+    <t>15조 2195억 3666만</t>
   </si>
   <si>
     <t>2</t>
@@ -318,57 +318,57 @@
     <t>신궁</t>
   </si>
   <si>
+    <t>14조 951억 2182만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>12조 6365억 3160만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>10조 7888억 6150만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>14조 951억 2182만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>12조 6365억 3160만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>10조 6714억 9011만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>9조 4831억 8007만</t>
   </si>
   <si>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>7조 3899억 9567만</t>
+    <t>8조 3534억 4319만</t>
   </si>
   <si>
     <t>7</t>
@@ -423,7 +423,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>5조 1472억 5810만</t>
+    <t>5조 1592억 3651만</t>
   </si>
   <si>
     <t>10</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>3조 8750억 1931만</t>
+    <t>4조 2089억 9652만</t>
   </si>
   <si>
     <t>12</t>
@@ -495,6 +495,21 @@
     <t>15</t>
   </si>
   <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>2조 5943억 9545만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
@@ -507,18 +522,6 @@
     <t>2조 5940억 8239만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>2조 5711억 1705만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -534,30 +537,27 @@
     <t>18</t>
   </si>
   <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>2조 5359억 851만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>꾸르꾸르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
     <t>2조 3765억 8123만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>2조 3302억 2720만</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
@@ -624,6 +624,18 @@
     <t>25</t>
   </si>
   <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>1조 8260억 5446만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>여눈</t>
   </si>
   <si>
@@ -633,7 +645,7 @@
     <t>1조 7856억 5439만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -645,18 +657,6 @@
     <t>1조 6923억 5834만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>1조 6435억 7464만</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
@@ -672,282 +672,270 @@
     <t>1조 2381억 1362만</t>
   </si>
   <si>
+    <t>증권보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>20조 4898억 61만</t>
+  </si>
+  <si>
+    <t>둥둥콩이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>19조 9942억 330만</t>
+  </si>
+  <si>
+    <t>가온스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17조 4585억 7977만</t>
+  </si>
+  <si>
+    <t>Canary</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Canary</t>
+  </si>
+  <si>
+    <t>15조 8193억 825만</t>
+  </si>
+  <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>13조 2156억 7422만</t>
+  </si>
+  <si>
+    <t>환생의불꼬츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>10조 9549억 8302만</t>
+  </si>
+  <si>
+    <t>밍진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
+  </si>
+  <si>
+    <t>8조 9166억 6911만</t>
+  </si>
+  <si>
+    <t>Naco</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Naco</t>
+  </si>
+  <si>
+    <t>6조 9849억 7135만</t>
+  </si>
+  <si>
+    <t>AKPS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
+  </si>
+  <si>
+    <t>6조 5629억 7412만</t>
+  </si>
+  <si>
+    <t>사나이기백황</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
+  </si>
+  <si>
+    <t>3조 8303억 3845만</t>
+  </si>
+  <si>
+    <t>토미오카상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
+  </si>
+  <si>
+    <t>3조 3002억 4541만</t>
+  </si>
+  <si>
+    <t>평평이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>3조 906억 3513만</t>
+  </si>
+  <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>2조 6702억 2482만</t>
+  </si>
+  <si>
+    <t>토니워터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
+  </si>
+  <si>
+    <t>2조 6162억 1545만</t>
+  </si>
+  <si>
+    <t>펑풀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
+  </si>
+  <si>
+    <t>2조 4885억 7115만</t>
+  </si>
+  <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 4258억 6186만</t>
+  </si>
+  <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 4177억 8071만</t>
+  </si>
+  <si>
+    <t>피어난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
+  </si>
+  <si>
+    <t>2조 305억 8537만</t>
+  </si>
+  <si>
+    <t>샤스찌에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
+  </si>
+  <si>
+    <t>1조 4976억 9640만</t>
+  </si>
+  <si>
+    <t>보동핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
+  </si>
+  <si>
+    <t>1조 1820억 5434만</t>
+  </si>
+  <si>
+    <t>싸토루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 1480억 9108만</t>
+  </si>
+  <si>
+    <t>지니좋아요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
+  </si>
+  <si>
+    <t>1조 666억 9786만</t>
+  </si>
+  <si>
+    <t>2026년1월30일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 129억 4198만</t>
+  </si>
+  <si>
+    <t>찐곽정근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>1조 24억 1640만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
+  </si>
+  <si>
+    <t>8747억 2403만</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Targa</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>5665억 5826만</t>
+  </si>
+  <si>
+    <t>애둘이에요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>5424억 3794만</t>
+  </si>
+  <si>
+    <t>짱창훈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
+  </si>
+  <si>
+    <t>3382억 604만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>혜영인기도1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81%EC%9D%B8%EA%B8%B0%EB%8F%841</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>11억 9359만</t>
-  </si>
-  <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>20조 4898억 61만</t>
-  </si>
-  <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>19조 9942억 330만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 4585억 7977만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>15조 8193억 825만</t>
-  </si>
-  <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>13조 2156억 7422만</t>
-  </si>
-  <si>
-    <t>환생의불꼬츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>10조 9549억 8302만</t>
-  </si>
-  <si>
-    <t>밍진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8조 9166억 6911만</t>
-  </si>
-  <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 9849억 7135만</t>
-  </si>
-  <si>
-    <t>AKPS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
-  </si>
-  <si>
-    <t>6조 5629억 7412만</t>
-  </si>
-  <si>
-    <t>사나이기백황</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
-  </si>
-  <si>
-    <t>3조 8303억 3845만</t>
-  </si>
-  <si>
-    <t>토미오카상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
-  </si>
-  <si>
-    <t>3조 3002억 4541만</t>
-  </si>
-  <si>
-    <t>평평이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>3조 906억 3513만</t>
-  </si>
-  <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>2조 6702억 2482만</t>
-  </si>
-  <si>
-    <t>토니워터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
-  </si>
-  <si>
-    <t>2조 6162억 1545만</t>
-  </si>
-  <si>
-    <t>펑풀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
-  </si>
-  <si>
-    <t>2조 4885억 7115만</t>
-  </si>
-  <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 4258억 6186만</t>
-  </si>
-  <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>2조 4177억 8071만</t>
-  </si>
-  <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>2조 305억 8537만</t>
-  </si>
-  <si>
-    <t>샤스찌에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
-  </si>
-  <si>
-    <t>1조 4976억 9640만</t>
-  </si>
-  <si>
-    <t>보동핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
-  </si>
-  <si>
-    <t>1조 1820억 5434만</t>
-  </si>
-  <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1조 1480억 9108만</t>
-  </si>
-  <si>
-    <t>지니좋아요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
-  </si>
-  <si>
-    <t>1조 666억 9786만</t>
-  </si>
-  <si>
-    <t>2026년1월30일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 129억 4198만</t>
-  </si>
-  <si>
-    <t>찐곽정근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>1조 24억 1640만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
-  </si>
-  <si>
-    <t>8747억 2403만</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Targa</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>5665억 5826만</t>
-  </si>
-  <si>
-    <t>애둘이에요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>5424억 3794만</t>
-  </si>
-  <si>
-    <t>짱창훈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
-  </si>
-  <si>
-    <t>3382억 604만</t>
-  </si>
-  <si>
     <t>구리구리뽕리</t>
   </si>
   <si>
@@ -1008,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
   </si>
   <si>
-    <t>4조 8099억 9932만</t>
+    <t>5조 2536억 3990만</t>
   </si>
   <si>
     <t>캐서린</t>
@@ -1053,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 9028억 9892만</t>
+    <t>3조 9211억 6160만</t>
   </si>
   <si>
     <t>졸귀</t>
@@ -1062,7 +1050,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
   </si>
   <si>
-    <t>3조 7479억 1222만</t>
+    <t>3조 8814억 6875만</t>
   </si>
   <si>
     <t>스파토이</t>
@@ -1074,6 +1062,15 @@
     <t>3조 1682억 6373만</t>
   </si>
   <si>
+    <t>YAMAMOTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
+  </si>
+  <si>
+    <t>3조 1669억 6472만</t>
+  </si>
+  <si>
     <t>픽홀로</t>
   </si>
   <si>
@@ -1083,15 +1080,6 @@
     <t>3조 727억 7187만</t>
   </si>
   <si>
-    <t>YAMAMOTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
-  </si>
-  <si>
-    <t>2조 9904억 3982만</t>
-  </si>
-  <si>
     <t>Rania</t>
   </si>
   <si>
@@ -1119,6 +1107,15 @@
     <t>2조 6406억 2681만</t>
   </si>
   <si>
+    <t>미진생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
+  </si>
+  <si>
+    <t>2조 3489억 4664만</t>
+  </si>
+  <si>
     <t>베르1</t>
   </si>
   <si>
@@ -1128,15 +1125,6 @@
     <t>2조 3313억 3223만</t>
   </si>
   <si>
-    <t>미진생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
-  </si>
-  <si>
-    <t>2조 2208억 3123만</t>
-  </si>
-  <si>
     <t>Uhani</t>
   </si>
   <si>
@@ -1197,7 +1185,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 6853억 2753만</t>
+    <t>1조 6886억 9312만</t>
   </si>
   <si>
     <t>도레스</t>
@@ -1227,7 +1215,7 @@
     <t>https://mgf.gg/contents/character.php?n=potato</t>
   </si>
   <si>
-    <t>8840억 8863만</t>
+    <t>9028억 2841만</t>
   </si>
   <si>
     <t>뀨래</t>
@@ -1998,7 +1986,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>74조 6379억 8782만</t>
+    <t>81조 3996억 4645만</t>
   </si>
   <si>
     <t>뽀대챠밍</t>
@@ -2007,7 +1995,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%8C%80%EC%B1%A0%EB%B0%8D</t>
   </si>
   <si>
-    <t>16조 6461억 6191만</t>
+    <t>16조 6533억 3835만</t>
   </si>
   <si>
     <t>신궝</t>
@@ -2073,6 +2061,15 @@
     <t>2조 6163억 1461만</t>
   </si>
   <si>
+    <t>기어피프스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%96%B4%ED%94%BC%ED%94%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>2조 5367억 3928만</t>
+  </si>
+  <si>
     <t>기둥1알2</t>
   </si>
   <si>
@@ -2082,15 +2079,6 @@
     <t>2조 4510억 6682만</t>
   </si>
   <si>
-    <t>기어피프스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%96%B4%ED%94%BC%ED%94%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>2조 2805억 2313만</t>
-  </si>
-  <si>
     <t>탱설</t>
   </si>
   <si>
@@ -2124,7 +2112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EC%A0%84%EC%82%AC</t>
   </si>
   <si>
-    <t>1조 4989억 7085만</t>
+    <t>1조 6291억 7772만</t>
   </si>
   <si>
     <t>Soul</t>
@@ -2238,7 +2226,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>1103억 3926만</t>
+    <t>1144억 1650만</t>
   </si>
   <si>
     <t>공쵸</t>
@@ -2247,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%B5%B8</t>
   </si>
   <si>
-    <t>878억 4235만</t>
+    <t>970억 8969만</t>
   </si>
 </sst>
 </file>
@@ -2971,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3071,10 +3059,10 @@
         <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3085,28 +3073,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3117,28 +3105,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3149,25 +3137,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>112</v>
@@ -3196,10 +3184,10 @@
         <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>116</v>
@@ -3228,7 +3216,7 @@
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>120</v>
@@ -3263,7 +3251,7 @@
         <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>126</v>
@@ -3295,7 +3283,7 @@
         <v>87</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>130</v>
@@ -3356,10 +3344,10 @@
         <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>140</v>
@@ -3423,7 +3411,7 @@
         <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>148</v>
@@ -3519,10 +3507,10 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3533,16 +3521,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -3554,7 +3542,7 @@
         <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3565,25 +3553,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>170</v>
@@ -3612,10 +3600,10 @@
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>174</v>
@@ -3647,7 +3635,7 @@
         <v>87</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>178</v>
@@ -3679,7 +3667,7 @@
         <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>182</v>
@@ -3711,7 +3699,7 @@
         <v>87</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>186</v>
@@ -3743,7 +3731,7 @@
         <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>190</v>
@@ -3775,7 +3763,7 @@
         <v>194</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>195</v>
@@ -3804,10 +3792,10 @@
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>199</v>
@@ -3836,10 +3824,10 @@
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>203</v>
@@ -3868,10 +3856,10 @@
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>207</v>
@@ -3912,40 +3900,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3975,7 +3931,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4036,13 +3991,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
@@ -4054,7 +4009,7 @@
         <v>120</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -4068,25 +4023,25 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4097,16 +4052,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -4118,7 +4073,7 @@
         <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4129,16 +4084,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -4150,7 +4105,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4161,16 +4116,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -4179,10 +4134,10 @@
         <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4196,13 +4151,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -4211,10 +4166,10 @@
         <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4228,13 +4183,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -4243,10 +4198,10 @@
         <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4260,13 +4215,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -4275,10 +4230,10 @@
         <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4292,25 +4247,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4324,25 +4279,25 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4356,13 +4311,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -4371,10 +4326,10 @@
         <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4388,13 +4343,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -4403,10 +4358,10 @@
         <v>87</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4420,25 +4375,25 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4452,13 +4407,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -4467,10 +4422,10 @@
         <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4484,13 +4439,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -4499,10 +4454,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4516,25 +4471,25 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4545,16 +4500,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -4566,7 +4521,7 @@
         <v>211</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4577,28 +4532,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4612,13 +4567,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -4630,7 +4585,7 @@
         <v>211</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4644,25 +4599,25 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4676,25 +4631,25 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4708,13 +4663,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -4726,7 +4681,7 @@
         <v>211</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4740,13 +4695,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -4758,7 +4713,7 @@
         <v>211</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4772,25 +4727,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4810,7 +4765,7 @@
         <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>86</v>
@@ -4819,10 +4774,10 @@
         <v>134</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4836,13 +4791,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -4851,10 +4806,10 @@
         <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4868,13 +4823,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -4883,10 +4838,10 @@
         <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4900,13 +4855,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -4915,10 +4870,10 @@
         <v>125</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4929,28 +4884,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -5054,7 +5009,7 @@
         <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -5066,7 +5021,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5080,13 +5035,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -5095,10 +5050,10 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5109,28 +5064,28 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5141,16 +5096,16 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -5159,10 +5114,10 @@
         <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5173,16 +5128,16 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -5194,7 +5149,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5208,13 +5163,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -5223,10 +5178,10 @@
         <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5240,25 +5195,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5272,13 +5227,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -5287,10 +5242,10 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5304,25 +5259,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5336,13 +5291,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -5351,10 +5306,10 @@
         <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5368,13 +5323,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -5386,7 +5341,7 @@
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5400,13 +5355,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -5418,7 +5373,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5432,13 +5387,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -5447,10 +5402,10 @@
         <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5464,25 +5419,25 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5496,25 +5451,25 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5528,13 +5483,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -5543,10 +5498,10 @@
         <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5557,16 +5512,16 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -5575,10 +5530,10 @@
         <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5589,16 +5544,16 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -5607,10 +5562,10 @@
         <v>134</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5624,25 +5579,25 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5656,25 +5611,25 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5688,13 +5643,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -5703,10 +5658,10 @@
         <v>87</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5720,13 +5675,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -5735,10 +5690,10 @@
         <v>134</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5752,25 +5707,25 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5784,25 +5739,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5816,13 +5771,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -5831,10 +5786,10 @@
         <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5848,25 +5803,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5880,13 +5835,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -5895,10 +5850,10 @@
         <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5912,13 +5867,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -5927,10 +5882,10 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5941,16 +5896,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -5959,10 +5914,10 @@
         <v>87</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5973,16 +5928,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -5991,10 +5946,10 @@
         <v>125</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6093,25 +6048,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6125,13 +6080,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -6140,10 +6095,10 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6154,16 +6109,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -6175,7 +6130,7 @@
         <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6186,16 +6141,16 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -6207,7 +6162,7 @@
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6218,28 +6173,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6253,13 +6208,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -6268,10 +6223,10 @@
         <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6285,25 +6240,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6317,13 +6272,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -6332,10 +6287,10 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6349,25 +6304,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6381,13 +6336,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -6396,10 +6351,10 @@
         <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6413,25 +6368,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6451,19 +6406,19 @@
         <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6477,25 +6432,25 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -6509,13 +6464,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -6524,10 +6479,10 @@
         <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6541,13 +6496,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -6559,7 +6514,7 @@
         <v>211</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6573,13 +6528,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -6588,10 +6543,10 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6602,28 +6557,28 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -6634,16 +6589,16 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -6652,10 +6607,10 @@
         <v>87</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6669,13 +6624,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -6684,10 +6639,10 @@
         <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6701,13 +6656,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -6719,7 +6674,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6733,13 +6688,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -6751,7 +6706,7 @@
         <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6765,13 +6720,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -6780,10 +6735,10 @@
         <v>87</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6797,13 +6752,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -6812,10 +6767,10 @@
         <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6829,25 +6784,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6861,13 +6816,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -6876,10 +6831,10 @@
         <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6893,13 +6848,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -6911,7 +6866,7 @@
         <v>211</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6925,25 +6880,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6957,13 +6912,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -6975,7 +6930,7 @@
         <v>211</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -6986,16 +6941,16 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -7004,10 +6959,10 @@
         <v>87</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -7018,16 +6973,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -7036,10 +6991,10 @@
         <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -7138,25 +7093,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -7170,13 +7125,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -7185,10 +7140,10 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -7199,16 +7154,16 @@
         <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -7217,10 +7172,10 @@
         <v>87</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -7231,28 +7186,28 @@
         <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -7263,16 +7218,16 @@
         <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -7281,10 +7236,10 @@
         <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -7298,13 +7253,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -7316,7 +7271,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -7336,7 +7291,7 @@
         <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -7345,10 +7300,10 @@
         <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -7362,13 +7317,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -7380,7 +7335,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -7394,25 +7349,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -7426,25 +7381,25 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -7458,13 +7413,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -7473,10 +7428,10 @@
         <v>87</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7490,13 +7445,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -7505,10 +7460,10 @@
         <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7522,13 +7477,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -7537,10 +7492,10 @@
         <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7554,13 +7509,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -7572,7 +7527,7 @@
         <v>211</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7586,13 +7541,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -7604,7 +7559,7 @@
         <v>211</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7618,13 +7573,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -7633,10 +7588,10 @@
         <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7647,28 +7602,28 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7679,28 +7634,28 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7714,25 +7669,25 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7746,25 +7701,25 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7778,25 +7733,25 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7810,25 +7765,25 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7842,13 +7797,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -7857,10 +7812,10 @@
         <v>87</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7874,25 +7829,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7906,13 +7861,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -7921,10 +7876,10 @@
         <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7938,13 +7893,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -7953,10 +7908,10 @@
         <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7970,13 +7925,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -7985,10 +7940,10 @@
         <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -8002,25 +7957,25 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -8031,28 +7986,28 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -8063,16 +8018,16 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -8081,10 +8036,10 @@
         <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -8189,19 +8144,19 @@
         <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8215,13 +8170,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -8230,10 +8185,10 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8244,16 +8199,16 @@
         <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -8262,10 +8217,10 @@
         <v>125</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8276,16 +8231,16 @@
         <v>60</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -8294,10 +8249,10 @@
         <v>87</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8308,16 +8263,16 @@
         <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -8329,7 +8284,7 @@
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8343,25 +8298,25 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8375,13 +8330,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -8390,10 +8345,10 @@
         <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8407,25 +8362,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8439,13 +8394,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -8454,10 +8409,10 @@
         <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8471,13 +8426,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -8489,7 +8444,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8503,25 +8458,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8535,13 +8490,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -8550,10 +8505,10 @@
         <v>87</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8567,25 +8522,25 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8599,25 +8554,25 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8631,25 +8586,25 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8663,13 +8618,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -8681,7 +8636,7 @@
         <v>135</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8692,16 +8647,16 @@
         <v>60</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -8713,7 +8668,7 @@
         <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8724,16 +8679,16 @@
         <v>60</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -8745,7 +8700,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8759,13 +8714,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -8774,10 +8729,10 @@
         <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8791,13 +8746,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -8806,10 +8761,10 @@
         <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8823,25 +8778,25 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8855,25 +8810,25 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8887,25 +8842,25 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8919,25 +8874,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8951,13 +8906,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -8966,10 +8921,10 @@
         <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9069,7 +9024,7 @@
         <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -9078,10 +9033,10 @@
         <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9095,25 +9050,25 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9124,16 +9079,16 @@
         <v>68</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -9142,10 +9097,10 @@
         <v>94</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9156,28 +9111,28 @@
         <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9188,28 +9143,28 @@
         <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9223,13 +9178,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -9241,7 +9196,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9255,13 +9210,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -9270,10 +9225,10 @@
         <v>134</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9287,13 +9242,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -9302,10 +9257,10 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9319,13 +9274,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -9337,7 +9292,7 @@
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9351,13 +9306,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -9366,10 +9321,10 @@
         <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9383,13 +9338,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -9398,10 +9353,10 @@
         <v>125</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9415,13 +9370,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -9430,10 +9385,10 @@
         <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9447,13 +9402,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -9462,10 +9417,10 @@
         <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9479,13 +9434,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -9494,10 +9449,10 @@
         <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9511,13 +9466,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -9526,10 +9481,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9543,13 +9498,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -9558,10 +9513,10 @@
         <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9572,28 +9527,28 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9604,16 +9559,16 @@
         <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -9625,7 +9580,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9639,13 +9594,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -9654,10 +9609,10 @@
         <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9671,13 +9626,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -9689,7 +9644,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9703,13 +9658,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -9718,10 +9673,10 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9735,25 +9690,25 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9767,25 +9722,25 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9799,25 +9754,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9831,13 +9786,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -9846,10 +9801,10 @@
         <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9863,25 +9818,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9895,13 +9850,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -9910,10 +9865,10 @@
         <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9927,13 +9882,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -9942,10 +9897,10 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -1770,7 +1770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%B8%84%ED%95%91</t>
   </si>
   <si>
-    <t>16조 2006억 7084만</t>
+    <t>16조 4918억 4615만</t>
   </si>
   <si>
     <t>걀보</t>
@@ -1791,6 +1791,15 @@
     <t>3조 5196억 4046만</t>
   </si>
   <si>
+    <t>랏뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>3조 1258억 3830만</t>
+  </si>
+  <si>
     <t>왕오이</t>
   </si>
   <si>
@@ -1800,13 +1809,13 @@
     <t>3조 78억 6848만</t>
   </si>
   <si>
-    <t>랏뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>2조 9878억 9689만</t>
+    <t>그냐앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%83%90%EC%95%99</t>
+  </si>
+  <si>
+    <t>2조 6959억 3259만</t>
   </si>
   <si>
     <t>이호은</t>
@@ -1836,15 +1845,6 @@
     <t>2조 5975억 5879만</t>
   </si>
   <si>
-    <t>그냐앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%83%90%EC%95%99</t>
-  </si>
-  <si>
-    <t>2조 5586억 3591만</t>
-  </si>
-  <si>
     <t>하깁s</t>
   </si>
   <si>
@@ -1860,7 +1860,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%A0%9C</t>
   </si>
   <si>
-    <t>2조 3811억 4994만</t>
+    <t>2조 4181억 16만</t>
   </si>
   <si>
     <t>은디탁</t>
@@ -1896,7 +1896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%AA%A8%EC%88%98%EB%B0%95</t>
   </si>
   <si>
-    <t>1조 9032억 8552만</t>
+    <t>1조 9175억 6016만</t>
   </si>
   <si>
     <t>부라</t>
@@ -1905,7 +1905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EB%9D%BC</t>
   </si>
   <si>
-    <t>1조 4029억 9332만</t>
+    <t>1조 4308억 7074만</t>
   </si>
   <si>
     <t>늙은마</t>
@@ -1914,7 +1914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8A%99%EC%9D%80%EB%A7%88</t>
   </si>
   <si>
-    <t>1조 3664억 3029만</t>
+    <t>1조 3816억 6012만</t>
   </si>
   <si>
     <t>라이언킹</t>
@@ -1932,7 +1932,7 @@
     <t>https://mgf.gg/contents/character.php?n=jinajina</t>
   </si>
   <si>
-    <t>1조 596억 5673만</t>
+    <t>1조 798억 1637만</t>
   </si>
   <si>
     <t>덕장이다습할</t>
@@ -1950,7 +1950,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%A0%EC%84%9D</t>
   </si>
   <si>
-    <t>9895억 7608만</t>
+    <t>1조 18억 5366만</t>
   </si>
   <si>
     <t>뿌베</t>
@@ -1959,7 +1959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%B2%A0</t>
   </si>
   <si>
-    <t>8781억 6967만</t>
+    <t>8847억 5595만</t>
   </si>
   <si>
     <t>챵술사</t>
@@ -8278,10 +8278,10 @@
         <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>588</v>
@@ -8310,10 +8310,10 @@
         <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>591</v>
@@ -8342,10 +8342,10 @@
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>594</v>
@@ -8374,10 +8374,10 @@
         <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>421</v>
+        <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>597</v>
@@ -8406,10 +8406,10 @@
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>421</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>600</v>
@@ -8441,7 +8441,7 @@
         <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>603</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'0FeroCity'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="729">
   <si>
     <t>guild_name</t>
   </si>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%ED%82%A5</t>
   </si>
   <si>
-    <t>5조 1554억 7179만</t>
+    <t>5조 2369억 9813만</t>
   </si>
   <si>
     <t>아옳옳</t>
@@ -1269,7 +1269,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%82%90%EC%98%88%EC%82%90</t>
   </si>
   <si>
-    <t>4조 3651억 8877만</t>
+    <t>4조 3725억 6768만</t>
   </si>
   <si>
     <t>나영석PDD</t>
@@ -1332,7 +1332,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8A%BC%ED%8A%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 6649억 5816만</t>
+    <t>1조 8056억 5657만</t>
   </si>
   <si>
     <t>전뱀</t>
@@ -1350,7 +1350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A6%88%EC%83%A4</t>
   </si>
   <si>
-    <t>1조 5502억 907만</t>
+    <t>1조 5525억 9388만</t>
   </si>
   <si>
     <t>갓겜이네메키</t>
@@ -1368,7 +1368,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%98%81%EC%A7%84</t>
   </si>
   <si>
-    <t>1조 3082억 4870만</t>
+    <t>1조 3086억 2532만</t>
   </si>
   <si>
     <t>몰랑초이</t>
@@ -1386,7 +1386,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%95%EC%A0%9C%EC%9C%A1%EA%B2%80</t>
   </si>
   <si>
-    <t>1조 1937억 6870만</t>
+    <t>1조 1974억 7786만</t>
   </si>
   <si>
     <t>말랑초이</t>
@@ -1413,7 +1413,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%ED%98%88%EB%8B%A8%EB%98%90</t>
   </si>
   <si>
-    <t>1조 713억 5364만</t>
+    <t>1조 857억 4649만</t>
   </si>
   <si>
     <t>Lim1t</t>
@@ -1443,15 +1443,6 @@
     <t>8767억 2508만</t>
   </si>
   <si>
-    <t>꽁꽁대마법사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EA%BD%81%EB%8C%80%EB%A7%88%EB%B2%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>8597억 9102만</t>
-  </si>
-  <si>
     <t>갱기님</t>
   </si>
   <si>
@@ -1467,16 +1458,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%ED%95%A9%EC%99%95</t>
   </si>
   <si>
-    <t>6721억 9754만</t>
-  </si>
-  <si>
-    <t>무카무카</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%B9%B4%EB%AC%B4%EC%B9%B4</t>
-  </si>
-  <si>
-    <t>3714억 9082만</t>
+    <t>6840억 1868만</t>
   </si>
   <si>
     <t>당양감</t>
@@ -1494,7 +1476,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%82%B4%EA%BC%AC%EC%96%91</t>
   </si>
   <si>
-    <t>44조 2369억 5678만</t>
+    <t>46조 7631억 7929만</t>
   </si>
   <si>
     <t>으닝닝맛섀도</t>
@@ -1512,7 +1494,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%98%EB%A6%ACv</t>
   </si>
   <si>
-    <t>15조 9087억 9473만</t>
+    <t>17조 1015억 3470만</t>
   </si>
   <si>
     <t>oFero라온o</t>
@@ -1530,7 +1512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%9D%B4%EC%81%A0%ED%82%A4%EC%9A%B0%EA%B9%85</t>
   </si>
   <si>
-    <t>6조 6329억 6628만</t>
+    <t>7조 1097억 2958만</t>
   </si>
   <si>
     <t>용이지니</t>
@@ -1539,7 +1521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4%EC%A7%80%EB%8B%88</t>
   </si>
   <si>
-    <t>4조 7494억 9458만</t>
+    <t>5조 666억 7809만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=oFero%EC%9B%94%ED%96%A5o</t>
@@ -1611,6 +1593,15 @@
     <t>1조 1730억 3808만</t>
   </si>
   <si>
+    <t>격통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A9%ED%86%B5</t>
+  </si>
+  <si>
+    <t>1조 1121억 9129만</t>
+  </si>
+  <si>
     <t>음묘우</t>
   </si>
   <si>
@@ -1620,22 +1611,13 @@
     <t>1조 211억 7612만</t>
   </si>
   <si>
-    <t>격통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A9%ED%86%B5</t>
-  </si>
-  <si>
-    <t>1조 4687만</t>
-  </si>
-  <si>
     <t>로절린드</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%A0%88%EB%A6%B0%EB%93%9C</t>
   </si>
   <si>
-    <t>9309억 1527만</t>
+    <t>9603억 4965만</t>
   </si>
   <si>
     <t>댕댕이완자</t>
@@ -1644,7 +1626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%95%EB%8C%95%EC%9D%B4%EC%99%84%EC%9E%90</t>
   </si>
   <si>
-    <t>8862억 2245만</t>
+    <t>8894억 6832만</t>
   </si>
   <si>
     <t>짱숍</t>
@@ -1680,7 +1662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%9D%BC%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
   </si>
   <si>
-    <t>6952억 2206만</t>
+    <t>7585억 1763만</t>
   </si>
   <si>
     <t>귀흑</t>
@@ -1707,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EB%8B%88</t>
   </si>
   <si>
-    <t>5398억 7985만</t>
+    <t>5459억 4798만</t>
   </si>
   <si>
     <t>솜쥬멐</t>
@@ -1734,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EA%B3%B5%EC%A3%BC</t>
   </si>
   <si>
-    <t>5050억 2198만</t>
+    <t>5054억 9265만</t>
   </si>
   <si>
     <t>녕죠</t>
@@ -5995,7 +5977,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6447,7 +6429,7 @@
         <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>433</v>
@@ -6860,10 +6842,10 @@
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>211</v>
+        <v>291</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>472</v>
@@ -6892,10 +6874,10 @@
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>291</v>
+        <v>161</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>475</v>
@@ -6924,10 +6906,10 @@
         <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>211</v>
+        <v>295</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>478</v>
@@ -6936,72 +6918,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7031,8 +6949,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7093,13 +7009,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
@@ -7111,7 +7027,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -7125,13 +7041,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -7143,7 +7059,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -7157,13 +7073,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -7175,7 +7091,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -7189,13 +7105,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -7207,7 +7123,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -7221,13 +7137,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -7239,7 +7155,7 @@
         <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -7253,13 +7169,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -7271,7 +7187,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -7291,7 +7207,7 @@
         <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -7303,7 +7219,7 @@
         <v>156</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -7317,13 +7233,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -7335,7 +7251,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -7349,13 +7265,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -7367,7 +7283,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -7381,13 +7297,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -7399,7 +7315,7 @@
         <v>161</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -7413,13 +7329,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -7431,7 +7347,7 @@
         <v>161</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7445,13 +7361,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -7463,7 +7379,7 @@
         <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7477,13 +7393,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -7495,7 +7411,7 @@
         <v>161</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7509,13 +7425,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -7527,7 +7443,7 @@
         <v>211</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7541,25 +7457,25 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7573,25 +7489,25 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7605,13 +7521,13 @@
         <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -7623,7 +7539,7 @@
         <v>161</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7637,13 +7553,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -7655,7 +7571,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7669,13 +7585,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -7687,7 +7603,7 @@
         <v>161</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7701,13 +7617,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -7719,7 +7635,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7733,13 +7649,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -7751,7 +7667,7 @@
         <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7765,13 +7681,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -7783,7 +7699,7 @@
         <v>211</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7797,13 +7713,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -7815,7 +7731,7 @@
         <v>276</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7829,13 +7745,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -7847,7 +7763,7 @@
         <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7861,13 +7777,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -7879,7 +7795,7 @@
         <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7893,13 +7809,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -7911,7 +7827,7 @@
         <v>276</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7925,13 +7841,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -7943,7 +7859,7 @@
         <v>291</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7957,13 +7873,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -7975,7 +7891,7 @@
         <v>276</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -7989,13 +7905,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -8007,7 +7923,7 @@
         <v>276</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -8021,13 +7937,13 @@
         <v>391</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -8036,10 +7952,10 @@
         <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -8144,7 +8060,7 @@
         <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -8156,7 +8072,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8170,13 +8086,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -8188,7 +8104,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8202,13 +8118,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -8220,7 +8136,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8234,13 +8150,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -8252,7 +8168,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8266,13 +8182,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -8284,7 +8200,7 @@
         <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8298,13 +8214,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -8316,7 +8232,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8330,13 +8246,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -8348,7 +8264,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8362,13 +8278,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -8380,7 +8296,7 @@
         <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8394,13 +8310,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -8412,7 +8328,7 @@
         <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8426,13 +8342,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -8444,7 +8360,7 @@
         <v>156</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8458,13 +8374,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -8476,7 +8392,7 @@
         <v>156</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8490,13 +8406,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -8508,7 +8424,7 @@
         <v>156</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8522,13 +8438,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -8540,7 +8456,7 @@
         <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8554,13 +8470,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -8572,7 +8488,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8586,13 +8502,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -8604,7 +8520,7 @@
         <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8618,13 +8534,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -8636,7 +8552,7 @@
         <v>135</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8650,13 +8566,13 @@
         <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -8668,7 +8584,7 @@
         <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8682,13 +8598,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -8700,7 +8616,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8714,13 +8630,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -8732,7 +8648,7 @@
         <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8746,13 +8662,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -8764,7 +8680,7 @@
         <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8778,13 +8694,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -8796,7 +8712,7 @@
         <v>156</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8810,13 +8726,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -8828,7 +8744,7 @@
         <v>161</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8842,13 +8758,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -8860,7 +8776,7 @@
         <v>276</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8874,13 +8790,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -8892,7 +8808,7 @@
         <v>156</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8906,13 +8822,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -8924,7 +8840,7 @@
         <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9024,7 +8940,7 @@
         <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -9033,10 +8949,10 @@
         <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9050,13 +8966,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -9068,7 +8984,7 @@
         <v>120</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9082,13 +8998,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -9100,7 +9016,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9114,13 +9030,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -9132,7 +9048,7 @@
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9146,13 +9062,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -9164,7 +9080,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9178,13 +9094,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -9196,7 +9112,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9210,13 +9126,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -9228,7 +9144,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9242,13 +9158,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -9260,7 +9176,7 @@
         <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9274,13 +9190,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -9292,7 +9208,7 @@
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9306,13 +9222,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -9324,7 +9240,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9338,13 +9254,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -9356,7 +9272,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9370,13 +9286,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -9388,7 +9304,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9402,13 +9318,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -9420,7 +9336,7 @@
         <v>161</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9434,13 +9350,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -9452,7 +9368,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9466,13 +9382,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -9484,7 +9400,7 @@
         <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9498,13 +9414,13 @@
         <v>158</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -9516,7 +9432,7 @@
         <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9530,13 +9446,13 @@
         <v>163</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -9548,7 +9464,7 @@
         <v>276</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9562,13 +9478,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -9580,7 +9496,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9594,13 +9510,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -9612,7 +9528,7 @@
         <v>276</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9626,13 +9542,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -9644,7 +9560,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9658,13 +9574,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -9676,7 +9592,7 @@
         <v>276</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9690,13 +9606,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -9705,10 +9621,10 @@
         <v>421</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9722,13 +9638,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -9737,10 +9653,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9754,13 +9670,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -9769,10 +9685,10 @@
         <v>421</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9786,13 +9702,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -9804,7 +9720,7 @@
         <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9818,13 +9734,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -9833,10 +9749,10 @@
         <v>421</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9850,13 +9766,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -9865,10 +9781,10 @@
         <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9882,13 +9798,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -9897,10 +9813,10 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -777,7 +777,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>3조 906억 3513만</t>
+    <t>3조 2987억 2385만</t>
   </si>
   <si>
     <t>천칠</t>
@@ -792,6 +792,15 @@
     <t>2조 6702억 2482만</t>
   </si>
   <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 6240억 7775만</t>
+  </si>
+  <si>
     <t>토니워터</t>
   </si>
   <si>
@@ -807,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
   </si>
   <si>
-    <t>2조 4885억 7115만</t>
+    <t>2조 4991억 587만</t>
   </si>
   <si>
     <t>화살대</t>
@@ -819,15 +828,6 @@
     <t>2조 4258억 6186만</t>
   </si>
   <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>2조 4177억 8071만</t>
-  </si>
-  <si>
     <t>피어난</t>
   </si>
   <si>
@@ -843,7 +843,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
   </si>
   <si>
-    <t>1조 4976억 9640만</t>
+    <t>1조 5997억 4972만</t>
+  </si>
+  <si>
+    <t>싸토루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 2713억 5948만</t>
   </si>
   <si>
     <t>보동핑</t>
@@ -852,19 +864,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 1820억 5434만</t>
-  </si>
-  <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1조 1480억 9108만</t>
+    <t>1조 1840억 5819만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -897,7 +897,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
   </si>
   <si>
-    <t>8747억 2403만</t>
+    <t>8949억 860만</t>
   </si>
   <si>
     <t>Targa</t>
@@ -4401,10 +4401,10 @@
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>255</v>
@@ -4433,7 +4433,7 @@
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>161</v>
@@ -4465,10 +4465,10 @@
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>261</v>
@@ -4497,10 +4497,10 @@
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>264</v>
@@ -4596,10 +4596,10 @@
         <v>99</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4613,13 +4613,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -4628,7 +4628,7 @@
         <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>276</v>
+        <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>277</v>
@@ -4724,7 +4724,7 @@
         <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>286</v>
@@ -4756,7 +4756,7 @@
         <v>134</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>288</v>
@@ -6621,7 +6621,7 @@
         <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>451</v>
@@ -6781,7 +6781,7 @@
         <v>105</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>466</v>
@@ -6813,7 +6813,7 @@
         <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>469</v>
@@ -7728,7 +7728,7 @@
         <v>87</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>546</v>
@@ -7760,7 +7760,7 @@
         <v>421</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>549</v>
@@ -7792,7 +7792,7 @@
         <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>552</v>
@@ -7824,7 +7824,7 @@
         <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>555</v>
@@ -7888,7 +7888,7 @@
         <v>421</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>561</v>
@@ -7920,7 +7920,7 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>564</v>
@@ -8773,7 +8773,7 @@
         <v>99</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>636</v>
@@ -8837,7 +8837,7 @@
         <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>642</v>
@@ -9461,7 +9461,7 @@
         <v>421</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>693</v>
@@ -9525,7 +9525,7 @@
         <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>699</v>
@@ -9589,7 +9589,7 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>705</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'0FeroCity'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="726">
   <si>
     <t>guild_name</t>
   </si>
@@ -300,7 +300,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 2195억 3666만</t>
+    <t>16조 7401억 1193만</t>
   </si>
   <si>
     <t>2</t>
@@ -351,7 +351,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>10조 7888억 6150만</t>
+    <t>10조 8032억 4305만</t>
   </si>
   <si>
     <t>5</t>
@@ -369,7 +369,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>9조 4831억 8007만</t>
+    <t>9조 7714억 2550만</t>
   </si>
   <si>
     <t>6</t>
@@ -381,7 +381,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>8조 3534억 4319만</t>
+    <t>8조 3610억 5502만</t>
   </si>
   <si>
     <t>7</t>
@@ -411,7 +411,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>5조 1968억 8766만</t>
+    <t>6조 62억 9031만</t>
   </si>
   <si>
     <t>9</t>
@@ -477,12 +477,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>3조 175억 79만</t>
+    <t>3조 2011억 997만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>2조 7171억 6721만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>쭌파파</t>
   </si>
   <si>
@@ -492,7 +504,7 @@
     <t>2조 6747억 6521만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -507,7 +519,7 @@
     <t>2조 5943억 9545만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -522,7 +534,7 @@
     <t>2조 5940억 8239만</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>강철고튠데</t>
@@ -534,18 +546,6 @@
     <t>2조 5595억 2만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>2조 5359억 851만</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
@@ -654,7 +654,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>1조 6923억 5834만</t>
+    <t>1조 7536억 1673만</t>
   </si>
   <si>
     <t>28</t>
@@ -672,6 +672,15 @@
     <t>1조 2381억 1362만</t>
   </si>
   <si>
+    <t>둥둥콩이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>21조 1132억 4874만</t>
+  </si>
+  <si>
     <t>증권보이</t>
   </si>
   <si>
@@ -681,15 +690,6 @@
     <t>20조 4898억 61만</t>
   </si>
   <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>19조 9942억 330만</t>
-  </si>
-  <si>
     <t>가온스</t>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <t>https://mgf.gg/contents/character.php?n=Canary</t>
   </si>
   <si>
-    <t>15조 8193억 825만</t>
+    <t>15조 9076억 6397만</t>
   </si>
   <si>
     <t>처히</t>
@@ -714,7 +714,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
   </si>
   <si>
-    <t>13조 2156억 7422만</t>
+    <t>13조 2232억 3999만</t>
   </si>
   <si>
     <t>환생의불꼬츠</t>
@@ -798,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
   </si>
   <si>
-    <t>2조 6240억 7775만</t>
+    <t>2조 6252억 4217만</t>
   </si>
   <si>
     <t>토니워터</t>
@@ -810,6 +810,15 @@
     <t>2조 6162억 1545만</t>
   </si>
   <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 5729억 5642만</t>
+  </si>
+  <si>
     <t>펑풀</t>
   </si>
   <si>
@@ -819,15 +828,6 @@
     <t>2조 4991억 587만</t>
   </si>
   <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 4258억 6186만</t>
-  </si>
-  <si>
     <t>피어난</t>
   </si>
   <si>
@@ -852,45 +852,45 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
   </si>
   <si>
+    <t>1조 3657억 2295만</t>
+  </si>
+  <si>
+    <t>보동핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
+  </si>
+  <si>
+    <t>1조 1840억 5819만</t>
+  </si>
+  <si>
+    <t>지니좋아요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
+  </si>
+  <si>
+    <t>1조 666억 9786만</t>
+  </si>
+  <si>
+    <t>2026년1월30일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 129억 4198만</t>
+  </si>
+  <si>
+    <t>찐곽정근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
     <t>95</t>
   </si>
   <si>
-    <t>1조 2713억 5948만</t>
-  </si>
-  <si>
-    <t>보동핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
-  </si>
-  <si>
-    <t>1조 1840억 5819만</t>
-  </si>
-  <si>
-    <t>지니좋아요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
-  </si>
-  <si>
-    <t>1조 666억 9786만</t>
-  </si>
-  <si>
-    <t>2026년1월30일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 129억 4198만</t>
-  </si>
-  <si>
-    <t>찐곽정근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
     <t>1조 24억 1640만</t>
   </si>
   <si>
@@ -951,7 +951,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>31조 4225억 3427만</t>
+    <t>32조 9473억 5428만</t>
   </si>
   <si>
     <t>소독약</t>
@@ -969,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>9조 5512억 2267만</t>
+    <t>12조 2134억 7541만</t>
   </si>
   <si>
     <t>휘정</t>
@@ -1014,7 +1014,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
   </si>
   <si>
-    <t>4조 6426억 6903만</t>
+    <t>4조 7044억 1961만</t>
   </si>
   <si>
     <t>강린</t>
@@ -1041,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 9211억 6160만</t>
+    <t>4조 372억 1982만</t>
   </si>
   <si>
     <t>졸귀</t>
@@ -1050,7 +1050,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
   </si>
   <si>
-    <t>3조 8814억 6875만</t>
+    <t>3조 9023억 745만</t>
   </si>
   <si>
     <t>스파토이</t>
@@ -1059,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 1682억 6373만</t>
+    <t>3조 2857억 8502만</t>
   </si>
   <si>
     <t>YAMAMOTO</t>
@@ -1080,6 +1080,15 @@
     <t>3조 727억 7187만</t>
   </si>
   <si>
+    <t>쟈라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>2조 9098억 1790만</t>
+  </si>
+  <si>
     <t>Rania</t>
   </si>
   <si>
@@ -1098,22 +1107,13 @@
     <t>2조 6490억 9667만</t>
   </si>
   <si>
-    <t>쟈라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>2조 6406억 2681만</t>
-  </si>
-  <si>
     <t>미진생</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
   </si>
   <si>
-    <t>2조 3489억 4664만</t>
+    <t>2조 3948억 1791만</t>
   </si>
   <si>
     <t>베르1</t>
@@ -1152,6 +1152,15 @@
     <t>1조 9072억 8066만</t>
   </si>
   <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1조 8429억 3125만</t>
+  </si>
+  <si>
     <t>별렉스b</t>
   </si>
   <si>
@@ -1161,13 +1170,13 @@
     <t>1조 8408억 8307만</t>
   </si>
   <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1조 8221억 8909만</t>
+    <t>양설유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 7462억 7709만</t>
   </si>
   <si>
     <t>가이아의격노</t>
@@ -1179,15 +1188,6 @@
     <t>1조 7212억 2724만</t>
   </si>
   <si>
-    <t>양설유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 6886억 9312만</t>
-  </si>
-  <si>
     <t>도레스</t>
   </si>
   <si>
@@ -1233,7 +1233,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EA%B2%A1</t>
   </si>
   <si>
-    <t>24조 8109억 8856만</t>
+    <t>24조 8464억 3573만</t>
   </si>
   <si>
     <t>과학실</t>
@@ -1242,7 +1242,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%ED%95%99%EC%8B%A4</t>
   </si>
   <si>
-    <t>16조 4231억 8160만</t>
+    <t>18조 8526억 4330만</t>
   </si>
   <si>
     <t>우주킥</t>
@@ -1251,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%ED%82%A5</t>
   </si>
   <si>
-    <t>5조 2369억 9813만</t>
+    <t>5조 2485억 7572만</t>
   </si>
   <si>
     <t>아옳옳</t>
@@ -1269,7 +1269,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%82%90%EC%98%88%EC%82%90</t>
   </si>
   <si>
-    <t>4조 3725억 6768만</t>
+    <t>4조 3733억 5098만</t>
   </si>
   <si>
     <t>나영석PDD</t>
@@ -1299,7 +1299,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>3조 1382억 9169만</t>
+    <t>3조 1832억 4975만</t>
   </si>
   <si>
     <t>꾸레밈</t>
@@ -1308,22 +1308,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A0%88%EB%B0%88</t>
   </si>
   <si>
-    <t>2조 8446억 5375만</t>
-  </si>
-  <si>
-    <t>백샤샥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%83%A4%EC%83%A5</t>
-  </si>
-  <si>
-    <t>2조 6717억 5668만</t>
+    <t>2조 8975억 7445만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%8B%88%EC%9D%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 3626억 1482만</t>
+    <t>2조 4730억 6872만</t>
   </si>
   <si>
     <t>서튼튼이</t>
@@ -1332,7 +1323,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8A%BC%ED%8A%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8056억 5657만</t>
+    <t>1조 8283억 1974만</t>
   </si>
   <si>
     <t>전뱀</t>
@@ -1350,7 +1341,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A6%88%EC%83%A4</t>
   </si>
   <si>
-    <t>1조 5525억 9388만</t>
+    <t>1조 5996억 6660만</t>
+  </si>
+  <si>
+    <t>하영진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%98%81%EC%A7%84</t>
+  </si>
+  <si>
+    <t>1조 3304억 8558만</t>
   </si>
   <si>
     <t>갓겜이네메키</t>
@@ -1362,15 +1362,6 @@
     <t>1조 3132억 1135만</t>
   </si>
   <si>
-    <t>하영진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%98%81%EC%A7%84</t>
-  </si>
-  <si>
-    <t>1조 3086억 2532만</t>
-  </si>
-  <si>
     <t>몰랑초이</t>
   </si>
   <si>
@@ -1440,7 +1431,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC</t>
   </si>
   <si>
-    <t>8767억 2508만</t>
+    <t>8772억 6329만</t>
   </si>
   <si>
     <t>갱기님</t>
@@ -1458,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%ED%95%A9%EC%99%95</t>
   </si>
   <si>
-    <t>6840억 1868만</t>
+    <t>6843억 7077만</t>
   </si>
   <si>
     <t>당양감</t>
@@ -1494,7 +1485,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%98%EB%A6%ACv</t>
   </si>
   <si>
-    <t>17조 1015억 3470만</t>
+    <t>17조 1047억 2004만</t>
   </si>
   <si>
     <t>oFero라온o</t>
@@ -1521,7 +1512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4%EC%A7%80%EB%8B%88</t>
   </si>
   <si>
-    <t>5조 666억 7809만</t>
+    <t>5조 741억 8033만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=oFero%EC%9B%94%ED%96%A5o</t>
@@ -1689,7 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EB%8B%88</t>
   </si>
   <si>
-    <t>5459억 4798만</t>
+    <t>5474억 9744만</t>
   </si>
   <si>
     <t>솜쥬멐</t>
@@ -1698,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%9C%EC%A5%AC%EB%A9%90</t>
   </si>
   <si>
-    <t>5232억 6927만</t>
+    <t>5406억 290만</t>
   </si>
   <si>
     <t>o루비녹스o</t>
@@ -1737,7 +1728,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>3148억 5543만</t>
+    <t>3203억 5341만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%8F%99</t>
@@ -1779,7 +1770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EB%9A%9C</t>
   </si>
   <si>
-    <t>3조 1258억 3830만</t>
+    <t>3조 1283억 9737만</t>
   </si>
   <si>
     <t>왕오이</t>
@@ -1791,6 +1782,15 @@
     <t>3조 78억 6848만</t>
   </si>
   <si>
+    <t>이호은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%98%B8%EC%9D%80</t>
+  </si>
+  <si>
+    <t>2조 7172억 9868만</t>
+  </si>
+  <si>
     <t>그냐앙</t>
   </si>
   <si>
@@ -1800,22 +1800,13 @@
     <t>2조 6959억 3259만</t>
   </si>
   <si>
-    <t>이호은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%98%B8%EC%9D%80</t>
-  </si>
-  <si>
-    <t>2조 6668억 5710만</t>
-  </si>
-  <si>
     <t>승호숍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%ED%98%B8%EC%88%8D</t>
   </si>
   <si>
-    <t>2조 6012억 7984만</t>
+    <t>2조 6053억 310만</t>
   </si>
   <si>
     <t>애기이잉</t>
@@ -1824,7 +1815,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9D%B4%EC%9E%89</t>
   </si>
   <si>
-    <t>2조 5975억 5879만</t>
+    <t>2조 6019억 4405만</t>
   </si>
   <si>
     <t>하깁s</t>
@@ -1950,7 +1941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%B5%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>8232억 8200만</t>
+    <t>8235억 1690만</t>
   </si>
   <si>
     <t>근카자</t>
@@ -1959,7 +1950,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%B9%B4%EC%9E%90</t>
   </si>
   <si>
-    <t>7815억 7513만</t>
+    <t>7924억 737만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B0%94</t>
@@ -2022,7 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%A4%EA%B4%9C</t>
   </si>
   <si>
-    <t>2조 7356억 9785만</t>
+    <t>2조 7723억 2323만</t>
   </si>
   <si>
     <t>다너리</t>
@@ -2067,7 +2058,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%EC%84%A4</t>
   </si>
   <si>
-    <t>2조 1604억 268만</t>
+    <t>2조 3337억 7615만</t>
   </si>
   <si>
     <t>쭝요</t>
@@ -2076,7 +2067,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%9D%EC%9A%94</t>
   </si>
   <si>
-    <t>1조 9050억 2724만</t>
+    <t>1조 9243억 3941만</t>
   </si>
   <si>
     <t>클리브</t>
@@ -2085,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EB%A6%AC%EB%B8%8C</t>
   </si>
   <si>
-    <t>1조 7955억 4901만</t>
+    <t>1조 9040억 9300만</t>
   </si>
   <si>
     <t>딸기전사</t>
@@ -2103,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=Soul</t>
   </si>
   <si>
-    <t>1조 3830억 6667만</t>
+    <t>1조 5924억 7433만</t>
   </si>
   <si>
     <t>소바킴</t>
@@ -2130,7 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%86%8D%EB%82%A8</t>
   </si>
   <si>
-    <t>9453억 1467만</t>
+    <t>1조 488억 1763만</t>
   </si>
   <si>
     <t>꼬맹츄</t>
@@ -2139,7 +2130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%A7%B9%EC%B8%84</t>
   </si>
   <si>
-    <t>6269억 6844만</t>
+    <t>6271억 4609만</t>
   </si>
   <si>
     <t>오렌지공쥬</t>
@@ -2157,7 +2148,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%9D%B8%ED%98%95</t>
   </si>
   <si>
-    <t>2451억 9307만</t>
+    <t>2815억 2930만</t>
   </si>
   <si>
     <t>진킹배</t>
@@ -2175,7 +2166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%83%81%EB%85%80</t>
   </si>
   <si>
-    <t>1818억 6075만</t>
+    <t>1821억 4567만</t>
   </si>
   <si>
     <t>희태바라기</t>
@@ -2208,7 +2199,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>1144억 1650만</t>
+    <t>1155억 4589만</t>
   </si>
   <si>
     <t>공쵸</t>
@@ -3422,10 +3413,10 @@
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>152</v>
@@ -3454,13 +3445,13 @@
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3471,16 +3462,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -3489,10 +3480,10 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3503,25 +3494,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>166</v>
@@ -3550,10 +3541,10 @@
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>170</v>
@@ -3585,7 +3576,7 @@
         <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>174</v>
@@ -3617,7 +3608,7 @@
         <v>87</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>178</v>
@@ -3649,7 +3640,7 @@
         <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>182</v>
@@ -3713,7 +3704,7 @@
         <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>190</v>
@@ -3745,7 +3736,7 @@
         <v>194</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>195</v>
@@ -3809,7 +3800,7 @@
         <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>203</v>
@@ -3985,7 +3976,7 @@
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>120</v>
@@ -4017,7 +4008,7 @@
         <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>120</v>
@@ -4308,7 +4299,7 @@
         <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>245</v>
@@ -4340,7 +4331,7 @@
         <v>87</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>248</v>
@@ -4436,7 +4427,7 @@
         <v>87</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>258</v>
@@ -4450,7 +4441,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>259</v>
@@ -4465,10 +4456,10 @@
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>261</v>
@@ -4482,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>262</v>
@@ -4497,10 +4488,10 @@
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>264</v>
@@ -4532,7 +4523,7 @@
         <v>105</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>267</v>
@@ -4596,10 +4587,10 @@
         <v>99</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4613,13 +4604,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -4631,7 +4622,7 @@
         <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4645,13 +4636,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -4663,7 +4654,7 @@
         <v>211</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4677,13 +4668,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -4695,7 +4686,7 @@
         <v>211</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4709,13 +4700,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -4724,7 +4715,7 @@
         <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>286</v>
@@ -4756,7 +4747,7 @@
         <v>134</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>288</v>
@@ -5384,7 +5375,7 @@
         <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>342</v>
@@ -5462,7 +5453,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>349</v>
@@ -5477,7 +5468,7 @@
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>100</v>
@@ -5494,7 +5485,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>352</v>
@@ -5509,7 +5500,7 @@
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>100</v>
@@ -5541,7 +5532,7 @@
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>100</v>
@@ -5640,7 +5631,7 @@
         <v>87</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>366</v>
@@ -5704,7 +5695,7 @@
         <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>372</v>
@@ -5733,10 +5724,10 @@
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>375</v>
@@ -5765,10 +5756,10 @@
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>378</v>
@@ -5797,10 +5788,10 @@
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>381</v>
@@ -5829,10 +5820,10 @@
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>384</v>
@@ -5864,7 +5855,7 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>387</v>
@@ -5896,7 +5887,7 @@
         <v>87</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>390</v>
@@ -5928,7 +5919,7 @@
         <v>125</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>394</v>
@@ -5977,7 +5968,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6205,7 +6196,7 @@
         <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>412</v>
@@ -6269,7 +6260,7 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>418</v>
@@ -6301,7 +6292,7 @@
         <v>421</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>422</v>
@@ -6333,7 +6324,7 @@
         <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>425</v>
@@ -6350,25 +6341,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>427</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>99</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6382,22 +6373,22 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>428</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>428</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>429</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>99</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>211</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>430</v>
@@ -6426,10 +6417,10 @@
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>433</v>
@@ -6461,7 +6452,7 @@
         <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>436</v>
@@ -6490,10 +6481,10 @@
         <v>93</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>439</v>
@@ -6507,7 +6498,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>440</v>
@@ -6525,7 +6516,7 @@
         <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>442</v>
@@ -6539,7 +6530,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>443</v>
@@ -6554,10 +6545,10 @@
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>445</v>
@@ -6586,10 +6577,10 @@
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>161</v>
+        <v>285</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>448</v>
@@ -6618,10 +6609,10 @@
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>451</v>
@@ -6650,7 +6641,7 @@
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>211</v>
@@ -6682,10 +6673,10 @@
         <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>457</v>
@@ -6714,10 +6705,10 @@
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>460</v>
@@ -6746,10 +6737,10 @@
         <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>161</v>
+        <v>285</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>463</v>
@@ -6778,10 +6769,10 @@
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>466</v>
@@ -6810,10 +6801,10 @@
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>469</v>
@@ -6842,10 +6833,10 @@
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>472</v>
@@ -6874,10 +6865,10 @@
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>475</v>
@@ -6886,40 +6877,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6948,7 +6907,6 @@
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7009,13 +6967,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
@@ -7027,7 +6985,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -7041,13 +6999,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -7059,7 +7017,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -7073,13 +7031,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -7091,7 +7049,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -7105,13 +7063,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -7123,7 +7081,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -7137,13 +7095,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -7152,10 +7110,10 @@
         <v>125</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -7169,13 +7127,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -7187,7 +7145,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -7207,7 +7165,7 @@
         <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -7216,10 +7174,10 @@
         <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -7233,13 +7191,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -7251,7 +7209,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -7265,13 +7223,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -7283,7 +7241,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -7297,13 +7255,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -7312,10 +7270,10 @@
         <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -7329,13 +7287,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -7344,10 +7302,10 @@
         <v>87</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7361,13 +7319,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -7376,10 +7334,10 @@
         <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7393,13 +7351,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -7408,10 +7366,10 @@
         <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7425,13 +7383,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -7443,7 +7401,7 @@
         <v>211</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7457,13 +7415,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -7472,10 +7430,10 @@
         <v>94</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7486,16 +7444,16 @@
         <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -7507,7 +7465,7 @@
         <v>211</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7518,16 +7476,16 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -7536,10 +7494,10 @@
         <v>421</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7553,13 +7511,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -7571,7 +7529,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7585,13 +7543,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -7600,10 +7558,10 @@
         <v>421</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7617,13 +7575,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -7635,7 +7593,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7649,13 +7607,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -7667,7 +7625,7 @@
         <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7681,13 +7639,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -7699,7 +7657,7 @@
         <v>211</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7713,13 +7671,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -7728,10 +7686,10 @@
         <v>87</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7745,13 +7703,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -7760,10 +7718,10 @@
         <v>421</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7777,13 +7735,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -7792,10 +7750,10 @@
         <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7809,13 +7767,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -7824,10 +7782,10 @@
         <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7841,13 +7799,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -7859,7 +7817,7 @@
         <v>291</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7873,13 +7831,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -7888,10 +7846,10 @@
         <v>421</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -7905,13 +7863,13 @@
         <v>300</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -7920,10 +7878,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -7937,13 +7895,13 @@
         <v>391</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -7952,10 +7910,10 @@
         <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -8060,7 +8018,7 @@
         <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -8072,7 +8030,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8086,13 +8044,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -8104,7 +8062,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8118,13 +8076,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -8136,7 +8094,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8150,13 +8108,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -8168,7 +8126,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8182,13 +8140,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -8197,10 +8155,10 @@
         <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8214,13 +8172,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -8232,7 +8190,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8246,25 +8204,25 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8278,25 +8236,25 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8310,13 +8268,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -8325,10 +8283,10 @@
         <v>421</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8342,13 +8300,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -8357,10 +8315,10 @@
         <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8374,13 +8332,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -8389,10 +8347,10 @@
         <v>99</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8406,13 +8364,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -8421,10 +8379,10 @@
         <v>87</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8438,13 +8396,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -8456,7 +8414,7 @@
         <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8470,13 +8428,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -8488,7 +8446,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8502,13 +8460,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -8517,10 +8475,10 @@
         <v>99</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8531,16 +8489,16 @@
         <v>60</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -8552,7 +8510,7 @@
         <v>135</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8563,16 +8521,16 @@
         <v>60</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -8584,7 +8542,7 @@
         <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8598,13 +8556,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -8616,7 +8574,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8630,13 +8588,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -8645,10 +8603,10 @@
         <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8662,13 +8620,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -8677,10 +8635,10 @@
         <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8694,13 +8652,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -8709,10 +8667,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8726,13 +8684,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -8741,10 +8699,10 @@
         <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8758,13 +8716,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -8773,10 +8731,10 @@
         <v>99</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8790,13 +8748,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -8805,10 +8763,10 @@
         <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8822,13 +8780,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -8837,10 +8795,10 @@
         <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8940,7 +8898,7 @@
         <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -8949,10 +8907,10 @@
         <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8966,13 +8924,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -8984,7 +8942,7 @@
         <v>120</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8998,13 +8956,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -9016,7 +8974,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9030,13 +8988,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -9048,7 +9006,7 @@
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9062,13 +9020,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -9080,7 +9038,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9094,13 +9052,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -9112,7 +9070,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9126,13 +9084,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -9144,7 +9102,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9158,13 +9116,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -9173,10 +9131,10 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9190,13 +9148,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -9208,7 +9166,7 @@
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9222,13 +9180,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -9240,7 +9198,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9254,13 +9212,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -9272,7 +9230,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9286,13 +9244,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -9304,7 +9262,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9318,13 +9276,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -9333,10 +9291,10 @@
         <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9350,13 +9308,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -9368,7 +9326,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9382,13 +9340,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -9400,7 +9358,7 @@
         <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9411,16 +9369,16 @@
         <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -9429,10 +9387,10 @@
         <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9443,16 +9401,16 @@
         <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -9461,10 +9419,10 @@
         <v>421</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9478,13 +9436,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -9496,7 +9454,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9510,13 +9468,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -9525,10 +9483,10 @@
         <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9542,13 +9500,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -9560,7 +9518,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9574,13 +9532,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -9589,10 +9547,10 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9606,13 +9564,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -9621,10 +9579,10 @@
         <v>421</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9638,13 +9596,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -9653,10 +9611,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9670,13 +9628,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -9685,10 +9643,10 @@
         <v>421</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>567</v>
+        <v>295</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9702,13 +9660,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -9720,7 +9678,7 @@
         <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9734,13 +9692,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -9749,10 +9707,10 @@
         <v>421</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9766,13 +9724,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -9781,10 +9739,10 @@
         <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9798,13 +9756,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -9813,10 +9771,10 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'0FeroCity'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">알바천국!$A$1:$J$29</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="705">
   <si>
     <t>guild_name</t>
   </si>
@@ -672,42 +672,6 @@
     <t>1조 2381억 1362만</t>
   </si>
   <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>21조 1132억 4874만</t>
-  </si>
-  <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>20조 4898억 61만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 4585억 7977만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>15조 9076억 6397만</t>
-  </si>
-  <si>
     <t>처히</t>
   </si>
   <si>
@@ -735,15 +699,6 @@
     <t>8조 9166억 6911만</t>
   </si>
   <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 9849억 7135만</t>
-  </si>
-  <si>
     <t>AKPS</t>
   </si>
   <si>
@@ -759,7 +714,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
   </si>
   <si>
-    <t>3조 8303억 3845만</t>
+    <t>3조 8357억 2589만</t>
   </si>
   <si>
     <t>토미오카상</t>
@@ -828,15 +783,6 @@
     <t>2조 4991억 587만</t>
   </si>
   <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>2조 305억 8537만</t>
-  </si>
-  <si>
     <t>샤스찌에</t>
   </si>
   <si>
@@ -846,22 +792,13 @@
     <t>1조 5997억 4972만</t>
   </si>
   <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>1조 3657억 2295만</t>
-  </si>
-  <si>
     <t>보동핑</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 1840억 5819만</t>
+    <t>1조 2405억 3789만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -933,270 +870,270 @@
     <t>3382억 604만</t>
   </si>
   <si>
+    <t>구리구리뽕리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>55억 5534만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>32조 9473억 5428만</t>
+  </si>
+  <si>
+    <t>소독약</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
+  </si>
+  <si>
+    <t>14조 6115억 5118만</t>
+  </si>
+  <si>
+    <t>주존사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>12조 2134억 7541만</t>
+  </si>
+  <si>
+    <t>휘정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
+  </si>
+  <si>
+    <t>7조 7401억 3625만</t>
+  </si>
+  <si>
+    <t>무피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
+  </si>
+  <si>
+    <t>6조 8401억 6735만</t>
+  </si>
+  <si>
+    <t>슈웃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
+  </si>
+  <si>
+    <t>5조 2536억 3990만</t>
+  </si>
+  <si>
+    <t>캐서린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>4조 7573억 2987만</t>
+  </si>
+  <si>
+    <t>파산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
+  </si>
+  <si>
+    <t>4조 7044억 1961만</t>
+  </si>
+  <si>
+    <t>강린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>4조 4116억 2751만</t>
+  </si>
+  <si>
+    <t>임나연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
+  </si>
+  <si>
+    <t>4조 450억 5646만</t>
+  </si>
+  <si>
+    <t>빡박이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 372억 1982만</t>
+  </si>
+  <si>
+    <t>졸귀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
+  </si>
+  <si>
+    <t>3조 9023억 745만</t>
+  </si>
+  <si>
+    <t>스파토이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 2857억 8502만</t>
+  </si>
+  <si>
+    <t>YAMAMOTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
+  </si>
+  <si>
+    <t>3조 1669억 6472만</t>
+  </si>
+  <si>
+    <t>픽홀로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3조 727억 7187만</t>
+  </si>
+  <si>
+    <t>쟈라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>2조 9098억 1790만</t>
+  </si>
+  <si>
+    <t>Rania</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rania</t>
+  </si>
+  <si>
+    <t>2조 6780억 7684만</t>
+  </si>
+  <si>
+    <t>바세린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>2조 6490억 9667만</t>
+  </si>
+  <si>
+    <t>미진생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
+  </si>
+  <si>
+    <t>2조 3948억 1791만</t>
+  </si>
+  <si>
+    <t>베르1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
+  </si>
+  <si>
+    <t>2조 3313억 3223만</t>
+  </si>
+  <si>
+    <t>Uhani</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
+  </si>
+  <si>
+    <t>2조 384억 6922만</t>
+  </si>
+  <si>
+    <t>쟁반짜장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2조 15억 7320만</t>
+  </si>
+  <si>
+    <t>하숑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
+  </si>
+  <si>
+    <t>1조 9072억 8066만</t>
+  </si>
+  <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1조 8429억 3125만</t>
+  </si>
+  <si>
+    <t>별렉스b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
+  </si>
+  <si>
+    <t>1조 8408억 8307만</t>
+  </si>
+  <si>
+    <t>양설유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 7462억 7709만</t>
+  </si>
+  <si>
+    <t>가이아의격노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
+  </si>
+  <si>
+    <t>1조 7212억 2724만</t>
+  </si>
+  <si>
+    <t>도레스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1조 1839억 1961만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>구리구리뽕리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>55억 5534만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>32조 9473억 5428만</t>
-  </si>
-  <si>
-    <t>소독약</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
-  </si>
-  <si>
-    <t>14조 6115억 5118만</t>
-  </si>
-  <si>
-    <t>주존사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>12조 2134억 7541만</t>
-  </si>
-  <si>
-    <t>휘정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
-  </si>
-  <si>
-    <t>7조 7401억 3625만</t>
-  </si>
-  <si>
-    <t>무피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
-  </si>
-  <si>
-    <t>6조 8401억 6735만</t>
-  </si>
-  <si>
-    <t>슈웃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
-  </si>
-  <si>
-    <t>5조 2536억 3990만</t>
-  </si>
-  <si>
-    <t>캐서린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>4조 7573억 2987만</t>
-  </si>
-  <si>
-    <t>파산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
-  </si>
-  <si>
-    <t>4조 7044억 1961만</t>
-  </si>
-  <si>
-    <t>강린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>4조 4116억 2751만</t>
-  </si>
-  <si>
-    <t>임나연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
-  </si>
-  <si>
-    <t>4조 450억 5646만</t>
-  </si>
-  <si>
-    <t>빡박이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 372억 1982만</t>
-  </si>
-  <si>
-    <t>졸귀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
-  </si>
-  <si>
-    <t>3조 9023억 745만</t>
-  </si>
-  <si>
-    <t>스파토이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3조 2857억 8502만</t>
-  </si>
-  <si>
-    <t>YAMAMOTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
-  </si>
-  <si>
-    <t>3조 1669억 6472만</t>
-  </si>
-  <si>
-    <t>픽홀로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3조 727억 7187만</t>
-  </si>
-  <si>
-    <t>쟈라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>2조 9098억 1790만</t>
-  </si>
-  <si>
-    <t>Rania</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rania</t>
-  </si>
-  <si>
-    <t>2조 6780억 7684만</t>
-  </si>
-  <si>
-    <t>바세린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>2조 6490억 9667만</t>
-  </si>
-  <si>
-    <t>미진생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
-  </si>
-  <si>
-    <t>2조 3948억 1791만</t>
-  </si>
-  <si>
-    <t>베르1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
-  </si>
-  <si>
-    <t>2조 3313억 3223만</t>
-  </si>
-  <si>
-    <t>Uhani</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
-  </si>
-  <si>
-    <t>2조 384억 6922만</t>
-  </si>
-  <si>
-    <t>쟁반짜장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2조 15억 7320만</t>
-  </si>
-  <si>
-    <t>하숑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
-  </si>
-  <si>
-    <t>1조 9072억 8066만</t>
-  </si>
-  <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1조 8429억 3125만</t>
-  </si>
-  <si>
-    <t>별렉스b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
-  </si>
-  <si>
-    <t>1조 8408억 8307만</t>
-  </si>
-  <si>
-    <t>양설유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 7462억 7709만</t>
-  </si>
-  <si>
-    <t>가이아의격노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
-  </si>
-  <si>
-    <t>1조 7212억 2724만</t>
-  </si>
-  <si>
-    <t>도레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1조 1839억 1961만</t>
-  </si>
-  <si>
     <t>양산호수공원</t>
   </si>
   <si>
@@ -1476,7 +1413,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%9D%EB%8B%9D%EB%A7%9B%EC%84%80%EB%8F%84</t>
   </si>
   <si>
-    <t>34조 5870억 7567만</t>
+    <t>38조 7302억 5673만</t>
   </si>
   <si>
     <t>캘리v</t>
@@ -1485,7 +1422,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%98%EB%A6%ACv</t>
   </si>
   <si>
-    <t>17조 1047억 2004만</t>
+    <t>17조 8319억 6127만</t>
   </si>
   <si>
     <t>oFero라온o</t>
@@ -1512,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4%EC%A7%80%EB%8B%88</t>
   </si>
   <si>
-    <t>5조 741억 8033만</t>
+    <t>5조 1037억 8896만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=oFero%EC%9B%94%ED%96%A5o</t>
@@ -1554,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
   </si>
   <si>
-    <t>1조 9279억 5199만</t>
+    <t>1조 9308억 2661만</t>
   </si>
   <si>
     <t>SPICY</t>
@@ -1563,7 +1500,7 @@
     <t>https://mgf.gg/contents/character.php?n=SPICY</t>
   </si>
   <si>
-    <t>1조 8417억 7765만</t>
+    <t>1조 8682억 1465만</t>
   </si>
   <si>
     <t>장행</t>
@@ -1572,7 +1509,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%96%89</t>
   </si>
   <si>
-    <t>1조 2312억 4703만</t>
+    <t>1조 2511억 2429만</t>
   </si>
   <si>
     <t>JUYs</t>
@@ -1590,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A9%ED%86%B5</t>
   </si>
   <si>
-    <t>1조 1121억 9129만</t>
+    <t>1조 1340억 5345만</t>
   </si>
   <si>
     <t>음묘우</t>
@@ -1674,22 +1611,31 @@
     <t>6222억 4063만</t>
   </si>
   <si>
+    <t>솜쥬멐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%9C%EC%A5%AC%EB%A9%90</t>
+  </si>
+  <si>
+    <t>5817억 1752만</t>
+  </si>
+  <si>
     <t>오렌지니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EB%8B%88</t>
   </si>
   <si>
-    <t>5474억 9744만</t>
-  </si>
-  <si>
-    <t>솜쥬멐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%9C%EC%A5%AC%EB%A9%90</t>
-  </si>
-  <si>
-    <t>5406억 290만</t>
+    <t>5682억 8299만</t>
+  </si>
+  <si>
+    <t>야옹이공주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EA%B3%B5%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>5228억 9257만</t>
   </si>
   <si>
     <t>o루비녹스o</t>
@@ -1699,15 +1645,6 @@
   </si>
   <si>
     <t>5065억 84만</t>
-  </si>
-  <si>
-    <t>야옹이공주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EA%B3%B5%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>5054억 9265만</t>
   </si>
   <si>
     <t>녕죠</t>
@@ -3911,7 +3848,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3976,10 +3913,10 @@
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>215</v>
@@ -4011,7 +3948,7 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>218</v>
@@ -4040,10 +3977,10 @@
         <v>93</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>221</v>
@@ -4072,10 +4009,10 @@
         <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>224</v>
@@ -4104,10 +4041,10 @@
         <v>93</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>227</v>
@@ -4136,10 +4073,10 @@
         <v>93</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>230</v>
@@ -4171,7 +4108,7 @@
         <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>233</v>
@@ -4200,13 +4137,13 @@
         <v>93</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>236</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4220,25 +4157,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4252,25 +4189,25 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4284,25 +4221,25 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4316,25 +4253,25 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4348,22 +4285,22 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>251</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>252</v>
@@ -4392,7 +4329,7 @@
         <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>211</v>
@@ -4427,7 +4364,7 @@
         <v>87</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>258</v>
@@ -4456,10 +4393,10 @@
         <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>261</v>
@@ -4488,13 +4425,13 @@
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4508,22 +4445,22 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>265</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>265</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>266</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>267</v>
@@ -4552,13 +4489,13 @@
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4572,25 +4509,25 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>211</v>
+        <v>274</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4604,25 +4541,25 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4636,256 +4573,32 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J23"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4909,13 +4622,6 @@
     <hyperlink ref="E21" r:id="rId20"/>
     <hyperlink ref="E22" r:id="rId21"/>
     <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4982,7 +4688,7 @@
         <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -4994,7 +4700,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5008,13 +4714,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -5026,7 +4732,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5040,13 +4746,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -5058,7 +4764,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5072,13 +4778,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -5090,7 +4796,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5104,13 +4810,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -5122,7 +4828,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5136,13 +4842,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -5154,7 +4860,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5168,13 +4874,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -5186,7 +4892,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5200,13 +4906,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -5218,7 +4924,7 @@
         <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5232,13 +4938,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -5250,7 +4956,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5264,13 +4970,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -5282,7 +4988,7 @@
         <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5296,13 +5002,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -5314,7 +5020,7 @@
         <v>135</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5328,13 +5034,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -5346,7 +5052,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5360,13 +5066,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -5378,7 +5084,7 @@
         <v>160</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5392,13 +5098,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -5410,7 +5116,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5424,13 +5130,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -5442,7 +5148,7 @@
         <v>100</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5456,13 +5162,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -5474,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5488,13 +5194,13 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -5506,7 +5212,7 @@
         <v>100</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5520,13 +5226,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -5538,7 +5244,7 @@
         <v>100</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5552,13 +5258,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -5570,7 +5276,7 @@
         <v>135</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5584,13 +5290,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -5602,7 +5308,7 @@
         <v>100</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5616,13 +5322,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -5634,7 +5340,7 @@
         <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5648,13 +5354,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -5666,7 +5372,7 @@
         <v>100</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5680,13 +5386,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -5698,7 +5404,7 @@
         <v>160</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5712,13 +5418,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -5730,7 +5436,7 @@
         <v>160</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5744,13 +5450,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -5762,7 +5468,7 @@
         <v>135</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5776,13 +5482,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -5794,7 +5500,7 @@
         <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5808,13 +5514,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -5826,7 +5532,7 @@
         <v>160</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5840,13 +5546,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -5858,7 +5564,7 @@
         <v>160</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5869,16 +5575,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -5890,7 +5596,7 @@
         <v>165</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5901,16 +5607,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -5922,7 +5628,7 @@
         <v>165</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6021,13 +5727,13 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
@@ -6039,7 +5745,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6053,13 +5759,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -6071,7 +5777,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6085,13 +5791,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -6103,7 +5809,7 @@
         <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6117,13 +5823,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -6135,7 +5841,7 @@
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6149,13 +5855,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -6167,7 +5873,7 @@
         <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6181,13 +5887,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -6199,7 +5905,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6213,13 +5919,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -6231,7 +5937,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6245,13 +5951,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -6263,7 +5969,7 @@
         <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6277,25 +5983,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>160</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6309,13 +6015,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -6327,7 +6033,7 @@
         <v>160</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6347,7 +6053,7 @@
         <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
@@ -6359,7 +6065,7 @@
         <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6373,13 +6079,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -6391,7 +6097,7 @@
         <v>211</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6405,13 +6111,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -6423,7 +6129,7 @@
         <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -6437,13 +6143,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -6455,7 +6161,7 @@
         <v>165</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6469,13 +6175,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -6487,7 +6193,7 @@
         <v>165</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6501,13 +6207,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -6519,7 +6225,7 @@
         <v>165</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6533,13 +6239,13 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -6551,7 +6257,7 @@
         <v>165</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -6565,13 +6271,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -6580,10 +6286,10 @@
         <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6597,13 +6303,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -6615,7 +6321,7 @@
         <v>211</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6629,13 +6335,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -6647,7 +6353,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6661,13 +6367,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -6679,7 +6385,7 @@
         <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6693,13 +6399,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -6711,7 +6417,7 @@
         <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6725,13 +6431,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -6740,10 +6446,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6757,13 +6463,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -6772,10 +6478,10 @@
         <v>87</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6789,13 +6495,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -6804,10 +6510,10 @@
         <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6821,13 +6527,13 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
@@ -6839,7 +6545,7 @@
         <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6853,13 +6559,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -6868,10 +6574,10 @@
         <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6967,25 +6673,25 @@
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6999,13 +6705,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -7017,7 +6723,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>481</v>
+        <v>460</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -7031,13 +6737,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -7049,7 +6755,7 @@
         <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -7063,25 +6769,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -7095,13 +6801,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -7113,7 +6819,7 @@
         <v>160</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -7127,13 +6833,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -7145,7 +6851,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -7165,7 +6871,7 @@
         <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>86</v>
@@ -7177,7 +6883,7 @@
         <v>160</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -7191,13 +6897,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -7209,7 +6915,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>498</v>
+        <v>477</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -7223,13 +6929,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>499</v>
+        <v>478</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>499</v>
+        <v>478</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>500</v>
+        <v>479</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -7241,7 +6947,7 @@
         <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -7255,13 +6961,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>502</v>
+        <v>481</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>502</v>
+        <v>481</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>503</v>
+        <v>482</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -7273,7 +6979,7 @@
         <v>165</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -7287,13 +6993,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -7305,7 +7011,7 @@
         <v>165</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7319,13 +7025,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -7337,7 +7043,7 @@
         <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>510</v>
+        <v>489</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7351,13 +7057,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>511</v>
+        <v>490</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>490</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>512</v>
+        <v>491</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -7369,7 +7075,7 @@
         <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>513</v>
+        <v>492</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7383,13 +7089,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -7401,7 +7107,7 @@
         <v>211</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7415,13 +7121,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -7433,7 +7139,7 @@
         <v>165</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7447,13 +7153,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -7465,7 +7171,7 @@
         <v>211</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7479,25 +7185,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7511,25 +7217,25 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7543,25 +7249,25 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7575,25 +7281,25 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7607,13 +7313,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -7625,7 +7331,7 @@
         <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7639,25 +7345,25 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>211</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7671,13 +7377,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -7686,10 +7392,10 @@
         <v>87</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7703,25 +7409,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7735,25 +7441,25 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7767,25 +7473,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7799,25 +7505,25 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>87</v>
+        <v>400</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7831,25 +7537,25 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>421</v>
+        <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -7860,16 +7566,16 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>93</v>
@@ -7878,10 +7584,10 @@
         <v>105</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -7892,16 +7598,16 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>93</v>
@@ -7910,10 +7616,10 @@
         <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -8018,7 +7724,7 @@
         <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -8030,7 +7736,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8044,13 +7750,13 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
@@ -8062,7 +7768,7 @@
         <v>111</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8076,13 +7782,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -8094,7 +7800,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8108,13 +7814,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
@@ -8126,7 +7832,7 @@
         <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8140,13 +7846,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -8158,7 +7864,7 @@
         <v>160</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8172,13 +7878,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -8190,7 +7896,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8204,13 +7910,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -8222,7 +7928,7 @@
         <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8236,13 +7942,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -8254,7 +7960,7 @@
         <v>135</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8268,25 +7974,25 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8300,13 +8006,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -8318,7 +8024,7 @@
         <v>160</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8332,13 +8038,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -8350,7 +8056,7 @@
         <v>160</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8364,13 +8070,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -8382,7 +8088,7 @@
         <v>160</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8396,13 +8102,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -8414,7 +8120,7 @@
         <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8428,13 +8134,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -8446,7 +8152,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8460,13 +8166,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -8478,7 +8184,7 @@
         <v>160</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8492,13 +8198,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -8510,7 +8216,7 @@
         <v>135</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8524,13 +8230,13 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
@@ -8542,7 +8248,7 @@
         <v>135</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8556,13 +8262,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -8574,7 +8280,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8588,13 +8294,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -8606,7 +8312,7 @@
         <v>160</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8620,13 +8326,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -8638,7 +8344,7 @@
         <v>160</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8652,13 +8358,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -8670,7 +8376,7 @@
         <v>160</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8684,13 +8390,13 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
@@ -8702,7 +8408,7 @@
         <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8716,13 +8422,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -8731,10 +8437,10 @@
         <v>99</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8748,13 +8454,13 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
@@ -8766,7 +8472,7 @@
         <v>160</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8780,13 +8486,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -8795,10 +8501,10 @@
         <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8898,7 +8604,7 @@
         <v>75</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>86</v>
@@ -8907,10 +8613,10 @@
         <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8924,25 +8630,25 @@
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8956,13 +8662,13 @@
         <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>93</v>
@@ -8974,7 +8680,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8988,25 +8694,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9020,13 +8726,13 @@
         <v>107</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>93</v>
@@ -9038,7 +8744,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9052,13 +8758,13 @@
         <v>113</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>93</v>
@@ -9070,7 +8776,7 @@
         <v>135</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9084,13 +8790,13 @@
         <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>93</v>
@@ -9102,7 +8808,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9116,13 +8822,13 @@
         <v>122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>93</v>
@@ -9134,7 +8840,7 @@
         <v>160</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9148,13 +8854,13 @@
         <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>93</v>
@@ -9166,7 +8872,7 @@
         <v>135</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9180,13 +8886,13 @@
         <v>131</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>93</v>
@@ -9198,7 +8904,7 @@
         <v>135</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9212,13 +8918,13 @@
         <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>93</v>
@@ -9230,7 +8936,7 @@
         <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9244,13 +8950,13 @@
         <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
@@ -9262,7 +8968,7 @@
         <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9276,13 +8982,13 @@
         <v>145</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>93</v>
@@ -9294,7 +9000,7 @@
         <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>678</v>
+        <v>657</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9308,13 +9014,13 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>679</v>
+        <v>658</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>679</v>
+        <v>658</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>680</v>
+        <v>659</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>93</v>
@@ -9326,7 +9032,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>681</v>
+        <v>660</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9340,13 +9046,13 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>682</v>
+        <v>661</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>682</v>
+        <v>661</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>93</v>
@@ -9358,7 +9064,7 @@
         <v>135</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9372,13 +9078,13 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>93</v>
@@ -9390,7 +9096,7 @@
         <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9404,25 +9110,25 @@
         <v>162</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>688</v>
+        <v>667</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>688</v>
+        <v>667</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>690</v>
+        <v>669</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9436,13 +9142,13 @@
         <v>167</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>93</v>
@@ -9454,7 +9160,7 @@
         <v>211</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9468,13 +9174,13 @@
         <v>171</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>93</v>
@@ -9483,10 +9189,10 @@
         <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9500,13 +9206,13 @@
         <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>93</v>
@@ -9518,7 +9224,7 @@
         <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9532,13 +9238,13 @@
         <v>179</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>93</v>
@@ -9547,10 +9253,10 @@
         <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9564,25 +9270,25 @@
         <v>183</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9596,13 +9302,13 @@
         <v>187</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>93</v>
@@ -9611,10 +9317,10 @@
         <v>105</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9628,25 +9334,25 @@
         <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9660,13 +9366,13 @@
         <v>196</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>93</v>
@@ -9675,10 +9381,10 @@
         <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9692,25 +9398,25 @@
         <v>200</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9724,13 +9430,13 @@
         <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>93</v>
@@ -9739,10 +9445,10 @@
         <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9756,13 +9462,13 @@
         <v>208</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>93</v>
@@ -9771,10 +9477,10 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">알바천국!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">풍년순대국밥!$A$1:$J$26</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="707">
   <si>
     <t>guild_name</t>
   </si>
@@ -123,7 +123,7 @@
     <t>10위</t>
   </si>
   <si>
-    <t>Lv.6</t>
+    <t>Lv.7</t>
   </si>
   <si>
     <t>124조 4701억 3596만</t>
@@ -177,9 +177,6 @@
     <t>18위</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
     <t>120조 7753억 7512만</t>
   </si>
   <si>
@@ -351,7 +348,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>10조 8032억 4305만</t>
+    <t>10조 8080억 1797만</t>
   </si>
   <si>
     <t>5</t>
@@ -369,7 +366,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>9조 7714억 2550만</t>
+    <t>9조 7862억 1841만</t>
   </si>
   <si>
     <t>6</t>
@@ -411,7 +408,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>6조 62억 9031만</t>
+    <t>6조 140억 9399만</t>
   </si>
   <si>
     <t>9</t>
@@ -438,37 +435,52 @@
     <t>나이트로드</t>
   </si>
   <si>
+    <t>4조 5676억 7592만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>4조 2387억 6610만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 6676억 5224만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
     <t>99</t>
   </si>
   <si>
-    <t>4조 4313억 1006만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>4조 2089억 9652만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
     <t>3조 3846억 5890만</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>므고</t>
@@ -480,7 +492,19 @@
     <t>3조 2011억 997만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>2조 8180억 4925만</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -492,7 +516,7 @@
     <t>2조 7171억 6721만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>17</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -504,7 +528,22 @@
     <t>2조 6747억 6521만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2조 6008억 7148만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -513,28 +552,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
     <t>2조 5943억 9545만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>2조 5940억 8239만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>20</t>
   </si>
   <si>
     <t>강철고튠데</t>
@@ -546,19 +567,7 @@
     <t>2조 5595억 2만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>2조 3765억 8123만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -567,10 +576,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 2480억 2119만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>2조 3068억 391만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>겨울바다</t>
@@ -579,10 +588,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>2조 1038억 6635만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>2조 3067억 6242만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>여븨</t>
@@ -594,7 +603,7 @@
     <t>2조 737억 3833만</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -606,7 +615,7 @@
     <t>1조 9311억 8518만</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -621,7 +630,7 @@
     <t>1조 9171억 4797만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>데드캣</t>
@@ -633,7 +642,7 @@
     <t>1조 8260억 5446만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>여눈</t>
@@ -645,7 +654,7 @@
     <t>1조 7856억 5439만</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -657,7 +666,7 @@
     <t>1조 7536억 1673만</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>욤지</t>
@@ -678,7 +687,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
   </si>
   <si>
-    <t>13조 2232억 3999만</t>
+    <t>13조 5574억 3249만</t>
   </si>
   <si>
     <t>환생의불꼬츠</t>
@@ -714,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
   </si>
   <si>
-    <t>3조 8357억 2589만</t>
+    <t>3조 9540억 9597만</t>
   </si>
   <si>
     <t>토미오카상</t>
@@ -735,6 +744,15 @@
     <t>3조 2987억 2385만</t>
   </si>
   <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 6773억 6238만</t>
+  </si>
+  <si>
     <t>천칠</t>
   </si>
   <si>
@@ -747,15 +765,6 @@
     <t>2조 6702억 2482만</t>
   </si>
   <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>2조 6252억 4217만</t>
-  </si>
-  <si>
     <t>토니워터</t>
   </si>
   <si>
@@ -771,7 +780,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
   </si>
   <si>
-    <t>2조 5729억 5642만</t>
+    <t>2조 5820억 8150만</t>
   </si>
   <si>
     <t>펑풀</t>
@@ -798,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 2405억 3789만</t>
+    <t>1조 3357억 7546만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -834,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
   </si>
   <si>
-    <t>8949억 860만</t>
+    <t>8969억 3132만</t>
   </si>
   <si>
     <t>Targa</t>
@@ -858,7 +867,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>5424억 3794만</t>
+    <t>5504억 9405만</t>
   </si>
   <si>
     <t>짱창훈</t>
@@ -885,7 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>32조 9473억 5428만</t>
+    <t>33조 337억 4026만</t>
   </si>
   <si>
     <t>소독약</t>
@@ -921,7 +930,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
   </si>
   <si>
-    <t>6조 8401억 6735만</t>
+    <t>7조 1037억 1996만</t>
+  </si>
+  <si>
+    <t>파산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
+  </si>
+  <si>
+    <t>5조 2663억 2599만</t>
   </si>
   <si>
     <t>슈웃</t>
@@ -939,16 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
   </si>
   <si>
-    <t>4조 7573억 2987만</t>
-  </si>
-  <si>
-    <t>파산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
-  </si>
-  <si>
-    <t>4조 7044억 1961만</t>
+    <t>5조 884억 8079만</t>
   </si>
   <si>
     <t>강린</t>
@@ -966,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
   </si>
   <si>
-    <t>4조 450억 5646만</t>
+    <t>4조 1387억 9300만</t>
   </si>
   <si>
     <t>빡박이</t>
@@ -1047,7 +1056,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
   </si>
   <si>
-    <t>2조 3948억 1791만</t>
+    <t>2조 4299억 8920만</t>
   </si>
   <si>
     <t>베르1</t>
@@ -1056,7 +1065,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
   </si>
   <si>
-    <t>2조 3313억 3223만</t>
+    <t>2조 3381억 4735만</t>
   </si>
   <si>
     <t>Uhani</t>
@@ -1083,7 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
   </si>
   <si>
-    <t>1조 9072억 8066만</t>
+    <t>1조 9726억 8087만</t>
   </si>
   <si>
     <t>깅궁둥</t>
@@ -1104,6 +1113,15 @@
     <t>1조 8408억 8307만</t>
   </si>
   <si>
+    <t>가이아의격노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
+  </si>
+  <si>
+    <t>1조 8332억 4883만</t>
+  </si>
+  <si>
     <t>양설유</t>
   </si>
   <si>
@@ -1113,15 +1131,6 @@
     <t>1조 7462억 7709만</t>
   </si>
   <si>
-    <t>가이아의격노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
-  </si>
-  <si>
-    <t>1조 7212억 2724만</t>
-  </si>
-  <si>
     <t>도레스</t>
   </si>
   <si>
@@ -1131,9 +1140,6 @@
     <t>1조 1839억 1961만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>양산호수공원</t>
   </si>
   <si>
@@ -1152,7 +1158,7 @@
     <t>https://mgf.gg/contents/character.php?n=potato</t>
   </si>
   <si>
-    <t>9028억 2841만</t>
+    <t>9636억 4989만</t>
   </si>
   <si>
     <t>뀨래</t>
@@ -1170,7 +1176,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EA%B2%A1</t>
   </si>
   <si>
-    <t>24조 8464억 3573만</t>
+    <t>25조 2647억 3158만</t>
   </si>
   <si>
     <t>과학실</t>
@@ -1245,7 +1251,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A0%88%EB%B0%88</t>
   </si>
   <si>
-    <t>2조 8975억 7445만</t>
+    <t>2조 9816억 5861만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%8B%88%EC%9D%B4%EC%9D%B4</t>
@@ -1260,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8A%BC%ED%8A%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8283억 1974만</t>
+    <t>1조 8418억 8431만</t>
   </si>
   <si>
     <t>전뱀</t>
@@ -1287,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%98%81%EC%A7%84</t>
   </si>
   <si>
-    <t>1조 3304억 8558만</t>
+    <t>1조 3328억 3105만</t>
   </si>
   <si>
     <t>갓겜이네메키</t>
@@ -1299,6 +1305,15 @@
     <t>1조 3132억 1135만</t>
   </si>
   <si>
+    <t>말랑초이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%B4%88%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 2375억 2438만</t>
+  </si>
+  <si>
     <t>몰랑초이</t>
   </si>
   <si>
@@ -1314,16 +1329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%95%EC%A0%9C%EC%9C%A1%EA%B2%80</t>
   </si>
   <si>
-    <t>1조 1974억 7786만</t>
-  </si>
-  <si>
-    <t>말랑초이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%B4%88%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 1905억 2792만</t>
+    <t>1조 2185억 6415만</t>
   </si>
   <si>
     <t>항뷰리</t>
@@ -1368,7 +1374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC</t>
   </si>
   <si>
-    <t>8772억 6329만</t>
+    <t>8843억 5383만</t>
   </si>
   <si>
     <t>갱기님</t>
@@ -1386,7 +1392,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%ED%95%A9%EC%99%95</t>
   </si>
   <si>
-    <t>6843억 7077만</t>
+    <t>6861억 1489만</t>
   </si>
   <si>
     <t>당양감</t>
@@ -1527,7 +1533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A9%ED%86%B5</t>
   </si>
   <si>
-    <t>1조 1340억 5345만</t>
+    <t>1조 1650억 878만</t>
   </si>
   <si>
     <t>음묘우</t>
@@ -1617,7 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%9C%EC%A5%AC%EB%A9%90</t>
   </si>
   <si>
-    <t>5817억 1752만</t>
+    <t>5960억 8308만</t>
   </si>
   <si>
     <t>오렌지니</t>
@@ -1635,7 +1641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EA%B3%B5%EC%A3%BC</t>
   </si>
   <si>
-    <t>5228억 9257만</t>
+    <t>5235억 1311만</t>
   </si>
   <si>
     <t>o루비녹스o</t>
@@ -1665,7 +1671,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>3203억 5341만</t>
+    <t>3348억 1501만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%8F%99</t>
@@ -1680,7 +1686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%B8%84%ED%95%91</t>
   </si>
   <si>
-    <t>16조 4918억 4615만</t>
+    <t>18조 4270억 8576만</t>
   </si>
   <si>
     <t>걀보</t>
@@ -1725,7 +1731,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%98%B8%EC%9D%80</t>
   </si>
   <si>
-    <t>2조 7172억 9868만</t>
+    <t>2조 8767억 4562만</t>
+  </si>
+  <si>
+    <t>애기이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 7202억 3568만</t>
   </si>
   <si>
     <t>그냐앙</t>
@@ -1734,7 +1749,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%83%90%EC%95%99</t>
   </si>
   <si>
-    <t>2조 6959억 3259만</t>
+    <t>2조 7129억 9189만</t>
+  </si>
+  <si>
+    <t>야제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>2조 6847억 4633만</t>
   </si>
   <si>
     <t>승호숍</t>
@@ -1746,31 +1770,13 @@
     <t>2조 6053억 310만</t>
   </si>
   <si>
-    <t>애기이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 6019억 4405만</t>
-  </si>
-  <si>
     <t>하깁s</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EA%B9%81s</t>
   </si>
   <si>
-    <t>2조 5026억 3120만</t>
-  </si>
-  <si>
-    <t>야제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>2조 4181억 16만</t>
+    <t>2조 6043억 5354만</t>
   </si>
   <si>
     <t>은디탁</t>
@@ -1779,7 +1785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%94%94%ED%83%81</t>
   </si>
   <si>
-    <t>2조 3265억 106만</t>
+    <t>2조 4095억 1005만</t>
   </si>
   <si>
     <t>맛조개</t>
@@ -1842,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=jinajina</t>
   </si>
   <si>
-    <t>1조 798억 1637만</t>
+    <t>1조 1393억 8236만</t>
   </si>
   <si>
     <t>덕장이다습할</t>
@@ -1860,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%A0%EC%84%9D</t>
   </si>
   <si>
-    <t>1조 18억 5366만</t>
+    <t>1조 90억 7869만</t>
   </si>
   <si>
     <t>뿌베</t>
@@ -1869,7 +1875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%B2%A0</t>
   </si>
   <si>
-    <t>8847억 5595만</t>
+    <t>9121억 6356만</t>
   </si>
   <si>
     <t>챵술사</t>
@@ -1878,7 +1884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%B5%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>8235억 1690만</t>
+    <t>8248억 9362만</t>
   </si>
   <si>
     <t>근카자</t>
@@ -1896,7 +1902,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>81조 3996억 4645만</t>
+    <t>83조 4142억 8929만</t>
   </si>
   <si>
     <t>뽀대챠밍</t>
@@ -1905,7 +1911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%8C%80%EC%B1%A0%EB%B0%8D</t>
   </si>
   <si>
-    <t>16조 6533억 3835만</t>
+    <t>16조 7960억 1040만</t>
   </si>
   <si>
     <t>신궝</t>
@@ -1914,7 +1920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%9D</t>
   </si>
   <si>
-    <t>5조 3802억 3621만</t>
+    <t>5조 4044억 1039만</t>
   </si>
   <si>
     <t>미니두두</t>
@@ -1935,6 +1941,15 @@
     <t>3조 3293억 9219만</t>
   </si>
   <si>
+    <t>기어피프스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%96%B4%ED%94%BC%ED%94%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>2조 9286억 754만</t>
+  </si>
+  <si>
     <t>13ang뱅사거리</t>
   </si>
   <si>
@@ -1944,6 +1959,15 @@
     <t>2조 8570억 3491만</t>
   </si>
   <si>
+    <t>님이럴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%EC%9D%B4%EB%9F%B4</t>
+  </si>
+  <si>
+    <t>2조 8238억 1258만</t>
+  </si>
+  <si>
     <t>꽤괜</t>
   </si>
   <si>
@@ -1959,25 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%84%88%EB%A6%AC</t>
   </si>
   <si>
-    <t>2조 6580억 9672만</t>
-  </si>
-  <si>
-    <t>님이럴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%EC%9D%B4%EB%9F%B4</t>
-  </si>
-  <si>
-    <t>2조 6163억 1461만</t>
-  </si>
-  <si>
-    <t>기어피프스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%96%B4%ED%94%BC%ED%94%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>2조 5367억 3928만</t>
+    <t>2조 7363억 4028만</t>
   </si>
   <si>
     <t>기둥1알2</t>
@@ -2004,7 +2010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%9D%EC%9A%94</t>
   </si>
   <si>
-    <t>1조 9243억 3941만</t>
+    <t>2조 506억 487만</t>
   </si>
   <si>
     <t>클리브</t>
@@ -2067,7 +2073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%A7%B9%EC%B8%84</t>
   </si>
   <si>
-    <t>6271억 4609만</t>
+    <t>6402억 299만</t>
   </si>
   <si>
     <t>오렌지공쥬</t>
@@ -2085,7 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%9D%B8%ED%98%95</t>
   </si>
   <si>
-    <t>2815억 2930만</t>
+    <t>2886억 7992만</t>
   </si>
   <si>
     <t>진킹배</t>
@@ -2106,25 +2112,25 @@
     <t>1821억 4567만</t>
   </si>
   <si>
+    <t>힐러충충이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%9F%AC%EC%B6%A9%EC%B6%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1548억 1059만</t>
+  </si>
+  <si>
     <t>희태바라기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%ED%83%9C%EB%B0%94%EB%9D%BC%EA%B8%B0</t>
   </si>
   <si>
-    <t>1314억 8598만</t>
-  </si>
-  <si>
-    <t>힐러충충이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%9F%AC%EC%B6%A9%EC%B6%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1301억 1590만</t>
+    <t>1381억 1656만</t>
   </si>
   <si>
     <t>머랭키쿠</t>
@@ -2711,19 +2717,19 @@
         <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>34</v>
@@ -2731,40 +2737,40 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>34</v>
@@ -2772,22 +2778,22 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>18</v>
@@ -2796,16 +2802,16 @@
         <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>24</v>
@@ -2813,40 +2819,40 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>24</v>
@@ -2869,7 +2875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2887,28 +2893,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2919,7 +2925,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2928,19 +2934,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2951,28 +2957,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2983,28 +2989,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3015,28 +3021,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3047,28 +3053,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3079,28 +3085,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3111,28 +3117,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3143,28 +3149,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3175,28 +3181,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3207,28 +3213,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3239,28 +3245,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3271,28 +3277,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3303,25 +3309,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>148</v>
@@ -3347,13 +3353,13 @@
         <v>151</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>152</v>
@@ -3379,13 +3385,13 @@
         <v>155</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>156</v>
@@ -3411,16 +3417,16 @@
         <v>159</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3431,28 +3437,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3463,28 +3469,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3495,28 +3501,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3527,28 +3533,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3559,28 +3565,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3591,28 +3597,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3623,28 +3629,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3655,28 +3661,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3687,28 +3693,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3719,28 +3725,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3751,28 +3757,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3783,35 +3789,67 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3841,6 +3879,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3866,28 +3905,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3898,28 +3937,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -3930,28 +3969,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -3962,28 +4001,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -3994,28 +4033,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4026,28 +4065,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4058,28 +4097,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4090,28 +4129,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4122,28 +4161,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>236</v>
+        <v>124</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4154,28 +4193,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>211</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4186,28 +4225,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4218,28 +4257,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4250,28 +4289,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4282,28 +4321,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4317,25 +4356,25 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4349,25 +4388,25 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4381,25 +4420,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4410,28 +4449,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4442,7 +4481,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>33</v>
@@ -4451,19 +4490,19 @@
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4474,28 +4513,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4506,28 +4545,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4538,28 +4577,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4570,28 +4609,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4647,28 +4686,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4679,7 +4718,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>42</v>
@@ -4688,19 +4727,19 @@
         <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4711,28 +4750,28 @@
         <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4743,28 +4782,28 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4775,28 +4814,28 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4807,28 +4846,28 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4839,28 +4878,28 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4871,28 +4910,28 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4903,28 +4942,28 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4935,28 +4974,28 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4967,28 +5006,28 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4999,28 +5038,28 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5031,28 +5070,28 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5063,28 +5102,28 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5098,25 +5137,25 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5130,25 +5169,25 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5162,25 +5201,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5191,28 +5230,28 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5223,28 +5262,28 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5255,28 +5294,28 @@
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5287,28 +5326,28 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5319,28 +5358,28 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5351,28 +5390,28 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5383,28 +5422,28 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5415,28 +5454,28 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5447,28 +5486,28 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5479,28 +5518,28 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5511,28 +5550,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5543,28 +5582,28 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5575,28 +5614,28 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>366</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5607,28 +5646,28 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5692,28 +5731,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5724,28 +5763,28 @@
         <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -5756,28 +5795,28 @@
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -5788,28 +5827,28 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -5820,28 +5859,28 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -5852,28 +5891,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -5884,28 +5923,28 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -5916,28 +5955,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -5948,28 +5987,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -5980,28 +6019,28 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6012,28 +6051,28 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6044,28 +6083,28 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6076,28 +6115,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6108,28 +6147,28 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -6143,25 +6182,25 @@
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6175,25 +6214,25 @@
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6207,25 +6246,25 @@
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6236,28 +6275,28 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -6268,28 +6307,28 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6300,28 +6339,28 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6332,28 +6371,28 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6364,28 +6403,28 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6396,28 +6435,28 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6428,28 +6467,28 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6460,28 +6499,28 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6492,28 +6531,28 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6524,28 +6563,28 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6556,28 +6595,28 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6638,28 +6677,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6667,31 +6706,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6699,31 +6738,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6731,31 +6770,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6763,31 +6802,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6795,31 +6834,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6827,31 +6866,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6859,31 +6898,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6891,31 +6930,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6923,31 +6962,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6955,31 +6994,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6987,31 +7026,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -7019,31 +7058,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -7051,31 +7090,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7083,31 +7122,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7115,31 +7154,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7147,31 +7186,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7179,31 +7218,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7211,31 +7250,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7243,31 +7282,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7275,31 +7314,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7307,31 +7346,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7339,31 +7378,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7371,31 +7410,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7403,31 +7442,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7435,31 +7474,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7467,31 +7506,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7499,31 +7538,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7531,31 +7570,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -7563,31 +7602,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>366</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -7595,31 +7634,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -7683,28 +7722,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -7712,31 +7751,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7744,31 +7783,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7776,31 +7815,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7808,31 +7847,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7840,31 +7879,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7872,31 +7911,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7904,31 +7943,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7936,31 +7975,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7968,31 +8007,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>400</v>
+        <v>124</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8000,31 +8039,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8032,31 +8071,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>99</v>
+        <v>402</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8064,31 +8103,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8096,31 +8135,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8128,31 +8167,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8160,31 +8199,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8192,31 +8231,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8224,31 +8263,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8256,31 +8295,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8288,31 +8327,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8320,31 +8359,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8352,31 +8391,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8384,31 +8423,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8416,31 +8455,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8448,31 +8487,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8480,31 +8519,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8563,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -8592,31 +8631,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8624,31 +8663,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8656,31 +8695,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8688,31 +8727,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8720,31 +8759,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8752,31 +8791,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8784,31 +8823,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8816,31 +8855,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8848,31 +8887,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8880,31 +8919,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8912,31 +8951,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8944,31 +8983,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8976,31 +9015,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9008,31 +9047,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9040,31 +9079,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9072,31 +9111,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9104,31 +9143,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9136,31 +9175,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9168,31 +9207,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9200,31 +9239,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9232,31 +9271,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9264,31 +9303,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9296,31 +9335,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9328,31 +9367,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9360,31 +9399,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>402</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>274</v>
+        <v>695</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9392,31 +9431,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>400</v>
+        <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>696</v>
+        <v>277</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9424,31 +9463,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9456,31 +9495,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>700</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -9,22 +9,22 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="부계둘" sheetId="3" r:id="rId3"/>
-    <sheet name="숑숑" sheetId="4" r:id="rId4"/>
-    <sheet name="또래" sheetId="5" r:id="rId5"/>
-    <sheet name="0FeroCity" sheetId="6" r:id="rId6"/>
-    <sheet name="풍년순대국밥" sheetId="7" r:id="rId7"/>
-    <sheet name="알바천국" sheetId="8" r:id="rId8"/>
+    <sheet name="숑숑" sheetId="3" r:id="rId3"/>
+    <sheet name="또래" sheetId="4" r:id="rId4"/>
+    <sheet name="0FeroCity" sheetId="5" r:id="rId5"/>
+    <sheet name="풍년순대국밥" sheetId="6" r:id="rId6"/>
+    <sheet name="알바천국" sheetId="7" r:id="rId7"/>
+    <sheet name="부계둘" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'0FeroCity'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'0FeroCity'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">또래!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">또래!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">부계둘!$A$1:$J$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">알바천국!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">풍년순대국밥!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">숑숑!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">알바천국!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">풍년순대국밥!$A$1:$J$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,6 +108,132 @@
     <t>2026.04.11</t>
   </si>
   <si>
+    <t>숑숑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>13위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>129조 2754억 1292만</t>
+  </si>
+  <si>
+    <t>소통 잘하시는분들 환영! 투력1조이상! 가입 전 꼭 귓문의 부탁드려용 문의는(강린)</t>
+  </si>
+  <si>
+    <t>숑이</t>
+  </si>
+  <si>
+    <t>또래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%98%90%EB%9E%98</t>
+  </si>
+  <si>
+    <t>Scania 26</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>18위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>120조 7753억 7512만</t>
+  </si>
+  <si>
+    <t>꾸래 또래 원정대 가입문의 (숀오공,인순,나영석PDD)</t>
+  </si>
+  <si>
+    <t>또니이이</t>
+  </si>
+  <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
+    <t>0FeroCity</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=0FeroCity</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>19위</t>
+  </si>
+  <si>
+    <t>123조 8057억 8607만</t>
+  </si>
+  <si>
+    <t>0FeroCity길드입니다 길드가입신청시 귓으로 먼저 문의 주세요 무조건 길갑신청부터 하시면 거절합니다</t>
+  </si>
+  <si>
+    <t>oFero월향o</t>
+  </si>
+  <si>
+    <t>풍년순대국밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%92%8D%EB%85%84%EC%88%9C%EB%8C%80%EA%B5%AD%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>126조 1298억 4614만</t>
+  </si>
+  <si>
+    <t>길드가입조건:투력2조이상 (오픈톡 필수참여) 길드컨텐츠 열심히 하는분들 환영 입니다. 문의- 망동, 밍츄핑, 갱미킴</t>
+  </si>
+  <si>
+    <t>망동</t>
+  </si>
+  <si>
+    <t>알바천국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%95%8C%EB%B0%94%EC%B2%9C%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>Scania 1</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>35위</t>
+  </si>
+  <si>
+    <t>127조 9583억 5595만</t>
+  </si>
+  <si>
+    <t>1일 미접 ,길컨 미참 추방/건물업 필/롱런 하실 분/길톡 필수/7000억 이상/문의 선귓</t>
+  </si>
+  <si>
+    <t>선바</t>
+  </si>
+  <si>
     <t>부계둘</t>
   </si>
   <si>
@@ -123,9 +249,6 @@
     <t>10위</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
     <t>124조 4701억 3596만</t>
   </si>
   <si>
@@ -135,129 +258,6 @@
     <t>홍춘삼</t>
   </si>
   <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>숑숑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>13위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>129조 2754억 1292만</t>
-  </si>
-  <si>
-    <t>소통 잘하시는분들 환영! 투력1조이상! 가입 전 꼭 귓문의 부탁드려용 문의는(강린)</t>
-  </si>
-  <si>
-    <t>숑이</t>
-  </si>
-  <si>
-    <t>또래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%98%90%EB%9E%98</t>
-  </si>
-  <si>
-    <t>Scania 26</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>18위</t>
-  </si>
-  <si>
-    <t>120조 7753억 7512만</t>
-  </si>
-  <si>
-    <t>꾸래 또래 원정대 가입문의 (숀오공,인순,나영석PDD)</t>
-  </si>
-  <si>
-    <t>또니이이</t>
-  </si>
-  <si>
-    <t>0FeroCity</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=0FeroCity</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>19위</t>
-  </si>
-  <si>
-    <t>123조 8057억 8607만</t>
-  </si>
-  <si>
-    <t>0FeroCity길드입니다 길드가입신청시 귓으로 먼저 문의 주세요 무조건 길갑신청부터 하시면 거절합니다</t>
-  </si>
-  <si>
-    <t>oFero월향o</t>
-  </si>
-  <si>
-    <t>풍년순대국밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%92%8D%EB%85%84%EC%88%9C%EB%8C%80%EA%B5%AD%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>Scania 4</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>126조 1298억 4614만</t>
-  </si>
-  <si>
-    <t>길드가입조건:투력2조이상 (오픈톡 필수참여) 길드컨텐츠 열심히 하는분들 환영 입니다. 문의- 망동, 밍츄핑, 갱미킴</t>
-  </si>
-  <si>
-    <t>망동</t>
-  </si>
-  <si>
-    <t>알바천국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%95%8C%EB%B0%94%EC%B2%9C%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>Scania 1</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>35위</t>
-  </si>
-  <si>
-    <t>127조 9583억 5595만</t>
-  </si>
-  <si>
-    <t>1일 미접 ,길컨 미참 추방/건물업 필/롱런 하실 분/길톡 필수/7000억 이상/문의 선귓</t>
-  </si>
-  <si>
-    <t>선바</t>
-  </si>
-  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -297,7 +297,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>16조 7401억 1193만</t>
+    <t>17조 1695억 4531만</t>
   </si>
   <si>
     <t>2</t>
@@ -447,7 +447,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 2387억 6610만</t>
+    <t>4조 2993억 5963만</t>
   </si>
   <si>
     <t>12</t>
@@ -681,6 +681,1281 @@
     <t>1조 2381억 1362만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>33조 337억 4026만</t>
+  </si>
+  <si>
+    <t>소독약</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
+  </si>
+  <si>
+    <t>14조 6115억 5118만</t>
+  </si>
+  <si>
+    <t>주존사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>12조 2134억 7541만</t>
+  </si>
+  <si>
+    <t>휘정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
+  </si>
+  <si>
+    <t>7조 7401억 3625만</t>
+  </si>
+  <si>
+    <t>무피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
+  </si>
+  <si>
+    <t>7조 1037억 1996만</t>
+  </si>
+  <si>
+    <t>파산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
+  </si>
+  <si>
+    <t>5조 2663억 2599만</t>
+  </si>
+  <si>
+    <t>슈웃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
+  </si>
+  <si>
+    <t>5조 2536억 3990만</t>
+  </si>
+  <si>
+    <t>캐서린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>5조 884억 8079만</t>
+  </si>
+  <si>
+    <t>강린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>4조 4116억 2751만</t>
+  </si>
+  <si>
+    <t>임나연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
+  </si>
+  <si>
+    <t>4조 1387억 9300만</t>
+  </si>
+  <si>
+    <t>빡박이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 372억 1982만</t>
+  </si>
+  <si>
+    <t>졸귀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
+  </si>
+  <si>
+    <t>3조 9023억 745만</t>
+  </si>
+  <si>
+    <t>스파토이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 2857억 8502만</t>
+  </si>
+  <si>
+    <t>YAMAMOTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
+  </si>
+  <si>
+    <t>3조 1669억 6472만</t>
+  </si>
+  <si>
+    <t>픽홀로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3조 727억 7187만</t>
+  </si>
+  <si>
+    <t>쟈라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>2조 9098억 1790만</t>
+  </si>
+  <si>
+    <t>Rania</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rania</t>
+  </si>
+  <si>
+    <t>2조 6780억 7684만</t>
+  </si>
+  <si>
+    <t>바세린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>2조 6490억 9667만</t>
+  </si>
+  <si>
+    <t>미진생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
+  </si>
+  <si>
+    <t>2조 4299억 8920만</t>
+  </si>
+  <si>
+    <t>베르1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
+  </si>
+  <si>
+    <t>2조 3381억 4735만</t>
+  </si>
+  <si>
+    <t>Uhani</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
+  </si>
+  <si>
+    <t>2조 384억 6922만</t>
+  </si>
+  <si>
+    <t>쟁반짜장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2조 15억 7320만</t>
+  </si>
+  <si>
+    <t>하숑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
+  </si>
+  <si>
+    <t>1조 9726억 8087만</t>
+  </si>
+  <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1조 8429억 3125만</t>
+  </si>
+  <si>
+    <t>별렉스b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
+  </si>
+  <si>
+    <t>1조 8408억 8307만</t>
+  </si>
+  <si>
+    <t>가이아의격노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
+  </si>
+  <si>
+    <t>1조 8332억 4883만</t>
+  </si>
+  <si>
+    <t>양설유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 7462억 7709만</t>
+  </si>
+  <si>
+    <t>도레스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1조 1839억 1961만</t>
+  </si>
+  <si>
+    <t>양산호수공원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 1318억 9672만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=potato</t>
+  </si>
+  <si>
+    <t>9636억 4989만</t>
+  </si>
+  <si>
+    <t>뀨래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EB%9E%98</t>
+  </si>
+  <si>
+    <t>41조 4986억 7830만</t>
+  </si>
+  <si>
+    <t>호겡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EA%B2%A1</t>
+  </si>
+  <si>
+    <t>25조 2647억 3158만</t>
+  </si>
+  <si>
+    <t>과학실</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%ED%95%99%EC%8B%A4</t>
+  </si>
+  <si>
+    <t>18조 8526억 4330만</t>
+  </si>
+  <si>
+    <t>우주킥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%ED%82%A5</t>
+  </si>
+  <si>
+    <t>5조 2485억 7572만</t>
+  </si>
+  <si>
+    <t>아옳옳</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%98%B3%EC%98%B3</t>
+  </si>
+  <si>
+    <t>4조 3994억 5106만</t>
+  </si>
+  <si>
+    <t>해삐예삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%82%90%EC%98%88%EC%82%90</t>
+  </si>
+  <si>
+    <t>4조 3733억 5098만</t>
+  </si>
+  <si>
+    <t>나영석PDD</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%98%81%EC%84%9DPDD</t>
+  </si>
+  <si>
+    <t>4조 276억 1258만</t>
+  </si>
+  <si>
+    <t>뜨막</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A7%89</t>
+  </si>
+  <si>
+    <t>3조 8020억 7051만</t>
+  </si>
+  <si>
+    <t>싱그러운생귤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B1%EA%B7%B8%EB%9F%AC%EC%9A%B4%EC%83%9D%EA%B7%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>3조 1832억 4975만</t>
+  </si>
+  <si>
+    <t>꾸레밈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A0%88%EB%B0%88</t>
+  </si>
+  <si>
+    <t>2조 9816억 5861만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%8B%88%EC%9D%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 4730억 6872만</t>
+  </si>
+  <si>
+    <t>서튼튼이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8A%BC%ED%8A%BC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 8418억 8431만</t>
+  </si>
+  <si>
+    <t>전뱀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EB%B1%80</t>
+  </si>
+  <si>
+    <t>1조 6908억 8745만</t>
+  </si>
+  <si>
+    <t>라즈샤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A6%88%EC%83%A4</t>
+  </si>
+  <si>
+    <t>1조 5996억 6660만</t>
+  </si>
+  <si>
+    <t>하영진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%98%81%EC%A7%84</t>
+  </si>
+  <si>
+    <t>1조 3331억 472만</t>
+  </si>
+  <si>
+    <t>갓겜이네메키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EC%9D%B4%EB%84%A4%EB%A9%94%ED%82%A4</t>
+  </si>
+  <si>
+    <t>1조 3132억 1135만</t>
+  </si>
+  <si>
+    <t>말랑초이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%B4%88%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 2375억 2438만</t>
+  </si>
+  <si>
+    <t>몰랑초이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9E%91%EC%B4%88%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 2347억 8879만</t>
+  </si>
+  <si>
+    <t>대박제육검</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%95%EC%A0%9C%EC%9C%A1%EA%B2%80</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 2185억 6415만</t>
+  </si>
+  <si>
+    <t>항뷰리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EB%B7%B0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1조 1629억 7713만</t>
+  </si>
+  <si>
+    <t>순혈단또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%ED%98%88%EB%8B%A8%EB%98%90</t>
+  </si>
+  <si>
+    <t>1조 857억 4649만</t>
+  </si>
+  <si>
+    <t>Lim1t</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Lim1t</t>
+  </si>
+  <si>
+    <t>9694억 4875만</t>
+  </si>
+  <si>
+    <t>히빌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%B9%8C</t>
+  </si>
+  <si>
+    <t>9460억 3345만</t>
+  </si>
+  <si>
+    <t>봉구리구리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>8854억 9428만</t>
+  </si>
+  <si>
+    <t>갱기님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B1%EA%B8%B0%EB%8B%98</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>8307억 3657만</t>
+  </si>
+  <si>
+    <t>복합왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%ED%95%A9%EC%99%95</t>
+  </si>
+  <si>
+    <t>6862억 9343만</t>
+  </si>
+  <si>
+    <t>당양감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EC%96%91%EA%B0%90</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>1800억 8890만</t>
+  </si>
+  <si>
+    <t>다내꼬양</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%82%B4%EA%BC%AC%EC%96%91</t>
+  </si>
+  <si>
+    <t>46조 7631억 7929만</t>
+  </si>
+  <si>
+    <t>으닝닝맛섀도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%9D%EB%8B%9D%EB%A7%9B%EC%84%80%EB%8F%84</t>
+  </si>
+  <si>
+    <t>38조 7302억 5673만</t>
+  </si>
+  <si>
+    <t>캘리v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%98%EB%A6%ACv</t>
+  </si>
+  <si>
+    <t>17조 8319억 6127만</t>
+  </si>
+  <si>
+    <t>oFero라온o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=oFero%EB%9D%BC%EC%98%A8o</t>
+  </si>
+  <si>
+    <t>10조 9434억 7404만</t>
+  </si>
+  <si>
+    <t>메이쁠키우깅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%9D%B4%EC%81%A0%ED%82%A4%EC%9A%B0%EA%B9%85</t>
+  </si>
+  <si>
+    <t>7조 1097억 2958만</t>
+  </si>
+  <si>
+    <t>용이지니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4%EC%A7%80%EB%8B%88</t>
+  </si>
+  <si>
+    <t>5조 1037억 8896만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=oFero%EC%9B%94%ED%96%A5o</t>
+  </si>
+  <si>
+    <t>2조 5315억 4295만</t>
+  </si>
+  <si>
+    <t>크래쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EB%9E%98%EC%89%AC</t>
+  </si>
+  <si>
+    <t>2조 4938억 7965만</t>
+  </si>
+  <si>
+    <t>곡부공씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A1%EB%B6%80%EA%B3%B5%EC%94%A8</t>
+  </si>
+  <si>
+    <t>2조 3103억 5819만</t>
+  </si>
+  <si>
+    <t>기묘함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%AC%98%ED%95%A8</t>
+  </si>
+  <si>
+    <t>1조 9377억 2581만</t>
+  </si>
+  <si>
+    <t>한맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>1조 9308억 2661만</t>
+  </si>
+  <si>
+    <t>SPICY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SPICY</t>
+  </si>
+  <si>
+    <t>1조 8682억 1465만</t>
+  </si>
+  <si>
+    <t>장행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%96%89</t>
+  </si>
+  <si>
+    <t>1조 2511억 2429만</t>
+  </si>
+  <si>
+    <t>JUYs</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JUYs</t>
+  </si>
+  <si>
+    <t>1조 1730억 3808만</t>
+  </si>
+  <si>
+    <t>격통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A9%ED%86%B5</t>
+  </si>
+  <si>
+    <t>1조 1650억 878만</t>
+  </si>
+  <si>
+    <t>음묘우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8C%EB%AC%98%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1조 211억 7612만</t>
+  </si>
+  <si>
+    <t>로절린드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%A0%88%EB%A6%B0%EB%93%9C</t>
+  </si>
+  <si>
+    <t>9603억 4965만</t>
+  </si>
+  <si>
+    <t>댕댕이완자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%95%EB%8C%95%EC%9D%B4%EC%99%84%EC%9E%90</t>
+  </si>
+  <si>
+    <t>8894억 6832만</t>
+  </si>
+  <si>
+    <t>짱숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%88%8D</t>
+  </si>
+  <si>
+    <t>8495억 9841만</t>
+  </si>
+  <si>
+    <t>빙걸공듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EA%B1%B8%EA%B3%B5%EB%93%80</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>7994억 5718만</t>
+  </si>
+  <si>
+    <t>명왕하데스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%99%95%ED%95%98%EB%8D%B0%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>7944억 74만</t>
+  </si>
+  <si>
+    <t>보라물망초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%9D%BC%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
+  </si>
+  <si>
+    <t>7585억 1763만</t>
+  </si>
+  <si>
+    <t>귀흑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%ED%9D%91</t>
+  </si>
+  <si>
+    <t>6262억 4501만</t>
+  </si>
+  <si>
+    <t>소망님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%A7%9D%EB%8B%98</t>
+  </si>
+  <si>
+    <t>6222억 4063만</t>
+  </si>
+  <si>
+    <t>솜쥬멐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%9C%EC%A5%AC%EB%A9%90</t>
+  </si>
+  <si>
+    <t>5960억 8308만</t>
+  </si>
+  <si>
+    <t>오렌지니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EB%8B%88</t>
+  </si>
+  <si>
+    <t>5682억 8299만</t>
+  </si>
+  <si>
+    <t>야옹이공주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EA%B3%B5%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>5235억 1311만</t>
+  </si>
+  <si>
+    <t>o루비녹스o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%A3%A8%EB%B9%84%EB%85%B9%EC%8A%A4o</t>
+  </si>
+  <si>
+    <t>5065억 84만</t>
+  </si>
+  <si>
+    <t>녕죠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%95%EC%A3%A0</t>
+  </si>
+  <si>
+    <t>3798억 9522만</t>
+  </si>
+  <si>
+    <t>어뭉지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EB%AD%89%EC%A7%80</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>3348억 1501만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%8F%99</t>
+  </si>
+  <si>
+    <t>65조 8528억 9645만</t>
+  </si>
+  <si>
+    <t>밍츄핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%B8%84%ED%95%91</t>
+  </si>
+  <si>
+    <t>18조 4270억 8576만</t>
+  </si>
+  <si>
+    <t>걀보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%80%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>12조 8057억 8952만</t>
+  </si>
+  <si>
+    <t>님하하하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%ED%95%98%ED%95%98%ED%95%98</t>
+  </si>
+  <si>
+    <t>3조 5196억 4046만</t>
+  </si>
+  <si>
+    <t>랏뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>3조 1283억 9737만</t>
+  </si>
+  <si>
+    <t>왕오이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%98%A4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 78억 6848만</t>
+  </si>
+  <si>
+    <t>이호은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%98%B8%EC%9D%80</t>
+  </si>
+  <si>
+    <t>2조 8767억 4562만</t>
+  </si>
+  <si>
+    <t>그냐앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%83%90%EC%95%99</t>
+  </si>
+  <si>
+    <t>2조 7816억 961만</t>
+  </si>
+  <si>
+    <t>애기이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 7202억 3568만</t>
+  </si>
+  <si>
+    <t>야제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>2조 6847억 4633만</t>
+  </si>
+  <si>
+    <t>승호숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%ED%98%B8%EC%88%8D</t>
+  </si>
+  <si>
+    <t>2조 6053억 310만</t>
+  </si>
+  <si>
+    <t>하깁s</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EA%B9%81s</t>
+  </si>
+  <si>
+    <t>2조 6043억 5354만</t>
+  </si>
+  <si>
+    <t>은디탁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%94%94%ED%83%81</t>
+  </si>
+  <si>
+    <t>2조 4095억 1005만</t>
+  </si>
+  <si>
+    <t>맛조개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EC%A1%B0%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>2조 2619억 9857만</t>
+  </si>
+  <si>
+    <t>갱미킴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B1%EB%AF%B8%ED%82%B4</t>
+  </si>
+  <si>
+    <t>2조 453억 2315만</t>
+  </si>
+  <si>
+    <t>네모수박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%AA%A8%EC%88%98%EB%B0%95</t>
+  </si>
+  <si>
+    <t>1조 9175억 6016만</t>
+  </si>
+  <si>
+    <t>부라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 4308억 7074만</t>
+  </si>
+  <si>
+    <t>늙은마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8A%99%EC%9D%80%EB%A7%88</t>
+  </si>
+  <si>
+    <t>1조 3816억 6012만</t>
+  </si>
+  <si>
+    <t>라이언킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%9D%B4%EC%96%B8%ED%82%B9</t>
+  </si>
+  <si>
+    <t>1조 2524억 293만</t>
+  </si>
+  <si>
+    <t>jinajina</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=jinajina</t>
+  </si>
+  <si>
+    <t>1조 1393억 8236만</t>
+  </si>
+  <si>
+    <t>덕장이다습할</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EC%9E%A5%EC%9D%B4%EB%8B%A4%EC%8A%B5%ED%95%A0</t>
+  </si>
+  <si>
+    <t>1조 238억 9969만</t>
+  </si>
+  <si>
+    <t>켠석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BC%A0%EC%84%9D</t>
+  </si>
+  <si>
+    <t>1조 90억 7869만</t>
+  </si>
+  <si>
+    <t>뿌베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>9121억 6356만</t>
+  </si>
+  <si>
+    <t>챵술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%B5%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>8248억 9362만</t>
+  </si>
+  <si>
+    <t>근카자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%B9%B4%EC%9E%90</t>
+  </si>
+  <si>
+    <t>7924억 737만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B0%94</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>83조 4142억 8929만</t>
+  </si>
+  <si>
+    <t>뽀대챠밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%8C%80%EC%B1%A0%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>16조 7960억 1040만</t>
+  </si>
+  <si>
+    <t>신궝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%9D</t>
+  </si>
+  <si>
+    <t>5조 5446억 791만</t>
+  </si>
+  <si>
+    <t>미니두두</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EB%8B%88%EB%91%90%EB%91%90</t>
+  </si>
+  <si>
+    <t>4조 9192억 7882만</t>
+  </si>
+  <si>
+    <t>창창창</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EC%B0%BD%EC%B0%BD</t>
+  </si>
+  <si>
+    <t>3조 3293억 9219만</t>
+  </si>
+  <si>
+    <t>기어피프스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%96%B4%ED%94%BC%ED%94%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>2조 9286억 754만</t>
+  </si>
+  <si>
+    <t>13ang뱅사거리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=13ang%EB%B1%85%EC%82%AC%EA%B1%B0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 8570억 3491만</t>
+  </si>
+  <si>
+    <t>님이럴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%EC%9D%B4%EB%9F%B4</t>
+  </si>
+  <si>
+    <t>2조 8238억 1258만</t>
+  </si>
+  <si>
+    <t>꽤괜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%A4%EA%B4%9C</t>
+  </si>
+  <si>
+    <t>2조 7723억 2323만</t>
+  </si>
+  <si>
+    <t>다너리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%84%88%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 7363억 4028만</t>
+  </si>
+  <si>
+    <t>기둥1알2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%91%A51%EC%95%8C2</t>
+  </si>
+  <si>
+    <t>2조 4510억 6682만</t>
+  </si>
+  <si>
+    <t>탱설</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%EC%84%A4</t>
+  </si>
+  <si>
+    <t>2조 3337억 7615만</t>
+  </si>
+  <si>
+    <t>쭝요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%9D%EC%9A%94</t>
+  </si>
+  <si>
+    <t>2조 506억 487만</t>
+  </si>
+  <si>
+    <t>클리브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EB%A6%AC%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>1조 9040억 9300만</t>
+  </si>
+  <si>
+    <t>딸기전사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EC%A0%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1조 6291억 7772만</t>
+  </si>
+  <si>
+    <t>Soul</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Soul</t>
+  </si>
+  <si>
+    <t>1조 5924억 7433만</t>
+  </si>
+  <si>
+    <t>소바킴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%94%ED%82%B4</t>
+  </si>
+  <si>
+    <t>1조 3608억 6383만</t>
+  </si>
+  <si>
+    <t>사과왕쟈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EC%99%95%EC%9F%88</t>
+  </si>
+  <si>
+    <t>1조 733억 7740만</t>
+  </si>
+  <si>
+    <t>상속남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%86%8D%EB%82%A8</t>
+  </si>
+  <si>
+    <t>1조 488억 1763만</t>
+  </si>
+  <si>
+    <t>꼬맹츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%A7%B9%EC%B8%84</t>
+  </si>
+  <si>
+    <t>6402억 299만</t>
+  </si>
+  <si>
+    <t>오렌지공쥬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EA%B3%B5%EC%A5%AC</t>
+  </si>
+  <si>
+    <t>5972억 280만</t>
+  </si>
+  <si>
+    <t>옴인형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%9D%B8%ED%98%95</t>
+  </si>
+  <si>
+    <t>2886억 7992만</t>
+  </si>
+  <si>
+    <t>진킹배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%82%B9%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>2183억 7005만</t>
+  </si>
+  <si>
+    <t>연상녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%83%81%EB%85%80</t>
+  </si>
+  <si>
+    <t>1821억 4567만</t>
+  </si>
+  <si>
+    <t>힐러충충이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%9F%AC%EC%B6%A9%EC%B6%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1548억 1059만</t>
+  </si>
+  <si>
+    <t>희태바라기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%ED%83%9C%EB%B0%94%EB%9D%BC%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1381억 1656만</t>
+  </si>
+  <si>
+    <t>머랭키쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EB%9E%AD%ED%82%A4%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1155억 4589만</t>
+  </si>
+  <si>
+    <t>공쵸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%B5%B8</t>
+  </si>
+  <si>
+    <t>970억 8969만</t>
+  </si>
+  <si>
     <t>처히</t>
   </si>
   <si>
@@ -759,12 +2034,18 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
     <t>2조 6702억 2482만</t>
   </si>
   <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 6342억 2078만</t>
+  </si>
+  <si>
     <t>토니워터</t>
   </si>
   <si>
@@ -774,15 +2055,6 @@
     <t>2조 6162억 1545만</t>
   </si>
   <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 5820억 8150만</t>
-  </si>
-  <si>
     <t>펑풀</t>
   </si>
   <si>
@@ -807,7 +2079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 3357억 7546만</t>
+    <t>1조 3542억 7780만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -834,9 +2106,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
     <t>1조 24억 1640만</t>
   </si>
   <si>
@@ -852,9 +2121,6 @@
     <t>https://mgf.gg/contents/character.php?n=Targa</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
     <t>5665억 5826만</t>
   </si>
   <si>
@@ -864,9 +2130,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
     <t>5504억 9405만</t>
   </si>
   <si>
@@ -889,1269 +2152,6 @@
   </si>
   <si>
     <t>55억 5534만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>33조 337억 4026만</t>
-  </si>
-  <si>
-    <t>소독약</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
-  </si>
-  <si>
-    <t>14조 6115억 5118만</t>
-  </si>
-  <si>
-    <t>주존사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>12조 2134억 7541만</t>
-  </si>
-  <si>
-    <t>휘정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
-  </si>
-  <si>
-    <t>7조 7401억 3625만</t>
-  </si>
-  <si>
-    <t>무피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
-  </si>
-  <si>
-    <t>7조 1037억 1996만</t>
-  </si>
-  <si>
-    <t>파산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
-  </si>
-  <si>
-    <t>5조 2663억 2599만</t>
-  </si>
-  <si>
-    <t>슈웃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
-  </si>
-  <si>
-    <t>5조 2536억 3990만</t>
-  </si>
-  <si>
-    <t>캐서린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>5조 884억 8079만</t>
-  </si>
-  <si>
-    <t>강린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>4조 4116억 2751만</t>
-  </si>
-  <si>
-    <t>임나연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
-  </si>
-  <si>
-    <t>4조 1387억 9300만</t>
-  </si>
-  <si>
-    <t>빡박이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 372억 1982만</t>
-  </si>
-  <si>
-    <t>졸귀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
-  </si>
-  <si>
-    <t>3조 9023억 745만</t>
-  </si>
-  <si>
-    <t>스파토이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3조 2857억 8502만</t>
-  </si>
-  <si>
-    <t>YAMAMOTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
-  </si>
-  <si>
-    <t>3조 1669억 6472만</t>
-  </si>
-  <si>
-    <t>픽홀로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3조 727억 7187만</t>
-  </si>
-  <si>
-    <t>쟈라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>2조 9098억 1790만</t>
-  </si>
-  <si>
-    <t>Rania</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rania</t>
-  </si>
-  <si>
-    <t>2조 6780억 7684만</t>
-  </si>
-  <si>
-    <t>바세린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>2조 6490억 9667만</t>
-  </si>
-  <si>
-    <t>미진생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
-  </si>
-  <si>
-    <t>2조 4299억 8920만</t>
-  </si>
-  <si>
-    <t>베르1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
-  </si>
-  <si>
-    <t>2조 3381억 4735만</t>
-  </si>
-  <si>
-    <t>Uhani</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
-  </si>
-  <si>
-    <t>2조 384억 6922만</t>
-  </si>
-  <si>
-    <t>쟁반짜장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2조 15억 7320만</t>
-  </si>
-  <si>
-    <t>하숑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
-  </si>
-  <si>
-    <t>1조 9726억 8087만</t>
-  </si>
-  <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1조 8429억 3125만</t>
-  </si>
-  <si>
-    <t>별렉스b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
-  </si>
-  <si>
-    <t>1조 8408억 8307만</t>
-  </si>
-  <si>
-    <t>가이아의격노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
-  </si>
-  <si>
-    <t>1조 8332억 4883만</t>
-  </si>
-  <si>
-    <t>양설유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 7462억 7709만</t>
-  </si>
-  <si>
-    <t>도레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1조 1839억 1961만</t>
-  </si>
-  <si>
-    <t>양산호수공원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1조 1318억 9672만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>potato</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=potato</t>
-  </si>
-  <si>
-    <t>9636억 4989만</t>
-  </si>
-  <si>
-    <t>뀨래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EB%9E%98</t>
-  </si>
-  <si>
-    <t>41조 4986억 7830만</t>
-  </si>
-  <si>
-    <t>호겡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EA%B2%A1</t>
-  </si>
-  <si>
-    <t>25조 2647억 3158만</t>
-  </si>
-  <si>
-    <t>과학실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BC%ED%95%99%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>18조 8526억 4330만</t>
-  </si>
-  <si>
-    <t>우주킥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%ED%82%A5</t>
-  </si>
-  <si>
-    <t>5조 2485억 7572만</t>
-  </si>
-  <si>
-    <t>아옳옳</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%98%B3%EC%98%B3</t>
-  </si>
-  <si>
-    <t>4조 3994억 5106만</t>
-  </si>
-  <si>
-    <t>해삐예삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%82%90%EC%98%88%EC%82%90</t>
-  </si>
-  <si>
-    <t>4조 3733억 5098만</t>
-  </si>
-  <si>
-    <t>나영석PDD</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%98%81%EC%84%9DPDD</t>
-  </si>
-  <si>
-    <t>4조 276억 1258만</t>
-  </si>
-  <si>
-    <t>뜨막</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A7%89</t>
-  </si>
-  <si>
-    <t>3조 8020억 7051만</t>
-  </si>
-  <si>
-    <t>싱그러운생귤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B1%EA%B7%B8%EB%9F%AC%EC%9A%B4%EC%83%9D%EA%B7%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>3조 1832억 4975만</t>
-  </si>
-  <si>
-    <t>꾸레밈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A0%88%EB%B0%88</t>
-  </si>
-  <si>
-    <t>2조 9816억 5861만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%8B%88%EC%9D%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2조 4730억 6872만</t>
-  </si>
-  <si>
-    <t>서튼튼이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8A%BC%ED%8A%BC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 8418억 8431만</t>
-  </si>
-  <si>
-    <t>전뱀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EB%B1%80</t>
-  </si>
-  <si>
-    <t>1조 6648억 8244만</t>
-  </si>
-  <si>
-    <t>라즈샤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%A6%88%EC%83%A4</t>
-  </si>
-  <si>
-    <t>1조 5996억 6660만</t>
-  </si>
-  <si>
-    <t>하영진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%98%81%EC%A7%84</t>
-  </si>
-  <si>
-    <t>1조 3328억 3105만</t>
-  </si>
-  <si>
-    <t>갓겜이네메키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B2%9C%EC%9D%B4%EB%84%A4%EB%A9%94%ED%82%A4</t>
-  </si>
-  <si>
-    <t>1조 3132억 1135만</t>
-  </si>
-  <si>
-    <t>말랑초이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%B4%88%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 2375억 2438만</t>
-  </si>
-  <si>
-    <t>몰랑초이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%B0%EB%9E%91%EC%B4%88%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 2347억 8879만</t>
-  </si>
-  <si>
-    <t>대박제육검</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%95%EC%A0%9C%EC%9C%A1%EA%B2%80</t>
-  </si>
-  <si>
-    <t>1조 2185억 6415만</t>
-  </si>
-  <si>
-    <t>항뷰리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EB%B7%B0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 1629억 7713만</t>
-  </si>
-  <si>
-    <t>순혈단또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%ED%98%88%EB%8B%A8%EB%98%90</t>
-  </si>
-  <si>
-    <t>1조 857억 4649만</t>
-  </si>
-  <si>
-    <t>Lim1t</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Lim1t</t>
-  </si>
-  <si>
-    <t>9694억 4875만</t>
-  </si>
-  <si>
-    <t>히빌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%B9%8C</t>
-  </si>
-  <si>
-    <t>9460억 3345만</t>
-  </si>
-  <si>
-    <t>봉구리구리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>8843억 5383만</t>
-  </si>
-  <si>
-    <t>갱기님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B1%EA%B8%B0%EB%8B%98</t>
-  </si>
-  <si>
-    <t>8307억 3657만</t>
-  </si>
-  <si>
-    <t>복합왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%ED%95%A9%EC%99%95</t>
-  </si>
-  <si>
-    <t>6861억 1489만</t>
-  </si>
-  <si>
-    <t>당양감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EC%96%91%EA%B0%90</t>
-  </si>
-  <si>
-    <t>1800억 8890만</t>
-  </si>
-  <si>
-    <t>다내꼬양</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%82%B4%EA%BC%AC%EC%96%91</t>
-  </si>
-  <si>
-    <t>46조 7631억 7929만</t>
-  </si>
-  <si>
-    <t>으닝닝맛섀도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%9D%EB%8B%9D%EB%A7%9B%EC%84%80%EB%8F%84</t>
-  </si>
-  <si>
-    <t>38조 7302억 5673만</t>
-  </si>
-  <si>
-    <t>캘리v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%98%EB%A6%ACv</t>
-  </si>
-  <si>
-    <t>17조 8319억 6127만</t>
-  </si>
-  <si>
-    <t>oFero라온o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=oFero%EB%9D%BC%EC%98%A8o</t>
-  </si>
-  <si>
-    <t>10조 9434억 7404만</t>
-  </si>
-  <si>
-    <t>메이쁠키우깅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%9D%B4%EC%81%A0%ED%82%A4%EC%9A%B0%EA%B9%85</t>
-  </si>
-  <si>
-    <t>7조 1097억 2958만</t>
-  </si>
-  <si>
-    <t>용이지니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4%EC%A7%80%EB%8B%88</t>
-  </si>
-  <si>
-    <t>5조 1037억 8896만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=oFero%EC%9B%94%ED%96%A5o</t>
-  </si>
-  <si>
-    <t>2조 5315억 4295만</t>
-  </si>
-  <si>
-    <t>크래쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EB%9E%98%EC%89%AC</t>
-  </si>
-  <si>
-    <t>2조 4938억 7965만</t>
-  </si>
-  <si>
-    <t>곡부공씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A1%EB%B6%80%EA%B3%B5%EC%94%A8</t>
-  </si>
-  <si>
-    <t>2조 3103억 5819만</t>
-  </si>
-  <si>
-    <t>기묘함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%AC%98%ED%95%A8</t>
-  </si>
-  <si>
-    <t>1조 9377억 2581만</t>
-  </si>
-  <si>
-    <t>한맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>1조 9308억 2661만</t>
-  </si>
-  <si>
-    <t>SPICY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SPICY</t>
-  </si>
-  <si>
-    <t>1조 8682억 1465만</t>
-  </si>
-  <si>
-    <t>장행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%96%89</t>
-  </si>
-  <si>
-    <t>1조 2511억 2429만</t>
-  </si>
-  <si>
-    <t>JUYs</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JUYs</t>
-  </si>
-  <si>
-    <t>1조 1730억 3808만</t>
-  </si>
-  <si>
-    <t>격통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A9%ED%86%B5</t>
-  </si>
-  <si>
-    <t>1조 1650억 878만</t>
-  </si>
-  <si>
-    <t>음묘우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%8C%EB%AC%98%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>1조 211억 7612만</t>
-  </si>
-  <si>
-    <t>로절린드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%A0%88%EB%A6%B0%EB%93%9C</t>
-  </si>
-  <si>
-    <t>9603억 4965만</t>
-  </si>
-  <si>
-    <t>댕댕이완자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%95%EB%8C%95%EC%9D%B4%EC%99%84%EC%9E%90</t>
-  </si>
-  <si>
-    <t>8894억 6832만</t>
-  </si>
-  <si>
-    <t>짱숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%88%8D</t>
-  </si>
-  <si>
-    <t>8495억 9841만</t>
-  </si>
-  <si>
-    <t>빙걸공듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%99%EA%B1%B8%EA%B3%B5%EB%93%80</t>
-  </si>
-  <si>
-    <t>7994억 5718만</t>
-  </si>
-  <si>
-    <t>명왕하데스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%99%95%ED%95%98%EB%8D%B0%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>7944억 74만</t>
-  </si>
-  <si>
-    <t>보라물망초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%9D%BC%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
-  </si>
-  <si>
-    <t>7585억 1763만</t>
-  </si>
-  <si>
-    <t>귀흑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%ED%9D%91</t>
-  </si>
-  <si>
-    <t>6262억 4501만</t>
-  </si>
-  <si>
-    <t>소망님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%A7%9D%EB%8B%98</t>
-  </si>
-  <si>
-    <t>6222억 4063만</t>
-  </si>
-  <si>
-    <t>솜쥬멐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%9C%EC%A5%AC%EB%A9%90</t>
-  </si>
-  <si>
-    <t>5960억 8308만</t>
-  </si>
-  <si>
-    <t>오렌지니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EB%8B%88</t>
-  </si>
-  <si>
-    <t>5682억 8299만</t>
-  </si>
-  <si>
-    <t>야옹이공주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%98%B9%EC%9D%B4%EA%B3%B5%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>5235억 1311만</t>
-  </si>
-  <si>
-    <t>o루비녹스o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%A3%A8%EB%B9%84%EB%85%B9%EC%8A%A4o</t>
-  </si>
-  <si>
-    <t>5065억 84만</t>
-  </si>
-  <si>
-    <t>녕죠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%85%95%EC%A3%A0</t>
-  </si>
-  <si>
-    <t>3798억 9522만</t>
-  </si>
-  <si>
-    <t>어뭉지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%EB%AD%89%EC%A7%80</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>3348억 1501만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%8F%99</t>
-  </si>
-  <si>
-    <t>65조 8528억 9645만</t>
-  </si>
-  <si>
-    <t>밍츄핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%B8%84%ED%95%91</t>
-  </si>
-  <si>
-    <t>18조 4270억 8576만</t>
-  </si>
-  <si>
-    <t>걀보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%80%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>12조 8057억 8952만</t>
-  </si>
-  <si>
-    <t>님하하하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%ED%95%98%ED%95%98%ED%95%98</t>
-  </si>
-  <si>
-    <t>3조 5196억 4046만</t>
-  </si>
-  <si>
-    <t>랏뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>3조 1283억 9737만</t>
-  </si>
-  <si>
-    <t>왕오이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%98%A4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3조 78억 6848만</t>
-  </si>
-  <si>
-    <t>이호은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%98%B8%EC%9D%80</t>
-  </si>
-  <si>
-    <t>2조 8767억 4562만</t>
-  </si>
-  <si>
-    <t>애기이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 7202억 3568만</t>
-  </si>
-  <si>
-    <t>그냐앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%83%90%EC%95%99</t>
-  </si>
-  <si>
-    <t>2조 7129억 9189만</t>
-  </si>
-  <si>
-    <t>야제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>2조 6847억 4633만</t>
-  </si>
-  <si>
-    <t>승호숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%ED%98%B8%EC%88%8D</t>
-  </si>
-  <si>
-    <t>2조 6053억 310만</t>
-  </si>
-  <si>
-    <t>하깁s</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EA%B9%81s</t>
-  </si>
-  <si>
-    <t>2조 6043억 5354만</t>
-  </si>
-  <si>
-    <t>은디탁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%94%94%ED%83%81</t>
-  </si>
-  <si>
-    <t>2조 4095억 1005만</t>
-  </si>
-  <si>
-    <t>맛조개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EC%A1%B0%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>2조 2619억 9857만</t>
-  </si>
-  <si>
-    <t>갱미킴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B1%EB%AF%B8%ED%82%B4</t>
-  </si>
-  <si>
-    <t>2조 453억 2315만</t>
-  </si>
-  <si>
-    <t>네모수박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%AA%A8%EC%88%98%EB%B0%95</t>
-  </si>
-  <si>
-    <t>1조 9175억 6016만</t>
-  </si>
-  <si>
-    <t>부라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 4308억 7074만</t>
-  </si>
-  <si>
-    <t>늙은마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8A%99%EC%9D%80%EB%A7%88</t>
-  </si>
-  <si>
-    <t>1조 3816억 6012만</t>
-  </si>
-  <si>
-    <t>라이언킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%9D%B4%EC%96%B8%ED%82%B9</t>
-  </si>
-  <si>
-    <t>1조 2524억 293만</t>
-  </si>
-  <si>
-    <t>jinajina</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=jinajina</t>
-  </si>
-  <si>
-    <t>1조 1393억 8236만</t>
-  </si>
-  <si>
-    <t>덕장이다습할</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EC%9E%A5%EC%9D%B4%EB%8B%A4%EC%8A%B5%ED%95%A0</t>
-  </si>
-  <si>
-    <t>1조 238억 9969만</t>
-  </si>
-  <si>
-    <t>켠석</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BC%A0%EC%84%9D</t>
-  </si>
-  <si>
-    <t>1조 90억 7869만</t>
-  </si>
-  <si>
-    <t>뿌베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>9121억 6356만</t>
-  </si>
-  <si>
-    <t>챵술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%B5%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>8248억 9362만</t>
-  </si>
-  <si>
-    <t>근카자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%B9%B4%EC%9E%90</t>
-  </si>
-  <si>
-    <t>7924억 737만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B0%94</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>83조 4142억 8929만</t>
-  </si>
-  <si>
-    <t>뽀대챠밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%8C%80%EC%B1%A0%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>16조 7960억 1040만</t>
-  </si>
-  <si>
-    <t>신궝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%9D</t>
-  </si>
-  <si>
-    <t>5조 4044억 1039만</t>
-  </si>
-  <si>
-    <t>미니두두</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EB%8B%88%EB%91%90%EB%91%90</t>
-  </si>
-  <si>
-    <t>4조 9192억 7882만</t>
-  </si>
-  <si>
-    <t>창창창</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EC%B0%BD%EC%B0%BD</t>
-  </si>
-  <si>
-    <t>3조 3293억 9219만</t>
-  </si>
-  <si>
-    <t>기어피프스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%96%B4%ED%94%BC%ED%94%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>2조 9286억 754만</t>
-  </si>
-  <si>
-    <t>13ang뱅사거리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=13ang%EB%B1%85%EC%82%AC%EA%B1%B0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2조 8570억 3491만</t>
-  </si>
-  <si>
-    <t>님이럴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%EC%9D%B4%EB%9F%B4</t>
-  </si>
-  <si>
-    <t>2조 8238억 1258만</t>
-  </si>
-  <si>
-    <t>꽤괜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%A4%EA%B4%9C</t>
-  </si>
-  <si>
-    <t>2조 7723억 2323만</t>
-  </si>
-  <si>
-    <t>다너리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%84%88%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2조 7363억 4028만</t>
-  </si>
-  <si>
-    <t>기둥1알2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%91%A51%EC%95%8C2</t>
-  </si>
-  <si>
-    <t>2조 4510억 6682만</t>
-  </si>
-  <si>
-    <t>탱설</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%B1%EC%84%A4</t>
-  </si>
-  <si>
-    <t>2조 3337억 7615만</t>
-  </si>
-  <si>
-    <t>쭝요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%9D%EC%9A%94</t>
-  </si>
-  <si>
-    <t>2조 506억 487만</t>
-  </si>
-  <si>
-    <t>클리브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EB%A6%AC%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>1조 9040억 9300만</t>
-  </si>
-  <si>
-    <t>딸기전사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EA%B8%B0%EC%A0%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1조 6291억 7772만</t>
-  </si>
-  <si>
-    <t>Soul</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Soul</t>
-  </si>
-  <si>
-    <t>1조 5924억 7433만</t>
-  </si>
-  <si>
-    <t>소바킴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%94%ED%82%B4</t>
-  </si>
-  <si>
-    <t>1조 3608억 6383만</t>
-  </si>
-  <si>
-    <t>사과왕쟈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EC%99%95%EC%9F%88</t>
-  </si>
-  <si>
-    <t>1조 733억 7740만</t>
-  </si>
-  <si>
-    <t>상속남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%86%8D%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1조 488억 1763만</t>
-  </si>
-  <si>
-    <t>꼬맹츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%A7%B9%EC%B8%84</t>
-  </si>
-  <si>
-    <t>6402억 299만</t>
-  </si>
-  <si>
-    <t>오렌지공쥬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A0%8C%EC%A7%80%EA%B3%B5%EC%A5%AC</t>
-  </si>
-  <si>
-    <t>5972억 280만</t>
-  </si>
-  <si>
-    <t>옴인형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%9D%B8%ED%98%95</t>
-  </si>
-  <si>
-    <t>2886억 7992만</t>
-  </si>
-  <si>
-    <t>진킹배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%ED%82%B9%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>2183억 7005만</t>
-  </si>
-  <si>
-    <t>연상녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%83%81%EB%85%80</t>
-  </si>
-  <si>
-    <t>1821억 4567만</t>
-  </si>
-  <si>
-    <t>힐러충충이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%9F%AC%EC%B6%A9%EC%B6%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1548억 1059만</t>
-  </si>
-  <si>
-    <t>희태바라기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%ED%83%9C%EB%B0%94%EB%9D%BC%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1381억 1656만</t>
-  </si>
-  <si>
-    <t>머랭키쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EB%9E%AD%ED%82%A4%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1155억 4589만</t>
-  </si>
-  <si>
-    <t>공쵸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%B5%B8</t>
-  </si>
-  <si>
-    <t>970억 8969만</t>
   </si>
 </sst>
 </file>
@@ -2626,72 +2626,72 @@
         <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="I4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2717,10 +2717,10 @@
         <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>48</v>
@@ -2732,7 +2732,7 @@
         <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2755,13 +2755,13 @@
         <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>56</v>
@@ -2773,7 +2773,7 @@
         <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2796,13 +2796,13 @@
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>64</v>
@@ -2840,10 +2840,10 @@
         <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>72</v>
@@ -2855,7 +2855,7 @@
         <v>74</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3887,787 +3887,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J23"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4715,19 +3934,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>85</v>
@@ -4739,7 +3958,7 @@
         <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4747,19 +3966,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>288</v>
+        <v>218</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>289</v>
+        <v>219</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>92</v>
@@ -4771,7 +3990,7 @@
         <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4779,19 +3998,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>291</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>291</v>
+        <v>221</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>292</v>
+        <v>222</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>92</v>
@@ -4803,7 +4022,7 @@
         <v>110</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>293</v>
+        <v>223</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4811,19 +4030,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>294</v>
+        <v>224</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>294</v>
+        <v>224</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>295</v>
+        <v>225</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>92</v>
@@ -4835,7 +4054,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>296</v>
+        <v>226</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4843,19 +4062,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>297</v>
+        <v>227</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>298</v>
+        <v>228</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>92</v>
@@ -4867,7 +4086,7 @@
         <v>110</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4875,19 +4094,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>301</v>
+        <v>231</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>92</v>
@@ -4899,7 +4118,7 @@
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4907,19 +4126,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>304</v>
+        <v>234</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>92</v>
@@ -4931,7 +4150,7 @@
         <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>305</v>
+        <v>235</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4939,19 +4158,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>306</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>306</v>
+        <v>236</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>307</v>
+        <v>237</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -4963,7 +4182,7 @@
         <v>119</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>308</v>
+        <v>238</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4971,19 +4190,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
@@ -4995,7 +4214,7 @@
         <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>311</v>
+        <v>241</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5003,19 +4222,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>312</v>
+        <v>242</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>313</v>
+        <v>243</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>92</v>
@@ -5027,7 +4246,7 @@
         <v>99</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>314</v>
+        <v>244</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5035,19 +4254,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>316</v>
+        <v>246</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>92</v>
@@ -5059,7 +4278,7 @@
         <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>317</v>
+        <v>247</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5067,19 +4286,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>318</v>
+        <v>248</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>318</v>
+        <v>248</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>319</v>
+        <v>249</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>92</v>
@@ -5091,7 +4310,7 @@
         <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5099,19 +4318,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>321</v>
+        <v>251</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>321</v>
+        <v>251</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>322</v>
+        <v>252</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>92</v>
@@ -5123,7 +4342,7 @@
         <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>323</v>
+        <v>253</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5131,19 +4350,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>325</v>
+        <v>255</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>92</v>
@@ -5155,7 +4374,7 @@
         <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>326</v>
+        <v>256</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5163,19 +4382,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>327</v>
+        <v>257</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>327</v>
+        <v>257</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>328</v>
+        <v>258</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>92</v>
@@ -5187,7 +4406,7 @@
         <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>329</v>
+        <v>259</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5195,19 +4414,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>331</v>
+        <v>261</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -5219,7 +4438,7 @@
         <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>332</v>
+        <v>262</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5227,19 +4446,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>334</v>
+        <v>264</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
@@ -5251,7 +4470,7 @@
         <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>335</v>
+        <v>265</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5259,19 +4478,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>336</v>
+        <v>266</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>336</v>
+        <v>266</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>337</v>
+        <v>267</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>92</v>
@@ -5283,7 +4502,7 @@
         <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>338</v>
+        <v>268</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5291,19 +4510,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>339</v>
+        <v>269</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>92</v>
@@ -5315,7 +4534,7 @@
         <v>147</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>341</v>
+        <v>271</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5323,19 +4542,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>343</v>
+        <v>273</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
@@ -5347,7 +4566,7 @@
         <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>344</v>
+        <v>274</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5355,19 +4574,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>345</v>
+        <v>275</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>345</v>
+        <v>275</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
@@ -5379,7 +4598,7 @@
         <v>168</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5387,19 +4606,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>92</v>
@@ -5411,7 +4630,7 @@
         <v>99</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5419,19 +4638,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>352</v>
+        <v>282</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
@@ -5443,7 +4662,7 @@
         <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>353</v>
+        <v>283</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5451,19 +4670,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>355</v>
+        <v>285</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
@@ -5475,7 +4694,7 @@
         <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>356</v>
+        <v>286</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5483,19 +4702,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
@@ -5507,7 +4726,7 @@
         <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5515,19 +4734,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>92</v>
@@ -5539,7 +4758,7 @@
         <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>362</v>
+        <v>292</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5547,19 +4766,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>92</v>
@@ -5571,7 +4790,7 @@
         <v>168</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5579,19 +4798,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>366</v>
+        <v>296</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>366</v>
+        <v>296</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>367</v>
+        <v>297</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>92</v>
@@ -5603,7 +4822,7 @@
         <v>142</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>368</v>
+        <v>298</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5611,19 +4830,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>92</v>
@@ -5635,7 +4854,7 @@
         <v>168</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>371</v>
+        <v>301</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5643,19 +4862,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>92</v>
@@ -5667,7 +4886,7 @@
         <v>142</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>375</v>
+        <v>305</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5711,7 +4930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5760,19 +4979,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>377</v>
+        <v>307</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>92</v>
@@ -5784,27 +5003,27 @@
         <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>378</v>
+        <v>308</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>379</v>
+        <v>309</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>92</v>
@@ -5816,27 +5035,27 @@
         <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>381</v>
+        <v>311</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>383</v>
+        <v>313</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>92</v>
@@ -5848,27 +5067,27 @@
         <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>384</v>
+        <v>314</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>386</v>
+        <v>316</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>92</v>
@@ -5880,27 +5099,27 @@
         <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>387</v>
+        <v>317</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>389</v>
+        <v>319</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>92</v>
@@ -5912,27 +5131,27 @@
         <v>147</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>321</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>391</v>
+        <v>321</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>92</v>
@@ -5944,27 +5163,27 @@
         <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>393</v>
+        <v>323</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>395</v>
+        <v>325</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>92</v>
@@ -5976,27 +5195,27 @@
         <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>396</v>
+        <v>326</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>397</v>
+        <v>327</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>397</v>
+        <v>327</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>398</v>
+        <v>328</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -6008,59 +5227,59 @@
         <v>168</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>401</v>
+        <v>331</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>92</v>
@@ -6072,27 +5291,27 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>406</v>
+        <v>336</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>407</v>
+        <v>337</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>85</v>
@@ -6104,27 +5323,27 @@
         <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>409</v>
+        <v>339</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>409</v>
+        <v>339</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>92</v>
@@ -6136,27 +5355,27 @@
         <v>214</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>412</v>
+        <v>342</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>412</v>
+        <v>342</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>413</v>
+        <v>343</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>92</v>
@@ -6168,27 +5387,27 @@
         <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>414</v>
+        <v>344</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>416</v>
+        <v>346</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>92</v>
@@ -6200,27 +5419,27 @@
         <v>168</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>417</v>
+        <v>347</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>418</v>
+        <v>348</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>418</v>
+        <v>348</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>419</v>
+        <v>349</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>92</v>
@@ -6232,27 +5451,27 @@
         <v>168</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -6264,27 +5483,27 @@
         <v>168</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>425</v>
+        <v>355</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
@@ -6296,27 +5515,27 @@
         <v>214</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>426</v>
+        <v>356</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>427</v>
+        <v>357</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>427</v>
+        <v>357</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>428</v>
+        <v>358</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>92</v>
@@ -6328,27 +5547,27 @@
         <v>168</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>429</v>
+        <v>359</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>431</v>
+        <v>361</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>92</v>
@@ -6357,30 +5576,30 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>432</v>
+        <v>363</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>433</v>
+        <v>364</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>434</v>
+        <v>365</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
@@ -6392,27 +5611,27 @@
         <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>435</v>
+        <v>366</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>436</v>
+        <v>367</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>436</v>
+        <v>367</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>437</v>
+        <v>368</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
@@ -6424,27 +5643,27 @@
         <v>168</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>438</v>
+        <v>369</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>440</v>
+        <v>371</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>92</v>
@@ -6456,27 +5675,27 @@
         <v>168</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>443</v>
+        <v>374</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
@@ -6485,30 +5704,30 @@
         <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>445</v>
+        <v>376</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>445</v>
+        <v>376</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>446</v>
+        <v>377</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
@@ -6517,30 +5736,30 @@
         <v>86</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>447</v>
+        <v>378</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>448</v>
+        <v>379</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>448</v>
+        <v>379</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>449</v>
+        <v>380</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
@@ -6549,30 +5768,30 @@
         <v>109</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>273</v>
+        <v>381</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>452</v>
+        <v>384</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>92</v>
@@ -6584,27 +5803,27 @@
         <v>168</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>453</v>
+        <v>385</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>455</v>
+        <v>387</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>92</v>
@@ -6613,13 +5832,13 @@
         <v>86</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>277</v>
+        <v>388</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>456</v>
+        <v>389</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -6657,7 +5876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6706,51 +5925,51 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>457</v>
+        <v>390</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>457</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>458</v>
+        <v>391</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>459</v>
+        <v>392</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>460</v>
+        <v>393</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>460</v>
+        <v>393</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>92</v>
@@ -6762,27 +5981,27 @@
         <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>463</v>
+        <v>396</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>463</v>
+        <v>396</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>464</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>92</v>
@@ -6794,59 +6013,59 @@
         <v>110</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>465</v>
+        <v>398</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>467</v>
+        <v>400</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>468</v>
+        <v>401</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>469</v>
+        <v>402</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>469</v>
+        <v>402</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>92</v>
@@ -6858,27 +6077,27 @@
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>471</v>
+        <v>404</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>472</v>
+        <v>405</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>472</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>473</v>
+        <v>406</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>92</v>
@@ -6890,27 +6109,27 @@
         <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>474</v>
+        <v>407</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>475</v>
+        <v>408</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>85</v>
@@ -6922,27 +6141,27 @@
         <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>476</v>
+        <v>409</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>477</v>
+        <v>410</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>477</v>
+        <v>410</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>478</v>
+        <v>411</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -6954,27 +6173,27 @@
         <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>479</v>
+        <v>412</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>480</v>
+        <v>413</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>480</v>
+        <v>413</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>481</v>
+        <v>414</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
@@ -6986,27 +6205,27 @@
         <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>482</v>
+        <v>415</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>483</v>
+        <v>416</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>483</v>
+        <v>416</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>484</v>
+        <v>417</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>92</v>
@@ -7018,27 +6237,27 @@
         <v>168</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>485</v>
+        <v>418</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>486</v>
+        <v>419</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>486</v>
+        <v>419</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>487</v>
+        <v>420</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>92</v>
@@ -7050,27 +6269,27 @@
         <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>488</v>
+        <v>421</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>489</v>
+        <v>422</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>489</v>
+        <v>422</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>490</v>
+        <v>423</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>92</v>
@@ -7082,27 +6301,27 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>491</v>
+        <v>424</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>492</v>
+        <v>425</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>493</v>
+        <v>426</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>92</v>
@@ -7114,27 +6333,27 @@
         <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>494</v>
+        <v>427</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>495</v>
+        <v>428</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>496</v>
+        <v>429</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>92</v>
@@ -7146,27 +6365,27 @@
         <v>214</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>497</v>
+        <v>430</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>498</v>
+        <v>431</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>498</v>
+        <v>431</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>499</v>
+        <v>432</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>92</v>
@@ -7178,27 +6397,27 @@
         <v>168</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>500</v>
+        <v>433</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>501</v>
+        <v>434</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>501</v>
+        <v>434</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>502</v>
+        <v>435</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -7210,155 +6429,155 @@
         <v>214</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>503</v>
+        <v>436</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>504</v>
+        <v>437</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>504</v>
+        <v>437</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>505</v>
+        <v>438</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>168</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>506</v>
+        <v>439</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>507</v>
+        <v>440</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>507</v>
+        <v>440</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>508</v>
+        <v>441</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>509</v>
+        <v>442</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>510</v>
+        <v>443</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>510</v>
+        <v>443</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>511</v>
+        <v>444</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>168</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>512</v>
+        <v>445</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>513</v>
+        <v>446</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>513</v>
+        <v>446</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>514</v>
+        <v>447</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>242</v>
+        <v>448</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>515</v>
+        <v>449</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>516</v>
+        <v>450</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>516</v>
+        <v>450</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
@@ -7370,59 +6589,59 @@
         <v>214</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>518</v>
+        <v>452</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>519</v>
+        <v>453</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>519</v>
+        <v>453</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>521</v>
+        <v>455</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>523</v>
+        <v>457</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
@@ -7431,62 +6650,62 @@
         <v>86</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>524</v>
+        <v>458</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>525</v>
+        <v>459</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>525</v>
+        <v>459</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>526</v>
+        <v>460</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>527</v>
+        <v>461</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
@@ -7498,27 +6717,27 @@
         <v>214</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>530</v>
+        <v>464</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>531</v>
+        <v>465</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>92</v>
@@ -7527,62 +6746,62 @@
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>533</v>
+        <v>467</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>534</v>
+        <v>468</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>534</v>
+        <v>468</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>538</v>
+        <v>472</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>92</v>
@@ -7591,30 +6810,30 @@
         <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>273</v>
+        <v>381</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>540</v>
+        <v>474</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>540</v>
+        <v>474</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>541</v>
+        <v>475</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>92</v>
@@ -7623,30 +6842,30 @@
         <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>542</v>
+        <v>476</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>372</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>543</v>
+        <v>477</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>543</v>
+        <v>477</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>544</v>
+        <v>478</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>92</v>
@@ -7655,13 +6874,13 @@
         <v>86</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>545</v>
+        <v>479</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>546</v>
+        <v>480</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -7702,7 +6921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7751,19 +6970,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>547</v>
+        <v>481</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>85</v>
@@ -7775,7 +6994,7 @@
         <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>548</v>
+        <v>482</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7783,19 +7002,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>549</v>
+        <v>483</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>549</v>
+        <v>483</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>550</v>
+        <v>484</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>92</v>
@@ -7807,7 +7026,7 @@
         <v>110</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>551</v>
+        <v>485</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7815,19 +7034,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>552</v>
+        <v>486</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>552</v>
+        <v>486</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>92</v>
@@ -7839,7 +7058,7 @@
         <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>554</v>
+        <v>488</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7847,19 +7066,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>555</v>
+        <v>489</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>555</v>
+        <v>489</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>556</v>
+        <v>490</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>92</v>
@@ -7871,7 +7090,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>557</v>
+        <v>491</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7879,19 +7098,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>558</v>
+        <v>492</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>558</v>
+        <v>492</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>559</v>
+        <v>493</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>92</v>
@@ -7903,7 +7122,7 @@
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>560</v>
+        <v>494</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7911,19 +7130,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>561</v>
+        <v>495</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>561</v>
+        <v>495</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>562</v>
+        <v>496</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>92</v>
@@ -7935,7 +7154,7 @@
         <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>563</v>
+        <v>497</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7943,19 +7162,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>564</v>
+        <v>498</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>564</v>
+        <v>498</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>565</v>
+        <v>499</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>92</v>
@@ -7967,7 +7186,7 @@
         <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>566</v>
+        <v>500</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7975,19 +7194,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>567</v>
+        <v>501</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>567</v>
+        <v>501</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>568</v>
+        <v>502</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -7996,10 +7215,10 @@
         <v>124</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>569</v>
+        <v>503</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8007,19 +7226,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>571</v>
+        <v>505</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
@@ -8028,10 +7247,10 @@
         <v>124</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>572</v>
+        <v>506</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8039,19 +7258,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>573</v>
+        <v>507</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>573</v>
+        <v>507</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>574</v>
+        <v>508</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>92</v>
@@ -8063,7 +7282,7 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>575</v>
+        <v>509</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8071,31 +7290,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>576</v>
+        <v>510</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>576</v>
+        <v>510</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>577</v>
+        <v>511</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>168</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>578</v>
+        <v>512</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8103,19 +7322,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>579</v>
+        <v>513</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>579</v>
+        <v>513</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>580</v>
+        <v>514</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>92</v>
@@ -8127,7 +7346,7 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>581</v>
+        <v>515</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8135,19 +7354,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>582</v>
+        <v>516</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>582</v>
+        <v>516</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>583</v>
+        <v>517</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>92</v>
@@ -8159,7 +7378,7 @@
         <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>584</v>
+        <v>518</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8167,19 +7386,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>585</v>
+        <v>519</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>585</v>
+        <v>519</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>586</v>
+        <v>520</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>92</v>
@@ -8191,7 +7410,7 @@
         <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8199,19 +7418,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>588</v>
+        <v>522</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>588</v>
+        <v>522</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>589</v>
+        <v>523</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>92</v>
@@ -8223,7 +7442,7 @@
         <v>142</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>590</v>
+        <v>524</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8231,19 +7450,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>591</v>
+        <v>525</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>591</v>
+        <v>525</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>592</v>
+        <v>526</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -8255,7 +7474,7 @@
         <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>593</v>
+        <v>527</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8263,19 +7482,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>594</v>
+        <v>528</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>594</v>
+        <v>528</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>595</v>
+        <v>529</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
@@ -8287,7 +7506,7 @@
         <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>596</v>
+        <v>530</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8295,19 +7514,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>598</v>
+        <v>532</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>92</v>
@@ -8319,7 +7538,7 @@
         <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>599</v>
+        <v>533</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8327,19 +7546,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>600</v>
+        <v>534</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>600</v>
+        <v>534</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>601</v>
+        <v>535</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>92</v>
@@ -8351,7 +7570,7 @@
         <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>602</v>
+        <v>536</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8359,19 +7578,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>603</v>
+        <v>537</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>603</v>
+        <v>537</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>604</v>
+        <v>538</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
@@ -8383,7 +7602,7 @@
         <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>605</v>
+        <v>539</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8391,19 +7610,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>606</v>
+        <v>540</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>606</v>
+        <v>540</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>607</v>
+        <v>541</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
@@ -8415,7 +7634,7 @@
         <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>608</v>
+        <v>542</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8423,19 +7642,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>609</v>
+        <v>543</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>610</v>
+        <v>544</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>92</v>
@@ -8447,7 +7666,7 @@
         <v>168</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>611</v>
+        <v>545</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8455,19 +7674,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>612</v>
+        <v>546</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>612</v>
+        <v>546</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>613</v>
+        <v>547</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
@@ -8476,10 +7695,10 @@
         <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8487,19 +7706,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>615</v>
+        <v>549</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>616</v>
+        <v>550</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
@@ -8511,7 +7730,7 @@
         <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>617</v>
+        <v>551</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8519,19 +7738,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>618</v>
+        <v>552</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>618</v>
+        <v>552</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>619</v>
+        <v>553</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
@@ -8540,10 +7759,10 @@
         <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>620</v>
+        <v>554</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8582,7 +7801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8631,19 +7850,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>621</v>
+        <v>555</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>85</v>
@@ -8652,10 +7871,10 @@
         <v>124</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>622</v>
+        <v>556</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>623</v>
+        <v>557</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8663,31 +7882,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>624</v>
+        <v>558</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>624</v>
+        <v>558</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>625</v>
+        <v>559</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>626</v>
+        <v>560</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8695,19 +7914,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>627</v>
+        <v>561</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>92</v>
@@ -8719,7 +7938,7 @@
         <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>629</v>
+        <v>563</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8727,31 +7946,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>630</v>
+        <v>564</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>630</v>
+        <v>564</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>631</v>
+        <v>565</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>147</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>632</v>
+        <v>566</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8759,19 +7978,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>633</v>
+        <v>567</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>633</v>
+        <v>567</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>634</v>
+        <v>568</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>92</v>
@@ -8783,7 +8002,7 @@
         <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>635</v>
+        <v>569</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8791,19 +8010,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>636</v>
+        <v>570</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>636</v>
+        <v>570</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>637</v>
+        <v>571</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>92</v>
@@ -8815,7 +8034,7 @@
         <v>147</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>638</v>
+        <v>572</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8823,19 +8042,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>639</v>
+        <v>573</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>639</v>
+        <v>573</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>640</v>
+        <v>574</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>92</v>
@@ -8847,7 +8066,7 @@
         <v>147</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>641</v>
+        <v>575</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8855,19 +8074,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>642</v>
+        <v>576</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>642</v>
+        <v>576</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>643</v>
+        <v>577</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>92</v>
@@ -8879,7 +8098,7 @@
         <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>644</v>
+        <v>578</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8887,19 +8106,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>645</v>
+        <v>579</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>645</v>
+        <v>579</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>646</v>
+        <v>580</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>92</v>
@@ -8911,7 +8130,7 @@
         <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>647</v>
+        <v>581</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8919,19 +8138,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>648</v>
+        <v>582</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>648</v>
+        <v>582</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>649</v>
+        <v>583</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>92</v>
@@ -8943,7 +8162,7 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>650</v>
+        <v>584</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8951,19 +8170,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>651</v>
+        <v>585</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>651</v>
+        <v>585</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>652</v>
+        <v>586</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>92</v>
@@ -8975,7 +8194,7 @@
         <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>653</v>
+        <v>587</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8983,19 +8202,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>654</v>
+        <v>588</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>654</v>
+        <v>588</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>655</v>
+        <v>589</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>92</v>
@@ -9007,7 +8226,7 @@
         <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>656</v>
+        <v>590</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9015,19 +8234,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>657</v>
+        <v>591</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>657</v>
+        <v>591</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>658</v>
+        <v>592</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>92</v>
@@ -9039,7 +8258,7 @@
         <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>659</v>
+        <v>593</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9047,19 +8266,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>660</v>
+        <v>594</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>660</v>
+        <v>594</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>661</v>
+        <v>595</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>92</v>
@@ -9071,7 +8290,7 @@
         <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>662</v>
+        <v>596</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9079,19 +8298,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>663</v>
+        <v>597</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>664</v>
+        <v>598</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>92</v>
@@ -9103,7 +8322,7 @@
         <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>665</v>
+        <v>599</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9111,19 +8330,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>666</v>
+        <v>600</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>666</v>
+        <v>600</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>667</v>
+        <v>601</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -9135,7 +8354,7 @@
         <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>668</v>
+        <v>602</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9143,31 +8362,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9175,19 +8394,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>672</v>
+        <v>606</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>672</v>
+        <v>606</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>673</v>
+        <v>607</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>92</v>
@@ -9199,7 +8418,7 @@
         <v>214</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>674</v>
+        <v>608</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9207,19 +8426,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>92</v>
@@ -9228,10 +8447,10 @@
         <v>124</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>677</v>
+        <v>611</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9239,19 +8458,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>679</v>
+        <v>613</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>92</v>
@@ -9263,7 +8482,7 @@
         <v>214</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>680</v>
+        <v>614</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9271,19 +8490,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>681</v>
+        <v>615</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>681</v>
+        <v>615</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>682</v>
+        <v>616</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>92</v>
@@ -9292,10 +8511,10 @@
         <v>93</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>683</v>
+        <v>617</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9303,31 +8522,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>685</v>
+        <v>619</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>545</v>
+        <v>479</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>686</v>
+        <v>620</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9335,19 +8554,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>687</v>
+        <v>621</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>687</v>
+        <v>621</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>688</v>
+        <v>622</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>92</v>
@@ -9356,10 +8575,10 @@
         <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>545</v>
+        <v>479</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>689</v>
+        <v>623</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9367,31 +8586,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>690</v>
+        <v>624</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>690</v>
+        <v>624</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>691</v>
+        <v>625</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>388</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>692</v>
+        <v>626</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9399,31 +8618,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>693</v>
+        <v>627</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>693</v>
+        <v>627</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>694</v>
+        <v>628</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>695</v>
+        <v>629</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>696</v>
+        <v>630</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9431,19 +8650,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>697</v>
+        <v>631</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>697</v>
+        <v>631</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>698</v>
+        <v>632</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>92</v>
@@ -9452,10 +8671,10 @@
         <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>388</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>699</v>
+        <v>633</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9463,19 +8682,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>700</v>
+        <v>634</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>700</v>
+        <v>634</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>701</v>
+        <v>635</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>92</v>
@@ -9484,10 +8703,10 @@
         <v>86</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>702</v>
+        <v>636</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>703</v>
+        <v>637</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9495,19 +8714,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>704</v>
+        <v>638</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>704</v>
+        <v>638</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>705</v>
+        <v>639</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>92</v>
@@ -9516,10 +8735,10 @@
         <v>86</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>702</v>
+        <v>636</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>706</v>
+        <v>640</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9559,4 +8778,785 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J23"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%98%EB%A6%ACv</t>
   </si>
   <si>
-    <t>19조 8537억 9210만</t>
+    <t>19조 8633억 3393만</t>
   </si>
   <si>
     <t>oFero라온o</t>
@@ -1563,7 +1563,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8A%BC%ED%8A%BC%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 104억 2129만</t>
+    <t>2조 1058억 3293만</t>
   </si>
   <si>
     <t>전뱀</t>
@@ -2181,7 +2181,7 @@
     <t>81</t>
   </si>
   <si>
-    <t>57억 3736만</t>
+    <t>68억 654만</t>
   </si>
 </sst>
 </file>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -84,108 +84,108 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>12위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>171조 6820억 7377만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.04.17</t>
+  </si>
+  <si>
+    <t>초코나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>167조 6081억 6238만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
+    <t>블랙소울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
     <t>380</t>
   </si>
   <si>
-    <t>12위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>171조 6820억 7377만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.04.17</t>
-  </si>
-  <si>
-    <t>초코나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>171조 9975억 7642만</t>
+  </si>
+  <si>
+    <t>보심</t>
+  </si>
+  <si>
+    <t>다다익선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
   </si>
   <si>
     <t>386</t>
   </si>
   <si>
-    <t>8위</t>
-  </si>
-  <si>
-    <t>167조 6081억 6238만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
-    <t>블랙소울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>171조 9975억 7642만</t>
-  </si>
-  <si>
-    <t>보심</t>
-  </si>
-  <si>
-    <t>다다익선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>169조 3419억 6601만</t>
+  </si>
+  <si>
+    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>비련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
   </si>
   <si>
     <t>385</t>
   </si>
   <si>
-    <t>7위</t>
-  </si>
-  <si>
-    <t>169조 3419억 6601만</t>
-  </si>
-  <si>
-    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>비련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
     <t>34위</t>
   </si>
   <si>
@@ -204,7 +204,7 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>381</t>
+    <t>382</t>
   </si>
   <si>
     <t>33위</t>
@@ -231,7 +231,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>382</t>
+    <t>383</t>
   </si>
   <si>
     <t>Lv.6</t>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -285,7 +285,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>22조 5686억 1996만</t>
+    <t>22조 7699억 4133만</t>
   </si>
   <si>
     <t>2</t>
@@ -435,12 +435,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 5125억 6849만</t>
+    <t>4조 9239억 3208만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>4조 3189억 8200만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -453,7 +465,7 @@
     <t>4조 2010억 1283만</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>므고</t>
@@ -465,7 +477,7 @@
     <t>4조 1502억 5010만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -480,7 +492,7 @@
     <t>3조 6989억 1308만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -495,18 +507,6 @@
     <t>3조 6112억 850만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>3조 5215억 9190만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -546,6 +546,18 @@
     <t>20</t>
   </si>
   <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 7646억 9816만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>겨울바다</t>
   </si>
   <si>
@@ -555,21 +567,21 @@
     <t>2조 7544억 9536만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>덕르코프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 7199억 9178만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 5691억 3500만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>강철고튠데</t>
   </si>
   <si>
@@ -577,18 +589,6 @@
   </si>
   <si>
     <t>2조 5595억 2만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 3162억 528만</t>
   </si>
   <si>
     <t>24</t>
@@ -3447,13 +3447,13 @@
         <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3464,25 +3464,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>143</v>
@@ -3511,13 +3511,13 @@
         <v>88</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3528,16 +3528,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
@@ -3546,10 +3546,10 @@
         <v>119</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3560,16 +3560,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -3578,7 +3578,7 @@
         <v>119</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>157</v>
@@ -3642,7 +3642,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>165</v>
@@ -3703,10 +3703,10 @@
         <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>173</v>
@@ -3735,10 +3735,10 @@
         <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>177</v>
@@ -3767,10 +3767,10 @@
         <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>181</v>
@@ -3799,10 +3799,10 @@
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>185</v>
@@ -3834,7 +3834,7 @@
         <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>189</v>
@@ -3866,7 +3866,7 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>193</v>
@@ -3898,7 +3898,7 @@
         <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>197</v>
@@ -3930,7 +3930,7 @@
         <v>201</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>202</v>
@@ -3962,7 +3962,7 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>206</v>
@@ -4207,7 +4207,7 @@
         <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>224</v>
@@ -4509,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>252</v>
@@ -4559,7 +4559,7 @@
         <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>257</v>
@@ -4573,7 +4573,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>258</v>
@@ -4605,7 +4605,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>261</v>
@@ -4687,7 +4687,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>269</v>
@@ -4783,7 +4783,7 @@
         <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>278</v>
@@ -4847,7 +4847,7 @@
         <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>284</v>
@@ -4879,7 +4879,7 @@
         <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>287</v>
@@ -4943,7 +4943,7 @@
         <v>129</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>293</v>
@@ -4975,7 +4975,7 @@
         <v>119</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>296</v>
@@ -5007,7 +5007,7 @@
         <v>119</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
@@ -5347,7 +5347,7 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5475,7 +5475,7 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>334</v>
@@ -5507,7 +5507,7 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>337</v>
@@ -5521,7 +5521,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>338</v>
@@ -5539,7 +5539,7 @@
         <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>340</v>
@@ -5571,7 +5571,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>343</v>
@@ -5585,7 +5585,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>344</v>
@@ -5617,7 +5617,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>347</v>
@@ -5635,7 +5635,7 @@
         <v>119</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>349</v>
@@ -5667,7 +5667,7 @@
         <v>217</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>352</v>
@@ -5699,7 +5699,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>355</v>
@@ -5763,7 +5763,7 @@
         <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>361</v>
@@ -5827,7 +5827,7 @@
         <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>367</v>
@@ -5923,7 +5923,7 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>376</v>
@@ -6296,7 +6296,7 @@
         <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>406</v>
@@ -6328,7 +6328,7 @@
         <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>408</v>
@@ -6392,7 +6392,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>414</v>
@@ -6424,7 +6424,7 @@
         <v>82</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>417</v>
@@ -6456,7 +6456,7 @@
         <v>119</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>420</v>
@@ -6488,7 +6488,7 @@
         <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>423</v>
@@ -6520,7 +6520,7 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>426</v>
@@ -6552,7 +6552,7 @@
         <v>201</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>429</v>
@@ -6566,7 +6566,7 @@
         <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>430</v>
@@ -6584,7 +6584,7 @@
         <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>432</v>
@@ -6616,7 +6616,7 @@
         <v>119</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>435</v>
@@ -6630,7 +6630,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>436</v>
@@ -6648,7 +6648,7 @@
         <v>201</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>438</v>
@@ -6662,7 +6662,7 @@
         <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>439</v>
@@ -6680,7 +6680,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>441</v>
@@ -6712,7 +6712,7 @@
         <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>444</v>
@@ -6744,7 +6744,7 @@
         <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>447</v>
@@ -6776,7 +6776,7 @@
         <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>450</v>
@@ -6808,7 +6808,7 @@
         <v>119</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>453</v>
@@ -6840,7 +6840,7 @@
         <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>456</v>
@@ -6904,7 +6904,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>462</v>
@@ -6968,7 +6968,7 @@
         <v>201</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>468</v>
@@ -7000,7 +7000,7 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>471</v>
@@ -7032,7 +7032,7 @@
         <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>474</v>
@@ -7064,7 +7064,7 @@
         <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>477</v>
@@ -7096,7 +7096,7 @@
         <v>129</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>480</v>
@@ -7406,7 +7406,7 @@
         <v>393</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>502</v>
@@ -7534,7 +7534,7 @@
         <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>514</v>
@@ -7566,7 +7566,7 @@
         <v>119</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>517</v>
@@ -7630,7 +7630,7 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>523</v>
@@ -7644,7 +7644,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>524</v>
@@ -7662,7 +7662,7 @@
         <v>217</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>526</v>
@@ -7694,7 +7694,7 @@
         <v>119</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>529</v>
@@ -7708,7 +7708,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>530</v>
@@ -7726,7 +7726,7 @@
         <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>532</v>
@@ -7740,7 +7740,7 @@
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>533</v>
@@ -7758,7 +7758,7 @@
         <v>119</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>535</v>
@@ -7790,7 +7790,7 @@
         <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>538</v>
@@ -7822,7 +7822,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>541</v>
@@ -7854,7 +7854,7 @@
         <v>119</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>544</v>
@@ -7886,7 +7886,7 @@
         <v>217</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>547</v>
@@ -7918,7 +7918,7 @@
         <v>217</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>550</v>
@@ -8078,7 +8078,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>565</v>
@@ -8451,7 +8451,7 @@
         <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>591</v>
@@ -8483,7 +8483,7 @@
         <v>217</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>594</v>
@@ -8515,7 +8515,7 @@
         <v>393</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>597</v>
@@ -8547,7 +8547,7 @@
         <v>119</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>600</v>
@@ -8579,7 +8579,7 @@
         <v>119</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>603</v>
@@ -8643,7 +8643,7 @@
         <v>217</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>609</v>
@@ -8689,7 +8689,7 @@
         <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>613</v>
@@ -8753,7 +8753,7 @@
         <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>619</v>
@@ -8785,7 +8785,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>623</v>
@@ -9367,7 +9367,7 @@
         <v>393</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>674</v>
@@ -9431,7 +9431,7 @@
         <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>679</v>
@@ -9495,7 +9495,7 @@
         <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>685</v>
@@ -9591,7 +9591,7 @@
         <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>694</v>
@@ -9701,7 +9701,7 @@
         <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>704</v>
@@ -9765,7 +9765,7 @@
         <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>710</v>
@@ -9797,7 +9797,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>713</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -10,19 +10,19 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="초코나라" sheetId="3" r:id="rId3"/>
-    <sheet name="블랙소울" sheetId="4" r:id="rId4"/>
-    <sheet name="다다익선" sheetId="5" r:id="rId5"/>
+    <sheet name="다다익선" sheetId="4" r:id="rId4"/>
+    <sheet name="블랙소울" sheetId="5" r:id="rId5"/>
     <sheet name="비련" sheetId="6" r:id="rId6"/>
     <sheet name="밀크런" sheetId="7" r:id="rId7"/>
     <sheet name="털미녀" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">다다익선!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">다다익선!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">블랙소울!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블랙소울!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">초코나라!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">털미녀!$A$1:$J$31</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="757">
   <si>
     <t>guild_name</t>
   </si>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>171조 6820억 7377만</t>
+    <t>171조 8825억 4334만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -129,6 +129,33 @@
     <t>초코남</t>
   </si>
   <si>
+    <t>다다익선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>169조 3419억 6601만</t>
+  </si>
+  <si>
+    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
     <t>블랙소울</t>
   </si>
   <si>
@@ -141,39 +168,12 @@
     <t>380</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
     <t>171조 9975억 7642만</t>
   </si>
   <si>
     <t>보심</t>
   </si>
   <si>
-    <t>다다익선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>7위</t>
-  </si>
-  <si>
-    <t>169조 3419억 6601만</t>
-  </si>
-  <si>
-    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>비련</t>
   </si>
   <si>
@@ -378,7 +378,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>6조 9065억 9844만</t>
+    <t>6조 9158억 4470만</t>
   </si>
   <si>
     <t>8</t>
@@ -402,6 +402,21 @@
     <t>9</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>5조 7798억 2930만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
@@ -411,21 +426,6 @@
     <t>5조 5324억 9799만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>5조 3916억 4603만</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -462,7 +462,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 2010억 1283만</t>
+    <t>4조 2090억 334만</t>
   </si>
   <si>
     <t>14</t>
@@ -474,7 +474,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 1502억 5010만</t>
+    <t>4조 1855억 6129만</t>
   </si>
   <si>
     <t>15</t>
@@ -489,7 +489,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 6989억 1308만</t>
+    <t>3조 7011억 1668만</t>
   </si>
   <si>
     <t>16</t>
@@ -510,6 +510,18 @@
     <t>17</t>
   </si>
   <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>3조 5006억 2017만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>쭌파파</t>
   </si>
   <si>
@@ -519,18 +531,6 @@
     <t>3조 3744억 7808만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>3조 2687억 7234만</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
@@ -540,7 +540,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>2조 8414억 2069만</t>
+    <t>2조 8438억 7638만</t>
   </si>
   <si>
     <t>20</t>
@@ -558,42 +558,54 @@
     <t>21</t>
   </si>
   <si>
-    <t>겨울바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2조 7544억 9536만</t>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 5691억 3500만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 5691억 3500만</t>
+    <t>강철고튠데</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
+  </si>
+  <si>
+    <t>2조 5595억 2만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>2조 5595억 2만</t>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2조 2322억 7931만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 2114억 104만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>여눈</t>
   </si>
   <si>
@@ -603,18 +615,6 @@
     <t>2조 1697억 686만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>2조 689억 590만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -639,307 +639,577 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1조 9531억 7029만</t>
+    <t>2조 123억 3425만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 9311억 8518만</t>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>1조 8260억 5446만</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>1조 8260억 5446만</t>
+    <t>욤지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1조 2511억 5308만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>49조 2974억 7037만</t>
+  </si>
+  <si>
+    <t>표창도적도아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%8F%84%EC%A0%81%EB%8F%84%EC%95%84</t>
+  </si>
+  <si>
+    <t>11조 7679억 3143만</t>
+  </si>
+  <si>
+    <t>멈디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
+  </si>
+  <si>
+    <t>8조 7298억 6806만</t>
+  </si>
+  <si>
+    <t>사숩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
+  </si>
+  <si>
+    <t>5조 5293억 2722만</t>
+  </si>
+  <si>
+    <t>포도맛맥플</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
+  </si>
+  <si>
+    <t>5조 5063억 9381만</t>
+  </si>
+  <si>
+    <t>또긔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
+  </si>
+  <si>
+    <t>5조 851억 8688만</t>
+  </si>
+  <si>
+    <t>연바기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 423억 1022만</t>
+  </si>
+  <si>
+    <t>스라차차소스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4조 4251억 700만</t>
+  </si>
+  <si>
+    <t>썬콜법사도희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>4조 4002억 6957만</t>
+  </si>
+  <si>
+    <t>김롸아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
+  </si>
+  <si>
+    <t>4조 2083억 2801만</t>
+  </si>
+  <si>
+    <t>단비둘기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>4조 1661억 5652만</t>
+  </si>
+  <si>
+    <t>우치앵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
+  </si>
+  <si>
+    <t>4조 1593억 8820만</t>
+  </si>
+  <si>
+    <t>limno</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=limno</t>
+  </si>
+  <si>
+    <t>4조 949억 6945만</t>
+  </si>
+  <si>
+    <t>A7R4</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
+  </si>
+  <si>
+    <t>4조 228억 3239만</t>
+  </si>
+  <si>
+    <t>린샹판</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
+  </si>
+  <si>
+    <t>3조 9070억 9307만</t>
+  </si>
+  <si>
+    <t>불곰파워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>3조 8704억 9855만</t>
+  </si>
+  <si>
+    <t>낮잠중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
+  </si>
+  <si>
+    <t>3조 7328억 8158만</t>
+  </si>
+  <si>
+    <t>히어로경원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
+  </si>
+  <si>
+    <t>3조 5815억 2733만</t>
+  </si>
+  <si>
+    <t>까만색양갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>3조 2765억 9656만</t>
+  </si>
+  <si>
+    <t>zl지존썬콜lz</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
+  </si>
+  <si>
+    <t>2조 9577억 2892만</t>
+  </si>
+  <si>
+    <t>용날라가유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%82%A0%EB%9D%BC%EA%B0%80%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>2조 8720억 7370만</t>
+  </si>
+  <si>
+    <t>구파발메타몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>2조 6615억 1282만</t>
+  </si>
+  <si>
+    <t>무쿠미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2조 6218억 2197만</t>
+  </si>
+  <si>
+    <t>구파발고양이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 5544억 1026만</t>
+  </si>
+  <si>
+    <t>투둠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
+  </si>
+  <si>
+    <t>2조 5460억 8723만</t>
+  </si>
+  <si>
+    <t>도윤파덜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
+  </si>
+  <si>
+    <t>2조 4831억 3573만</t>
+  </si>
+  <si>
+    <t>썹웨피망빼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
+  </si>
+  <si>
+    <t>2조 1443억 2003만</t>
+  </si>
+  <si>
+    <t>극쪽이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 3635억 2018만</t>
+  </si>
+  <si>
+    <t>토리파더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>6694억 8101만</t>
+  </si>
+  <si>
+    <t>눈꽃물망초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
+  </si>
+  <si>
+    <t>62조 2166억 4623만</t>
+  </si>
+  <si>
+    <t>포르쉐718</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
+  </si>
+  <si>
+    <t>31조 8467억 8491만</t>
+  </si>
+  <si>
+    <t>초보자시프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
+  </si>
+  <si>
+    <t>12조 7467억 6404만</t>
+  </si>
+  <si>
+    <t>뒁글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
+  </si>
+  <si>
+    <t>7조 4323억 4086만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
+  </si>
+  <si>
+    <t>6조 5551억 1272만</t>
+  </si>
+  <si>
+    <t>공대애봉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6조 1078억 1847만</t>
+  </si>
+  <si>
+    <t>언기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 8317억 2691만</t>
+  </si>
+  <si>
+    <t>우타이테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
+  </si>
+  <si>
+    <t>3조 1626억 7757만</t>
+  </si>
+  <si>
+    <t>JAEYA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
+  </si>
+  <si>
+    <t>3조 341억 6644만</t>
+  </si>
+  <si>
+    <t>묘목키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>2조 9134억 1617만</t>
+  </si>
+  <si>
+    <t>토르릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>2조 6088억 9213만</t>
+  </si>
+  <si>
+    <t>따뜻한배추</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
+  </si>
+  <si>
+    <t>2조 6034억 2629만</t>
+  </si>
+  <si>
+    <t>웅쟈쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2조 6011억 8785만</t>
+  </si>
+  <si>
+    <t>범지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
+  </si>
+  <si>
+    <t>2조 5176억 2671만</t>
+  </si>
+  <si>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>2조 2067억 5600만</t>
+  </si>
+  <si>
+    <t>맛닭꼬시멘토</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EB%8B%AD%EA%BC%AC%EC%8B%9C%EB%A9%98%ED%86%A0</t>
+  </si>
+  <si>
+    <t>1조 9631억 5670만</t>
+  </si>
+  <si>
+    <t>l우주아이l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=l%EC%9A%B0%EC%A3%BC%EC%95%84%EC%9D%B4l</t>
+  </si>
+  <si>
+    <t>1조 8665억 1909만</t>
+  </si>
+  <si>
+    <t>김주왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
+  </si>
+  <si>
+    <t>1조 7576억 7248만</t>
+  </si>
+  <si>
+    <t>원투아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>1조 6548억 9077만</t>
+  </si>
+  <si>
+    <t>아쿠마불독</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
+  </si>
+  <si>
+    <t>1조 5736억 7345만</t>
+  </si>
+  <si>
+    <t>밍고스틴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
+  </si>
+  <si>
+    <t>1조 5542억 7500만</t>
+  </si>
+  <si>
+    <t>옵션키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1조 5177억 8617만</t>
+  </si>
+  <si>
+    <t>l성연l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=l%EC%84%B1%EC%97%B0l</t>
+  </si>
+  <si>
+    <t>1조 5034억 5667만</t>
+  </si>
+  <si>
+    <t>반창환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%B0%BD%ED%99%98</t>
+  </si>
+  <si>
+    <t>1조 4334억 2117만</t>
+  </si>
+  <si>
+    <t>오늘밤은삐딱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%B0%A4%EC%9D%80%EC%82%90%EB%94%B1</t>
+  </si>
+  <si>
+    <t>1조 3938억 5415만</t>
+  </si>
+  <si>
+    <t>타락파워스님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1조 3752억 1802만</t>
+  </si>
+  <si>
+    <t>맨해라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%ED%95%B4%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 3635억 8399만</t>
+  </si>
+  <si>
+    <t>몽실망실토실</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
+  </si>
+  <si>
+    <t>1조 3591억 3020만</t>
+  </si>
+  <si>
+    <t>2D파트장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>8659억 8895만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>욤지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 2511억 5308만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>47조 3281억 3319만</t>
-  </si>
-  <si>
-    <t>표창도적도아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%8F%84%EC%A0%81%EB%8F%84%EC%95%84</t>
-  </si>
-  <si>
-    <t>11조 7584억 1658만</t>
-  </si>
-  <si>
-    <t>멈디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
-  </si>
-  <si>
-    <t>8조 7298억 6806만</t>
-  </si>
-  <si>
-    <t>사숩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
-  </si>
-  <si>
-    <t>5조 4537억 6936만</t>
-  </si>
-  <si>
-    <t>포도맛맥플</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
-  </si>
-  <si>
-    <t>5조 3978억 574만</t>
-  </si>
-  <si>
-    <t>또긔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
-  </si>
-  <si>
-    <t>5조 196억 2797만</t>
-  </si>
-  <si>
-    <t>연바기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>4조 9385억 9389만</t>
-  </si>
-  <si>
-    <t>스라차차소스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>4조 4036억 8847만</t>
-  </si>
-  <si>
-    <t>썬콜법사도희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>4조 4002억 6957만</t>
-  </si>
-  <si>
-    <t>limno</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=limno</t>
-  </si>
-  <si>
-    <t>4조 435억 4034만</t>
-  </si>
-  <si>
-    <t>A7R4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
-  </si>
-  <si>
-    <t>3조 9943억 7560만</t>
-  </si>
-  <si>
-    <t>단비둘기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>3조 8352억 9776만</t>
-  </si>
-  <si>
-    <t>김롸아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
-  </si>
-  <si>
-    <t>3조 8292억 2567만</t>
-  </si>
-  <si>
-    <t>우치앵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
-  </si>
-  <si>
-    <t>3조 7603억 2830만</t>
-  </si>
-  <si>
-    <t>낮잠중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
-  </si>
-  <si>
-    <t>3조 7328억 8158만</t>
-  </si>
-  <si>
-    <t>불곰파워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>3조 4231억 3644만</t>
-  </si>
-  <si>
-    <t>린샹판</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
-  </si>
-  <si>
-    <t>3조 4029억 844만</t>
-  </si>
-  <si>
-    <t>까만색양갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>2조 9796억 9663만</t>
-  </si>
-  <si>
-    <t>히어로경원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
-  </si>
-  <si>
-    <t>2조 8615억 4068만</t>
-  </si>
-  <si>
-    <t>zl지존썬콜lz</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
-  </si>
-  <si>
-    <t>2조 8613억 7141만</t>
-  </si>
-  <si>
-    <t>용날라가유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%82%A0%EB%9D%BC%EA%B0%80%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>2조 6742억 6169만</t>
-  </si>
-  <si>
-    <t>구파발메타몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>2조 6615억 1282만</t>
-  </si>
-  <si>
-    <t>무쿠미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2조 6194억 1535만</t>
-  </si>
-  <si>
-    <t>투둠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
-  </si>
-  <si>
-    <t>2조 5460억 8723만</t>
-  </si>
-  <si>
-    <t>구파발고양이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2조 5289억 2233만</t>
-  </si>
-  <si>
-    <t>도윤파덜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
-  </si>
-  <si>
-    <t>2조 4831억 3573만</t>
-  </si>
-  <si>
-    <t>썹웨피망빼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
-  </si>
-  <si>
-    <t>2조 1443억 2003만</t>
-  </si>
-  <si>
-    <t>극쪽이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 3635억 2018만</t>
-  </si>
-  <si>
-    <t>토리파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>6574억 2290만</t>
+    <t>주니이옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
+  </si>
+  <si>
+    <t>5937억 1485만</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>체시어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
+  </si>
+  <si>
+    <t>5753억 5581만</t>
   </si>
   <si>
     <t>상현별</t>
@@ -1216,285 +1486,6 @@
   </si>
   <si>
     <t>2814억 451만</t>
-  </si>
-  <si>
-    <t>눈꽃물망초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
-  </si>
-  <si>
-    <t>62조 2166억 4623만</t>
-  </si>
-  <si>
-    <t>포르쉐718</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
-  </si>
-  <si>
-    <t>27조 1819억 7423만</t>
-  </si>
-  <si>
-    <t>초보자시프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
-  </si>
-  <si>
-    <t>12조 1461억 2846만</t>
-  </si>
-  <si>
-    <t>뒁글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
-  </si>
-  <si>
-    <t>7조 4323억 4086만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
-  </si>
-  <si>
-    <t>6조 5430억 4724만</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 2380억 5981만</t>
-  </si>
-  <si>
-    <t>언기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>4조 4290억 3154만</t>
-  </si>
-  <si>
-    <t>우타이테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
-  </si>
-  <si>
-    <t>3조 1626억 7757만</t>
-  </si>
-  <si>
-    <t>JAEYA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
-  </si>
-  <si>
-    <t>3조 341억 6644만</t>
-  </si>
-  <si>
-    <t>묘목키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>2조 7553억 443만</t>
-  </si>
-  <si>
-    <t>웅쟈쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2조 6011억 8785만</t>
-  </si>
-  <si>
-    <t>따뜻한배추</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
-  </si>
-  <si>
-    <t>2조 5537억 4984만</t>
-  </si>
-  <si>
-    <t>범지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
-  </si>
-  <si>
-    <t>2조 5176억 2671만</t>
-  </si>
-  <si>
-    <t>토르릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>2조 3370억 9204만</t>
-  </si>
-  <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>2조 2067억 5600만</t>
-  </si>
-  <si>
-    <t>l우주아이l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=l%EC%9A%B0%EC%A3%BC%EC%95%84%EC%9D%B4l</t>
-  </si>
-  <si>
-    <t>1조 8665억 1909만</t>
-  </si>
-  <si>
-    <t>김주왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
-  </si>
-  <si>
-    <t>1조 7065억 9161만</t>
-  </si>
-  <si>
-    <t>원투아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>1조 6548억 9077만</t>
-  </si>
-  <si>
-    <t>밍고스틴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
-  </si>
-  <si>
-    <t>1조 5477억 2333만</t>
-  </si>
-  <si>
-    <t>아쿠마불독</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
-  </si>
-  <si>
-    <t>1조 5416억 9062만</t>
-  </si>
-  <si>
-    <t>맛닭꼬시멘토</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EB%8B%AD%EA%BC%AC%EC%8B%9C%EB%A9%98%ED%86%A0</t>
-  </si>
-  <si>
-    <t>1조 5027억 68만</t>
-  </si>
-  <si>
-    <t>옵션키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1조 4950억 839만</t>
-  </si>
-  <si>
-    <t>반창환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%B0%BD%ED%99%98</t>
-  </si>
-  <si>
-    <t>1조 4334억 2117만</t>
-  </si>
-  <si>
-    <t>타락파워스님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1조 3752억 1802만</t>
-  </si>
-  <si>
-    <t>몽실망실토실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>1조 3591억 3020만</t>
-  </si>
-  <si>
-    <t>맨해라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%ED%95%B4%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 3561억 2173만</t>
-  </si>
-  <si>
-    <t>l성연l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=l%EC%84%B1%EC%97%B0l</t>
-  </si>
-  <si>
-    <t>1조 3264억 1153만</t>
-  </si>
-  <si>
-    <t>오늘밤은삐딱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%B0%A4%EC%9D%80%EC%82%90%EB%94%B1</t>
-  </si>
-  <si>
-    <t>1조 3134억 9137만</t>
-  </si>
-  <si>
-    <t>2D파트장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>8636억 898만</t>
-  </si>
-  <si>
-    <t>주니이옹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
-  </si>
-  <si>
-    <t>5937억 1485만</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>체시어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
-  </si>
-  <si>
-    <t>5329억 9408만</t>
   </si>
   <si>
     <t>량용</t>
@@ -2830,20 +2821,22 @@
         <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="L4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2851,38 +2844,36 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
         <v>46</v>
       </c>
@@ -2954,7 +2945,7 @@
         <v>58</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>59</v>
@@ -2992,7 +2983,7 @@
         <v>66</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>67</v>
@@ -3030,7 +3021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3351,13 +3342,13 @@
         <v>88</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3368,22 +3359,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>120</v>
@@ -3610,7 +3601,7 @@
         <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>161</v>
@@ -3642,7 +3633,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>165</v>
@@ -3735,10 +3726,10 @@
         <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>177</v>
@@ -3767,10 +3758,10 @@
         <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>181</v>
@@ -3799,10 +3790,10 @@
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>185</v>
@@ -3831,7 +3822,7 @@
         <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>151</v>
@@ -3962,7 +3953,7 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>206</v>
@@ -3991,52 +3982,20 @@
         <v>88</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4067,7 +4026,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4134,19 +4092,19 @@
         <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4160,13 +4118,13 @@
         <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>88</v>
@@ -4178,7 +4136,7 @@
         <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4192,13 +4150,13 @@
         <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>88</v>
@@ -4207,10 +4165,10 @@
         <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4224,13 +4182,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>88</v>
@@ -4242,7 +4200,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4256,13 +4214,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>88</v>
@@ -4274,7 +4232,7 @@
         <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4288,13 +4246,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>88</v>
@@ -4306,7 +4264,7 @@
         <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4320,13 +4278,13 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>88</v>
@@ -4338,7 +4296,7 @@
         <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4352,13 +4310,13 @@
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>88</v>
@@ -4370,7 +4328,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4384,13 +4342,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>88</v>
@@ -4402,7 +4360,7 @@
         <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4413,28 +4371,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4448,13 +4406,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>88</v>
@@ -4463,10 +4421,10 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4480,13 +4438,13 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>88</v>
@@ -4495,10 +4453,10 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4512,25 +4470,25 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4544,13 +4502,13 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>88</v>
@@ -4559,10 +4517,10 @@
         <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4576,25 +4534,25 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4608,13 +4566,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -4626,7 +4584,7 @@
         <v>120</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4640,25 +4598,25 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4672,25 +4630,25 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4704,25 +4662,25 @@
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4736,13 +4694,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>88</v>
@@ -4754,7 +4712,7 @@
         <v>120</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4768,13 +4726,13 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>88</v>
@@ -4786,7 +4744,7 @@
         <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4800,13 +4758,13 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>88</v>
@@ -4818,7 +4776,7 @@
         <v>120</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4832,13 +4790,13 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>88</v>
@@ -4847,10 +4805,10 @@
         <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4864,25 +4822,25 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4896,25 +4854,25 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4928,25 +4886,25 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4960,13 +4918,13 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>88</v>
@@ -4978,7 +4936,7 @@
         <v>142</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4992,13 +4950,13 @@
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>88</v>
@@ -5010,7 +4968,7 @@
         <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5024,13 +4982,13 @@
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>88</v>
@@ -5039,10 +4997,10 @@
         <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5087,1051 +5045,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J31"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6179,19 +5092,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>395</v>
+        <v>299</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>395</v>
+        <v>299</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>396</v>
+        <v>300</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>88</v>
@@ -6203,7 +5116,7 @@
         <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>397</v>
+        <v>301</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6211,19 +5124,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>398</v>
+        <v>302</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>398</v>
+        <v>302</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>399</v>
+        <v>303</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>88</v>
@@ -6235,7 +5148,7 @@
         <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>400</v>
+        <v>304</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6243,19 +5156,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>401</v>
+        <v>305</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>401</v>
+        <v>305</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>402</v>
+        <v>306</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>88</v>
@@ -6267,7 +5180,7 @@
         <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>403</v>
+        <v>307</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6275,19 +5188,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>404</v>
+        <v>308</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>404</v>
+        <v>308</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>405</v>
+        <v>309</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>88</v>
@@ -6299,7 +5212,7 @@
         <v>142</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>406</v>
+        <v>310</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6307,19 +5220,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>407</v>
+        <v>311</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>81</v>
@@ -6331,7 +5244,7 @@
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>408</v>
+        <v>312</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6339,19 +5252,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>409</v>
+        <v>313</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>409</v>
+        <v>313</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>410</v>
+        <v>314</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>88</v>
@@ -6363,7 +5276,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>411</v>
+        <v>315</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6371,19 +5284,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>412</v>
+        <v>316</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>412</v>
+        <v>316</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>88</v>
@@ -6395,7 +5308,7 @@
         <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>414</v>
+        <v>318</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6403,19 +5316,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>415</v>
+        <v>319</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>415</v>
+        <v>319</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>416</v>
+        <v>320</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>88</v>
@@ -6427,7 +5340,7 @@
         <v>156</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>417</v>
+        <v>321</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6435,19 +5348,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>418</v>
+        <v>322</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>418</v>
+        <v>322</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>419</v>
+        <v>323</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>88</v>
@@ -6459,7 +5372,7 @@
         <v>156</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>420</v>
+        <v>324</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6467,19 +5380,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>421</v>
+        <v>325</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>422</v>
+        <v>326</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>88</v>
@@ -6491,7 +5404,7 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>423</v>
+        <v>327</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6499,31 +5412,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>424</v>
+        <v>328</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>424</v>
+        <v>328</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>425</v>
+        <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>426</v>
+        <v>330</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6531,19 +5444,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>427</v>
+        <v>331</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>427</v>
+        <v>331</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>428</v>
+        <v>332</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>88</v>
@@ -6555,7 +5468,7 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>429</v>
+        <v>333</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6563,31 +5476,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>430</v>
+        <v>334</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>430</v>
+        <v>334</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>431</v>
+        <v>335</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>432</v>
+        <v>336</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6595,31 +5508,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>433</v>
+        <v>337</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>433</v>
+        <v>337</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>434</v>
+        <v>338</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>435</v>
+        <v>339</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6627,19 +5540,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>436</v>
+        <v>340</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>436</v>
+        <v>340</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>437</v>
+        <v>341</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
@@ -6651,7 +5564,7 @@
         <v>151</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>438</v>
+        <v>342</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6659,31 +5572,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>439</v>
+        <v>343</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>439</v>
+        <v>343</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>440</v>
+        <v>344</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>441</v>
+        <v>345</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6691,31 +5604,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>442</v>
+        <v>346</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>442</v>
+        <v>346</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>444</v>
+        <v>348</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6723,31 +5636,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>445</v>
+        <v>349</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>445</v>
+        <v>349</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>446</v>
+        <v>350</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>447</v>
+        <v>351</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6755,31 +5668,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>448</v>
+        <v>352</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>448</v>
+        <v>352</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>449</v>
+        <v>353</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>450</v>
+        <v>354</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6787,19 +5700,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>451</v>
+        <v>355</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>451</v>
+        <v>355</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>452</v>
+        <v>356</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>88</v>
@@ -6811,7 +5724,7 @@
         <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>453</v>
+        <v>357</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6819,31 +5732,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>454</v>
+        <v>358</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>454</v>
+        <v>358</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>455</v>
+        <v>359</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>456</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6851,19 +5764,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>457</v>
+        <v>361</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>457</v>
+        <v>361</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>458</v>
+        <v>362</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>88</v>
@@ -6872,10 +5785,10 @@
         <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>459</v>
+        <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6883,31 +5796,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>460</v>
+        <v>364</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>460</v>
+        <v>364</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>461</v>
+        <v>365</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>462</v>
+        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6915,31 +5828,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>463</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>463</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>464</v>
+        <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>465</v>
+        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6947,31 +5860,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>466</v>
+        <v>370</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>467</v>
+        <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>468</v>
+        <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6979,19 +5892,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>469</v>
+        <v>373</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>469</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>470</v>
+        <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>88</v>
@@ -7003,7 +5916,7 @@
         <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>471</v>
+        <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7011,19 +5924,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>472</v>
+        <v>376</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>473</v>
+        <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>88</v>
@@ -7035,7 +5948,7 @@
         <v>151</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>474</v>
+        <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7043,31 +5956,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>475</v>
+        <v>379</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>475</v>
+        <v>379</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>476</v>
+        <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>477</v>
+        <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7075,31 +5988,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>478</v>
+        <v>382</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>478</v>
+        <v>382</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>479</v>
+        <v>383</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>480</v>
+        <v>384</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7107,19 +6020,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>211</v>
+        <v>385</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>481</v>
+        <v>386</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>481</v>
+        <v>386</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>482</v>
+        <v>387</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>88</v>
@@ -7128,10 +6041,10 @@
         <v>119</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>483</v>
+        <v>388</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7139,19 +6052,19 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>484</v>
+        <v>389</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>485</v>
+        <v>390</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>485</v>
+        <v>390</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>486</v>
+        <v>391</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>88</v>
@@ -7160,10 +6073,10 @@
         <v>201</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>487</v>
+        <v>392</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>24</v>
@@ -7208,6 +6121,1051 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J31"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -7263,25 +7221,25 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7295,13 +7253,13 @@
         <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>88</v>
@@ -7313,7 +7271,7 @@
         <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7327,13 +7285,13 @@
         <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>88</v>
@@ -7345,7 +7303,7 @@
         <v>120</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7365,7 +7323,7 @@
         <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>81</v>
@@ -7377,7 +7335,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7391,25 +7349,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7423,13 +7381,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>88</v>
@@ -7441,7 +7399,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7455,25 +7413,25 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>120</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7487,13 +7445,13 @@
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>88</v>
@@ -7505,7 +7463,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7519,13 +7477,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>88</v>
@@ -7537,7 +7495,7 @@
         <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7548,16 +7506,16 @@
         <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>88</v>
@@ -7569,7 +7527,7 @@
         <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7583,13 +7541,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>88</v>
@@ -7601,7 +7559,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7615,13 +7573,13 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>88</v>
@@ -7633,7 +7591,7 @@
         <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7647,25 +7605,25 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7679,13 +7637,13 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>88</v>
@@ -7697,7 +7655,7 @@
         <v>151</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7711,13 +7669,13 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
@@ -7729,7 +7687,7 @@
         <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7743,13 +7701,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -7761,7 +7719,7 @@
         <v>151</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7775,13 +7733,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>88</v>
@@ -7793,7 +7751,7 @@
         <v>151</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7807,13 +7765,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>88</v>
@@ -7825,7 +7783,7 @@
         <v>151</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7839,13 +7797,13 @@
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>88</v>
@@ -7857,7 +7815,7 @@
         <v>151</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7871,25 +7829,25 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7903,25 +7861,25 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7935,25 +7893,25 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7967,25 +7925,25 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7999,13 +7957,13 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>88</v>
@@ -8014,10 +7972,10 @@
         <v>119</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8031,25 +7989,25 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8063,13 +8021,13 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>88</v>
@@ -8081,7 +8039,7 @@
         <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8095,13 +8053,13 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>88</v>
@@ -8110,10 +8068,10 @@
         <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8127,13 +8085,13 @@
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>88</v>
@@ -8142,10 +8100,10 @@
         <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8159,13 +8117,13 @@
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>88</v>
@@ -8174,10 +8132,10 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8188,16 +8146,16 @@
         <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>211</v>
+        <v>385</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>88</v>
@@ -8206,10 +8164,10 @@
         <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8308,13 +8266,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>88</v>
@@ -8323,10 +8281,10 @@
         <v>119</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8340,13 +8298,13 @@
         <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>88</v>
@@ -8358,7 +8316,7 @@
         <v>101</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8378,7 +8336,7 @@
         <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>81</v>
@@ -8390,7 +8348,7 @@
         <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8404,13 +8362,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>88</v>
@@ -8422,7 +8380,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8436,13 +8394,13 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>88</v>
@@ -8454,7 +8412,7 @@
         <v>156</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8468,25 +8426,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>142</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8500,25 +8458,25 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>156</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8532,13 +8490,13 @@
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>88</v>
@@ -8550,7 +8508,7 @@
         <v>151</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8564,13 +8522,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>88</v>
@@ -8582,7 +8540,7 @@
         <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8593,16 +8551,16 @@
         <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>88</v>
@@ -8611,10 +8569,10 @@
         <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8628,25 +8586,25 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8660,13 +8618,13 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>88</v>
@@ -8675,10 +8633,10 @@
         <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8692,13 +8650,13 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>88</v>
@@ -8707,10 +8665,10 @@
         <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8724,13 +8682,13 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>88</v>
@@ -8739,10 +8697,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8756,13 +8714,13 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
@@ -8771,10 +8729,10 @@
         <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8788,13 +8746,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -8803,10 +8761,10 @@
         <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8820,13 +8778,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>88</v>
@@ -8835,10 +8793,10 @@
         <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8852,25 +8810,25 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8884,25 +8842,25 @@
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8916,13 +8874,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>88</v>
@@ -8931,10 +8889,10 @@
         <v>119</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8948,13 +8906,13 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>88</v>
@@ -8963,10 +8921,10 @@
         <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8980,13 +8938,13 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>88</v>
@@ -8995,10 +8953,10 @@
         <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9012,13 +8970,13 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>88</v>
@@ -9027,10 +8985,10 @@
         <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>386</v>
+        <v>476</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -9044,25 +9002,25 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9076,13 +9034,13 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>88</v>
@@ -9091,10 +9049,10 @@
         <v>119</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9108,13 +9066,13 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>88</v>
@@ -9123,10 +9081,10 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9140,25 +9098,25 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9172,25 +9130,25 @@
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9204,25 +9162,25 @@
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9320,13 +9278,13 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>88</v>
@@ -9338,7 +9296,7 @@
         <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9352,25 +9310,25 @@
         <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9390,7 +9348,7 @@
         <v>70</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>81</v>
@@ -9399,10 +9357,10 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9416,13 +9374,13 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>88</v>
@@ -9434,7 +9392,7 @@
         <v>151</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9448,25 +9406,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9480,13 +9438,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>88</v>
@@ -9498,7 +9456,7 @@
         <v>151</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9512,13 +9470,13 @@
         <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>88</v>
@@ -9527,10 +9485,10 @@
         <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9544,13 +9502,13 @@
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>88</v>
@@ -9559,10 +9517,10 @@
         <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9576,13 +9534,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>88</v>
@@ -9594,7 +9552,7 @@
         <v>151</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9605,28 +9563,28 @@
         <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9640,13 +9598,13 @@
         <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>88</v>
@@ -9655,10 +9613,10 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9672,13 +9630,13 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>88</v>
@@ -9687,10 +9645,10 @@
         <v>82</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9704,13 +9662,13 @@
         <v>139</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>88</v>
@@ -9719,10 +9677,10 @@
         <v>119</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9736,25 +9694,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9768,25 +9726,25 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9800,13 +9758,13 @@
         <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>88</v>
@@ -9815,10 +9773,10 @@
         <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9832,13 +9790,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>88</v>
@@ -9847,10 +9805,10 @@
         <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9864,25 +9822,25 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9896,13 +9854,13 @@
         <v>166</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>88</v>
@@ -9911,10 +9869,10 @@
         <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9928,13 +9886,13 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>88</v>
@@ -9943,10 +9901,10 @@
         <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9960,13 +9918,13 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>88</v>
@@ -9975,10 +9933,10 @@
         <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9992,25 +9950,25 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>379</v>
+        <v>469</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -10024,25 +9982,25 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>393</v>
+        <v>483</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>386</v>
+        <v>476</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10056,25 +10014,25 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10088,13 +10046,13 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>88</v>
@@ -10103,10 +10061,10 @@
         <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10120,13 +10078,13 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>88</v>
@@ -10135,10 +10093,10 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10152,13 +10110,13 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>88</v>
@@ -10167,10 +10125,10 @@
         <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10184,13 +10142,13 @@
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>88</v>
@@ -10199,10 +10157,10 @@
         <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>386</v>
+        <v>476</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10216,13 +10174,13 @@
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>88</v>
@@ -10231,10 +10189,10 @@
         <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10245,16 +10203,16 @@
         <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>211</v>
+        <v>385</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>88</v>
@@ -10263,10 +10221,10 @@
         <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="다다익선" sheetId="3" r:id="rId3"/>
-    <sheet name="초코나라" sheetId="4" r:id="rId4"/>
+    <sheet name="초코나라" sheetId="3" r:id="rId3"/>
+    <sheet name="다다익선" sheetId="4" r:id="rId4"/>
     <sheet name="블랙소울" sheetId="5" r:id="rId5"/>
     <sheet name="비련" sheetId="6" r:id="rId6"/>
     <sheet name="밀크런" sheetId="7" r:id="rId7"/>
@@ -18,12 +18,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">다다익선!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">다다익선!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블랙소울!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">초코나라!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">초코나라!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">털미녀!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="766">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>390</t>
+    <t>389</t>
   </si>
   <si>
     <t>13위</t>
@@ -96,7 +96,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>172조 8970억 7998만</t>
+    <t>173조 9352억 9390만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -108,6 +108,27 @@
     <t>2026.04.19</t>
   </si>
   <si>
+    <t>초코나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>9위</t>
+  </si>
+  <si>
+    <t>162조 1959억 1270만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
     <t>다다익선</t>
   </si>
   <si>
@@ -117,7 +138,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>370</t>
+    <t>371</t>
   </si>
   <si>
     <t>7위</t>
@@ -138,27 +159,6 @@
     <t>Pakistan</t>
   </si>
   <si>
-    <t>초코나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>162조 1959억 1270만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
     <t>블랙소울</t>
   </si>
   <si>
@@ -192,7 +192,7 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>383</t>
+    <t>384</t>
   </si>
   <si>
     <t>34위</t>
@@ -291,7 +291,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>23조 641억 4651만</t>
+    <t>26조 7249억 1381만</t>
   </si>
   <si>
     <t>2</t>
@@ -345,7 +345,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>12조 8368억 6384만</t>
+    <t>13조 1760억 5067만</t>
   </si>
   <si>
     <t>5</t>
@@ -360,7 +360,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>12조 6365억 3160만</t>
+    <t>12조 9053억 3941만</t>
   </si>
   <si>
     <t>6</t>
@@ -384,7 +384,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 1232억 2869만</t>
+    <t>7조 2859억 1203만</t>
   </si>
   <si>
     <t>8</t>
@@ -429,7 +429,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>5조 9591억 5169만</t>
+    <t>6조 623억 4209만</t>
   </si>
   <si>
     <t>11</t>
@@ -441,7 +441,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 9286억 68만</t>
+    <t>5조 3840억 4662만</t>
   </si>
   <si>
     <t>12</t>
@@ -453,7 +453,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 4114억 7192만</t>
+    <t>4조 7044억 9896만</t>
   </si>
   <si>
     <t>13</t>
@@ -480,12 +480,39 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 1855억 6129만</t>
+    <t>4조 1902억 7508만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>3조 9403억 5517만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 7580억 1099만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
@@ -495,10 +522,10 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 7219억 6524만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>3조 7369억 5836만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>강철고튠데</t>
@@ -510,22 +537,7 @@
     <t>3조 6838억 5909만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>3조 6572억 2213만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -537,7 +549,7 @@
     <t>3조 5006억 2017만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -549,7 +561,7 @@
     <t>3조 3744억 7808만</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -558,10 +570,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 316억 6665만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>3조 897억 1185만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -573,7 +585,7 @@
     <t>2조 7646억 9816만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>여븨</t>
@@ -582,10 +594,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 6571억 479만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>2조 6956억 5390만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -594,10 +606,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2조 2590억 8270만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>2조 3877억 7093만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -609,7 +621,7 @@
     <t>2조 2114억 104만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>여눈</t>
@@ -621,7 +633,7 @@
     <t>2조 1697억 686만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -636,7 +648,7 @@
     <t>2조 721억 7045만</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -648,7 +660,7 @@
     <t>2조 663억 1201만</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>데드캣</t>
@@ -657,10 +669,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>1조 8338억 6575만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>2조 131억 6518만</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>욤지</t>
@@ -675,13 +687,289 @@
     <t>1조 2511억 5308만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>55조 9250억 6727만</t>
+  </si>
+  <si>
+    <t>멈디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
+  </si>
+  <si>
+    <t>8조 7298억 6806만</t>
+  </si>
+  <si>
+    <t>유랑민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>7조 6431억 3041만</t>
+  </si>
+  <si>
+    <t>포도맛맥플</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
+  </si>
+  <si>
+    <t>6조 2321억 4833만</t>
+  </si>
+  <si>
+    <t>사숩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
+  </si>
+  <si>
+    <t>6조 2118억 8814만</t>
+  </si>
+  <si>
+    <t>연바기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 1263억 2717만</t>
+  </si>
+  <si>
+    <t>또긔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
+  </si>
+  <si>
+    <t>5조 1245억 9779만</t>
+  </si>
+  <si>
+    <t>limno</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=limno</t>
+  </si>
+  <si>
+    <t>4조 7958억 7796만</t>
+  </si>
+  <si>
+    <t>스라차차소스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4조 5203억 3982만</t>
+  </si>
+  <si>
+    <t>단비둘기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>4조 4323억 8120만</t>
+  </si>
+  <si>
+    <t>우치앵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
+  </si>
+  <si>
+    <t>4조 4132억 5832만</t>
+  </si>
+  <si>
+    <t>썬콜법사도희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>4조 4002억 6957만</t>
+  </si>
+  <si>
+    <t>김롸아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
+  </si>
+  <si>
+    <t>4조 3358억 9546만</t>
+  </si>
+  <si>
+    <t>린샹판</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
+  </si>
+  <si>
+    <t>4조 1779억 5565만</t>
+  </si>
+  <si>
+    <t>A7R4</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
+  </si>
+  <si>
+    <t>4조 1577억 9922만</t>
+  </si>
+  <si>
+    <t>불곰파워</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
+  </si>
+  <si>
+    <t>3조 8877억 52만</t>
+  </si>
+  <si>
+    <t>낮잠중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
+  </si>
+  <si>
+    <t>3조 7328억 8158만</t>
+  </si>
+  <si>
+    <t>히어로경원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
+  </si>
+  <si>
+    <t>3조 5815억 2733만</t>
+  </si>
+  <si>
+    <t>까만색양갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>3조 5727억 8462만</t>
+  </si>
+  <si>
+    <t>투둠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
+  </si>
+  <si>
+    <t>3조 2203억 7274만</t>
+  </si>
+  <si>
+    <t>구파발메타몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>3조 672억 4229만</t>
+  </si>
+  <si>
+    <t>썹웨피망빼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
+  </si>
+  <si>
+    <t>2조 9921억 3104만</t>
+  </si>
+  <si>
+    <t>zl지존썬콜lz</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
+  </si>
+  <si>
+    <t>2조 9755억 7551만</t>
+  </si>
+  <si>
+    <t>용날라가유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%82%A0%EB%9D%BC%EA%B0%80%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>2조 8720억 7370만</t>
+  </si>
+  <si>
+    <t>도윤파덜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
+  </si>
+  <si>
+    <t>2조 7551억 8984만</t>
+  </si>
+  <si>
+    <t>구파발고양이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 7336억 1161만</t>
+  </si>
+  <si>
+    <t>무쿠미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2조 7152억 5892만</t>
+  </si>
+  <si>
+    <t>극쪽이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 3635억 2018만</t>
+  </si>
+  <si>
+    <t>토리파더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>6911억 7781만</t>
+  </si>
+  <si>
+    <t>닼나왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%99%95</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1159억 6194만</t>
+  </si>
+  <si>
     <t>눈꽃물망초</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
   </si>
   <si>
-    <t>62조 2166억 4623만</t>
+    <t>82조 7627억 5178만</t>
   </si>
   <si>
     <t>포르쉐718</t>
@@ -699,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
   </si>
   <si>
-    <t>18조 9203억 5223만</t>
+    <t>19조 4507억 7530만</t>
   </si>
   <si>
     <t>뒁글</t>
@@ -708,13 +996,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
   </si>
   <si>
-    <t>9조 3521억 7994만</t>
+    <t>10조 1552억 8473만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
   </si>
   <si>
-    <t>7조 622억 1067만</t>
+    <t>7조 746억 9423만</t>
   </si>
   <si>
     <t>공대애봉이</t>
@@ -723,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>6조 1078억 1847만</t>
+    <t>6조 2243억 5276만</t>
   </si>
   <si>
     <t>언기</t>
@@ -741,7 +1029,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
   </si>
   <si>
-    <t>3조 1626억 7757만</t>
+    <t>3조 4263억 218만</t>
+  </si>
+  <si>
+    <t>토르릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>3조 2674억 3350만</t>
   </si>
   <si>
     <t>묘목키우기</t>
@@ -750,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>3조 689억 4904만</t>
+    <t>3조 2041억 8029만</t>
   </si>
   <si>
     <t>JAEYA</t>
@@ -762,13 +1059,13 @@
     <t>3조 341억 6644만</t>
   </si>
   <si>
-    <t>토르릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>2조 8210억 4236만</t>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>2조 8021억 3148만</t>
   </si>
   <si>
     <t>따뜻한배추</t>
@@ -798,13 +1095,13 @@
     <t>2조 5176억 2671만</t>
   </si>
   <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>2조 3356억 6642만</t>
+    <t>옵션키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>2조 4941억 8036만</t>
   </si>
   <si>
     <t>맛닭꼬시멘토</t>
@@ -813,7 +1110,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EB%8B%AD%EA%BC%AC%EC%8B%9C%EB%A9%98%ED%86%A0</t>
   </si>
   <si>
-    <t>1조 9631억 5670만</t>
+    <t>2조 1614억 5837만</t>
+  </si>
+  <si>
+    <t>밍고스틴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
+  </si>
+  <si>
+    <t>1조 9758억 7765만</t>
   </si>
   <si>
     <t>l우주아이l</t>
@@ -831,16 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
   </si>
   <si>
-    <t>1조 8721억 530만</t>
-  </si>
-  <si>
-    <t>밍고스틴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
-  </si>
-  <si>
-    <t>1조 8245억 2588만</t>
+    <t>1조 8894억 8517만</t>
   </si>
   <si>
     <t>원투아빠</t>
@@ -849,7 +1146,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>1조 7472억 9454만</t>
+    <t>1조 8175억 7825만</t>
   </si>
   <si>
     <t>아쿠마불독</t>
@@ -858,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>1조 5857억 5574만</t>
+    <t>1조 7057억 8729만</t>
   </si>
   <si>
     <t>l성연l</t>
@@ -870,13 +1167,13 @@
     <t>1조 5698억 7903만</t>
   </si>
   <si>
-    <t>옵션키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1조 5600억 4312만</t>
+    <t>맨해라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%ED%95%B4%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 4856억 7272만</t>
   </si>
   <si>
     <t>몽실망실토실</t>
@@ -888,22 +1185,13 @@
     <t>1조 4533억 737만</t>
   </si>
   <si>
-    <t>맨해라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%ED%95%B4%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 4036억 6449만</t>
-  </si>
-  <si>
     <t>오늘밤은삐딱</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%B0%A4%EC%9D%80%EC%82%90%EB%94%B1</t>
   </si>
   <si>
-    <t>1조 3938억 5415만</t>
+    <t>1조 4359억 5363만</t>
   </si>
   <si>
     <t>타락파워스님</t>
@@ -921,7 +1209,16 @@
     <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
   </si>
   <si>
-    <t>9399억 5138만</t>
+    <t>9494억 6037만</t>
+  </si>
+  <si>
+    <t>체시어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
+  </si>
+  <si>
+    <t>7168억 9216만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -930,283 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
   </si>
   <si>
-    <t>6641억 5282만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>체시어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
-  </si>
-  <si>
-    <t>5776억 562만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>51조 8759억 6562만</t>
-  </si>
-  <si>
-    <t>멈디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
-  </si>
-  <si>
-    <t>8조 7298억 6806만</t>
-  </si>
-  <si>
-    <t>유랑민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>7조 5637억 66만</t>
-  </si>
-  <si>
-    <t>사숩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
-  </si>
-  <si>
-    <t>5조 6530억 8881만</t>
-  </si>
-  <si>
-    <t>포도맛맥플</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
-  </si>
-  <si>
-    <t>5조 5934억 8506만</t>
-  </si>
-  <si>
-    <t>또긔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
-  </si>
-  <si>
-    <t>5조 998억 1564만</t>
-  </si>
-  <si>
-    <t>연바기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 423억 1022만</t>
-  </si>
-  <si>
-    <t>스라차차소스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>4조 5203억 3982만</t>
-  </si>
-  <si>
-    <t>썬콜법사도희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>4조 4002억 6957만</t>
-  </si>
-  <si>
-    <t>우치앵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
-  </si>
-  <si>
-    <t>4조 2529억 1330만</t>
-  </si>
-  <si>
-    <t>limno</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=limno</t>
-  </si>
-  <si>
-    <t>4조 2376억 8105만</t>
-  </si>
-  <si>
-    <t>김롸아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
-  </si>
-  <si>
-    <t>4조 2083억 2801만</t>
-  </si>
-  <si>
-    <t>단비둘기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>4조 1661억 5652만</t>
-  </si>
-  <si>
-    <t>A7R4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
-  </si>
-  <si>
-    <t>4조 702억 645만</t>
-  </si>
-  <si>
-    <t>린샹판</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
-  </si>
-  <si>
-    <t>3조 9840억 7632만</t>
-  </si>
-  <si>
-    <t>불곰파워</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
-  </si>
-  <si>
-    <t>3조 8704억 9855만</t>
-  </si>
-  <si>
-    <t>낮잠중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
-  </si>
-  <si>
-    <t>3조 7328억 8158만</t>
-  </si>
-  <si>
-    <t>히어로경원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
-  </si>
-  <si>
-    <t>3조 5815억 2733만</t>
-  </si>
-  <si>
-    <t>까만색양갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>3조 3736억 4336만</t>
-  </si>
-  <si>
-    <t>투둠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
-  </si>
-  <si>
-    <t>3조 374억 6255만</t>
-  </si>
-  <si>
-    <t>zl지존썬콜lz</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
-  </si>
-  <si>
-    <t>2조 9577억 2892만</t>
-  </si>
-  <si>
-    <t>썹웨피망빼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
-  </si>
-  <si>
-    <t>2조 9067억 9789만</t>
-  </si>
-  <si>
-    <t>용날라가유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%82%A0%EB%9D%BC%EA%B0%80%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>2조 8720억 7370만</t>
-  </si>
-  <si>
-    <t>도윤파덜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
-  </si>
-  <si>
-    <t>2조 7543억 4082만</t>
-  </si>
-  <si>
-    <t>구파발메타몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>2조 7308억 6877만</t>
-  </si>
-  <si>
-    <t>무쿠미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2조 6257억 9911만</t>
-  </si>
-  <si>
-    <t>구파발고양이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2조 5622억 9482만</t>
-  </si>
-  <si>
-    <t>극쪽이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 3635억 2018만</t>
-  </si>
-  <si>
-    <t>토리파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>6911억 7781만</t>
+    <t>6723억 693만</t>
   </si>
   <si>
     <t>상현별</t>
@@ -1215,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
   </si>
   <si>
-    <t>58조 6421억 9967만</t>
+    <t>58조 9678억 1733만</t>
   </si>
   <si>
     <t>말랑콩닥</t>
@@ -1251,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
   </si>
   <si>
-    <t>6조 7946억 2714만</t>
+    <t>7조 2701억 9712만</t>
   </si>
   <si>
     <t>찌율</t>
@@ -1260,7 +1281,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
   </si>
   <si>
-    <t>6조 5302억 7386만</t>
+    <t>7조 422억 148만</t>
+  </si>
+  <si>
+    <t>메키현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%ED%98%84</t>
+  </si>
+  <si>
+    <t>6조 3623억 121만</t>
   </si>
   <si>
     <t>감자도리유지</t>
@@ -1272,15 +1302,6 @@
     <t>6조 624억 3694만</t>
   </si>
   <si>
-    <t>메키현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%ED%98%84</t>
-  </si>
-  <si>
-    <t>5조 8233억 7749만</t>
-  </si>
-  <si>
     <t>엠비피</t>
   </si>
   <si>
@@ -1296,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%83%81%EA%B8%89%EC%A1%B0%EC%A4%80%EA%B2%BD</t>
   </si>
   <si>
-    <t>4조 6684억 9233만</t>
+    <t>4조 9723억 4674만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
@@ -1311,13 +1332,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
   </si>
   <si>
-    <t>2조 8871억 8324만</t>
-  </si>
-  <si>
-    <t>포무최고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%AC%B4%EC%B5%9C%EA%B3%A0</t>
+    <t>3조 342억 2516만</t>
+  </si>
+  <si>
+    <t>별밖에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
   </si>
   <si>
     <t>2조 5929억 5049만</t>
@@ -1329,7 +1350,7 @@
     <t>https://mgf.gg/contents/character.php?n=87%EA%B0%95%ED%83%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>2조 4814억 2204만</t>
+    <t>2조 5822억 3298만</t>
   </si>
   <si>
     <t>용감한순대국</t>
@@ -1338,7 +1359,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
   </si>
   <si>
-    <t>2조 3897억 4858만</t>
+    <t>2조 4837억 7658만</t>
+  </si>
+  <si>
+    <t>양념반탈리반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%85%90%EB%B0%98%ED%83%88%EB%A6%AC%EB%B0%98</t>
+  </si>
+  <si>
+    <t>2조 551억 3619만</t>
   </si>
   <si>
     <t>박예쁜</t>
@@ -1359,22 +1389,22 @@
     <t>1조 9399억 58만</t>
   </si>
   <si>
-    <t>양념반탈리반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%85%90%EB%B0%98%ED%83%88%EB%A6%AC%EB%B0%98</t>
-  </si>
-  <si>
-    <t>1조 8429억 114만</t>
-  </si>
-  <si>
     <t>맹루미</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%B9%EB%A3%A8%EB%AF%B8</t>
   </si>
   <si>
-    <t>1조 7936억 7321만</t>
+    <t>1조 8462억 6458만</t>
+  </si>
+  <si>
+    <t>신궁초보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%B4%88%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>1조 7224억 9946만</t>
   </si>
   <si>
     <t>쿰척쿰쳑</t>
@@ -1386,6 +1416,15 @@
     <t>1조 5888억 7783만</t>
   </si>
   <si>
+    <t>옹야미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>1조 5502억 9779만</t>
+  </si>
+  <si>
     <t>판별식</t>
   </si>
   <si>
@@ -1395,31 +1434,13 @@
     <t>1조 5313억 7684만</t>
   </si>
   <si>
-    <t>옹야미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1조 5266억 2834만</t>
-  </si>
-  <si>
-    <t>신궁초보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%B4%88%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>1조 5104억 4251만</t>
-  </si>
-  <si>
     <t>루맹이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 3943억 4638만</t>
+    <t>1조 4467억 8723만</t>
   </si>
   <si>
     <t>츄쁜</t>
@@ -1428,7 +1449,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
   </si>
   <si>
-    <t>8485억 7798만</t>
+    <t>9393억 8181만</t>
   </si>
   <si>
     <t>한닝</t>
@@ -1449,7 +1470,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>6667억 327만</t>
+    <t>7024억 2835만</t>
   </si>
   <si>
     <t>놀면머하니</t>
@@ -1461,7 +1482,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>5065억 1113만</t>
+    <t>5188억 6506만</t>
   </si>
   <si>
     <t>뮴뮴뮴뮴뮴</t>
@@ -1470,7 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4</t>
   </si>
   <si>
-    <t>4697억 9524만</t>
+    <t>5122억 1979만</t>
   </si>
   <si>
     <t>키워봄</t>
@@ -1503,7 +1524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%B4%89e</t>
   </si>
   <si>
-    <t>43조 8489억 512만</t>
+    <t>47조 7864억 3172만</t>
   </si>
   <si>
     <t>가나디도둑</t>
@@ -1512,13 +1533,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%82%98%EB%94%94%EB%8F%84%EB%91%91</t>
   </si>
   <si>
-    <t>10조 4628억 2175만</t>
+    <t>11조 2008억 5773만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%86%ED%94%84</t>
   </si>
   <si>
-    <t>8조 6232억 231만</t>
+    <t>9조 3130억 5850만</t>
   </si>
   <si>
     <t>조영현2</t>
@@ -1527,7 +1548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%98%81%ED%98%842</t>
   </si>
   <si>
-    <t>7조 489억 6555만</t>
+    <t>7조 3275억 5543만</t>
   </si>
   <si>
     <t>정신못차림</t>
@@ -1536,7 +1557,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>5조 840억 116만</t>
+    <t>5조 1244억 9622만</t>
   </si>
   <si>
     <t>캔터베리</t>
@@ -1545,7 +1566,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%ED%84%B0%EB%B2%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>4조 4995억 5029만</t>
+    <t>4조 5323억 7837만</t>
   </si>
   <si>
     <t>핫딜패스</t>
@@ -1563,7 +1584,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EA%B2%BD%EB%82%98%EB%9D%BC</t>
   </si>
   <si>
-    <t>3조 3554억 354만</t>
+    <t>3조 9876억 2416만</t>
+  </si>
+  <si>
+    <t>햐밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%90%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>3조 7517억 4264만</t>
   </si>
   <si>
     <t>빅밥</t>
@@ -1572,7 +1602,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
   </si>
   <si>
-    <t>3조 864억 5050만</t>
+    <t>3조 3008억 8482만</t>
   </si>
   <si>
     <t>하눌이야</t>
@@ -1581,16 +1611,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%88%8C%EC%9D%B4%EC%95%BC</t>
   </si>
   <si>
-    <t>2조 8428억 2912만</t>
-  </si>
-  <si>
-    <t>햐밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%90%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>2조 7691억 6941만</t>
+    <t>2조 8701억 128만</t>
   </si>
   <si>
     <t>풰른</t>
@@ -1602,6 +1623,15 @@
     <t>2조 3185억 9393만</t>
   </si>
   <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Scope</t>
+  </si>
+  <si>
+    <t>2조 1746억 7603만</t>
+  </si>
+  <si>
     <t>아무렇게할래</t>
   </si>
   <si>
@@ -1611,22 +1641,13 @@
     <t>2조 351억 8824만</t>
   </si>
   <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Scope</t>
-  </si>
-  <si>
-    <t>1조 9453억 8712만</t>
-  </si>
-  <si>
     <t>리디엘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%94%94%EC%97%98</t>
   </si>
   <si>
-    <t>1조 9269억 2591만</t>
+    <t>1조 9545억 2589만</t>
   </si>
   <si>
     <t>산로지노</t>
@@ -1635,7 +1656,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
   </si>
   <si>
-    <t>1조 8158억 107만</t>
+    <t>1조 8644억 5489만</t>
   </si>
   <si>
     <t>떠하야</t>
@@ -1647,6 +1668,15 @@
     <t>1조 6841억 6677만</t>
   </si>
   <si>
+    <t>흙심이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 6815억 8335만</t>
+  </si>
+  <si>
     <t>포근해</t>
   </si>
   <si>
@@ -1656,13 +1686,13 @@
     <t>1조 6535억 1416만</t>
   </si>
   <si>
-    <t>흙심이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 4811억 6139만</t>
+    <t>Azham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Azham</t>
+  </si>
+  <si>
+    <t>1조 4452억 8437만</t>
   </si>
   <si>
     <t>별잇</t>
@@ -1671,7 +1701,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%9E%87</t>
   </si>
   <si>
-    <t>1조 4243억 3912만</t>
+    <t>1조 4341억 5998만</t>
   </si>
   <si>
     <t>이즈뤼얼</t>
@@ -1683,22 +1713,13 @@
     <t>1조 3103억 8234만</t>
   </si>
   <si>
-    <t>Azham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Azham</t>
-  </si>
-  <si>
-    <t>1조 2706억 63만</t>
-  </si>
-  <si>
     <t>Porto</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Porto</t>
   </si>
   <si>
-    <t>1조 1682억 6935만</t>
+    <t>1조 2456억 9871만</t>
   </si>
   <si>
     <t>비라비스</t>
@@ -1734,7 +1755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%A0%A4%EA%B9%8C%EA%B8%B0</t>
   </si>
   <si>
-    <t>7134억 5540만</t>
+    <t>7164억 8743만</t>
   </si>
   <si>
     <t>뽀미l</t>
@@ -1743,7 +1764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
   </si>
   <si>
-    <t>5273억 3563만</t>
+    <t>5408억 9659만</t>
   </si>
   <si>
     <t>짜뇨</t>
@@ -1752,7 +1773,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%87%A8</t>
   </si>
   <si>
-    <t>4663억 6077만</t>
+    <t>4926억 6527만</t>
   </si>
   <si>
     <t>동띠</t>
@@ -1761,7 +1782,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9D%A0</t>
   </si>
   <si>
-    <t>106조 2824억 4986만</t>
+    <t>105</t>
+  </si>
+  <si>
+    <t>111조 3496억 2045만</t>
   </si>
   <si>
     <t>나무키우기</t>
@@ -1770,13 +1794,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%AC%B4%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>25조 6950억 8301만</t>
+    <t>27조 8463억 6887만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EB%8C%80</t>
   </si>
   <si>
-    <t>15조 3158억 598만</t>
+    <t>16조 4610억 1635만</t>
   </si>
   <si>
     <t>원남</t>
@@ -1785,7 +1809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
   </si>
   <si>
-    <t>4조 8166억 8241만</t>
+    <t>5조 3213억 2399만</t>
   </si>
   <si>
     <t>숍솝</t>
@@ -1794,7 +1818,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%8D%EC%86%9D</t>
   </si>
   <si>
-    <t>3조 7617억 5164만</t>
+    <t>4조 3745억 1323만</t>
   </si>
   <si>
     <t>정뽀</t>
@@ -1803,7 +1827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%BD%80</t>
   </si>
   <si>
-    <t>2조 4491억 273만</t>
+    <t>2조 4846억 9505만</t>
   </si>
   <si>
     <t>동동띠</t>
@@ -1812,7 +1836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%8F%99%EB%9D%A0</t>
   </si>
   <si>
-    <t>2조 2594억 884만</t>
+    <t>2조 4714억 1678만</t>
   </si>
   <si>
     <t>단정이</t>
@@ -1821,7 +1845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 7505억 4222만</t>
+    <t>1조 8009억 7716만</t>
   </si>
   <si>
     <t>지구뿌셔</t>
@@ -1830,7 +1854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>1조 3744억 3780만</t>
+    <t>1조 6092억 9048만</t>
   </si>
   <si>
     <t>꼬햄</t>
@@ -1839,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%ED%96%84</t>
   </si>
   <si>
-    <t>1조 3691억 2057만</t>
+    <t>1조 4985억 8369만</t>
   </si>
   <si>
     <t>사맛</t>
@@ -1848,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%9B</t>
   </si>
   <si>
-    <t>8877억 2379만</t>
+    <t>9328억 1058만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1857,7 +1881,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
   </si>
   <si>
-    <t>8227억 1634만</t>
+    <t>8633억 7335만</t>
+  </si>
+  <si>
+    <t>자쿰키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%BF%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>7799억 8675만</t>
   </si>
   <si>
     <t>갓굴</t>
@@ -1866,16 +1899,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
   </si>
   <si>
-    <t>6116억 5819만</t>
-  </si>
-  <si>
-    <t>자쿰키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%BF%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5560억 4809만</t>
+    <t>6183억 1836만</t>
   </si>
   <si>
     <t>김딸충</t>
@@ -1887,13 +1911,22 @@
     <t>5445억 772만</t>
   </si>
   <si>
+    <t>당겨쏴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B2%A8%EC%8F%B4</t>
+  </si>
+  <si>
+    <t>5076억 6526만</t>
+  </si>
+  <si>
     <t>귀쮸</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
   </si>
   <si>
-    <t>4775억 725만</t>
+    <t>5055억 4169만</t>
   </si>
   <si>
     <t>은단월</t>
@@ -1902,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
   </si>
   <si>
-    <t>4176억 2661만</t>
+    <t>4239억 2965만</t>
   </si>
   <si>
     <t>알뺘노</t>
@@ -1920,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
   </si>
   <si>
-    <t>3829억 2518만</t>
+    <t>3892억 4377만</t>
   </si>
   <si>
     <t>비비다</t>
@@ -1929,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%8B%A4</t>
   </si>
   <si>
-    <t>3826억 9989만</t>
+    <t>3853억 2536만</t>
   </si>
   <si>
     <t>투냉</t>
@@ -1938,7 +1971,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
   </si>
   <si>
-    <t>3341억 4686만</t>
+    <t>3571억 5697만</t>
+  </si>
+  <si>
+    <t>사과클럽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
+  </si>
+  <si>
+    <t>3194억 8001만</t>
   </si>
   <si>
     <t>차눅</t>
@@ -1947,16 +1989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
   </si>
   <si>
-    <t>3072억 6766만</t>
-  </si>
-  <si>
-    <t>사과클럽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
-  </si>
-  <si>
-    <t>2869억 2409만</t>
+    <t>3090억 5869만</t>
   </si>
   <si>
     <t>팔나무</t>
@@ -1965,7 +1998,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%82%98%EB%AC%B4</t>
   </si>
   <si>
-    <t>2209억 790만</t>
+    <t>2220억 7076만</t>
+  </si>
+  <si>
+    <t>반빔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B9%94</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1848억 4734만</t>
   </si>
   <si>
     <t>53다2329</t>
@@ -1974,22 +2019,7 @@
     <t>https://mgf.gg/contents/character.php?n=53%EB%8B%A42329</t>
   </si>
   <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1635억 7963만</t>
-  </si>
-  <si>
-    <t>반빔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%B9%94</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>1631억 2492만</t>
+    <t>1802억 3208만</t>
   </si>
   <si>
     <t>강진현</t>
@@ -2001,7 +2031,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>1134억 5165만</t>
+    <t>1408억 7411만</t>
   </si>
   <si>
     <t>으뭉</t>
@@ -2010,7 +2040,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%AD%89</t>
   </si>
   <si>
-    <t>1064억 7117만</t>
+    <t>1328억 4922만</t>
+  </si>
+  <si>
+    <t>길지녁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%A7%80%EB%85%81</t>
+  </si>
+  <si>
+    <t>1107억 3260만</t>
+  </si>
+  <si>
+    <t>31</t>
   </si>
   <si>
     <t>나루토토</t>
@@ -2019,16 +2061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%A3%A8%ED%86%A0%ED%86%A0</t>
   </si>
   <si>
-    <t>932억 1980만</t>
-  </si>
-  <si>
-    <t>길지녁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%A7%80%EB%85%81</t>
-  </si>
-  <si>
-    <t>804억 5737만</t>
+    <t>1005억 1586만</t>
   </si>
   <si>
     <t>아포짓</t>
@@ -2043,7 +2076,7 @@
     <t>https://mgf.gg/contents/character.php?n=86%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>2조 3471억 9720만</t>
+    <t>2조 4008억 6766만</t>
   </si>
   <si>
     <t>꿍물</t>
@@ -2052,7 +2085,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%8D%EB%AC%BC</t>
   </si>
   <si>
-    <t>1조 8946억 1696만</t>
+    <t>2조 537억 1290만</t>
   </si>
   <si>
     <t>끽스</t>
@@ -2061,7 +2094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
   </si>
   <si>
-    <t>1조 8440억 7830만</t>
+    <t>2조 346억 8875만</t>
   </si>
   <si>
     <t>델타시그마</t>
@@ -2070,7 +2103,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>1조 7896억 9978만</t>
+    <t>1조 9081억 8193만</t>
+  </si>
+  <si>
+    <t>흑인드록바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%EB%93%9C%EB%A1%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>1조 7974억 7119만</t>
+  </si>
+  <si>
+    <t>부산형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1조 6661억 9523만</t>
   </si>
   <si>
     <t>다있다하노</t>
@@ -2082,31 +2133,13 @@
     <t>1조 6567억 5333만</t>
   </si>
   <si>
-    <t>흑인드록바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%EB%93%9C%EB%A1%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>1조 6461억 9501만</t>
-  </si>
-  <si>
-    <t>부산형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1조 5727억 6555만</t>
-  </si>
-  <si>
     <t>밀가루죽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EA%B0%80%EB%A3%A8%EC%A3%BD</t>
   </si>
   <si>
-    <t>1조 5331억 3919만</t>
+    <t>1조 5984억 7872만</t>
   </si>
   <si>
     <t>전팡</t>
@@ -2115,7 +2148,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8C%A1</t>
   </si>
   <si>
-    <t>1조 4600억 3065만</t>
+    <t>1조 4766억 2667만</t>
+  </si>
+  <si>
+    <t>딴모</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
+  </si>
+  <si>
+    <t>1조 4155억 2267만</t>
+  </si>
+  <si>
+    <t>또유유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%9C%A0%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 3917억 5229만</t>
   </si>
   <si>
     <t>한콩순</t>
@@ -2124,25 +2175,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1조 3599억 7921만</t>
-  </si>
-  <si>
-    <t>딴모</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
-  </si>
-  <si>
-    <t>1조 3310억 8154만</t>
-  </si>
-  <si>
-    <t>또유유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%9C%A0%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 3270억 1963만</t>
+    <t>1조 3872억 8557만</t>
   </si>
   <si>
     <t>야로야옹</t>
@@ -2151,7 +2184,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
   </si>
   <si>
-    <t>1조 2825억 1493만</t>
+    <t>1조 3484억 3131만</t>
+  </si>
+  <si>
+    <t>사람님아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
+  </si>
+  <si>
+    <t>1조 1686억 8214만</t>
   </si>
   <si>
     <t>웅잉당</t>
@@ -2160,16 +2202,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>1조 1236억 5453만</t>
-  </si>
-  <si>
-    <t>사람님아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
-  </si>
-  <si>
-    <t>1조 747억 8318만</t>
+    <t>1조 1607억 9158만</t>
+  </si>
+  <si>
+    <t>비숍마로밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%A7%88%EB%A1%9C%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>1조 199억 4572만</t>
   </si>
   <si>
     <t>흑인햄찌</t>
@@ -2178,7 +2220,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
   </si>
   <si>
-    <t>9767억 3299만</t>
+    <t>1조 187억 7000만</t>
   </si>
   <si>
     <t>은둔형오덕후</t>
@@ -2187,16 +2229,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%91%94%ED%98%95%EC%98%A4%EB%8D%95%ED%9B%84</t>
   </si>
   <si>
-    <t>9327억 569만</t>
-  </si>
-  <si>
-    <t>비숍마로밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%A7%88%EB%A1%9C%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>8707억 3893만</t>
+    <t>1조 159억 8602만</t>
   </si>
   <si>
     <t>민초양갱</t>
@@ -2214,7 +2247,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
   </si>
   <si>
-    <t>7557억 6838만</t>
+    <t>8010억 6425만</t>
+  </si>
+  <si>
+    <t>에머슨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
+  </si>
+  <si>
+    <t>7979억 3286만</t>
+  </si>
+  <si>
+    <t>섀레기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>7635억 7468만</t>
   </si>
   <si>
     <t>존못에겐남짱</t>
@@ -2223,25 +2274,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
   </si>
   <si>
-    <t>7421억 7028만</t>
-  </si>
-  <si>
-    <t>에머슨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
-  </si>
-  <si>
-    <t>7230억 9647만</t>
-  </si>
-  <si>
-    <t>섀레기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>7221억 3070만</t>
+    <t>7434억 977만</t>
+  </si>
+  <si>
+    <t>뉴비i</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
+  </si>
+  <si>
+    <t>6349억 3895만</t>
+  </si>
+  <si>
+    <t>스피드노멘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
+  </si>
+  <si>
+    <t>6224억 6936만</t>
   </si>
   <si>
     <t>서울아우</t>
@@ -2253,24 +2304,6 @@
     <t>6115억 8271만</t>
   </si>
   <si>
-    <t>스피드노멘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
-  </si>
-  <si>
-    <t>6046억 7478만</t>
-  </si>
-  <si>
-    <t>뉴비i</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
-  </si>
-  <si>
-    <t>5555억 2487만</t>
-  </si>
-  <si>
     <t>두부장구니</t>
   </si>
   <si>
@@ -2286,7 +2319,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9E%84%EB%AA%BD%EC%88%9C</t>
   </si>
   <si>
-    <t>3446억 7297만</t>
+    <t>3988억 8503만</t>
   </si>
   <si>
     <t>오리박사</t>
@@ -2295,7 +2328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B0%95%EC%82%AC</t>
   </si>
   <si>
-    <t>3201억 9808만</t>
+    <t>3310억 3794만</t>
   </si>
 </sst>
 </file>
@@ -2779,19 +2812,17 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2799,36 +2830,38 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
@@ -2859,10 +2892,10 @@
         <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>47</v>
@@ -2901,7 +2934,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>55</v>
@@ -2939,7 +2972,7 @@
         <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -2977,13 +3010,13 @@
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>70</v>
@@ -3015,13 +3048,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
@@ -3528,13 +3560,13 @@
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3545,25 +3577,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>158</v>
@@ -3624,10 +3656,10 @@
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>167</v>
@@ -3659,7 +3691,7 @@
         <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>171</v>
@@ -3688,7 +3720,7 @@
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>122</v>
@@ -3720,10 +3752,10 @@
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>179</v>
@@ -3755,7 +3787,7 @@
         <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>183</v>
@@ -3787,7 +3819,7 @@
         <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>187</v>
@@ -3816,10 +3848,10 @@
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>191</v>
@@ -3848,10 +3880,10 @@
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>195</v>
@@ -3880,13 +3912,13 @@
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3897,25 +3929,25 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>204</v>
@@ -3944,7 +3976,7 @@
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>122</v>
@@ -3976,20 +4008,52 @@
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="J30" s="2" t="s">
+      <c r="H31" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4020,6 +4084,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4080,25 +4145,25 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>214</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>214</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4112,25 +4177,25 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4144,13 +4209,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -4159,10 +4224,10 @@
         <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4176,25 +4241,25 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4208,16 +4273,16 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>231</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>84</v>
@@ -4226,7 +4291,7 @@
         <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4240,25 +4305,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4272,13 +4337,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
@@ -4287,10 +4352,10 @@
         <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4304,25 +4369,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4336,25 +4401,25 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4368,25 +4433,25 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4400,25 +4465,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4432,25 +4497,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4464,13 +4529,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -4479,10 +4544,10 @@
         <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4496,25 +4561,25 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4528,25 +4593,25 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4557,28 +4622,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4592,25 +4657,25 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4624,25 +4689,25 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4656,25 +4721,25 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4688,25 +4753,25 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4720,13 +4785,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -4735,10 +4800,10 @@
         <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4752,25 +4817,25 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4784,13 +4849,13 @@
         <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -4799,10 +4864,10 @@
         <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4816,25 +4881,25 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>199</v>
+        <v>121</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4848,25 +4913,25 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4880,25 +4945,25 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4909,28 +4974,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4944,25 +5009,25 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4976,25 +5041,25 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5005,28 +5070,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>212</v>
+        <v>308</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5072,7 +5137,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5119,31 +5184,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>203</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>306</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5151,31 +5216,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5183,19 +5248,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -5204,10 +5269,10 @@
         <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5215,31 +5280,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5247,31 +5312,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>317</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>317</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5279,31 +5344,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5311,31 +5376,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5343,31 +5408,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5375,31 +5440,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5407,19 +5472,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -5428,10 +5493,10 @@
         <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5439,31 +5504,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5471,31 +5536,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5503,31 +5568,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5535,19 +5600,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -5556,10 +5621,10 @@
         <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5567,31 +5632,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5599,31 +5664,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5631,19 +5696,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -5652,10 +5717,10 @@
         <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5663,31 +5728,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5695,31 +5760,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5727,31 +5792,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5759,31 +5824,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5791,19 +5856,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -5812,10 +5877,10 @@
         <v>121</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5823,31 +5888,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5855,31 +5920,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5887,31 +5952,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5919,31 +5984,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5951,31 +6016,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5983,31 +6048,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>162</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6015,38 +6080,70 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>96</v>
+        <v>203</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6077,6 +6174,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6137,13 +6235,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -6152,10 +6250,10 @@
         <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>306</v>
+        <v>220</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>49</v>
@@ -6169,13 +6267,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -6184,10 +6282,10 @@
         <v>108</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>49</v>
@@ -6201,25 +6299,25 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>49</v>
@@ -6233,13 +6331,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -6251,7 +6349,7 @@
         <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>49</v>
@@ -6265,13 +6363,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -6283,7 +6381,7 @@
         <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>49</v>
@@ -6297,13 +6395,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -6315,7 +6413,7 @@
         <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>49</v>
@@ -6329,25 +6427,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>305</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>49</v>
@@ -6361,25 +6459,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>49</v>
@@ -6393,13 +6491,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -6411,7 +6509,7 @@
         <v>122</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>49</v>
@@ -6425,25 +6523,25 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>122</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>49</v>
@@ -6463,7 +6561,7 @@
         <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>83</v>
@@ -6475,7 +6573,7 @@
         <v>122</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>49</v>
@@ -6489,13 +6587,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -6504,10 +6602,10 @@
         <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -6521,13 +6619,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
@@ -6539,7 +6637,7 @@
         <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>49</v>
@@ -6553,13 +6651,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
@@ -6568,10 +6666,10 @@
         <v>108</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>49</v>
@@ -6585,13 +6683,13 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -6600,10 +6698,10 @@
         <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>49</v>
@@ -6614,28 +6712,28 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>49</v>
@@ -6649,25 +6747,25 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>49</v>
@@ -6681,25 +6779,25 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>49</v>
@@ -6713,13 +6811,13 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
@@ -6728,10 +6826,10 @@
         <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>49</v>
@@ -6745,25 +6843,25 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>49</v>
@@ -6777,13 +6875,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -6792,10 +6890,10 @@
         <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>49</v>
@@ -6809,13 +6907,13 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
@@ -6824,10 +6922,10 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>49</v>
@@ -6841,25 +6939,25 @@
         <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>49</v>
@@ -6873,13 +6971,13 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -6888,10 +6986,10 @@
         <v>131</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>49</v>
@@ -6905,13 +7003,13 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
@@ -6920,10 +7018,10 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>49</v>
@@ -6937,13 +7035,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -6952,10 +7050,10 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>49</v>
@@ -6966,16 +7064,16 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -6984,10 +7082,10 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>49</v>
@@ -7001,13 +7099,13 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -7016,10 +7114,10 @@
         <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>49</v>
@@ -7033,13 +7131,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -7048,10 +7146,10 @@
         <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>49</v>
@@ -7062,28 +7160,28 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>49</v>
@@ -7182,25 +7280,25 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>306</v>
+        <v>220</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7214,13 +7312,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -7232,7 +7330,7 @@
         <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7246,13 +7344,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -7261,10 +7359,10 @@
         <v>121</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7284,7 +7382,7 @@
         <v>57</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>83</v>
@@ -7296,7 +7394,7 @@
         <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7310,25 +7408,25 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7342,13 +7440,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
@@ -7357,10 +7455,10 @@
         <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7374,25 +7472,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7406,13 +7504,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -7424,7 +7522,7 @@
         <v>122</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7438,13 +7536,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -7453,10 +7551,10 @@
         <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7470,13 +7568,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -7485,10 +7583,10 @@
         <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7502,25 +7600,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7534,25 +7632,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7566,25 +7664,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>122</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7598,25 +7696,25 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7630,25 +7728,25 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7659,16 +7757,16 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
@@ -7677,10 +7775,10 @@
         <v>121</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7694,13 +7792,13 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
@@ -7709,10 +7807,10 @@
         <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7726,13 +7824,13 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -7741,10 +7839,10 @@
         <v>108</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7758,25 +7856,25 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7790,25 +7888,25 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>305</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7822,25 +7920,25 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7854,25 +7952,25 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7886,25 +7984,25 @@
         <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>305</v>
+        <v>131</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7918,13 +8016,13 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -7933,10 +8031,10 @@
         <v>121</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7950,25 +8048,25 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7982,13 +8080,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -7997,10 +8095,10 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8011,16 +8109,16 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
@@ -8029,10 +8127,10 @@
         <v>108</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8046,13 +8144,13 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -8061,10 +8159,10 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8078,13 +8176,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -8093,10 +8191,10 @@
         <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8107,16 +8205,16 @@
         <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -8125,10 +8223,10 @@
         <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8174,7 +8272,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -8227,13 +8325,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
@@ -8242,10 +8340,10 @@
         <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>306</v>
+        <v>583</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8259,13 +8357,13 @@
         <v>87</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>90</v>
@@ -8277,7 +8375,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8297,7 +8395,7 @@
         <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>83</v>
@@ -8309,7 +8407,7 @@
         <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8323,13 +8421,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -8341,7 +8439,7 @@
         <v>122</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8355,13 +8453,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -8373,7 +8471,7 @@
         <v>144</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8387,25 +8485,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8419,25 +8517,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8451,13 +8549,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -8466,10 +8564,10 @@
         <v>121</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8483,13 +8581,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -8498,10 +8596,10 @@
         <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8515,13 +8613,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -8530,10 +8628,10 @@
         <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8547,25 +8645,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8579,13 +8677,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -8594,10 +8692,10 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8611,25 +8709,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>212</v>
+        <v>478</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8643,25 +8741,25 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>471</v>
+        <v>216</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8675,13 +8773,13 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
@@ -8690,10 +8788,10 @@
         <v>108</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8704,28 +8802,28 @@
         <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8739,25 +8837,25 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8771,25 +8869,25 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8803,25 +8901,25 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>305</v>
+        <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8835,25 +8933,25 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8867,13 +8965,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -8882,10 +8980,10 @@
         <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>212</v>
+        <v>482</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8899,25 +8997,25 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>475</v>
+        <v>216</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8931,13 +9029,13 @@
         <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
@@ -8946,10 +9044,10 @@
         <v>102</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8963,13 +9061,13 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
@@ -8978,10 +9076,10 @@
         <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8995,25 +9093,25 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9027,13 +9125,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -9042,10 +9140,10 @@
         <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9056,28 +9154,28 @@
         <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>121</v>
+        <v>489</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>655</v>
+        <v>308</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9091,25 +9189,25 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9123,25 +9221,25 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>655</v>
+        <v>308</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9152,35 +9250,67 @@
         <v>58</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="I32" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J32"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -9212,6 +9342,7 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
+    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9272,25 +9403,25 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>49</v>
@@ -9310,7 +9441,7 @@
         <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
@@ -9319,10 +9450,10 @@
         <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>49</v>
@@ -9336,25 +9467,25 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>305</v>
+        <v>219</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>49</v>
@@ -9368,13 +9499,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>90</v>
@@ -9383,10 +9514,10 @@
         <v>121</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>49</v>
@@ -9400,13 +9531,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>90</v>
@@ -9415,10 +9546,10 @@
         <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>49</v>
@@ -9432,25 +9563,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>49</v>
@@ -9464,25 +9595,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>49</v>
@@ -9496,25 +9627,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>49</v>
@@ -9528,13 +9659,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>90</v>
@@ -9543,10 +9674,10 @@
         <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>49</v>
@@ -9560,13 +9691,13 @@
         <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>90</v>
@@ -9575,10 +9706,10 @@
         <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>49</v>
@@ -9592,25 +9723,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>471</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>49</v>
@@ -9624,13 +9755,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>90</v>
@@ -9639,10 +9770,10 @@
         <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>49</v>
@@ -9656,25 +9787,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>212</v>
+        <v>478</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>49</v>
@@ -9688,25 +9819,25 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>49</v>
@@ -9720,25 +9851,25 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>482</v>
+        <v>219</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>471</v>
+        <v>216</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>49</v>
@@ -9749,28 +9880,28 @@
         <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>305</v>
+        <v>489</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>212</v>
+        <v>478</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>49</v>
@@ -9784,25 +9915,25 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>49</v>
@@ -9816,25 +9947,25 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>471</v>
+        <v>162</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>49</v>
@@ -9848,25 +9979,25 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>305</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>212</v>
+        <v>478</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>49</v>
@@ -9880,13 +10011,13 @@
         <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>90</v>
@@ -9895,10 +10026,10 @@
         <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>49</v>
@@ -9912,13 +10043,13 @@
         <v>176</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>90</v>
@@ -9927,10 +10058,10 @@
         <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>49</v>
@@ -9944,25 +10075,25 @@
         <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>305</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>471</v>
+        <v>216</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>49</v>
@@ -9976,25 +10107,25 @@
         <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>49</v>
@@ -10008,25 +10139,25 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>49</v>
@@ -10040,25 +10171,25 @@
         <v>192</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>482</v>
+        <v>219</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>483</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>49</v>
@@ -10072,13 +10203,13 @@
         <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>90</v>
@@ -10087,10 +10218,10 @@
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>49</v>
@@ -10101,28 +10232,28 @@
         <v>65</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>305</v>
+        <v>489</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>212</v>
+        <v>482</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>49</v>
@@ -10136,13 +10267,13 @@
         <v>205</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>90</v>
@@ -10151,10 +10282,10 @@
         <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>49</v>
@@ -10168,13 +10299,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>90</v>
@@ -10183,10 +10314,10 @@
         <v>108</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>651</v>
+        <v>490</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>49</v>
@@ -10197,16 +10328,16 @@
         <v>65</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>300</v>
+        <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>90</v>
@@ -10215,10 +10346,10 @@
         <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>49</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -294,7 +294,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>26조 8075억 1513만</t>
+    <t>26조 9119억 7254만</t>
   </si>
   <si>
     <t>2</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 1815억 3519만</t>
+    <t>11조 2700억 9574만</t>
   </si>
   <si>
     <t>7</t>
@@ -444,7 +444,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>5조 3918억 8444만</t>
+    <t>5조 4012억 9996만</t>
   </si>
   <si>
     <t>12</t>
@@ -531,6 +531,18 @@
     <t>18</t>
   </si>
   <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>3조 7004억 1459만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>강철고튠데</t>
   </si>
   <si>
@@ -540,7 +552,7 @@
     <t>3조 6838억 5909만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -552,18 +564,6 @@
     <t>3조 5006억 2017만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>3조 3744억 7808만</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -1452,7 +1452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
   </si>
   <si>
-    <t>9393억 8181만</t>
+    <t>9867억 4666만</t>
   </si>
   <si>
     <t>한닝</t>
@@ -2079,6 +2079,15 @@
     <t>2조 5697억 511만</t>
   </si>
   <si>
+    <t>다있다하노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 639억 8631만</t>
+  </si>
+  <si>
     <t>꿍물</t>
   </si>
   <si>
@@ -2112,7 +2121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>1조 9304억 3968만</t>
+    <t>1조 9368억 4330만</t>
   </si>
   <si>
     <t>부산형님</t>
@@ -2124,15 +2133,6 @@
     <t>1조 7518억 9109만</t>
   </si>
   <si>
-    <t>다있다하노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
-  </si>
-  <si>
-    <t>1조 6567억 5333만</t>
-  </si>
-  <si>
     <t>밀가루죽</t>
   </si>
   <si>
@@ -2193,7 +2193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
   </si>
   <si>
-    <t>1조 2505억 1277만</t>
+    <t>1조 2728억 4415만</t>
   </si>
   <si>
     <t>웅잉당</t>
@@ -2241,6 +2241,15 @@
     <t>8442억 674만</t>
   </si>
   <si>
+    <t>존못에겐남짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>8418억 8268만</t>
+  </si>
+  <si>
     <t>민초양갱</t>
   </si>
   <si>
@@ -2266,15 +2275,6 @@
   </si>
   <si>
     <t>8104억 8651만</t>
-  </si>
-  <si>
-    <t>존못에겐남짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>7731억 4133만</t>
   </si>
   <si>
     <t>서울아우</t>
@@ -3656,7 +3656,7 @@
         <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>123</v>
@@ -3688,10 +3688,10 @@
         <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>172</v>
@@ -3723,7 +3723,7 @@
         <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>176</v>
@@ -9479,7 +9479,7 @@
         <v>91</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>158</v>
@@ -9511,10 +9511,10 @@
         <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>687</v>
@@ -9543,10 +9543,10 @@
         <v>91</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>690</v>
@@ -9575,10 +9575,10 @@
         <v>91</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>693</v>
@@ -9607,10 +9607,10 @@
         <v>91</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>696</v>
@@ -9639,7 +9639,7 @@
         <v>91</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>158</v>
@@ -10055,10 +10055,10 @@
         <v>91</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>738</v>
@@ -10087,10 +10087,10 @@
         <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>741</v>
@@ -10119,7 +10119,7 @@
         <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>217</v>
@@ -10151,7 +10151,7 @@
         <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>217</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">다다익선!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블랙소울!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블랙소울!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">초코나라!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="757">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,136 +84,136 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>13위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>207조 5902억 4049만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.04.24</t>
+  </si>
+  <si>
+    <t>다다익선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>232조 749억 1226만</t>
+  </si>
+  <si>
+    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>초코나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>9위</t>
+  </si>
+  <si>
+    <t>184조 9581억 307만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
+    <t>블랙소울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>205조 3800억 4104만</t>
+  </si>
+  <si>
+    <t>보심</t>
+  </si>
+  <si>
+    <t>비련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>215조 2154억 2346만</t>
+  </si>
+  <si>
+    <t>비련길드 모집조건 : 투력 5000억 이상 일일기부 300+ 길컨 참여자</t>
+  </si>
+  <si>
+    <t>렆프</t>
+  </si>
+  <si>
+    <t>밀크런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
+  </si>
+  <si>
     <t>383</t>
   </si>
   <si>
-    <t>13위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>205조 1988억 390만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.04.23</t>
-  </si>
-  <si>
-    <t>다다익선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8B%A4%EB%8B%A4%EC%9D%B5%EC%84%A0</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
-  </si>
-  <si>
-    <t>356</t>
-  </si>
-  <si>
-    <t>7위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>229조 6878억 6723만</t>
-  </si>
-  <si>
-    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>초코나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>406</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>183조 1413억 2665만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
-    <t>블랙소울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>392</t>
+    <t>31위</t>
   </si>
   <si>
     <t>29명</t>
   </si>
   <si>
-    <t>197조 3802억 1808만</t>
-  </si>
-  <si>
-    <t>보심</t>
-  </si>
-  <si>
-    <t>비련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>211조 4082억 2472만</t>
-  </si>
-  <si>
-    <t>비련길드 모집조건 : 투력 5000억 이상 일일기부 300+ 길컨 참여자</t>
-  </si>
-  <si>
-    <t>렆프</t>
-  </si>
-  <si>
-    <t>밀크런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>31위</t>
-  </si>
-  <si>
-    <t>207조 5226억 4350만</t>
+    <t>213조 3484억 8742만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요</t>
@@ -240,7 +240,7 @@
     <t>Lv.6</t>
   </si>
   <si>
-    <t>41조 107억 6648만</t>
+    <t>42조 495억 6258만</t>
   </si>
   <si>
     <t>*투력 2조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
@@ -324,25 +324,28 @@
     <t>다크나이트</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>18조 9253억 9203만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>18조 9253억 9203만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>13조 6857억 1215만</t>
+    <t>13조 9322억 7271만</t>
   </si>
   <si>
     <t>5</t>
@@ -357,9 +360,6 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>13조 2229억 5022만</t>
   </si>
   <si>
@@ -372,7 +372,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 9024억 8753만</t>
+    <t>11조 9918억 5094만</t>
   </si>
   <si>
     <t>7</t>
@@ -384,7 +384,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 3060억 3289만</t>
+    <t>7조 6289억 5284만</t>
   </si>
   <si>
     <t>8</t>
@@ -396,7 +396,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>6조 9166억 3772만</t>
+    <t>7조 551억 4048만</t>
   </si>
   <si>
     <t>9</t>
@@ -417,6 +417,21 @@
     <t>10</t>
   </si>
   <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 4404억 299만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>반도</t>
   </si>
   <si>
@@ -426,24 +441,9 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>6조 4098억 9503만</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>6조 3741억 1635만</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -465,12 +465,24 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 7743억 4977만</t>
+    <t>4조 9320억 5638만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>4조 4924억 651만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -483,18 +495,6 @@
     <t>4조 3985억 226만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>4조 3196억 9131만</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -504,7 +504,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>4조 203억 9184만</t>
+    <t>4조 253억 5355만</t>
   </si>
   <si>
     <t>17</t>
@@ -516,7 +516,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>3조 9403억 5517만</t>
+    <t>4조 51억 9443만</t>
   </si>
   <si>
     <t>18</t>
@@ -531,31 +531,31 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 8421억 7386만</t>
+    <t>3조 9719억 6394만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>3조 9234억 6313만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
   </si>
   <si>
-    <t>3조 8160억 9740만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>3조 6883억 4554만</t>
+    <t>3조 8330억 4982만</t>
   </si>
   <si>
     <t>21</t>
@@ -579,7 +579,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 1414억 4138만</t>
+    <t>3조 2913억 5806만</t>
   </si>
   <si>
     <t>23</t>
@@ -591,12 +591,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 8575억 4038만</t>
+    <t>2조 9098억 6694만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 7544억 4887만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>여븨</t>
   </si>
   <si>
@@ -606,7 +618,7 @@
     <t>2조 7026억 5570만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -618,7 +630,7 @@
     <t>2조 5587억 7219만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -633,7 +645,7 @@
     <t>2조 4292억 9347만</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -648,18 +660,6 @@
     <t>2조 3877억 7093만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2조 2116억 3503만</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 239억 9809만</t>
+    <t>2조 246억 6143만</t>
   </si>
   <si>
     <t>눈꽃물망초</t>
@@ -708,7 +708,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
   </si>
   <si>
-    <t>22조 6023억 9573만</t>
+    <t>24조 2321억 8274만</t>
   </si>
   <si>
     <t>뒁글</t>
@@ -723,7 +723,7 @@
     <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
   </si>
   <si>
-    <t>8조 3231억 2506만</t>
+    <t>8조 3374억 4650만</t>
   </si>
   <si>
     <t>공대애봉이</t>
@@ -732,7 +732,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>6조 2708억 2453만</t>
+    <t>6조 3554억 1327만</t>
   </si>
   <si>
     <t>언기</t>
@@ -750,7 +750,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>3조 5684억 3417만</t>
+    <t>3조 5995억 1775만</t>
+  </si>
+  <si>
+    <t>우타이테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
+  </si>
+  <si>
+    <t>3조 5482억 6503만</t>
   </si>
   <si>
     <t>토르릿</t>
@@ -762,15 +771,6 @@
     <t>3조 4904억 8991만</t>
   </si>
   <si>
-    <t>우타이테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
-  </si>
-  <si>
-    <t>3조 4542억 6996만</t>
-  </si>
-  <si>
     <t>따뜻한배추</t>
   </si>
   <si>
@@ -798,6 +798,24 @@
     <t>3조 308억 2909만</t>
   </si>
   <si>
+    <t>원투아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>3조 65억 3471만</t>
+  </si>
+  <si>
+    <t>옵션키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>2조 8191억 1235만</t>
+  </si>
+  <si>
     <t>샤생니임</t>
   </si>
   <si>
@@ -807,24 +825,6 @@
     <t>2조 8021억 3148만</t>
   </si>
   <si>
-    <t>원투아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 7880억 749만</t>
-  </si>
-  <si>
-    <t>옵션키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>2조 7530억 3443만</t>
-  </si>
-  <si>
     <t>웅쟈쓰</t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
   </si>
   <si>
-    <t>2조 527억 6719만</t>
+    <t>2조 1399억 5697만</t>
   </si>
   <si>
     <t>l우주아이l</t>
@@ -867,7 +867,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
   </si>
   <si>
-    <t>1조 9192억 4028만</t>
+    <t>1조 9211억 367만</t>
   </si>
   <si>
     <t>아쿠마불독</t>
@@ -876,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>1조 7442억 8437만</t>
+    <t>1조 7776억 1533만</t>
   </si>
   <si>
     <t>l성연l</t>
@@ -894,7 +894,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%ED%95%B4%EB%9D%BC</t>
   </si>
   <si>
-    <t>1조 5841억 9742만</t>
+    <t>1조 6250억 1694만</t>
   </si>
   <si>
     <t>몽실망실토실</t>
@@ -930,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
   </si>
   <si>
-    <t>9757억 5246만</t>
+    <t>1조 558억 316만</t>
   </si>
   <si>
     <t>체시어</t>
@@ -939,7 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
   </si>
   <si>
-    <t>7491억 9634만</t>
+    <t>7546억 603만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -957,7 +957,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>61조 5327억 4675만</t>
+    <t>61조 9021억 3304만</t>
   </si>
   <si>
     <t>멈디</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
   </si>
   <si>
-    <t>8조 8226억 6552만</t>
+    <t>9조 731억 3944만</t>
   </si>
   <si>
     <t>유랑민</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
   </si>
   <si>
-    <t>8조 2650억 6376만</t>
+    <t>8조 2861억 3144만</t>
   </si>
   <si>
     <t>사숩</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
   </si>
   <si>
-    <t>6조 9189억 8881만</t>
+    <t>6조 9212억 9274만</t>
   </si>
   <si>
     <t>포도맛맥플</t>
@@ -993,7 +993,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
   </si>
   <si>
-    <t>6조 7040억 3156만</t>
+    <t>6조 7242억 9747만</t>
   </si>
   <si>
     <t>단비둘기</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>5조 3329억 3711만</t>
+    <t>5조 3443억 5362만</t>
   </si>
   <si>
     <t>또긔</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
   </si>
   <si>
-    <t>5조 1956억 8667만</t>
+    <t>5조 2247억 7862만</t>
   </si>
   <si>
     <t>김롸아</t>
@@ -1032,6 +1032,15 @@
     <t>4조 9484억 9382만</t>
   </si>
   <si>
+    <t>스라차차소스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4조 8288억 9135만</t>
+  </si>
+  <si>
     <t>limno</t>
   </si>
   <si>
@@ -1041,13 +1050,13 @@
     <t>4조 8032억 5155만</t>
   </si>
   <si>
-    <t>스라차차소스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>4조 7531억 1742만</t>
+    <t>썬콜법사도희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>4조 7497억 1387만</t>
   </si>
   <si>
     <t>까만색양갱</t>
@@ -1056,16 +1065,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
   </si>
   <si>
-    <t>4조 6105억 6232만</t>
-  </si>
-  <si>
-    <t>썬콜법사도희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>4조 4948억 2437만</t>
+    <t>4조 6798억 6076만</t>
+  </si>
+  <si>
+    <t>우치앵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
+  </si>
+  <si>
+    <t>4조 4852억 9083만</t>
+  </si>
+  <si>
+    <t>A7R4</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
+  </si>
+  <si>
+    <t>4조 4816억 9310만</t>
   </si>
   <si>
     <t>린샹판</t>
@@ -1074,25 +1092,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
   </si>
   <si>
-    <t>4조 4621억 2747만</t>
-  </si>
-  <si>
-    <t>우치앵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
-  </si>
-  <si>
-    <t>4조 4481억 7475만</t>
-  </si>
-  <si>
-    <t>A7R4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
-  </si>
-  <si>
-    <t>4조 3112억 1382만</t>
+    <t>4조 4684억 3530만</t>
   </si>
   <si>
     <t>불곰파워</t>
@@ -1110,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
   </si>
   <si>
-    <t>3조 7328억 8158만</t>
+    <t>3조 7462억 3938만</t>
   </si>
   <si>
     <t>히어로경원</t>
@@ -1131,22 +1131,22 @@
     <t>3조 5138억 8631만</t>
   </si>
   <si>
+    <t>썹웨피망빼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
+  </si>
+  <si>
+    <t>3조 4902억 2435만</t>
+  </si>
+  <si>
     <t>투둠</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
   </si>
   <si>
-    <t>3조 3125억 4975만</t>
-  </si>
-  <si>
-    <t>썹웨피망빼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
-  </si>
-  <si>
-    <t>3조 2535억 7607만</t>
+    <t>3조 3481억 2261만</t>
   </si>
   <si>
     <t>무쿠미</t>
@@ -1158,6 +1158,15 @@
     <t>3조 982억 7937만</t>
   </si>
   <si>
+    <t>도윤파덜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
+  </si>
+  <si>
+    <t>3조 425억 7859만</t>
+  </si>
+  <si>
     <t>zl지존썬콜lz</t>
   </si>
   <si>
@@ -1176,22 +1185,13 @@
     <t>2조 8720억 7370만</t>
   </si>
   <si>
-    <t>도윤파덜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
-  </si>
-  <si>
-    <t>2조 8297억 5007만</t>
-  </si>
-  <si>
     <t>구파발고양이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 7654억 1555만</t>
+    <t>2조 7824억 1307만</t>
   </si>
   <si>
     <t>극쪽이</t>
@@ -1200,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 4809억 5088만</t>
+    <t>1조 4836억 6380만</t>
   </si>
   <si>
     <t>토리파더</t>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>7569억 4282만</t>
+    <t>7631억 8989만</t>
   </si>
   <si>
     <t>닼나왕</t>
@@ -1230,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
   </si>
   <si>
-    <t>61조 8137억 6645만</t>
+    <t>66조 1808억 8271만</t>
   </si>
   <si>
     <t>말랑콩닥</t>
@@ -1239,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
   </si>
   <si>
-    <t>21조 7720억 8769만</t>
+    <t>21조 8736억 4851만</t>
   </si>
   <si>
     <t>안루핑</t>
@@ -1248,7 +1248,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A3%A8%ED%95%91</t>
   </si>
   <si>
-    <t>18조 719억 4159만</t>
+    <t>18조 1491억 4830만</t>
   </si>
   <si>
     <t>귀심</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
   </si>
   <si>
-    <t>8조 1211억 4054만</t>
+    <t>8조 1725억 8355만</t>
   </si>
   <si>
     <t>루나스틱</t>
@@ -1320,7 +1320,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EB%B9%84%ED%94%BC</t>
   </si>
   <si>
-    <t>5조 8291억 6750만</t>
+    <t>5조 8405억 3727만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
   </si>
   <si>
-    <t>3조 7162억 9263만</t>
+    <t>3조 8327억 2483만</t>
   </si>
   <si>
     <t>용감한순대국</t>
@@ -1344,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
   </si>
   <si>
-    <t>2조 7334억 3590만</t>
+    <t>2조 9002억 4344만</t>
   </si>
   <si>
     <t>별밖에</t>
@@ -1353,7 +1353,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
   </si>
   <si>
-    <t>2조 6844억 3894만</t>
+    <t>2조 8075억 5141만</t>
+  </si>
+  <si>
+    <t>곱션이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EC%85%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 5677억 5836만</t>
   </si>
   <si>
     <t>양념반탈리반</t>
@@ -1371,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EB%91%98%EC%95%84%EB%B2%94</t>
   </si>
   <si>
-    <t>2조 3367억 3094만</t>
+    <t>2조 3721억 7391만</t>
   </si>
   <si>
     <t>박예쁜</t>
@@ -1380,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
   </si>
   <si>
-    <t>1조 9897억 2989만</t>
+    <t>2조 1139억 4649만</t>
   </si>
   <si>
     <t>판별식</t>
@@ -1416,28 +1425,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
   </si>
   <si>
+    <t>1조 5829억 9952만</t>
+  </si>
+  <si>
+    <t>루맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 5332억 241만</t>
+  </si>
+  <si>
+    <t>츄쁜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
+  </si>
+  <si>
+    <t>1조 424억 2465만</t>
+  </si>
+  <si>
+    <t>박마리아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
+  </si>
+  <si>
     <t>96</t>
   </si>
   <si>
-    <t>1조 5502억 9779만</t>
-  </si>
-  <si>
-    <t>루맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 5332억 241만</t>
-  </si>
-  <si>
-    <t>츄쁜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
-  </si>
-  <si>
-    <t>1조 414억 7183만</t>
+    <t>9457억 4652만</t>
   </si>
   <si>
     <t>한닝</t>
@@ -1446,16 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
   </si>
   <si>
-    <t>8643억 1943만</t>
-  </si>
-  <si>
-    <t>박마리아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
-  </si>
-  <si>
-    <t>7966억 4793만</t>
+    <t>9249억 7350만</t>
   </si>
   <si>
     <t>뮴뮴뮴뮴뮴</t>
@@ -1464,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4</t>
   </si>
   <si>
-    <t>6633억 9663만</t>
+    <t>6645억 6390만</t>
   </si>
   <si>
     <t>놀면머하니</t>
@@ -1488,7 +1497,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>3789억 6305만</t>
+    <t>3917억 4482만</t>
   </si>
   <si>
     <t>량용</t>
@@ -1500,7 +1509,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>67조 3308억 4555만</t>
+    <t>67조 6801억 2693만</t>
   </si>
   <si>
     <t>달봉e</t>
@@ -1518,7 +1527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%82%98%EB%94%94%EB%8F%84%EB%91%91</t>
   </si>
   <si>
-    <t>11조 4444억 3158만</t>
+    <t>12조 875억 7214만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%86%ED%94%84</t>
@@ -1533,7 +1542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%98%81%ED%98%842</t>
   </si>
   <si>
-    <t>7조 5596억 9835만</t>
+    <t>7조 9593억 2402만</t>
   </si>
   <si>
     <t>정신못차림</t>
@@ -1542,7 +1551,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>5조 8802억 236만</t>
+    <t>6조 93억 3774만</t>
+  </si>
+  <si>
+    <t>핫딜패스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%ED%8C%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4조 6737억 2415만</t>
   </si>
   <si>
     <t>캔터베리</t>
@@ -1554,15 +1572,6 @@
     <t>4조 5801억 8016만</t>
   </si>
   <si>
-    <t>핫딜패스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%ED%8C%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>4조 4029억 484만</t>
-  </si>
-  <si>
     <t>안경나라</t>
   </si>
   <si>
@@ -1572,6 +1581,15 @@
     <t>4조 3133억 5612만</t>
   </si>
   <si>
+    <t>하콩치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%BD%A9%EC%B9%98</t>
+  </si>
+  <si>
+    <t>3조 7615억 6767만</t>
+  </si>
+  <si>
     <t>햐밍</t>
   </si>
   <si>
@@ -1587,7 +1605,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%ED%94%8C%EC%8A%A4%ED%85%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 5898억 1670만</t>
+    <t>3조 6102억 4835만</t>
   </si>
   <si>
     <t>빅밥</t>
@@ -1596,7 +1614,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
   </si>
   <si>
-    <t>3조 4976억 3713만</t>
+    <t>3조 5574억 9485만</t>
   </si>
   <si>
     <t>하눌이야</t>
@@ -1605,16 +1623,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%88%8C%EC%9D%B4%EC%95%BC</t>
   </si>
   <si>
-    <t>3조 1870억 3355만</t>
-  </si>
-  <si>
-    <t>하콩치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%BD%A9%EC%B9%98</t>
-  </si>
-  <si>
-    <t>2조 8008억 1429만</t>
+    <t>3조 2348억 7561만</t>
   </si>
   <si>
     <t>Scope</t>
@@ -1626,13 +1635,22 @@
     <t>2조 7096억 2142만</t>
   </si>
   <si>
+    <t>아무렇게할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AC%B4%EB%A0%87%EA%B2%8C%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>2조 6557억 4207만</t>
+  </si>
+  <si>
     <t>산로지노</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 1756억 8741만</t>
+    <t>2조 2038억 9802만</t>
   </si>
   <si>
     <t>리디엘</t>
@@ -1641,16 +1659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%94%94%EC%97%98</t>
   </si>
   <si>
-    <t>2조 554억 2622만</t>
-  </si>
-  <si>
-    <t>아무렇게할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AC%B4%EB%A0%87%EA%B2%8C%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>2조 351억 8824만</t>
+    <t>2조 982억 6070만</t>
   </si>
   <si>
     <t>별잇</t>
@@ -1668,7 +1677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 7613억 6203만</t>
+    <t>1조 8053억 9608만</t>
   </si>
   <si>
     <t>떠하야</t>
@@ -1686,7 +1695,7 @@
     <t>https://mgf.gg/contents/character.php?n=Azham</t>
   </si>
   <si>
-    <t>1조 4912억 2288만</t>
+    <t>1조 5399억 8510만</t>
   </si>
   <si>
     <t>이즈뤼얼</t>
@@ -1695,7 +1704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A6%88%EB%A4%BC%EC%96%BC</t>
   </si>
   <si>
-    <t>1조 3821억 3424만</t>
+    <t>1조 4109억 293만</t>
   </si>
   <si>
     <t>Porto</t>
@@ -1704,7 +1713,7 @@
     <t>https://mgf.gg/contents/character.php?n=Porto</t>
   </si>
   <si>
-    <t>1조 2756억 9524만</t>
+    <t>1조 3279억 5327만</t>
   </si>
   <si>
     <t>비라비스</t>
@@ -1713,7 +1722,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%9D%BC%EB%B9%84%EC%8A%A4</t>
   </si>
   <si>
-    <t>1조 1351억 189만</t>
+    <t>1조 1710억 5246만</t>
   </si>
   <si>
     <t>호빵현</t>
@@ -1722,7 +1731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%B9%B5%ED%98%84</t>
   </si>
   <si>
-    <t>9083억 3727만</t>
+    <t>9096억 5200만</t>
   </si>
   <si>
     <t>후려까기</t>
@@ -1731,7 +1740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%A0%A4%EA%B9%8C%EA%B8%B0</t>
   </si>
   <si>
-    <t>8547억 3259만</t>
+    <t>8636억 9674만</t>
   </si>
   <si>
     <t>쥐이에이</t>
@@ -1740,7 +1749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>8312억 1915만</t>
+    <t>8338억 8982만</t>
   </si>
   <si>
     <t>짜뇨</t>
@@ -1749,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%87%A8</t>
   </si>
   <si>
-    <t>5851억 104만</t>
+    <t>5962억 6625만</t>
   </si>
   <si>
     <t>뽀미l</t>
@@ -1758,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
   </si>
   <si>
-    <t>5716억 4463만</t>
+    <t>5724억 6904만</t>
   </si>
   <si>
     <t>동띠</t>
@@ -1782,7 +1791,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EB%8C%80</t>
   </si>
   <si>
-    <t>16조 4610억 1635만</t>
+    <t>20조 9250억 1712만</t>
   </si>
   <si>
     <t>원남</t>
@@ -1791,7 +1800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
   </si>
   <si>
-    <t>5조 4653억 4085만</t>
+    <t>6조 3037억 7810만</t>
   </si>
   <si>
     <t>숍솝</t>
@@ -1818,7 +1827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%BD%80</t>
   </si>
   <si>
-    <t>2조 9912억 3084만</t>
+    <t>3조 2368억 1696만</t>
   </si>
   <si>
     <t>단정이</t>
@@ -1827,7 +1836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8282억 1196만</t>
+    <t>1조 8308억 3230만</t>
   </si>
   <si>
     <t>지구뿌셔</t>
@@ -1836,7 +1845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>1조 7300억 4517만</t>
+    <t>1조 7531억 9060만</t>
   </si>
   <si>
     <t>꼬햄</t>
@@ -1854,7 +1863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%9B</t>
   </si>
   <si>
-    <t>1조 952억 205만</t>
+    <t>1조 988억 4836만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1863,7 +1872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
   </si>
   <si>
-    <t>8633억 7335만</t>
+    <t>8968억 7516만</t>
   </si>
   <si>
     <t>자쿰키우기</t>
@@ -1875,7 +1884,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>8050억 4960만</t>
+    <t>8415억 3336만</t>
   </si>
   <si>
     <t>갓굴</t>
@@ -1884,7 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
   </si>
   <si>
-    <t>7004억 8105만</t>
+    <t>7178억 6669만</t>
   </si>
   <si>
     <t>귀쮸</t>
@@ -1893,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
   </si>
   <si>
-    <t>5709억 6195만</t>
+    <t>5776억 6573만</t>
   </si>
   <si>
     <t>당겨쏴</t>
@@ -1902,7 +1911,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B2%A8%EC%8F%B4</t>
   </si>
   <si>
-    <t>5363억 5128만</t>
+    <t>5767억 1756만</t>
+  </si>
+  <si>
+    <t>은단월</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
+  </si>
+  <si>
+    <t>5148억 4658만</t>
   </si>
   <si>
     <t>Viceversa</t>
@@ -1911,7 +1929,7 @@
     <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
   </si>
   <si>
-    <t>4925억 967만</t>
+    <t>5062억 9151만</t>
   </si>
   <si>
     <t>알뺘노</t>
@@ -1923,13 +1941,13 @@
     <t>4920억 9616만</t>
   </si>
   <si>
-    <t>은단월</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
-  </si>
-  <si>
-    <t>4768억 6045만</t>
+    <t>비비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>4455억 4351만</t>
   </si>
   <si>
     <t>투냉</t>
@@ -1941,22 +1959,22 @@
     <t>4367억 2276만</t>
   </si>
   <si>
-    <t>비비다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>4205억 2494만</t>
-  </si>
-  <si>
     <t>진1용</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%841%EC%9A%A9</t>
   </si>
   <si>
-    <t>3571억 6142만</t>
+    <t>3638억 9246만</t>
+  </si>
+  <si>
+    <t>차눅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
+  </si>
+  <si>
+    <t>3359억 9618만</t>
   </si>
   <si>
     <t>사과클럽</t>
@@ -1965,16 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
   </si>
   <si>
-    <t>3285억 6079만</t>
-  </si>
-  <si>
-    <t>차눅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
-  </si>
-  <si>
-    <t>3232억 3558만</t>
+    <t>3322억 6101만</t>
   </si>
   <si>
     <t>팔나무</t>
@@ -2004,7 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%A7%84%ED%98%84</t>
   </si>
   <si>
-    <t>1542억 4222만</t>
+    <t>1551억 9576만</t>
   </si>
   <si>
     <t>나루토토</t>
@@ -2013,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%A3%A8%ED%86%A0%ED%86%A0</t>
   </si>
   <si>
-    <t>1338억 8472만</t>
+    <t>1411억 7436만</t>
   </si>
   <si>
     <t>길지녁</t>
@@ -2022,7 +2031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%A7%80%EB%85%81</t>
   </si>
   <si>
-    <t>1159억 5658만</t>
+    <t>1204억 986만</t>
   </si>
   <si>
     <t>아포짓</t>
@@ -2037,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=86%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>2조 6514억 1854만</t>
+    <t>2조 8543억 3630만</t>
   </si>
   <si>
     <t>꿍물</t>
@@ -2046,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%8D%EB%AC%BC</t>
   </si>
   <si>
-    <t>2조 1329억 2620만</t>
+    <t>2조 2085억 8783만</t>
   </si>
   <si>
     <t>끽스</t>
@@ -2055,7 +2064,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
   </si>
   <si>
-    <t>2조 726억 707만</t>
+    <t>2조 1020억 7884만</t>
+  </si>
+  <si>
+    <t>부산형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>2조 669억 2668만</t>
   </si>
   <si>
     <t>다있다하노</t>
@@ -2067,22 +2085,13 @@
     <t>2조 639억 8631만</t>
   </si>
   <si>
-    <t>부산형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>2조 379억 964만</t>
-  </si>
-  <si>
     <t>델타시그마</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>2조 287억 4104만</t>
+    <t>2조 499억 1970만</t>
   </si>
   <si>
     <t>흑인드록바</t>
@@ -2100,7 +2109,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8C%A1</t>
   </si>
   <si>
-    <t>1조 7375억 2724만</t>
+    <t>1조 7702억 2214만</t>
   </si>
   <si>
     <t>밀가루죽</t>
@@ -2109,7 +2118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EA%B0%80%EB%A3%A8%EC%A3%BD</t>
   </si>
   <si>
-    <t>1조 6177억 4021만</t>
+    <t>1조 7380억 2779만</t>
   </si>
   <si>
     <t>한콩순</t>
@@ -2118,7 +2127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1조 5893억 6350만</t>
+    <t>1조 6190억 485만</t>
   </si>
   <si>
     <t>딴모</t>
@@ -2127,7 +2136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
   </si>
   <si>
-    <t>1조 5030억 8793만</t>
+    <t>1조 5319억 7630만</t>
   </si>
   <si>
     <t>또유유</t>
@@ -2136,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%9C%A0%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 4029억 8791만</t>
+    <t>1조 4531억 4364만</t>
   </si>
   <si>
     <t>야로야옹</t>
@@ -2145,7 +2154,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
   </si>
   <si>
-    <t>1조 3484억 3131만</t>
+    <t>1조 4507억 6254만</t>
+  </si>
+  <si>
+    <t>웅잉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>1조 3449억 2728만</t>
   </si>
   <si>
     <t>사람님아</t>
@@ -2154,16 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
   </si>
   <si>
-    <t>1조 2728억 4415만</t>
-  </si>
-  <si>
-    <t>웅잉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>1조 2270억 4040만</t>
+    <t>1조 2937억 8613만</t>
   </si>
   <si>
     <t>비숍마로밍</t>
@@ -2181,7 +2190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
   </si>
   <si>
-    <t>1조 814억 8825만</t>
+    <t>1조 1007억 6481만</t>
   </si>
   <si>
     <t>은둔형오덕후</t>
@@ -2190,7 +2199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%91%94%ED%98%95%EC%98%A4%EB%8D%95%ED%9B%84</t>
   </si>
   <si>
-    <t>1조 416억 9919만</t>
+    <t>1조 925억 1378만</t>
   </si>
   <si>
     <t>하랸</t>
@@ -2199,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
   </si>
   <si>
-    <t>9190억 883만</t>
+    <t>9218억 3384만</t>
   </si>
   <si>
     <t>에머슨</t>
@@ -2208,7 +2217,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
   </si>
   <si>
-    <t>8422억 2034만</t>
+    <t>8697억 5673만</t>
+  </si>
+  <si>
+    <t>민초양갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%B4%88%EC%96%91%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>8468억 6271만</t>
   </si>
   <si>
     <t>존못에겐남짱</t>
@@ -2220,22 +2238,13 @@
     <t>8418억 8268만</t>
   </si>
   <si>
-    <t>민초양갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%B4%88%EC%96%91%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>8285억 4067만</t>
-  </si>
-  <si>
     <t>섀레기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
   </si>
   <si>
-    <t>8250억 2411만</t>
+    <t>8383억 4352만</t>
   </si>
   <si>
     <t>서울아우</t>
@@ -2253,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
   </si>
   <si>
-    <t>6990억 5835만</t>
+    <t>7118억 4351만</t>
   </si>
   <si>
     <t>뉴비i</t>
@@ -2271,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B6%80%EC%9E%A5%EA%B5%AC%EB%8B%88</t>
   </si>
   <si>
-    <t>4628억 4330만</t>
+    <t>4789억 8706만</t>
   </si>
   <si>
     <t>아임몽순</t>
@@ -2283,7 +2292,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>4363억 4675만</t>
+    <t>4530억 4502만</t>
   </si>
   <si>
     <t>오리박사</t>
@@ -2859,14 +2868,14 @@
         <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2874,25 +2883,25 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2901,13 +2910,13 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2915,31 +2924,31 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>60</v>
@@ -3175,10 +3184,10 @@
         <v>102</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3189,25 +3198,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>109</v>
@@ -3271,7 +3280,7 @@
         <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>117</v>
@@ -3303,7 +3312,7 @@
         <v>102</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>121</v>
@@ -3335,7 +3344,7 @@
         <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>126</v>
@@ -3364,13 +3373,13 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3381,25 +3390,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>136</v>
@@ -3431,7 +3440,7 @@
         <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>140</v>
@@ -3463,7 +3472,7 @@
         <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>144</v>
@@ -3492,13 +3501,13 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3509,25 +3518,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>153</v>
@@ -3559,7 +3568,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>157</v>
@@ -3591,7 +3600,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>161</v>
@@ -3652,10 +3661,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>170</v>
@@ -3684,10 +3693,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>174</v>
@@ -3716,10 +3725,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>178</v>
@@ -3751,7 +3760,7 @@
         <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>182</v>
@@ -3783,7 +3792,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>186</v>
@@ -3812,10 +3821,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>190</v>
@@ -3844,10 +3853,10 @@
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>194</v>
@@ -3876,13 +3885,13 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3893,28 +3902,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="H28" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3925,25 +3934,25 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>208</v>
@@ -4007,7 +4016,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>216</v>
@@ -4121,7 +4130,7 @@
         <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>91</v>
@@ -4156,7 +4165,7 @@
         <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>222</v>
@@ -4188,7 +4197,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>225</v>
@@ -4220,7 +4229,7 @@
         <v>125</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>228</v>
@@ -4234,7 +4243,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>33</v>
@@ -4252,7 +4261,7 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>230</v>
@@ -4284,7 +4293,7 @@
         <v>125</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>233</v>
@@ -4316,7 +4325,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>236</v>
@@ -4348,7 +4357,7 @@
         <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>239</v>
@@ -4377,10 +4386,10 @@
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>242</v>
@@ -4409,10 +4418,10 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>245</v>
@@ -4426,7 +4435,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>246</v>
@@ -4441,10 +4450,10 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>248</v>
@@ -4476,7 +4485,7 @@
         <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>251</v>
@@ -4505,7 +4514,7 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>165</v>
@@ -4537,10 +4546,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>257</v>
@@ -4554,7 +4563,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>258</v>
@@ -4569,7 +4578,7 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>165</v>
@@ -4601,10 +4610,10 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>263</v>
@@ -4636,7 +4645,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>266</v>
@@ -4668,7 +4677,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>269</v>
@@ -4700,7 +4709,7 @@
         <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>272</v>
@@ -4764,7 +4773,7 @@
         <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>278</v>
@@ -4860,7 +4869,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>287</v>
@@ -4889,7 +4898,7 @@
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>165</v>
@@ -4924,7 +4933,7 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>293</v>
@@ -4938,7 +4947,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>294</v>
@@ -4970,7 +4979,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>297</v>
@@ -4985,10 +4994,10 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
@@ -5017,10 +5026,10 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>302</v>
@@ -5052,7 +5061,7 @@
         <v>125</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>305</v>
@@ -5201,7 +5210,7 @@
         <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>311</v>
@@ -5265,7 +5274,7 @@
         <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>317</v>
@@ -5279,7 +5288,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>318</v>
@@ -5297,7 +5306,7 @@
         <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>320</v>
@@ -5329,7 +5338,7 @@
         <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>323</v>
@@ -5361,7 +5370,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>326</v>
@@ -5390,10 +5399,10 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>329</v>
@@ -5425,7 +5434,7 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>332</v>
@@ -5457,7 +5466,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>335</v>
@@ -5471,7 +5480,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>336</v>
@@ -5489,7 +5498,7 @@
         <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>338</v>
@@ -5518,10 +5527,10 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>341</v>
@@ -5550,10 +5559,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>344</v>
@@ -5582,10 +5591,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>347</v>
@@ -5599,7 +5608,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>348</v>
@@ -5617,7 +5626,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>350</v>
@@ -5646,10 +5655,10 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>353</v>
@@ -5681,7 +5690,7 @@
         <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>356</v>
@@ -5713,7 +5722,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>359</v>
@@ -5745,7 +5754,7 @@
         <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>362</v>
@@ -5777,7 +5786,7 @@
         <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>365</v>
@@ -5806,10 +5815,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>368</v>
@@ -5838,10 +5847,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>371</v>
@@ -5873,7 +5882,7 @@
         <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>374</v>
@@ -5902,10 +5911,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>377</v>
@@ -5937,7 +5946,7 @@
         <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>380</v>
@@ -5966,10 +5975,10 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>383</v>
@@ -5983,7 +5992,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>384</v>
@@ -6001,7 +6010,7 @@
         <v>102</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>386</v>
@@ -6015,7 +6024,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>387</v>
@@ -6062,10 +6071,10 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>392</v>
@@ -6146,7 +6155,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6246,7 +6255,7 @@
         <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>402</v>
@@ -6278,7 +6287,7 @@
         <v>307</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>405</v>
@@ -6310,7 +6319,7 @@
         <v>96</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>408</v>
@@ -6324,7 +6333,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>409</v>
@@ -6342,7 +6351,7 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>411</v>
@@ -6374,7 +6383,7 @@
         <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>414</v>
@@ -6406,7 +6415,7 @@
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>417</v>
@@ -6438,7 +6447,7 @@
         <v>307</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>420</v>
@@ -6470,7 +6479,7 @@
         <v>307</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>423</v>
@@ -6502,7 +6511,7 @@
         <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>426</v>
@@ -6516,7 +6525,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>427</v>
@@ -6534,7 +6543,7 @@
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>429</v>
@@ -6551,10 +6560,10 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>430</v>
@@ -6566,7 +6575,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>431</v>
@@ -6598,7 +6607,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>434</v>
@@ -6630,7 +6639,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>437</v>
@@ -6644,7 +6653,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>438</v>
@@ -6662,7 +6671,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>440</v>
@@ -6691,10 +6700,10 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>443</v>
@@ -6723,10 +6732,10 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>307</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>446</v>
@@ -6755,7 +6764,7 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>165</v>
@@ -6787,10 +6796,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>452</v>
@@ -6819,7 +6828,7 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>165</v>
@@ -6851,7 +6860,7 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>165</v>
@@ -6883,13 +6892,13 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6903,25 +6912,25 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6935,25 +6944,25 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6967,25 +6976,25 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6999,13 +7008,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -7014,7 +7023,7 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>474</v>
@@ -7028,7 +7037,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>475</v>
@@ -7043,10 +7052,10 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>477</v>
@@ -7060,7 +7069,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>478</v>
@@ -7078,10 +7087,10 @@
         <v>125</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7095,32 +7104,64 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7151,6 +7192,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7205,19 +7247,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
@@ -7226,10 +7268,10 @@
         <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7237,19 +7279,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
@@ -7261,7 +7303,7 @@
         <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7269,19 +7311,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
@@ -7290,10 +7332,10 @@
         <v>125</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7301,19 +7343,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7322,10 +7364,10 @@
         <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7333,31 +7375,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7365,19 +7407,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -7386,10 +7428,10 @@
         <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7397,31 +7439,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>307</v>
+        <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7429,31 +7471,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7461,19 +7503,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -7482,10 +7524,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7493,31 +7535,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7525,31 +7567,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7557,31 +7599,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7589,31 +7631,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7621,19 +7663,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
@@ -7642,10 +7684,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7653,19 +7695,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -7674,10 +7716,10 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7685,31 +7727,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7717,31 +7759,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7749,19 +7791,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -7773,7 +7815,7 @@
         <v>165</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7781,19 +7823,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
@@ -7805,7 +7847,7 @@
         <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7813,19 +7855,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
@@ -7837,7 +7879,7 @@
         <v>165</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7845,19 +7887,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
@@ -7869,7 +7911,7 @@
         <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7877,19 +7919,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
@@ -7898,10 +7940,10 @@
         <v>307</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7909,31 +7951,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7941,19 +7983,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
@@ -7962,10 +8004,10 @@
         <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7973,19 +8015,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
@@ -7994,10 +8036,10 @@
         <v>307</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8005,19 +8047,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -8026,10 +8068,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8037,19 +8079,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -8058,10 +8100,10 @@
         <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8069,19 +8111,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
@@ -8093,7 +8135,7 @@
         <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8101,19 +8143,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
@@ -8122,10 +8164,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8133,19 +8175,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
@@ -8154,10 +8196,10 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8250,19 +8292,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
@@ -8271,10 +8313,10 @@
         <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8282,19 +8324,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
@@ -8303,10 +8345,10 @@
         <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8314,7 +8356,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
@@ -8326,7 +8368,7 @@
         <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8335,10 +8377,10 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8346,19 +8388,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
@@ -8367,10 +8409,10 @@
         <v>125</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8378,19 +8420,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
@@ -8399,10 +8441,10 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8410,31 +8452,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8442,19 +8484,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
@@ -8463,10 +8505,10 @@
         <v>307</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8474,19 +8516,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
@@ -8498,7 +8540,7 @@
         <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8506,19 +8548,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -8527,10 +8569,10 @@
         <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8538,19 +8580,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
@@ -8559,10 +8601,10 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>461</v>
+        <v>207</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8570,19 +8612,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
@@ -8594,7 +8636,7 @@
         <v>165</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8602,19 +8644,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
@@ -8623,10 +8665,10 @@
         <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8634,19 +8676,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
@@ -8655,10 +8697,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8666,19 +8708,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
@@ -8687,10 +8729,10 @@
         <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>461</v>
+        <v>207</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8698,19 +8740,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -8719,10 +8761,10 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8730,19 +8772,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
@@ -8751,10 +8793,10 @@
         <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>480</v>
+        <v>616</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8762,19 +8804,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
@@ -8783,10 +8825,10 @@
         <v>307</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8794,31 +8836,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>96</v>
+        <v>307</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>613</v>
+        <v>473</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8826,31 +8868,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>307</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>461</v>
+        <v>616</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8858,19 +8900,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
@@ -8879,10 +8921,10 @@
         <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>461</v>
+        <v>616</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8890,19 +8932,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
@@ -8911,10 +8953,10 @@
         <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>613</v>
+        <v>473</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8922,19 +8964,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
@@ -8943,10 +8985,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8954,31 +8996,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>480</v>
+        <v>616</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8986,31 +9028,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>613</v>
+        <v>483</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9018,19 +9060,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
@@ -9039,10 +9081,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9050,31 +9092,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9082,19 +9124,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -9106,7 +9148,7 @@
         <v>395</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9114,19 +9156,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
@@ -9138,7 +9180,7 @@
         <v>395</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9146,19 +9188,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
@@ -9170,7 +9212,7 @@
         <v>395</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9268,25 +9310,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9306,7 +9348,7 @@
         <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -9315,10 +9357,10 @@
         <v>90</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9332,13 +9374,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
@@ -9347,10 +9389,10 @@
         <v>307</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9364,13 +9406,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
@@ -9382,7 +9424,7 @@
         <v>165</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9393,28 +9435,28 @@
         <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9428,25 +9470,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9460,13 +9502,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
@@ -9478,7 +9520,7 @@
         <v>165</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9492,13 +9534,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
@@ -9507,10 +9549,10 @@
         <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9524,13 +9566,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -9539,10 +9581,10 @@
         <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9556,13 +9598,13 @@
         <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
@@ -9571,10 +9613,10 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9585,16 +9627,16 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
@@ -9603,10 +9645,10 @@
         <v>125</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9620,13 +9662,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
@@ -9635,10 +9677,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9652,13 +9694,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
@@ -9667,10 +9709,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9684,25 +9726,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9713,28 +9755,28 @@
         <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>307</v>
+        <v>487</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>203</v>
+        <v>473</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9748,25 +9790,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>484</v>
+        <v>307</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>461</v>
+        <v>207</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9780,13 +9822,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
@@ -9795,10 +9837,10 @@
         <v>307</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9812,13 +9854,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -9827,10 +9869,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9844,13 +9886,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
@@ -9859,10 +9901,10 @@
         <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9876,13 +9918,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
@@ -9891,10 +9933,10 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9908,13 +9950,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
@@ -9923,10 +9965,10 @@
         <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9940,25 +9982,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>461</v>
+        <v>207</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9972,25 +10014,25 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>203</v>
+        <v>473</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10004,13 +10046,13 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
@@ -10019,10 +10061,10 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10036,25 +10078,25 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10068,13 +10110,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -10083,10 +10125,10 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10097,16 +10139,16 @@
         <v>63</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -10115,10 +10157,10 @@
         <v>307</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10129,16 +10171,16 @@
         <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
@@ -10147,10 +10189,10 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10164,13 +10206,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
@@ -10179,10 +10221,10 @@
         <v>96</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10196,13 +10238,13 @@
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
@@ -10211,10 +10253,10 @@
         <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>749</v>
+        <v>483</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">다다익선!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블랙소울!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">초코나라!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">털미녀!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="754">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>389</t>
+    <t>388</t>
   </si>
   <si>
     <t>13위</t>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>207조 5902억 4049만</t>
+    <t>209조 35억 7298만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,7 +105,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.24</t>
+    <t>2026.04.25</t>
   </si>
   <si>
     <t>다다익선</t>
@@ -117,7 +117,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>357</t>
+    <t>353</t>
   </si>
   <si>
     <t>7위</t>
@@ -126,10 +126,10 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>232조 749억 1226만</t>
-  </si>
-  <si>
-    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 5000억 이상 재밌게 소통하면서 게임하실 분 귓주세요</t>
+    <t>243조 6929억 9337만</t>
+  </si>
+  <si>
+    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 2조 이상 재밌게 소통하면서 게임하실 분 공대애봉이/뒁글 문의 주세요</t>
   </si>
   <si>
     <t>Pakistan</t>
@@ -144,13 +144,13 @@
     <t>Scania 18</t>
   </si>
   <si>
-    <t>410</t>
+    <t>407</t>
   </si>
   <si>
     <t>9위</t>
   </si>
   <si>
-    <t>184조 9581억 307만</t>
+    <t>188조 6243억 8462만</t>
   </si>
   <si>
     <t>초코남</t>
@@ -165,10 +165,10 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>205조 3800억 4104만</t>
+    <t>391</t>
+  </si>
+  <si>
+    <t>207조 5113억 6750만</t>
   </si>
   <si>
     <t>보심</t>
@@ -183,37 +183,37 @@
     <t>Scania 27</t>
   </si>
   <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>32위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>213조 171억 8829만</t>
+  </si>
+  <si>
+    <t>비련길드 모집조건 : 투력 9000억 이상 일일기부 300+ 길컨 참여자</t>
+  </si>
+  <si>
+    <t>렆프</t>
+  </si>
+  <si>
+    <t>밀크런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
+  </si>
+  <si>
     <t>377</t>
   </si>
   <si>
     <t>30위</t>
   </si>
   <si>
-    <t>215조 2154억 2346만</t>
-  </si>
-  <si>
-    <t>비련길드 모집조건 : 투력 5000억 이상 일일기부 300+ 길컨 참여자</t>
-  </si>
-  <si>
-    <t>렆프</t>
-  </si>
-  <si>
-    <t>밀크런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>31위</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>213조 3484억 8742만</t>
+    <t>219조 9916억 9267만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요</t>
@@ -231,7 +231,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>1017</t>
+    <t>993</t>
   </si>
   <si>
     <t>8위</t>
@@ -240,7 +240,7 @@
     <t>Lv.6</t>
   </si>
   <si>
-    <t>42조 495억 6258만</t>
+    <t>44조 3405억 6852만</t>
   </si>
   <si>
     <t>*투력 2조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
@@ -288,7 +288,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 4446억 2204만</t>
+    <t>28조 5981억 2484만</t>
   </si>
   <si>
     <t>2</t>
@@ -384,7 +384,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6289억 5284만</t>
+    <t>7조 6510억 5207만</t>
   </si>
   <si>
     <t>8</t>
@@ -396,7 +396,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 551억 4048만</t>
+    <t>7조 2489억 9522만</t>
   </si>
   <si>
     <t>9</t>
@@ -417,31 +417,31 @@
     <t>10</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 4940억 3502만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>6조 4404억 299만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>6조 4098억 9503만</t>
+    <t>6조 4649억 8468만</t>
   </si>
   <si>
     <t>12</t>
@@ -465,7 +465,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 9320억 5638만</t>
+    <t>4조 9811억 5357만</t>
   </si>
   <si>
     <t>14</t>
@@ -477,12 +477,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 4924억 651만</t>
+    <t>4조 5621억 2305만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 4977억 2832만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -495,7 +510,19 @@
     <t>4조 3985억 226만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>4조 645억 8550만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -507,7 +534,7 @@
     <t>4조 253억 5355만</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -519,22 +546,7 @@
     <t>4조 51억 9443만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>3조 9719억 6394만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -546,18 +558,6 @@
     <t>3조 9234억 6313만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>3조 8330억 4982만</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -579,7 +579,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 2913억 5806만</t>
+    <t>3조 3151억 5874만</t>
   </si>
   <si>
     <t>23</t>
@@ -615,7 +615,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 7026억 5570만</t>
+    <t>2조 7249억 3293만</t>
   </si>
   <si>
     <t>26</t>
@@ -657,7 +657,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>2조 3877억 7093만</t>
+    <t>2조 3986억 360만</t>
   </si>
   <si>
     <t>29</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 246억 6143만</t>
+    <t>2조 267억 9109만</t>
   </si>
   <si>
     <t>눈꽃물망초</t>
@@ -708,7 +708,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
   </si>
   <si>
-    <t>24조 2321억 8274만</t>
+    <t>24조 3331억 917만</t>
   </si>
   <si>
     <t>뒁글</t>
@@ -717,13 +717,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
   </si>
   <si>
-    <t>10조 1552억 8473만</t>
+    <t>11조 179억 4686만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
   </si>
   <si>
-    <t>8조 3374억 4650만</t>
+    <t>10조 5813억 9883만</t>
+  </si>
+  <si>
+    <t>나윤v파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>8조 1426억 8228만</t>
   </si>
   <si>
     <t>공대애봉이</t>
@@ -732,7 +741,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>6조 3554억 1327만</t>
+    <t>7조 1421억 1914만</t>
   </si>
   <si>
     <t>언기</t>
@@ -750,7 +759,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>3조 5995억 1775만</t>
+    <t>3조 8072억 7398만</t>
+  </si>
+  <si>
+    <t>JAEYA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
+  </si>
+  <si>
+    <t>3조 6163억 8359만</t>
   </si>
   <si>
     <t>우타이테</t>
@@ -777,16 +795,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
   </si>
   <si>
-    <t>3조 2001억 6814만</t>
-  </si>
-  <si>
-    <t>JAEYA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
-  </si>
-  <si>
-    <t>3조 341억 6644만</t>
+    <t>3조 3370억 3156만</t>
+  </si>
+  <si>
+    <t>원투아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>3조 879억 5142만</t>
+  </si>
+  <si>
+    <t>웅쟈쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
+  </si>
+  <si>
+    <t>3조 839억 9560만</t>
+  </si>
+  <si>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>3조 334억 6300만</t>
   </si>
   <si>
     <t>범지</t>
@@ -798,40 +834,13 @@
     <t>3조 308억 2909만</t>
   </si>
   <si>
-    <t>원투아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>3조 65억 3471만</t>
-  </si>
-  <si>
     <t>옵션키우기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>2조 8191억 1235만</t>
-  </si>
-  <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>2조 8021억 3148만</t>
-  </si>
-  <si>
-    <t>웅쟈쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2조 6011억 8785만</t>
+    <t>2조 9852억 8751만</t>
   </si>
   <si>
     <t>맛닭꼬시멘토</t>
@@ -849,7 +858,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
   </si>
   <si>
-    <t>2조 1399억 5697만</t>
+    <t>2조 1440억 966만</t>
   </si>
   <si>
     <t>l우주아이l</t>
@@ -867,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
   </si>
   <si>
-    <t>1조 9211억 367만</t>
+    <t>1조 9739억 7744만</t>
   </si>
   <si>
     <t>아쿠마불독</t>
@@ -888,15 +897,6 @@
     <t>1조 7306억 4932만</t>
   </si>
   <si>
-    <t>맨해라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%ED%95%B4%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 6250억 1694만</t>
-  </si>
-  <si>
     <t>몽실망실토실</t>
   </si>
   <si>
@@ -921,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
   </si>
   <si>
-    <t>1조 3752억 1802만</t>
+    <t>1조 4039억 1202만</t>
   </si>
   <si>
     <t>2D파트장</t>
@@ -939,7 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
   </si>
   <si>
-    <t>7546억 603만</t>
+    <t>8117억 9060만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -948,7 +948,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
   </si>
   <si>
-    <t>7065억 975만</t>
+    <t>7135억 2533만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
@@ -957,7 +957,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>61조 9021억 3304만</t>
+    <t>63조 709억 7251만</t>
   </si>
   <si>
     <t>멈디</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
   </si>
   <si>
-    <t>9조 731억 3944만</t>
+    <t>9조 8949억 9692만</t>
   </si>
   <si>
     <t>유랑민</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
   </si>
   <si>
-    <t>8조 2861억 3144만</t>
+    <t>8조 3698억 9861만</t>
   </si>
   <si>
     <t>사숩</t>
@@ -984,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
   </si>
   <si>
-    <t>6조 9212억 9274만</t>
+    <t>7조 3316억 9144만</t>
   </si>
   <si>
     <t>포도맛맥플</t>
@@ -996,13 +996,31 @@
     <t>6조 7242억 9747만</t>
   </si>
   <si>
+    <t>김롸아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
+  </si>
+  <si>
+    <t>5조 5660억 6217만</t>
+  </si>
+  <si>
+    <t>연바기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 5028억 9343만</t>
+  </si>
+  <si>
     <t>단비둘기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>5조 3443억 5362만</t>
+    <t>5조 3516억 9005만</t>
   </si>
   <si>
     <t>또긔</t>
@@ -1011,25 +1029,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
   </si>
   <si>
-    <t>5조 2857억 8963만</t>
-  </si>
-  <si>
-    <t>연바기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 2247억 7862만</t>
-  </si>
-  <si>
-    <t>김롸아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
-  </si>
-  <si>
-    <t>4조 9484억 9382만</t>
+    <t>5조 2991억 2456만</t>
+  </si>
+  <si>
+    <t>썬콜법사도희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>4조 8953억 1210만</t>
   </si>
   <si>
     <t>스라차차소스</t>
@@ -1038,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
   </si>
   <si>
-    <t>4조 8288억 9135만</t>
+    <t>4조 8611억 1747만</t>
   </si>
   <si>
     <t>limno</t>
@@ -1050,22 +1059,13 @@
     <t>4조 8032억 5155만</t>
   </si>
   <si>
-    <t>썬콜법사도희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>4조 7497억 1387만</t>
-  </si>
-  <si>
     <t>까만색양갱</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
   </si>
   <si>
-    <t>4조 6798억 6076만</t>
+    <t>4조 7051억 84만</t>
   </si>
   <si>
     <t>우치앵</t>
@@ -1101,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
   </si>
   <si>
-    <t>3조 8877억 52만</t>
+    <t>3조 8980억 8058만</t>
   </si>
   <si>
     <t>낮잠중</t>
@@ -1110,7 +1110,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
   </si>
   <si>
-    <t>3조 7462억 3938만</t>
+    <t>3조 7502억 4877만</t>
   </si>
   <si>
     <t>히어로경원</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
   </si>
   <si>
-    <t>3조 5815억 2733만</t>
+    <t>3조 6715억 746만</t>
   </si>
   <si>
     <t>구파발메타몽</t>
@@ -1128,7 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
   </si>
   <si>
-    <t>3조 5138억 8631만</t>
+    <t>3조 5209억 8214만</t>
   </si>
   <si>
     <t>썹웨피망빼</t>
@@ -1137,7 +1137,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
   </si>
   <si>
-    <t>3조 4902억 2435만</t>
+    <t>3조 4938억 6546만</t>
   </si>
   <si>
     <t>투둠</t>
@@ -1155,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
   </si>
   <si>
-    <t>3조 982억 7937만</t>
+    <t>3조 1114억 9712만</t>
   </si>
   <si>
     <t>도윤파덜</t>
@@ -1191,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 7824억 1307만</t>
+    <t>2조 7891억 5193만</t>
   </si>
   <si>
     <t>극쪽이</t>
@@ -1221,7 +1221,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1276억 8970만</t>
+    <t>1279억 8370만</t>
   </si>
   <si>
     <t>상현별</t>
@@ -1230,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
   </si>
   <si>
-    <t>66조 1808억 8271만</t>
+    <t>67조 8159억 3094만</t>
   </si>
   <si>
     <t>말랑콩닥</t>
@@ -1239,7 +1239,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
   </si>
   <si>
-    <t>21조 8736억 4851만</t>
+    <t>23조 4649억 2048만</t>
   </si>
   <si>
     <t>안루핑</t>
@@ -1266,7 +1266,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
   </si>
   <si>
-    <t>8조 1725억 8355만</t>
+    <t>8조 1843억 9177만</t>
   </si>
   <si>
     <t>루나스틱</t>
@@ -1275,7 +1275,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
   </si>
   <si>
-    <t>7조 5164억 4572만</t>
+    <t>7조 7509억 5317만</t>
   </si>
   <si>
     <t>메키현</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
   </si>
   <si>
-    <t>3조 8327억 2483만</t>
+    <t>3조 8401억 1645만</t>
   </si>
   <si>
     <t>용감한순대국</t>
@@ -1344,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
   </si>
   <si>
-    <t>2조 9002억 4344만</t>
+    <t>3조 1034억 1903만</t>
   </si>
   <si>
     <t>별밖에</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EB%91%98%EC%95%84%EB%B2%94</t>
   </si>
   <si>
-    <t>2조 3721억 7391만</t>
+    <t>2조 3756억 8523만</t>
   </si>
   <si>
     <t>박예쁜</t>
@@ -1392,6 +1392,24 @@
     <t>2조 1139억 4649만</t>
   </si>
   <si>
+    <t>신궁초보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%B4%88%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>2조 483억 9026만</t>
+  </si>
+  <si>
+    <t>쿰척쿰쳑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
+  </si>
+  <si>
+    <t>2조 405억 4024만</t>
+  </si>
+  <si>
     <t>판별식</t>
   </si>
   <si>
@@ -1401,22 +1419,13 @@
     <t>1조 9179억 5132만</t>
   </si>
   <si>
-    <t>신궁초보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%B4%88%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>1조 7915억 9496만</t>
-  </si>
-  <si>
-    <t>쿰척쿰쳑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
-  </si>
-  <si>
-    <t>1조 5888억 7783만</t>
+    <t>루맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 6759억 7300만</t>
   </si>
   <si>
     <t>옹야미</t>
@@ -1425,16 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>1조 5829억 9952만</t>
-  </si>
-  <si>
-    <t>루맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 5332억 241만</t>
+    <t>1조 6078억 1739만</t>
   </si>
   <si>
     <t>츄쁜</t>
@@ -1443,7 +1443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
   </si>
   <si>
-    <t>1조 424억 2465만</t>
+    <t>1조 1058억 9560만</t>
   </si>
   <si>
     <t>박마리아</t>
@@ -1455,7 +1455,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>9457억 4652만</t>
+    <t>1조 637억 4045만</t>
   </si>
   <si>
     <t>한닝</t>
@@ -1464,7 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
   </si>
   <si>
-    <t>9249억 7350만</t>
+    <t>9670억 758만</t>
   </si>
   <si>
     <t>뮴뮴뮴뮴뮴</t>
@@ -1473,7 +1473,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4</t>
   </si>
   <si>
-    <t>6645억 6390만</t>
+    <t>6946억 6245만</t>
   </si>
   <si>
     <t>놀면머하니</t>
@@ -1482,22 +1482,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%86%80%EB%A9%B4%EB%A8%B8%ED%95%98%EB%8B%88</t>
   </si>
   <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>5440억 5993만</t>
+  </si>
+  <si>
+    <t>키워봄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%8C%EB%B4%84</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
     <t>94</t>
   </si>
   <si>
-    <t>5347억 6893만</t>
-  </si>
-  <si>
-    <t>키워봄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%8C%EB%B4%84</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>3917억 4482만</t>
+    <t>3947억 2191만</t>
   </si>
   <si>
     <t>량용</t>
@@ -1509,7 +1512,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>67조 6801억 2693만</t>
+    <t>67조 8839억 2862만</t>
   </si>
   <si>
     <t>달봉e</t>
@@ -1551,7 +1554,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>6조 93억 3774만</t>
+    <t>6조 3383억 866만</t>
   </si>
   <si>
     <t>핫딜패스</t>
@@ -1599,31 +1602,31 @@
     <t>3조 7517억 4264만</t>
   </si>
   <si>
+    <t>빅밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>3조 7406억 6792만</t>
+  </si>
+  <si>
     <t>템플스테이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%ED%94%8C%EC%8A%A4%ED%85%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 6102억 4835만</t>
-  </si>
-  <si>
-    <t>빅밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>3조 5574억 9485만</t>
-  </si>
-  <si>
-    <t>하눌이야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%88%8C%EC%9D%B4%EC%95%BC</t>
-  </si>
-  <si>
-    <t>3조 2348억 7561만</t>
+    <t>3조 7306억 1403만</t>
+  </si>
+  <si>
+    <t>아무렇게할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AC%B4%EB%A0%87%EA%B2%8C%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>3조 2335억 9930만</t>
   </si>
   <si>
     <t>Scope</t>
@@ -1635,22 +1638,13 @@
     <t>2조 7096억 2142만</t>
   </si>
   <si>
-    <t>아무렇게할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AC%B4%EB%A0%87%EA%B2%8C%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>2조 6557억 4207만</t>
-  </si>
-  <si>
     <t>산로지노</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 2038억 9802만</t>
+    <t>2조 2588억 477만</t>
   </si>
   <si>
     <t>리디엘</t>
@@ -1677,7 +1671,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8053억 9608만</t>
+    <t>1조 8326억 1914만</t>
+  </si>
+  <si>
+    <t>Azham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Azham</t>
+  </si>
+  <si>
+    <t>1조 7638억 9086만</t>
   </si>
   <si>
     <t>떠하야</t>
@@ -1686,16 +1689,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%ED%95%98%EC%95%BC</t>
   </si>
   <si>
-    <t>1조 7306억 6464만</t>
-  </si>
-  <si>
-    <t>Azham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Azham</t>
-  </si>
-  <si>
-    <t>1조 5399억 8510만</t>
+    <t>1조 7555억 1188만</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Porto</t>
+  </si>
+  <si>
+    <t>1조 4619억 7338만</t>
   </si>
   <si>
     <t>이즈뤼얼</t>
@@ -1704,16 +1707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A6%88%EB%A4%BC%EC%96%BC</t>
   </si>
   <si>
-    <t>1조 4109억 293만</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Porto</t>
-  </si>
-  <si>
-    <t>1조 3279억 5327만</t>
+    <t>1조 4396억 2824만</t>
   </si>
   <si>
     <t>비라비스</t>
@@ -1722,16 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%9D%BC%EB%B9%84%EC%8A%A4</t>
   </si>
   <si>
-    <t>1조 1710억 5246만</t>
-  </si>
-  <si>
-    <t>호빵현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%B9%B5%ED%98%84</t>
-  </si>
-  <si>
-    <t>9096억 5200만</t>
+    <t>1조 1712억 9229만</t>
   </si>
   <si>
     <t>후려까기</t>
@@ -1749,7 +1734,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>8338억 8982만</t>
+    <t>8534억 7427만</t>
+  </si>
+  <si>
+    <t>뽀미l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
+  </si>
+  <si>
+    <t>6413억 5862만</t>
   </si>
   <si>
     <t>짜뇨</t>
@@ -1761,15 +1755,6 @@
     <t>5962억 6625만</t>
   </si>
   <si>
-    <t>뽀미l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
-  </si>
-  <si>
-    <t>5724억 6904만</t>
-  </si>
-  <si>
     <t>동띠</t>
   </si>
   <si>
@@ -1785,7 +1770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%AC%B4%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>29조 4786억 2006만</t>
+    <t>34조 9382억 3297만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EB%8C%80</t>
@@ -1818,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%8F%99%EB%9D%A0</t>
   </si>
   <si>
-    <t>3조 4480억 7380만</t>
+    <t>3조 5363억 2259만</t>
   </si>
   <si>
     <t>정뽀</t>
@@ -1827,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%BD%80</t>
   </si>
   <si>
-    <t>3조 2368억 1696만</t>
+    <t>3조 5086억 4014만</t>
   </si>
   <si>
     <t>단정이</t>
@@ -1836,7 +1821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8308억 3230만</t>
+    <t>1조 8939억 2968만</t>
   </si>
   <si>
     <t>지구뿌셔</t>
@@ -1845,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>1조 7531억 9060만</t>
+    <t>1조 7889억 4240만</t>
   </si>
   <si>
     <t>꼬햄</t>
@@ -1863,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%9B</t>
   </si>
   <si>
-    <t>1조 988억 4836만</t>
+    <t>1조 1533억 9299만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1881,9 +1866,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%BF%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
     <t>8415억 3336만</t>
   </si>
   <si>
@@ -1893,7 +1875,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
   </si>
   <si>
-    <t>7178억 6669만</t>
+    <t>7297억 224만</t>
+  </si>
+  <si>
+    <t>다릿골</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%A6%BF%EA%B3%A8</t>
+  </si>
+  <si>
+    <t>7294억 9184만</t>
   </si>
   <si>
     <t>귀쮸</t>
@@ -1902,7 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
   </si>
   <si>
-    <t>5776억 6573만</t>
+    <t>6115억 4518만</t>
   </si>
   <si>
     <t>당겨쏴</t>
@@ -1911,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B2%A8%EC%8F%B4</t>
   </si>
   <si>
-    <t>5767억 1756만</t>
+    <t>5830억 5561만</t>
   </si>
   <si>
     <t>은단월</t>
@@ -1929,7 +1920,7 @@
     <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
   </si>
   <si>
-    <t>5062억 9151만</t>
+    <t>5093억 3264만</t>
   </si>
   <si>
     <t>알뺘노</t>
@@ -1941,6 +1932,15 @@
     <t>4920억 9616만</t>
   </si>
   <si>
+    <t>투냉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
+  </si>
+  <si>
+    <t>4517억 5087만</t>
+  </si>
+  <si>
     <t>비비다</t>
   </si>
   <si>
@@ -1950,22 +1950,22 @@
     <t>4455억 4351만</t>
   </si>
   <si>
-    <t>투냉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
-  </si>
-  <si>
-    <t>4367억 2276만</t>
-  </si>
-  <si>
     <t>진1용</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%841%EC%9A%A9</t>
   </si>
   <si>
-    <t>3638억 9246만</t>
+    <t>3824억 1297만</t>
+  </si>
+  <si>
+    <t>사과클럽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
+  </si>
+  <si>
+    <t>3657억 6955만</t>
   </si>
   <si>
     <t>차눅</t>
@@ -1977,22 +1977,13 @@
     <t>3359억 9618만</t>
   </si>
   <si>
-    <t>사과클럽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
-  </si>
-  <si>
-    <t>3322억 6101만</t>
-  </si>
-  <si>
     <t>팔나무</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%82%98%EB%AC%B4</t>
   </si>
   <si>
-    <t>2472억 5141만</t>
+    <t>2956억 3727만</t>
   </si>
   <si>
     <t>53다2329</t>
@@ -2004,7 +1995,16 @@
     <t>92</t>
   </si>
   <si>
-    <t>2431억 402만</t>
+    <t>2440억 2766만</t>
+  </si>
+  <si>
+    <t>나루토토</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%A3%A8%ED%86%A0%ED%86%A0</t>
+  </si>
+  <si>
+    <t>1590억 6119만</t>
   </si>
   <si>
     <t>강진현</t>
@@ -2013,16 +2013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%A7%84%ED%98%84</t>
   </si>
   <si>
-    <t>1551억 9576만</t>
-  </si>
-  <si>
-    <t>나루토토</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%A3%A8%ED%86%A0%ED%86%A0</t>
-  </si>
-  <si>
-    <t>1411억 7436만</t>
+    <t>1558억 3839만</t>
   </si>
   <si>
     <t>길지녁</t>
@@ -2031,7 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%A7%80%EB%85%81</t>
   </si>
   <si>
-    <t>1204억 986만</t>
+    <t>1475억 2490만</t>
   </si>
   <si>
     <t>아포짓</t>
@@ -2040,13 +2031,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%8F%AC%EC%A7%93</t>
   </si>
   <si>
-    <t>3조 3693억 2382만</t>
+    <t>3조 8153억 5647만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=86%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>2조 8543억 3630만</t>
+    <t>3조 624억 6790만</t>
+  </si>
+  <si>
+    <t>다있다하노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 3604억 8429만</t>
+  </si>
+  <si>
+    <t>델타시그마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>2조 2674억 4642만</t>
   </si>
   <si>
     <t>꿍물</t>
@@ -2055,7 +2064,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%8D%EB%AC%BC</t>
   </si>
   <si>
-    <t>2조 2085억 8783만</t>
+    <t>2조 2603억 2962만</t>
+  </si>
+  <si>
+    <t>부산형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>2조 1249억 8884만</t>
   </si>
   <si>
     <t>끽스</t>
@@ -2064,34 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
   </si>
   <si>
-    <t>2조 1020억 7884만</t>
-  </si>
-  <si>
-    <t>부산형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>2조 669억 2668만</t>
-  </si>
-  <si>
-    <t>다있다하노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 639억 8631만</t>
-  </si>
-  <si>
-    <t>델타시그마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>2조 499억 1970만</t>
+    <t>2조 1193억 2989만</t>
   </si>
   <si>
     <t>흑인드록바</t>
@@ -2103,13 +2094,31 @@
     <t>2조 11억 1978만</t>
   </si>
   <si>
+    <t>딴모</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
+  </si>
+  <si>
+    <t>1조 9217억 3565만</t>
+  </si>
+  <si>
     <t>전팡</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8C%A1</t>
   </si>
   <si>
-    <t>1조 7702억 2214만</t>
+    <t>1조 8307억 4393만</t>
+  </si>
+  <si>
+    <t>한콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>1조 7983억 71만</t>
   </si>
   <si>
     <t>밀가루죽</t>
@@ -2118,25 +2127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EA%B0%80%EB%A3%A8%EC%A3%BD</t>
   </si>
   <si>
-    <t>1조 7380억 2779만</t>
-  </si>
-  <si>
-    <t>한콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>1조 6190억 485만</t>
-  </si>
-  <si>
-    <t>딴모</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
-  </si>
-  <si>
-    <t>1조 5319억 7630만</t>
+    <t>1조 7454억 2451만</t>
   </si>
   <si>
     <t>또유유</t>
@@ -2145,7 +2136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%9C%A0%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 4531억 4364만</t>
+    <t>1조 5245억 986만</t>
   </si>
   <si>
     <t>야로야옹</t>
@@ -2154,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
   </si>
   <si>
-    <t>1조 4507억 6254만</t>
+    <t>1조 4904억 8375만</t>
   </si>
   <si>
     <t>웅잉당</t>
@@ -2163,7 +2154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>1조 3449억 2728만</t>
+    <t>1조 3836억 1749만</t>
   </si>
   <si>
     <t>사람님아</t>
@@ -2172,7 +2163,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
   </si>
   <si>
-    <t>1조 2937억 8613만</t>
+    <t>1조 2994억 5609만</t>
+  </si>
+  <si>
+    <t>흑인햄찌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>1조 1836억 4670만</t>
   </si>
   <si>
     <t>비숍마로밍</t>
@@ -2184,22 +2184,22 @@
     <t>1조 1488억 5053만</t>
   </si>
   <si>
-    <t>흑인햄찌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>1조 1007억 6481만</t>
-  </si>
-  <si>
     <t>은둔형오덕후</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%91%94%ED%98%95%EC%98%A4%EB%8D%95%ED%9B%84</t>
   </si>
   <si>
-    <t>1조 925억 1378만</t>
+    <t>1조 1113억 6681만</t>
+  </si>
+  <si>
+    <t>에머슨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
+  </si>
+  <si>
+    <t>9396억 6014만</t>
   </si>
   <si>
     <t>하랸</t>
@@ -2208,16 +2208,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
   </si>
   <si>
-    <t>9218억 3384만</t>
-  </si>
-  <si>
-    <t>에머슨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
-  </si>
-  <si>
-    <t>8697억 5673만</t>
+    <t>9305억 1567만</t>
+  </si>
+  <si>
+    <t>존못에겐남짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>8568억 6399만</t>
+  </si>
+  <si>
+    <t>섀레기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>8512억 8487만</t>
   </si>
   <si>
     <t>민초양갱</t>
@@ -2229,24 +2238,6 @@
     <t>8468억 6271만</t>
   </si>
   <si>
-    <t>존못에겐남짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>8418억 8268만</t>
-  </si>
-  <si>
-    <t>섀레기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>8383억 4352만</t>
-  </si>
-  <si>
     <t>서울아우</t>
   </si>
   <si>
@@ -2262,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
   </si>
   <si>
-    <t>7118억 4351만</t>
+    <t>7128억 1218만</t>
   </si>
   <si>
     <t>뉴비i</t>
@@ -2280,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B6%80%EC%9E%A5%EA%B5%AC%EB%8B%88</t>
   </si>
   <si>
-    <t>4789억 8706만</t>
+    <t>4802억 7206만</t>
   </si>
   <si>
     <t>아임몽순</t>
@@ -2292,7 +2283,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>4530억 4502만</t>
+    <t>4719억 7445만</t>
   </si>
   <si>
     <t>오리박사</t>
@@ -2907,16 +2898,16 @@
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2924,13 +2915,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
@@ -2939,16 +2930,16 @@
         <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>60</v>
@@ -3373,13 +3364,13 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3390,25 +3381,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>136</v>
@@ -3440,7 +3431,7 @@
         <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>140</v>
@@ -3472,7 +3463,7 @@
         <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>144</v>
@@ -3504,7 +3495,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>148</v>
@@ -3533,7 +3524,7 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>152</v>
@@ -3565,13 +3556,13 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3582,28 +3573,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3614,25 +3605,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>166</v>
@@ -3664,7 +3655,7 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>170</v>
@@ -3693,10 +3684,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>174</v>
@@ -3725,10 +3716,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>178</v>
@@ -3760,7 +3751,7 @@
         <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>182</v>
@@ -3792,7 +3783,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>186</v>
@@ -3824,7 +3815,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>190</v>
@@ -3888,7 +3879,7 @@
         <v>108</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>198</v>
@@ -3920,7 +3911,7 @@
         <v>202</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>203</v>
@@ -3984,7 +3975,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>212</v>
@@ -4016,7 +4007,7 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>216</v>
@@ -4229,7 +4220,7 @@
         <v>125</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>228</v>
@@ -4261,7 +4252,7 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>230</v>
@@ -4290,10 +4281,10 @@
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>233</v>
@@ -4322,10 +4313,10 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>236</v>
@@ -4357,7 +4348,7 @@
         <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>239</v>
@@ -4389,7 +4380,7 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>242</v>
@@ -4421,7 +4412,7 @@
         <v>125</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>245</v>
@@ -4435,7 +4426,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>246</v>
@@ -4450,10 +4441,10 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>248</v>
@@ -4485,7 +4476,7 @@
         <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>251</v>
@@ -4514,10 +4505,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>254</v>
@@ -4549,7 +4540,7 @@
         <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>257</v>
@@ -4578,10 +4569,10 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>260</v>
@@ -4613,7 +4604,7 @@
         <v>202</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>263</v>
@@ -4627,7 +4618,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>264</v>
@@ -4642,7 +4633,7 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>152</v>
@@ -4659,7 +4650,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>267</v>
@@ -4674,7 +4665,7 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>152</v>
@@ -4706,10 +4697,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>272</v>
@@ -4738,10 +4729,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>275</v>
@@ -4770,7 +4761,7 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>152</v>
@@ -4802,10 +4793,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>281</v>
@@ -4834,10 +4825,10 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>284</v>
@@ -4869,7 +4860,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>287</v>
@@ -4901,7 +4892,7 @@
         <v>202</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>290</v>
@@ -4965,7 +4956,7 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>296</v>
@@ -4994,10 +4985,10 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
@@ -5061,7 +5052,7 @@
         <v>125</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>305</v>
@@ -5119,7 +5110,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5210,7 +5201,7 @@
         <v>125</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>311</v>
@@ -5274,7 +5265,7 @@
         <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>317</v>
@@ -5367,7 +5358,7 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>103</v>
@@ -5399,7 +5390,7 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>103</v>
@@ -5463,7 +5454,7 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>103</v>
@@ -5480,7 +5471,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>336</v>
@@ -5527,7 +5518,7 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>103</v>
@@ -5562,7 +5553,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>344</v>
@@ -5594,7 +5585,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>347</v>
@@ -5626,7 +5617,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>350</v>
@@ -5658,7 +5649,7 @@
         <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>353</v>
@@ -5672,7 +5663,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>354</v>
@@ -5704,7 +5695,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>357</v>
@@ -5722,7 +5713,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>359</v>
@@ -5754,7 +5745,7 @@
         <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>362</v>
@@ -5786,7 +5777,7 @@
         <v>125</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>365</v>
@@ -5818,7 +5809,7 @@
         <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>368</v>
@@ -5850,7 +5841,7 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>371</v>
@@ -5882,7 +5873,7 @@
         <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>374</v>
@@ -5911,10 +5902,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>377</v>
@@ -5978,7 +5969,7 @@
         <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>383</v>
@@ -6042,7 +6033,7 @@
         <v>125</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>389</v>
@@ -6383,7 +6374,7 @@
         <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>414</v>
@@ -6415,7 +6406,7 @@
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>417</v>
@@ -6447,7 +6438,7 @@
         <v>307</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>420</v>
@@ -6525,7 +6516,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>427</v>
@@ -6543,7 +6534,7 @@
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>429</v>
@@ -6575,7 +6566,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>431</v>
@@ -6607,7 +6598,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>434</v>
@@ -6639,7 +6630,7 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>437</v>
@@ -6671,7 +6662,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>440</v>
@@ -6703,7 +6694,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>443</v>
@@ -6717,7 +6708,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>444</v>
@@ -6735,7 +6726,7 @@
         <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>446</v>
@@ -6749,7 +6740,7 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>447</v>
@@ -6767,7 +6758,7 @@
         <v>307</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>449</v>
@@ -6799,7 +6790,7 @@
         <v>125</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>452</v>
@@ -6828,10 +6819,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>455</v>
@@ -6860,10 +6851,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>458</v>
@@ -6895,7 +6886,7 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>461</v>
@@ -6924,7 +6915,7 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>207</v>
@@ -6956,7 +6947,7 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>207</v>
@@ -6991,7 +6982,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>470</v>
@@ -7055,7 +7046,7 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>473</v>
+        <v>207</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>477</v>
@@ -7151,10 +7142,10 @@
         <v>487</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7200,7 +7191,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7253,13 +7244,13 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
@@ -7268,10 +7259,10 @@
         <v>307</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7285,13 +7276,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
@@ -7303,7 +7294,7 @@
         <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7317,13 +7308,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
@@ -7335,7 +7326,7 @@
         <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7349,13 +7340,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7367,7 +7358,7 @@
         <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7381,13 +7372,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
@@ -7396,10 +7387,10 @@
         <v>487</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7413,13 +7404,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -7431,7 +7422,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7445,13 +7436,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
@@ -7460,10 +7451,10 @@
         <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7477,13 +7468,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
@@ -7495,7 +7486,7 @@
         <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7509,13 +7500,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -7524,10 +7515,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7541,13 +7532,13 @@
         <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
@@ -7556,10 +7547,10 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7570,16 +7561,16 @@
         <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
@@ -7588,10 +7579,10 @@
         <v>125</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7605,25 +7596,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7637,25 +7628,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7669,25 +7660,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7701,13 +7692,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -7716,10 +7707,10 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7733,25 +7724,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7762,28 +7753,28 @@
         <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7794,28 +7785,28 @@
         <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7829,13 +7820,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
@@ -7844,10 +7835,10 @@
         <v>307</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7861,13 +7852,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
@@ -7876,10 +7867,10 @@
         <v>307</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7893,13 +7884,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
@@ -7908,10 +7899,10 @@
         <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7925,25 +7916,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>307</v>
+        <v>125</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7957,25 +7948,25 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>207</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7989,25 +7980,25 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>207</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8021,25 +8012,25 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>307</v>
+        <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>207</v>
+        <v>473</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8053,25 +8044,25 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>473</v>
+        <v>152</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8085,13 +8076,13 @@
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -8103,7 +8094,7 @@
         <v>473</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8117,25 +8108,1004 @@
         <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>307</v>
+      </c>
       <c r="H29" s="2" t="s">
-        <v>165</v>
+        <v>395</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>572</v>
+        <v>657</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -8143,31 +9113,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>573</v>
+        <v>658</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>573</v>
+        <v>658</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>574</v>
+        <v>659</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>473</v>
+        <v>395</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>575</v>
+        <v>660</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -8175,31 +9145,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>576</v>
+        <v>661</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>576</v>
+        <v>661</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>577</v>
+        <v>662</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
+        <v>307</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>473</v>
+        <v>395</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>578</v>
+        <v>663</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -8243,1018 +9213,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -9310,13 +9268,13 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
@@ -9325,10 +9283,10 @@
         <v>487</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9348,7 +9306,7 @@
         <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -9357,10 +9315,10 @@
         <v>90</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9374,25 +9332,25 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>307</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9406,25 +9364,25 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9438,25 +9396,25 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>90</v>
+        <v>307</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9470,25 +9428,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9502,25 +9460,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9534,13 +9492,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
@@ -9552,7 +9510,7 @@
         <v>207</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9566,25 +9524,25 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>473</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9598,25 +9556,25 @@
         <v>127</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>207</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9627,16 +9585,16 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
@@ -9645,10 +9603,10 @@
         <v>125</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>616</v>
+        <v>473</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9662,13 +9620,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
@@ -9677,10 +9635,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9694,13 +9652,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
@@ -9709,10 +9667,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>473</v>
+        <v>207</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9726,13 +9684,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
@@ -9741,10 +9699,10 @@
         <v>487</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9758,13 +9716,13 @@
         <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -9776,7 +9734,7 @@
         <v>473</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9790,13 +9748,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
@@ -9808,7 +9766,7 @@
         <v>207</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9819,28 +9777,28 @@
         <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>207</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9851,28 +9809,28 @@
         <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>307</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>207</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9886,13 +9844,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
@@ -9904,7 +9862,7 @@
         <v>473</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9918,25 +9876,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>473</v>
+        <v>207</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9950,25 +9908,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>473</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9982,25 +9940,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>207</v>
+        <v>473</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -10014,25 +9972,25 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>473</v>
+        <v>207</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10046,25 +10004,25 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>473</v>
+        <v>207</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10078,13 +10036,13 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
@@ -10093,10 +10051,10 @@
         <v>487</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10110,13 +10068,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -10125,10 +10083,10 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>616</v>
+        <v>483</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10142,13 +10100,13 @@
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -10160,7 +10118,7 @@
         <v>207</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10174,13 +10132,13 @@
         <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
@@ -10189,10 +10147,10 @@
         <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>616</v>
+        <v>483</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10206,13 +10164,13 @@
         <v>209</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
@@ -10221,10 +10179,10 @@
         <v>96</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10238,13 +10196,13 @@
         <v>213</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
@@ -10253,10 +10211,10 @@
         <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -18,10 +18,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">다다익선!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">다다익선!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">블랙소울!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">초코나라!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">털미녀!$A$1:$J$31</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="756">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>388</t>
+    <t>394</t>
   </si>
   <si>
     <t>13위</t>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>209조 35억 7298만</t>
+    <t>210조 1486억 3414만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,7 +105,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.25</t>
+    <t>2026.04.26</t>
   </si>
   <si>
     <t>다다익선</t>
@@ -117,58 +117,61 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>353</t>
+    <t>348</t>
   </si>
   <si>
     <t>7위</t>
   </si>
   <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>263조 1222억 3913만</t>
+  </si>
+  <si>
+    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 2조 이상 재밌게 소통하면서 게임하실 분 공대애봉이/뒁글 문의 주세요</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>초코나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>9위</t>
+  </si>
+  <si>
+    <t>195조 4102억 9368만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
+    <t>블랙소울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
     <t>Lv.7</t>
   </si>
   <si>
-    <t>243조 6929억 9337만</t>
-  </si>
-  <si>
-    <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 2조 이상 재밌게 소통하면서 게임하실 분 공대애봉이/뒁글 문의 주세요</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>초코나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>188조 6243억 8462만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
-    <t>블랙소울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>207조 5113억 6750만</t>
+    <t>211조 7872억 5105만</t>
   </si>
   <si>
     <t>보심</t>
@@ -183,16 +186,13 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>32위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>213조 171억 8829만</t>
+    <t>384</t>
+  </si>
+  <si>
+    <t>31위</t>
+  </si>
+  <si>
+    <t>219조 2372억 9866만</t>
   </si>
   <si>
     <t>비련길드 모집조건 : 투력 9000억 이상 일일기부 300+ 길컨 참여자</t>
@@ -207,13 +207,13 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>377</t>
+    <t>383</t>
   </si>
   <si>
     <t>30위</t>
   </si>
   <si>
-    <t>219조 9916억 9267만</t>
+    <t>220조 4726억 4089만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요</t>
@@ -231,7 +231,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>993</t>
+    <t>990</t>
   </si>
   <si>
     <t>8위</t>
@@ -240,10 +240,10 @@
     <t>Lv.6</t>
   </si>
   <si>
-    <t>44조 3405억 6852만</t>
-  </si>
-  <si>
-    <t>*투력 2조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
+    <t>44조 9248억 967만</t>
+  </si>
+  <si>
+    <t>*투력 3조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
   </si>
   <si>
     <t>86미녀</t>
@@ -288,7 +288,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 5981억 2484만</t>
+    <t>28조 7523억 2933만</t>
   </si>
   <si>
     <t>2</t>
@@ -384,7 +384,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6510억 5207만</t>
+    <t>7조 6716억 4082만</t>
   </si>
   <si>
     <t>8</t>
@@ -396,12 +396,30 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 2489억 9522만</t>
+    <t>7조 3311억 6274만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 8265억 4136만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
@@ -414,24 +432,6 @@
     <t>6조 7155억 1566만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>6조 4940억 3502만</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -471,6 +471,21 @@
     <t>14</t>
   </si>
   <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>4조 6273억 4164만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>므고</t>
   </si>
   <si>
@@ -480,7 +495,7 @@
     <t>4조 5621억 2305만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -492,37 +507,34 @@
     <t>98</t>
   </si>
   <si>
-    <t>4조 4977억 2832만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>4조 3985억 226만</t>
+    <t>4조 5139억 1714만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>4조 3613억 1130만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>4조 645억 8550만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>4조 768억 9265만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -531,19 +543,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>4조 253억 5355만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>4조 51억 9443만</t>
+    <t>4조 366억 9775만</t>
   </si>
   <si>
     <t>20</t>
@@ -555,7 +555,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>3조 9234억 6313만</t>
+    <t>3조 9589억 1764만</t>
   </si>
   <si>
     <t>21</t>
@@ -579,7 +579,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 3151억 5874만</t>
+    <t>3조 3304억 6250만</t>
   </si>
   <si>
     <t>23</t>
@@ -591,7 +591,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 9098억 6694만</t>
+    <t>2조 9156억 802만</t>
   </si>
   <si>
     <t>24</t>
@@ -633,6 +633,18 @@
     <t>27</t>
   </si>
   <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2조 4519억 4405만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>불보독지</t>
   </si>
   <si>
@@ -645,292 +657,271 @@
     <t>2조 4292억 9347만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>2조 3292억 507만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>2조 275억 8658만</t>
+  </si>
+  <si>
+    <t>눈꽃물망초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
+  </si>
+  <si>
+    <t>94조 358억 5237만</t>
+  </si>
+  <si>
+    <t>포르쉐718</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
+  </si>
+  <si>
+    <t>41조 633억 2600만</t>
+  </si>
+  <si>
+    <t>초보자시프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
+  </si>
+  <si>
+    <t>33조 9782억 3943만</t>
+  </si>
+  <si>
+    <t>뒁글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
+  </si>
+  <si>
+    <t>11조 179억 4686만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
+  </si>
+  <si>
+    <t>10조 6618억 761만</t>
+  </si>
+  <si>
+    <t>나윤v파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>8조 2733억 5797만</t>
+  </si>
+  <si>
+    <t>공대애봉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7조 1582억 581만</t>
+  </si>
+  <si>
+    <t>언기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 8317억 2691만</t>
+  </si>
+  <si>
+    <t>묘목키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>3조 8072억 7398만</t>
+  </si>
+  <si>
+    <t>우타이테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
+  </si>
+  <si>
+    <t>3조 7854억 968만</t>
+  </si>
+  <si>
+    <t>JAEYA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
+  </si>
+  <si>
+    <t>3조 6163억 8359만</t>
+  </si>
+  <si>
+    <t>토르릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>3조 5930억 2375만</t>
+  </si>
+  <si>
+    <t>따뜻한배추</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
+  </si>
+  <si>
+    <t>3조 3385억 5610만</t>
+  </si>
+  <si>
+    <t>원투아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>3조 1612억 850만</t>
+  </si>
+  <si>
+    <t>옵션키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>3조 1343억 8370만</t>
+  </si>
+  <si>
+    <t>웅쟈쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
+  </si>
+  <si>
+    <t>3조 839억 9560만</t>
+  </si>
+  <si>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>3조 334억 6300만</t>
+  </si>
+  <si>
+    <t>범지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
+  </si>
+  <si>
+    <t>3조 308억 2909만</t>
+  </si>
+  <si>
+    <t>밍고스틴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
+  </si>
+  <si>
+    <t>2조 3213억 7264만</t>
+  </si>
+  <si>
+    <t>맛닭꼬시멘토</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EB%8B%AD%EA%BC%AC%EC%8B%9C%EB%A9%98%ED%86%A0</t>
+  </si>
+  <si>
+    <t>2조 1614억 5837만</t>
+  </si>
+  <si>
+    <t>김주왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
+  </si>
+  <si>
+    <t>2조 880억 7176만</t>
+  </si>
+  <si>
+    <t>l우주아이l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=l%EC%9A%B0%EC%A3%BC%EC%95%84%EC%9D%B4l</t>
+  </si>
+  <si>
+    <t>2조 24억 4824만</t>
+  </si>
+  <si>
+    <t>아쿠마불독</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
+  </si>
+  <si>
+    <t>1조 7967억 667만</t>
+  </si>
+  <si>
+    <t>타락파워스님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1조 5525억 1242만</t>
+  </si>
+  <si>
+    <t>몽실망실토실</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
+  </si>
+  <si>
+    <t>1조 4533억 737만</t>
+  </si>
+  <si>
+    <t>오늘밤은삐딱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%B0%A4%EC%9D%80%EC%82%90%EB%94%B1</t>
   </si>
   <si>
     <t>97</t>
   </si>
   <si>
-    <t>2조 3986억 360만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>2조 1697억 686만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>2조 267억 9109만</t>
-  </si>
-  <si>
-    <t>눈꽃물망초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
-  </si>
-  <si>
-    <t>94조 358억 5237만</t>
-  </si>
-  <si>
-    <t>포르쉐718</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
-  </si>
-  <si>
-    <t>31조 8467억 8491만</t>
-  </si>
-  <si>
-    <t>초보자시프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
-  </si>
-  <si>
-    <t>24조 3331억 917만</t>
-  </si>
-  <si>
-    <t>뒁글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
-  </si>
-  <si>
-    <t>11조 179억 4686만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
-  </si>
-  <si>
-    <t>10조 5813억 9883만</t>
-  </si>
-  <si>
-    <t>나윤v파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>8조 1426억 8228만</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7조 1421억 1914만</t>
-  </si>
-  <si>
-    <t>언기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 8317억 2691만</t>
-  </si>
-  <si>
-    <t>묘목키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>3조 8072억 7398만</t>
-  </si>
-  <si>
-    <t>JAEYA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
-  </si>
-  <si>
-    <t>3조 6163억 8359만</t>
-  </si>
-  <si>
-    <t>우타이테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
-  </si>
-  <si>
-    <t>3조 5482억 6503만</t>
-  </si>
-  <si>
-    <t>토르릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>3조 4904억 8991만</t>
-  </si>
-  <si>
-    <t>따뜻한배추</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
-  </si>
-  <si>
-    <t>3조 3370억 3156만</t>
-  </si>
-  <si>
-    <t>원투아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>3조 879억 5142만</t>
-  </si>
-  <si>
-    <t>웅쟈쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
-  </si>
-  <si>
-    <t>3조 839억 9560만</t>
-  </si>
-  <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>3조 334억 6300만</t>
-  </si>
-  <si>
-    <t>범지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
-  </si>
-  <si>
-    <t>3조 308억 2909만</t>
-  </si>
-  <si>
-    <t>옵션키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>2조 9852억 8751만</t>
-  </si>
-  <si>
-    <t>맛닭꼬시멘토</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EB%8B%AD%EA%BC%AC%EC%8B%9C%EB%A9%98%ED%86%A0</t>
-  </si>
-  <si>
-    <t>2조 1614억 5837만</t>
-  </si>
-  <si>
-    <t>밍고스틴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
-  </si>
-  <si>
-    <t>2조 1440억 966만</t>
-  </si>
-  <si>
-    <t>l우주아이l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=l%EC%9A%B0%EC%A3%BC%EC%95%84%EC%9D%B4l</t>
-  </si>
-  <si>
-    <t>2조 24억 4824만</t>
-  </si>
-  <si>
-    <t>김주왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
-  </si>
-  <si>
-    <t>1조 9739억 7744만</t>
-  </si>
-  <si>
-    <t>아쿠마불독</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
-  </si>
-  <si>
-    <t>1조 7776억 1533만</t>
-  </si>
-  <si>
-    <t>l성연l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=l%EC%84%B1%EC%97%B0l</t>
-  </si>
-  <si>
-    <t>1조 7306억 4932만</t>
-  </si>
-  <si>
-    <t>몽실망실토실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>1조 4533억 737만</t>
-  </si>
-  <si>
-    <t>오늘밤은삐딱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%8A%98%EB%B0%A4%EC%9D%80%EC%82%90%EB%94%B1</t>
-  </si>
-  <si>
     <t>1조 4441억 2474만</t>
   </si>
   <si>
-    <t>타락파워스님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1조 4039억 1202만</t>
-  </si>
-  <si>
     <t>2D파트장</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
   </si>
   <si>
-    <t>1조 558억 316만</t>
+    <t>1조 852억 4409만</t>
   </si>
   <si>
     <t>체시어</t>
@@ -939,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
   </si>
   <si>
-    <t>8117억 9060만</t>
+    <t>8131억 7811만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -948,7 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
   </si>
   <si>
-    <t>7135억 2533만</t>
+    <t>7988억 2463만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
@@ -957,7 +948,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>63조 709억 7251만</t>
+    <t>65조 9169억 3683만</t>
   </si>
   <si>
     <t>멈디</t>
@@ -966,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
   </si>
   <si>
-    <t>9조 8949억 9692만</t>
+    <t>10조 7386억 7227만</t>
   </si>
   <si>
     <t>유랑민</t>
@@ -984,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
   </si>
   <si>
-    <t>7조 3316억 9144만</t>
+    <t>7조 4032억 3525만</t>
   </si>
   <si>
     <t>포도맛맥플</t>
@@ -993,7 +984,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
   </si>
   <si>
-    <t>6조 7242억 9747만</t>
+    <t>6조 7589억 8990만</t>
   </si>
   <si>
     <t>김롸아</t>
@@ -1002,7 +993,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
   </si>
   <si>
-    <t>5조 5660억 6217만</t>
+    <t>5조 6993억 2936만</t>
+  </si>
+  <si>
+    <t>우치앵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
+  </si>
+  <si>
+    <t>5조 6337억 4302만</t>
   </si>
   <si>
     <t>연바기</t>
@@ -1020,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>5조 3516억 9005만</t>
+    <t>5조 3640억 5132만</t>
   </si>
   <si>
     <t>또긔</t>
@@ -1029,7 +1029,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
   </si>
   <si>
-    <t>5조 2991억 2456만</t>
+    <t>5조 3242억 7793만</t>
+  </si>
+  <si>
+    <t>린샹판</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
+  </si>
+  <si>
+    <t>5조 1400억 2266만</t>
   </si>
   <si>
     <t>썬콜법사도희</t>
@@ -1068,15 +1077,6 @@
     <t>4조 7051억 84만</t>
   </si>
   <si>
-    <t>우치앵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
-  </si>
-  <si>
-    <t>4조 4852억 9083만</t>
-  </si>
-  <si>
     <t>A7R4</t>
   </si>
   <si>
@@ -1086,15 +1086,6 @@
     <t>4조 4816억 9310만</t>
   </si>
   <si>
-    <t>린샹판</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
-  </si>
-  <si>
-    <t>4조 4684억 3530만</t>
-  </si>
-  <si>
     <t>불곰파워</t>
   </si>
   <si>
@@ -1110,7 +1101,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
   </si>
   <si>
-    <t>3조 7502억 4877만</t>
+    <t>3조 7626억 5636만</t>
+  </si>
+  <si>
+    <t>썹웨피망빼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
+  </si>
+  <si>
+    <t>3조 7546억 9317만</t>
   </si>
   <si>
     <t>히어로경원</t>
@@ -1119,7 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
   </si>
   <si>
-    <t>3조 6715억 746만</t>
+    <t>3조 7050억 6754만</t>
   </si>
   <si>
     <t>구파발메타몽</t>
@@ -1128,16 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
   </si>
   <si>
-    <t>3조 5209억 8214만</t>
-  </si>
-  <si>
-    <t>썹웨피망빼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
-  </si>
-  <si>
-    <t>3조 4938억 6546만</t>
+    <t>3조 5626억 2994만</t>
   </si>
   <si>
     <t>투둠</t>
@@ -1146,7 +1137,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
   </si>
   <si>
-    <t>3조 3481억 2261만</t>
+    <t>3조 4886억 4870만</t>
+  </si>
+  <si>
+    <t>도윤파덜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
+  </si>
+  <si>
+    <t>3조 2595억 5924만</t>
+  </si>
+  <si>
+    <t>zl지존썬콜lz</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
+  </si>
+  <si>
+    <t>3조 1273억 1464만</t>
   </si>
   <si>
     <t>무쿠미</t>
@@ -1158,24 +1167,6 @@
     <t>3조 1114억 9712만</t>
   </si>
   <si>
-    <t>도윤파덜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
-  </si>
-  <si>
-    <t>3조 425억 7859만</t>
-  </si>
-  <si>
-    <t>zl지존썬콜lz</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
-  </si>
-  <si>
-    <t>3조 129억 6771만</t>
-  </si>
-  <si>
     <t>용날라가유</t>
   </si>
   <si>
@@ -1191,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 7891억 5193만</t>
+    <t>2조 7930억 5041만</t>
   </si>
   <si>
     <t>극쪽이</t>
@@ -1200,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 4836억 6380만</t>
+    <t>1조 5699억 649만</t>
   </si>
   <si>
     <t>토리파더</t>
@@ -1209,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>7631억 8989만</t>
+    <t>7703억 104만</t>
   </si>
   <si>
     <t>닼나왕</t>
@@ -1221,7 +1212,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1279억 8370만</t>
+    <t>1362억 8894만</t>
   </si>
   <si>
     <t>상현별</t>
@@ -1230,7 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
   </si>
   <si>
-    <t>67조 8159억 3094만</t>
+    <t>68조 1997억 2808만</t>
   </si>
   <si>
     <t>말랑콩닥</t>
@@ -1239,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
   </si>
   <si>
-    <t>23조 4649억 2048만</t>
+    <t>23조 6316억 3798만</t>
   </si>
   <si>
     <t>안루핑</t>
@@ -1293,7 +1284,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%83%81%EA%B8%89%EC%A1%B0%EC%A4%80%EA%B2%BD</t>
   </si>
   <si>
-    <t>6조 684억 9571만</t>
+    <t>6조 6585억 6602만</t>
   </si>
   <si>
     <t>감자도리유지</t>
@@ -1320,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EB%B9%84%ED%94%BC</t>
   </si>
   <si>
-    <t>5조 8405억 3727만</t>
+    <t>5조 8472억 3465만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
@@ -1335,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
   </si>
   <si>
-    <t>3조 8401억 1645만</t>
+    <t>4조 1678억 7437만</t>
   </si>
   <si>
     <t>용감한순대국</t>
@@ -1353,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
   </si>
   <si>
-    <t>2조 8075억 5141만</t>
+    <t>2조 8458억 4628만</t>
   </si>
   <si>
     <t>곱션이</t>
@@ -1362,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EC%85%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 5677억 5836만</t>
+    <t>2조 5899억 3096만</t>
   </si>
   <si>
     <t>양념반탈리반</t>
@@ -1392,6 +1383,15 @@
     <t>2조 1139억 4649만</t>
   </si>
   <si>
+    <t>쿰척쿰쳑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
+  </si>
+  <si>
+    <t>2조 972억 4800만</t>
+  </si>
+  <si>
     <t>신궁초보</t>
   </si>
   <si>
@@ -1401,15 +1401,6 @@
     <t>2조 483억 9026만</t>
   </si>
   <si>
-    <t>쿰척쿰쳑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
-  </si>
-  <si>
-    <t>2조 405억 4024만</t>
-  </si>
-  <si>
     <t>판별식</t>
   </si>
   <si>
@@ -1419,6 +1410,15 @@
     <t>1조 9179억 5132만</t>
   </si>
   <si>
+    <t>옹야미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>1조 7700억 2940만</t>
+  </si>
+  <si>
     <t>루맹이</t>
   </si>
   <si>
@@ -1428,22 +1428,13 @@
     <t>1조 6759억 7300만</t>
   </si>
   <si>
-    <t>옹야미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1조 6078억 1739만</t>
-  </si>
-  <si>
     <t>츄쁜</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
   </si>
   <si>
-    <t>1조 1058억 9560만</t>
+    <t>1조 1335억 4299만</t>
   </si>
   <si>
     <t>박마리아</t>
@@ -1455,7 +1446,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>1조 637억 4045만</t>
+    <t>1조 645억 5505만</t>
   </si>
   <si>
     <t>한닝</t>
@@ -1464,7 +1455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
   </si>
   <si>
-    <t>9670억 758만</t>
+    <t>9945억 8723만</t>
   </si>
   <si>
     <t>뮴뮴뮴뮴뮴</t>
@@ -1473,7 +1464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4</t>
   </si>
   <si>
-    <t>6946억 6245만</t>
+    <t>8061억 1941만</t>
   </si>
   <si>
     <t>놀면머하니</t>
@@ -1485,7 +1476,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>5440억 5993만</t>
+    <t>5456억 6511만</t>
   </si>
   <si>
     <t>키워봄</t>
@@ -1500,7 +1491,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>3947억 2191만</t>
+    <t>4043억 1390만</t>
   </si>
   <si>
     <t>량용</t>
@@ -1512,7 +1503,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>67조 8839억 2862만</t>
+    <t>68조 4417억 7851만</t>
   </si>
   <si>
     <t>달봉e</t>
@@ -1554,7 +1545,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>6조 3383억 866만</t>
+    <t>6조 4753억 1198만</t>
   </si>
   <si>
     <t>핫딜패스</t>
@@ -1584,6 +1575,15 @@
     <t>4조 3133억 5612만</t>
   </si>
   <si>
+    <t>빅밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>3조 8230억 4635만</t>
+  </si>
+  <si>
     <t>하콩치</t>
   </si>
   <si>
@@ -1602,22 +1602,13 @@
     <t>3조 7517억 4264만</t>
   </si>
   <si>
-    <t>빅밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>3조 7406억 6792만</t>
-  </si>
-  <si>
     <t>템플스테이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%ED%94%8C%EC%8A%A4%ED%85%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 7306억 1403만</t>
+    <t>3조 7511억 4873만</t>
   </si>
   <si>
     <t>아무렇게할래</t>
@@ -1629,6 +1620,15 @@
     <t>3조 2335억 9930만</t>
   </si>
   <si>
+    <t>유쥬아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A5%AC%EC%95%84</t>
+  </si>
+  <si>
+    <t>2조 8014억 6559만</t>
+  </si>
+  <si>
     <t>Scope</t>
   </si>
   <si>
@@ -1644,7 +1644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 2588억 477만</t>
+    <t>2조 3212억 9041만</t>
   </si>
   <si>
     <t>리디엘</t>
@@ -1653,7 +1653,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%94%94%EC%97%98</t>
   </si>
   <si>
-    <t>2조 982억 6070만</t>
+    <t>2조 2974억 3159만</t>
   </si>
   <si>
     <t>별잇</t>
@@ -1662,7 +1662,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%9E%87</t>
   </si>
   <si>
-    <t>1조 9778억 5655만</t>
+    <t>2조 2286억 8898만</t>
+  </si>
+  <si>
+    <t>부울가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%9A%B8%EA%B0%80</t>
+  </si>
+  <si>
+    <t>1조 9067억 4086만</t>
   </si>
   <si>
     <t>흙심이</t>
@@ -1680,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=Azham</t>
   </si>
   <si>
-    <t>1조 7638억 9086만</t>
+    <t>1조 7844억 564만</t>
   </si>
   <si>
     <t>떠하야</t>
@@ -1689,7 +1698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%ED%95%98%EC%95%BC</t>
   </si>
   <si>
-    <t>1조 7555억 1188만</t>
+    <t>1조 7727억 9821만</t>
   </si>
   <si>
     <t>Porto</t>
@@ -1707,7 +1716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A6%88%EB%A4%BC%EC%96%BC</t>
   </si>
   <si>
-    <t>1조 4396억 2824만</t>
+    <t>1조 4582억 1847만</t>
   </si>
   <si>
     <t>비라비스</t>
@@ -1716,7 +1725,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%9D%BC%EB%B9%84%EC%8A%A4</t>
   </si>
   <si>
-    <t>1조 1712억 9229만</t>
+    <t>1조 3316억 488만</t>
+  </si>
+  <si>
+    <t>쥐이에이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8780억 2867만</t>
   </si>
   <si>
     <t>후려까기</t>
@@ -1728,22 +1746,13 @@
     <t>8636억 9674만</t>
   </si>
   <si>
-    <t>쥐이에이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8534억 7427만</t>
-  </si>
-  <si>
     <t>뽀미l</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
   </si>
   <si>
-    <t>6413억 5862만</t>
+    <t>7614억 9229만</t>
   </si>
   <si>
     <t>짜뇨</t>
@@ -1752,7 +1761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%87%A8</t>
   </si>
   <si>
-    <t>5962억 6625만</t>
+    <t>6391억 6462만</t>
   </si>
   <si>
     <t>동띠</t>
@@ -1785,7 +1794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
   </si>
   <si>
-    <t>6조 3037억 7810만</t>
+    <t>6조 3121억 6486만</t>
   </si>
   <si>
     <t>숍솝</t>
@@ -1803,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%8F%99%EB%9D%A0</t>
   </si>
   <si>
-    <t>3조 5363억 2259만</t>
+    <t>3조 5398억 5386만</t>
   </si>
   <si>
     <t>정뽀</t>
@@ -1821,7 +1830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8939억 2968만</t>
+    <t>1조 9459억 5450만</t>
   </si>
   <si>
     <t>지구뿌셔</t>
@@ -1830,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>1조 7889억 4240만</t>
+    <t>1조 7949억 2734만</t>
   </si>
   <si>
     <t>꼬햄</t>
@@ -1848,7 +1857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%9B</t>
   </si>
   <si>
-    <t>1조 1533억 9299만</t>
+    <t>1조 1560억 3647만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1857,7 +1866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
   </si>
   <si>
-    <t>8968억 7516만</t>
+    <t>9421억 6228만</t>
   </si>
   <si>
     <t>자쿰키우기</t>
@@ -1866,7 +1875,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%BF%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>8415억 3336만</t>
+    <t>8961억 7322만</t>
+  </si>
+  <si>
+    <t>다릿골</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%A6%BF%EA%B3%A8</t>
+  </si>
+  <si>
+    <t>7522억 3055만</t>
   </si>
   <si>
     <t>갓굴</t>
@@ -1875,16 +1893,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
   </si>
   <si>
-    <t>7297억 224만</t>
-  </si>
-  <si>
-    <t>다릿골</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%A6%BF%EA%B3%A8</t>
-  </si>
-  <si>
-    <t>7294억 9184만</t>
+    <t>7372억 158만</t>
   </si>
   <si>
     <t>귀쮸</t>
@@ -1893,7 +1902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
   </si>
   <si>
-    <t>6115억 4518만</t>
+    <t>6330억 9543만</t>
   </si>
   <si>
     <t>당겨쏴</t>
@@ -1902,7 +1911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B2%A8%EC%8F%B4</t>
   </si>
   <si>
-    <t>5830억 5561만</t>
+    <t>5840억 6560만</t>
   </si>
   <si>
     <t>은단월</t>
@@ -1911,7 +1920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
   </si>
   <si>
-    <t>5148억 4658만</t>
+    <t>5473억 8620만</t>
   </si>
   <si>
     <t>Viceversa</t>
@@ -1938,7 +1947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
   </si>
   <si>
-    <t>4517억 5087만</t>
+    <t>4586억 7349만</t>
   </si>
   <si>
     <t>비비다</t>
@@ -1956,7 +1965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%841%EC%9A%A9</t>
   </si>
   <si>
-    <t>3824억 1297만</t>
+    <t>3832억 2080만</t>
   </si>
   <si>
     <t>사과클럽</t>
@@ -1965,7 +1974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
   </si>
   <si>
-    <t>3657억 6955만</t>
+    <t>3754억 2462만</t>
   </si>
   <si>
     <t>차눅</t>
@@ -1974,7 +1983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
   </si>
   <si>
-    <t>3359억 9618만</t>
+    <t>3380억 8111만</t>
   </si>
   <si>
     <t>팔나무</t>
@@ -1983,7 +1992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%82%98%EB%AC%B4</t>
   </si>
   <si>
-    <t>2956억 3727만</t>
+    <t>2966억 3542만</t>
   </si>
   <si>
     <t>53다2329</t>
@@ -1995,7 +2004,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>2440억 2766만</t>
+    <t>2465억 5851만</t>
   </si>
   <si>
     <t>나루토토</t>
@@ -2031,13 +2040,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%8F%AC%EC%A7%93</t>
   </si>
   <si>
-    <t>3조 8153억 5647만</t>
+    <t>4조 710억 9220만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=86%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>3조 624억 6790만</t>
+    <t>3조 1058억 738만</t>
   </si>
   <si>
     <t>다있다하노</t>
@@ -2046,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 3604억 8429만</t>
+    <t>2조 4069억 8692만</t>
   </si>
   <si>
     <t>델타시그마</t>
@@ -2055,7 +2064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>2조 2674억 4642만</t>
+    <t>2조 2706억 9400만</t>
   </si>
   <si>
     <t>꿍물</t>
@@ -2073,7 +2082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>2조 1249억 8884만</t>
+    <t>2조 1279억 8468만</t>
   </si>
   <si>
     <t>끽스</t>
@@ -2082,7 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
   </si>
   <si>
-    <t>2조 1193억 2989만</t>
+    <t>2조 1219억 3007만</t>
   </si>
   <si>
     <t>흑인드록바</t>
@@ -2100,7 +2109,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
   </si>
   <si>
-    <t>1조 9217억 3565만</t>
+    <t>1조 9550억 7808만</t>
   </si>
   <si>
     <t>전팡</t>
@@ -2118,7 +2127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1조 7983억 71만</t>
+    <t>1조 8123억 1510만</t>
   </si>
   <si>
     <t>밀가루죽</t>
@@ -2127,7 +2136,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EA%B0%80%EB%A3%A8%EC%A3%BD</t>
   </si>
   <si>
-    <t>1조 7454억 2451만</t>
+    <t>1조 7994억 3437만</t>
+  </si>
+  <si>
+    <t>야로야옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
+  </si>
+  <si>
+    <t>1조 5975억 8791만</t>
   </si>
   <si>
     <t>또유유</t>
@@ -2139,22 +2157,13 @@
     <t>1조 5245억 986만</t>
   </si>
   <si>
-    <t>야로야옹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
-  </si>
-  <si>
-    <t>1조 4904억 8375만</t>
-  </si>
-  <si>
     <t>웅잉당</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>1조 3836억 1749만</t>
+    <t>1조 3968억 6957만</t>
   </si>
   <si>
     <t>사람님아</t>
@@ -2163,7 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
   </si>
   <si>
-    <t>1조 2994억 5609만</t>
+    <t>1조 3126억 2740만</t>
   </si>
   <si>
     <t>흑인햄찌</t>
@@ -2199,7 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
   </si>
   <si>
-    <t>9396억 6014만</t>
+    <t>9697억 2044만</t>
   </si>
   <si>
     <t>하랸</t>
@@ -2208,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
   </si>
   <si>
-    <t>9305억 1567만</t>
+    <t>9395억 8417만</t>
   </si>
   <si>
     <t>존못에겐남짱</t>
@@ -2217,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
   </si>
   <si>
-    <t>8568억 6399만</t>
+    <t>8763억 6277만</t>
   </si>
   <si>
     <t>섀레기</t>
@@ -2244,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%9A%B8%EC%95%84%EC%9A%B0</t>
   </si>
   <si>
-    <t>7654억 5939만</t>
+    <t>8342억 9381만</t>
   </si>
   <si>
     <t>스피드노멘</t>
@@ -2262,7 +2271,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
   </si>
   <si>
-    <t>6892억 3166만</t>
+    <t>7075억 5483만</t>
+  </si>
+  <si>
+    <t>아임몽순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9E%84%EB%AA%BD%EC%88%9C</t>
+  </si>
+  <si>
+    <t>4816억 386만</t>
   </si>
   <si>
     <t>두부장구니</t>
@@ -2271,19 +2289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B6%80%EC%9E%A5%EA%B5%AC%EB%8B%88</t>
   </si>
   <si>
-    <t>4802억 7206만</t>
-  </si>
-  <si>
-    <t>아임몽순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9E%84%EB%AA%BD%EC%88%9C</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>4719억 7445만</t>
+    <t>4812억 8494만</t>
   </si>
   <si>
     <t>오리박사</t>
@@ -2776,10 +2782,10 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>31</v>
@@ -2856,17 +2862,17 @@
         <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2874,31 +2880,31 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>53</v>
@@ -2927,7 +2933,7 @@
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>58</v>
@@ -2936,7 +2942,7 @@
         <v>59</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
@@ -3207,7 +3213,7 @@
         <v>108</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>109</v>
@@ -3335,10 +3341,10 @@
         <v>125</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3349,25 +3355,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>132</v>
@@ -3399,7 +3405,7 @@
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>136</v>
@@ -3431,7 +3437,7 @@
         <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>140</v>
@@ -3460,10 +3466,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>144</v>
@@ -3492,13 +3498,13 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3509,25 +3515,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>153</v>
@@ -3556,7 +3562,7 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>157</v>
@@ -3588,10 +3594,10 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>162</v>
@@ -3620,10 +3626,10 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>166</v>
@@ -3655,7 +3661,7 @@
         <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>170</v>
@@ -3687,7 +3693,7 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>174</v>
@@ -3716,10 +3722,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>178</v>
@@ -3748,10 +3754,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>182</v>
@@ -3783,7 +3789,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>186</v>
@@ -3815,7 +3821,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>190</v>
@@ -3879,7 +3885,7 @@
         <v>108</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>198</v>
@@ -3908,13 +3914,13 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3925,28 +3931,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="H29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3957,16 +3963,16 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
@@ -3975,10 +3981,10 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3989,16 +3995,16 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
@@ -4007,10 +4013,10 @@
         <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4056,7 +4062,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4109,25 +4115,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>91</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4141,13 +4147,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
@@ -4159,7 +4165,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4173,13 +4179,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
@@ -4188,10 +4194,10 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4205,25 +4211,25 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4243,7 +4249,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>82</v>
@@ -4252,10 +4258,10 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4269,13 +4275,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -4287,7 +4293,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4301,25 +4307,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4333,13 +4339,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
@@ -4348,10 +4354,10 @@
         <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4365,13 +4371,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -4380,10 +4386,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4394,28 +4400,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4429,25 +4435,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4461,25 +4467,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4493,25 +4499,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4525,13 +4531,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
@@ -4540,10 +4546,10 @@
         <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4554,28 +4560,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>157</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4589,25 +4595,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4621,25 +4627,25 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4653,13 +4659,13 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -4668,10 +4674,10 @@
         <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4685,25 +4691,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4717,25 +4723,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4749,25 +4755,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4781,25 +4787,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4813,25 +4819,25 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4845,13 +4851,13 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
@@ -4860,10 +4866,10 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4877,25 +4883,25 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4909,13 +4915,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -4924,7 +4930,7 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>293</v>
@@ -4953,10 +4959,10 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>296</v>
@@ -4970,7 +4976,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>297</v>
@@ -4985,10 +4991,10 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>152</v>
+        <v>292</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>299</v>
@@ -5002,7 +5008,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>300</v>
@@ -5017,10 +5023,10 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>302</v>
@@ -5029,40 +5035,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5093,7 +5067,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5110,7 +5083,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5160,19 +5133,19 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5186,25 +5159,25 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5218,13 +5191,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
@@ -5236,7 +5209,7 @@
         <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5250,13 +5223,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
@@ -5268,7 +5241,7 @@
         <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5282,13 +5255,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
@@ -5300,7 +5273,7 @@
         <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5314,13 +5287,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -5332,7 +5305,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5346,25 +5319,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5378,25 +5351,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5410,13 +5383,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -5428,7 +5401,7 @@
         <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5439,28 +5412,28 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5474,25 +5447,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5506,25 +5479,25 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5538,25 +5511,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5570,25 +5543,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5599,16 +5572,16 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -5617,10 +5590,10 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5634,25 +5607,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5666,13 +5639,13 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
@@ -5684,7 +5657,7 @@
         <v>103</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5698,13 +5671,13 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -5713,10 +5686,10 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5730,25 +5703,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5762,25 +5735,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5794,25 +5767,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5826,13 +5799,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
@@ -5841,10 +5814,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5858,13 +5831,13 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
@@ -5873,10 +5846,10 @@
         <v>125</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5890,25 +5863,25 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5922,25 +5895,25 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5954,25 +5927,25 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5986,13 +5959,13 @@
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -6004,7 +5977,7 @@
         <v>103</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6015,28 +5988,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6047,16 +6020,16 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
@@ -6065,10 +6038,10 @@
         <v>108</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6079,16 +6052,16 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
@@ -6097,10 +6070,10 @@
         <v>96</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6199,13 +6172,13 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
@@ -6217,7 +6190,7 @@
         <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6231,13 +6204,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
@@ -6249,7 +6222,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6263,25 +6236,25 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6295,13 +6268,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
@@ -6310,10 +6283,10 @@
         <v>96</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6327,13 +6300,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
@@ -6345,7 +6318,7 @@
         <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6359,13 +6332,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -6374,10 +6347,10 @@
         <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6391,13 +6364,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
@@ -6406,10 +6379,10 @@
         <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6423,25 +6396,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6455,25 +6428,25 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6484,28 +6457,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6519,13 +6492,13 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
@@ -6534,10 +6507,10 @@
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6551,13 +6524,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>82</v>
@@ -6566,10 +6539,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6583,13 +6556,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
@@ -6598,10 +6571,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6615,13 +6588,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
@@ -6630,10 +6603,10 @@
         <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6644,16 +6617,16 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -6662,10 +6635,10 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6679,13 +6652,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
@@ -6694,10 +6667,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6711,13 +6684,13 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
@@ -6726,10 +6699,10 @@
         <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6743,25 +6716,25 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6775,25 +6748,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6807,25 +6780,25 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6839,25 +6812,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6871,13 +6844,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
@@ -6886,10 +6859,10 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6903,25 +6876,25 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6935,25 +6908,25 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6967,13 +6940,13 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
@@ -6982,10 +6955,10 @@
         <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6999,13 +6972,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -7014,10 +6987,10 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7031,13 +7004,13 @@
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -7046,10 +7019,10 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7060,28 +7033,28 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7092,28 +7065,28 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7124,28 +7097,28 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7191,7 +7164,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7238,31 +7211,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -7270,31 +7243,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -7302,31 +7275,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -7334,7 +7307,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
@@ -7346,7 +7319,7 @@
         <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>82</v>
@@ -7358,7 +7331,7 @@
         <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -7366,31 +7339,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -7398,19 +7371,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -7422,7 +7395,7 @@
         <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -7430,19 +7403,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
@@ -7451,10 +7424,10 @@
         <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -7462,31 +7435,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -7494,19 +7467,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -7515,10 +7488,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -7526,31 +7499,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -7558,31 +7531,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -7590,31 +7563,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -7622,31 +7595,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7654,31 +7627,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7686,31 +7659,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7718,31 +7691,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7750,31 +7723,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7782,31 +7755,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>307</v>
+        <v>131</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7814,31 +7787,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7846,31 +7819,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>307</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7878,31 +7851,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>96</v>
+        <v>304</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7910,31 +7883,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>304</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7942,31 +7915,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7974,31 +7947,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>307</v>
+        <v>131</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8006,31 +7979,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>473</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -8038,31 +8011,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>96</v>
+        <v>304</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -8070,31 +8043,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>473</v>
+        <v>157</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -8102,38 +8075,102 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="H31" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -8163,6 +8200,8 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8223,25 +8262,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -8255,13 +8294,13 @@
         <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
@@ -8273,7 +8312,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -8293,7 +8332,7 @@
         <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>82</v>
@@ -8305,7 +8344,7 @@
         <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -8319,25 +8358,25 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -8351,13 +8390,13 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
@@ -8366,10 +8405,10 @@
         <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -8383,25 +8422,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -8415,25 +8454,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -8447,25 +8486,25 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -8479,25 +8518,25 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -8508,16 +8547,16 @@
         <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
@@ -8526,10 +8565,10 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -8543,25 +8582,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -8575,13 +8614,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
@@ -8590,10 +8629,10 @@
         <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -8607,13 +8646,13 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
@@ -8622,10 +8661,10 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -8639,13 +8678,13 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
@@ -8654,10 +8693,10 @@
         <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>207</v>
+        <v>485</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -8668,16 +8707,16 @@
         <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
@@ -8686,10 +8725,10 @@
         <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>488</v>
+        <v>292</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8703,13 +8742,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
@@ -8718,10 +8757,10 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -8735,13 +8774,13 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
@@ -8750,10 +8789,10 @@
         <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -8767,25 +8806,25 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -8799,25 +8838,25 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -8831,13 +8870,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
@@ -8846,10 +8885,10 @@
         <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -8863,25 +8902,25 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -8895,25 +8934,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -8927,13 +8966,13 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
@@ -8942,10 +8981,10 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -8959,13 +8998,13 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
@@ -8974,10 +9013,10 @@
         <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -8991,13 +9030,13 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
@@ -9006,10 +9045,10 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9023,13 +9062,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -9038,10 +9077,10 @@
         <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -9055,25 +9094,25 @@
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9084,28 +9123,28 @@
         <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -9116,28 +9155,28 @@
         <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -9148,28 +9187,28 @@
         <v>56</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -9268,25 +9307,25 @@
         <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -9306,7 +9345,7 @@
         <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>82</v>
@@ -9315,10 +9354,10 @@
         <v>90</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -9332,13 +9371,13 @@
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>89</v>
@@ -9347,10 +9386,10 @@
         <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -9364,13 +9403,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>89</v>
@@ -9379,10 +9418,10 @@
         <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -9396,25 +9435,25 @@
         <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -9428,13 +9467,13 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>89</v>
@@ -9443,10 +9482,10 @@
         <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -9460,25 +9499,25 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -9492,13 +9531,13 @@
         <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>89</v>
@@ -9507,10 +9546,10 @@
         <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -9524,13 +9563,13 @@
         <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>89</v>
@@ -9539,10 +9578,10 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -9553,16 +9592,16 @@
         <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>89</v>
@@ -9571,10 +9610,10 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -9588,25 +9627,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -9620,13 +9659,13 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>89</v>
@@ -9635,10 +9674,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -9652,25 +9691,25 @@
         <v>141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -9684,25 +9723,25 @@
         <v>145</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>152</v>
+        <v>292</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -9713,28 +9752,28 @@
         <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -9748,25 +9787,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -9780,13 +9819,13 @@
         <v>159</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>89</v>
@@ -9795,10 +9834,10 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -9812,25 +9851,25 @@
         <v>163</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -9844,13 +9883,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>89</v>
@@ -9859,10 +9898,10 @@
         <v>90</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -9876,13 +9915,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>89</v>
@@ -9891,10 +9930,10 @@
         <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -9908,13 +9947,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>89</v>
@@ -9923,10 +9962,10 @@
         <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -9940,25 +9979,25 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>473</v>
+        <v>292</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -9972,13 +10011,13 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>89</v>
@@ -9987,10 +10026,10 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -10004,25 +10043,25 @@
         <v>187</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -10036,25 +10075,25 @@
         <v>191</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -10068,13 +10107,13 @@
         <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>89</v>
@@ -10083,10 +10122,10 @@
         <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -10100,25 +10139,25 @@
         <v>199</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -10129,28 +10168,28 @@
         <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -10161,28 +10200,28 @@
         <v>63</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>749</v>
+        <v>480</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -10193,16 +10232,16 @@
         <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>89</v>
@@ -10211,10 +10250,10 @@
         <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>394</t>
+    <t>388</t>
   </si>
   <si>
     <t>13위</t>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>210조 1486억 3414만</t>
+    <t>220조 3391억 950만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,7 +105,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.26</t>
+    <t>2026.04.27</t>
   </si>
   <si>
     <t>다다익선</t>
@@ -117,7 +117,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>348</t>
+    <t>347</t>
   </si>
   <si>
     <t>7위</t>
@@ -126,7 +126,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>263조 1222억 3913만</t>
+    <t>270조 6099억 3096만</t>
   </si>
   <si>
     <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 2조 이상 재밌게 소통하면서 게임하실 분 공대애봉이/뒁글 문의 주세요</t>
@@ -144,34 +144,37 @@
     <t>Scania 18</t>
   </si>
   <si>
-    <t>408</t>
+    <t>404</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>203조 5486억 2127만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
+    <t>블랙소울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
+    <t>390</t>
   </si>
   <si>
     <t>9위</t>
   </si>
   <si>
-    <t>195조 4102억 9368만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
-    <t>블랙소울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
     <t>Lv.7</t>
   </si>
   <si>
-    <t>211조 7872억 5105만</t>
+    <t>217조 2992억 4294만</t>
   </si>
   <si>
     <t>보심</t>
@@ -186,13 +189,13 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>31위</t>
-  </si>
-  <si>
-    <t>219조 2372억 9866만</t>
+    <t>375</t>
+  </si>
+  <si>
+    <t>32위</t>
+  </si>
+  <si>
+    <t>231조 4366억 4246만</t>
   </si>
   <si>
     <t>비련길드 모집조건 : 투력 9000억 이상 일일기부 300+ 길컨 참여자</t>
@@ -207,13 +210,13 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>220조 4726억 4089만</t>
+    <t>368</t>
+  </si>
+  <si>
+    <t>29위</t>
+  </si>
+  <si>
+    <t>236조 8897억 1137만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요</t>
@@ -231,16 +234,13 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>990</t>
-  </si>
-  <si>
-    <t>8위</t>
+    <t>986</t>
   </si>
   <si>
     <t>Lv.6</t>
   </si>
   <si>
-    <t>44조 9248억 967만</t>
+    <t>46조 7509억 9810만</t>
   </si>
   <si>
     <t>*투력 3조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
@@ -288,21 +288,39 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 7523억 2933만</t>
+    <t>31조 4685억 9720만</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>21조 8866억 2814만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>큐샤프</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>신궁</t>
   </si>
   <si>
@@ -312,24 +330,6 @@
     <t>20조 8772억 7416만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>18조 9253억 9203만</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -345,7 +345,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>13조 9322억 7271만</t>
+    <t>14조 8623억 2147만</t>
   </si>
   <si>
     <t>5</t>
@@ -384,7 +384,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6716억 4082만</t>
+    <t>7조 6801억 1998만</t>
   </si>
   <si>
     <t>8</t>
@@ -396,7 +396,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 3311억 6274만</t>
+    <t>7조 5286억 8021만</t>
   </si>
   <si>
     <t>9</t>
@@ -414,7 +414,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>6조 8265억 4136만</t>
+    <t>7조 1219억 6098만</t>
   </si>
   <si>
     <t>10</t>
@@ -435,6 +435,18 @@
     <t>11</t>
   </si>
   <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>6조 5215억 1858만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
@@ -444,31 +456,58 @@
     <t>6조 4649억 8468만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>5조 4515억 8769만</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>5조 2258억 7841만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>흑두부</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 9811억 5357만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>5조 339억 2537만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 7304억 2040만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>4조 6479억 5302만</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -483,67 +522,28 @@
     <t>4조 6273억 4164만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>4조 5621억 2305만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>4조 5139억 1714만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>4조 3613억 1130만</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>4조 1571억 2932만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>4조 768억 9265만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>4조 366억 9775만</t>
+    <t>4조 1213억 1333만</t>
   </si>
   <si>
     <t>20</t>
@@ -555,7 +555,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>3조 9589억 1764만</t>
+    <t>3조 9882억 292만</t>
   </si>
   <si>
     <t>21</t>
@@ -579,7 +579,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 3304억 6250만</t>
+    <t>3조 4067억 1103만</t>
   </si>
   <si>
     <t>23</t>
@@ -591,12 +591,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 9156억 802만</t>
+    <t>2조 9483억 6909만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 8743억 5331만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>제스프리</t>
   </si>
   <si>
@@ -606,18 +618,6 @@
     <t>2조 7544억 4887만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 7249억 3293만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
   </si>
   <si>
-    <t>33조 9782억 3943만</t>
+    <t>37조 4129억 6987만</t>
   </si>
   <si>
     <t>뒁글</t>
@@ -714,13 +714,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
   </si>
   <si>
-    <t>11조 179억 4686만</t>
+    <t>11조 4219억 6965만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
   </si>
   <si>
-    <t>10조 6618억 761만</t>
+    <t>10조 9679억 8977만</t>
   </si>
   <si>
     <t>나윤v파파</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>8조 2733억 5797만</t>
+    <t>9조 2443억 7097만</t>
   </si>
   <si>
     <t>공대애봉이</t>
@@ -750,22 +750,31 @@
     <t>5조 8317억 2691만</t>
   </si>
   <si>
+    <t>우타이테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
+  </si>
+  <si>
+    <t>4조 1479억 6666만</t>
+  </si>
+  <si>
     <t>묘목키우기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>3조 8072억 7398만</t>
-  </si>
-  <si>
-    <t>우타이테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
-  </si>
-  <si>
-    <t>3조 7854억 968만</t>
+    <t>3조 8582억 8749만</t>
+  </si>
+  <si>
+    <t>따뜻한배추</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
+  </si>
+  <si>
+    <t>3조 8367억 2418만</t>
   </si>
   <si>
     <t>JAEYA</t>
@@ -774,7 +783,7 @@
     <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
   </si>
   <si>
-    <t>3조 6163억 8359만</t>
+    <t>3조 7985억 8217만</t>
   </si>
   <si>
     <t>토르릿</t>
@@ -783,16 +792,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
   </si>
   <si>
-    <t>3조 5930억 2375만</t>
-  </si>
-  <si>
-    <t>따뜻한배추</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
-  </si>
-  <si>
-    <t>3조 3385억 5610만</t>
+    <t>3조 6121억 5751만</t>
   </si>
   <si>
     <t>원투아빠</t>
@@ -801,7 +801,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>3조 1612억 850만</t>
+    <t>3조 4014억 8508만</t>
   </si>
   <si>
     <t>옵션키우기</t>
@@ -810,7 +810,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>3조 1343억 8370만</t>
+    <t>3조 2896억 910만</t>
+  </si>
+  <si>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>3조 2831억 7619만</t>
   </si>
   <si>
     <t>웅쟈쓰</t>
@@ -822,15 +831,6 @@
     <t>3조 839억 9560만</t>
   </si>
   <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>3조 334억 6300만</t>
-  </si>
-  <si>
     <t>범지</t>
   </si>
   <si>
@@ -846,7 +846,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
   </si>
   <si>
-    <t>2조 3213억 7264만</t>
+    <t>2조 6674억 9611만</t>
+  </si>
+  <si>
+    <t>김주왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
+  </si>
+  <si>
+    <t>2조 2096억 7298만</t>
   </si>
   <si>
     <t>맛닭꼬시멘토</t>
@@ -858,15 +867,6 @@
     <t>2조 1614억 5837만</t>
   </si>
   <si>
-    <t>김주왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
-  </si>
-  <si>
-    <t>2조 880억 7176만</t>
-  </si>
-  <si>
     <t>l우주아이l</t>
   </si>
   <si>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
   </si>
   <si>
-    <t>1조 4533억 737만</t>
+    <t>1조 4663억 8243만</t>
   </si>
   <si>
     <t>오늘밤은삐딱</t>
@@ -921,7 +921,7 @@
     <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
   </si>
   <si>
-    <t>1조 852억 4409만</t>
+    <t>1조 1301억 5672만</t>
   </si>
   <si>
     <t>체시어</t>
@@ -930,7 +930,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
   </si>
   <si>
-    <t>8131억 7811만</t>
+    <t>9009억 2311만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -948,7 +948,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>65조 9169억 3683만</t>
+    <t>66조 1265억 2928만</t>
   </si>
   <si>
     <t>멈디</t>
@@ -957,7 +957,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
   </si>
   <si>
-    <t>10조 7386억 7227만</t>
+    <t>10조 9788억 7013만</t>
   </si>
   <si>
     <t>유랑민</t>
@@ -966,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
   </si>
   <si>
-    <t>8조 3698억 9861만</t>
+    <t>9조 6774억 8828만</t>
   </si>
   <si>
     <t>사숩</t>
@@ -975,7 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
   </si>
   <si>
-    <t>7조 4032억 3525만</t>
+    <t>8조 3488억 4354만</t>
   </si>
   <si>
     <t>포도맛맥플</t>
@@ -984,7 +984,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
   </si>
   <si>
-    <t>6조 7589억 8990만</t>
+    <t>6조 9468억 8836만</t>
+  </si>
+  <si>
+    <t>또긔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
+  </si>
+  <si>
+    <t>6조 3143억 2942만</t>
+  </si>
+  <si>
+    <t>연바기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 7389억 6447만</t>
   </si>
   <si>
     <t>김롸아</t>
@@ -1002,16 +1020,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
   </si>
   <si>
-    <t>5조 6337억 4302만</t>
-  </si>
-  <si>
-    <t>연바기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 5028억 9343만</t>
+    <t>5조 6448억 3190만</t>
+  </si>
+  <si>
+    <t>썬콜법사도희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>5조 4528억 9216만</t>
   </si>
   <si>
     <t>단비둘기</t>
@@ -1020,16 +1038,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>5조 3640억 5132만</t>
-  </si>
-  <si>
-    <t>또긔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
-  </si>
-  <si>
-    <t>5조 3242억 7793만</t>
+    <t>5조 4060억 6735만</t>
+  </si>
+  <si>
+    <t>A7R4</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
+  </si>
+  <si>
+    <t>5조 1530억 2524만</t>
   </si>
   <si>
     <t>린샹판</t>
@@ -1041,13 +1059,22 @@
     <t>5조 1400억 2266만</t>
   </si>
   <si>
-    <t>썬콜법사도희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>4조 8953억 1210만</t>
+    <t>까만색양갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>4조 9594억 755만</t>
+  </si>
+  <si>
+    <t>limno</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=limno</t>
+  </si>
+  <si>
+    <t>4조 9037억 6342만</t>
   </si>
   <si>
     <t>스라차차소스</t>
@@ -1056,34 +1083,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
   </si>
   <si>
-    <t>4조 8611억 1747만</t>
-  </si>
-  <si>
-    <t>limno</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=limno</t>
-  </si>
-  <si>
-    <t>4조 8032억 5155만</t>
-  </si>
-  <si>
-    <t>까만색양갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>4조 7051억 84만</t>
-  </si>
-  <si>
-    <t>A7R4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=A7R4</t>
-  </si>
-  <si>
-    <t>4조 4816억 9310만</t>
+    <t>4조 8845억 7960만</t>
+  </si>
+  <si>
+    <t>도윤파덜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
+  </si>
+  <si>
+    <t>4조 865억 4637만</t>
   </si>
   <si>
     <t>불곰파워</t>
@@ -1113,13 +1122,22 @@
     <t>3조 7546억 9317만</t>
   </si>
   <si>
+    <t>무쿠미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>3조 7352억 6496만</t>
+  </si>
+  <si>
     <t>히어로경원</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
   </si>
   <si>
-    <t>3조 7050억 6754만</t>
+    <t>3조 7189억 9950만</t>
   </si>
   <si>
     <t>구파발메타몽</t>
@@ -1128,7 +1146,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
   </si>
   <si>
-    <t>3조 5626억 2994만</t>
+    <t>3조 5928억 836만</t>
   </si>
   <si>
     <t>투둠</t>
@@ -1137,16 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
   </si>
   <si>
-    <t>3조 4886억 4870만</t>
-  </si>
-  <si>
-    <t>도윤파덜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
-  </si>
-  <si>
-    <t>3조 2595억 5924만</t>
+    <t>3조 5378억 413만</t>
   </si>
   <si>
     <t>zl지존썬콜lz</t>
@@ -1155,16 +1164,16 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
   </si>
   <si>
-    <t>3조 1273억 1464만</t>
-  </si>
-  <si>
-    <t>무쿠미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>3조 1114억 9712만</t>
+    <t>3조 2951억 886만</t>
+  </si>
+  <si>
+    <t>구파발고양이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 474억 1671만</t>
   </si>
   <si>
     <t>용날라가유</t>
@@ -1176,22 +1185,13 @@
     <t>2조 8720억 7370만</t>
   </si>
   <si>
-    <t>구파발고양이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2조 7930억 5041만</t>
-  </si>
-  <si>
     <t>극쪽이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 5699억 649만</t>
+    <t>1조 9440억 8941만</t>
   </si>
   <si>
     <t>토리파더</t>
@@ -1200,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>7703억 104만</t>
+    <t>7854억 3707만</t>
   </si>
   <si>
     <t>닼나왕</t>
@@ -1209,802 +1209,811 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%BC%EB%82%98%EC%99%95</t>
   </si>
   <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1418억 922만</t>
+  </si>
+  <si>
+    <t>상현별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
+  </si>
+  <si>
+    <t>68조 1997억 2808만</t>
+  </si>
+  <si>
+    <t>말랑콩닥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
+  </si>
+  <si>
+    <t>24조 8873억 7474만</t>
+  </si>
+  <si>
+    <t>안루핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A3%A8%ED%95%91</t>
+  </si>
+  <si>
+    <t>18조 9219억 6773만</t>
+  </si>
+  <si>
+    <t>귀심</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>16조 1454억 9024만</t>
+  </si>
+  <si>
+    <t>찌율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>8조 4962억 4957만</t>
+  </si>
+  <si>
+    <t>루나스틱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
+  </si>
+  <si>
+    <t>8조 3984억 3791만</t>
+  </si>
+  <si>
+    <t>메키현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%ED%98%84</t>
+  </si>
+  <si>
+    <t>7조 1964억 4196만</t>
+  </si>
+  <si>
+    <t>최상급조준경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%83%81%EA%B8%89%EC%A1%B0%EC%A4%80%EA%B2%BD</t>
+  </si>
+  <si>
+    <t>6조 6585억 6602만</t>
+  </si>
+  <si>
+    <t>감자도리유지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%EC%9E%90%EB%8F%84%EB%A6%AC%EC%9C%A0%EC%A7%80</t>
+  </si>
+  <si>
+    <t>6조 624억 3694만</t>
+  </si>
+  <si>
+    <t>엠비피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EB%B9%84%ED%94%BC</t>
+  </si>
+  <si>
+    <t>5조 9530억 8663만</t>
+  </si>
+  <si>
+    <t>도맘가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A7%98%EA%B0%80</t>
+  </si>
+  <si>
+    <t>5조 8941억 4679만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>4조 4943억 4461만</t>
+  </si>
+  <si>
+    <t>브로큰애로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>4조 1678억 7437만</t>
+  </si>
+  <si>
+    <t>박예쁜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
+  </si>
+  <si>
+    <t>3조 2486억 2256만</t>
+  </si>
+  <si>
+    <t>용감한순대국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>3조 2359억 3617만</t>
+  </si>
+  <si>
+    <t>별밖에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
+  </si>
+  <si>
+    <t>2조 8635억 326만</t>
+  </si>
+  <si>
+    <t>곱션이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EC%85%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 7102억 8589만</t>
+  </si>
+  <si>
+    <t>양념반탈리반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%85%90%EB%B0%98%ED%83%88%EB%A6%AC%EB%B0%98</t>
+  </si>
+  <si>
+    <t>2조 5326억 3350만</t>
+  </si>
+  <si>
+    <t>딸둘아범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EB%91%98%EC%95%84%EB%B2%94</t>
+  </si>
+  <si>
+    <t>2조 3756억 8523만</t>
+  </si>
+  <si>
+    <t>쿰척쿰쳑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
+  </si>
+  <si>
+    <t>2조 1901억 2418만</t>
+  </si>
+  <si>
+    <t>신궁초보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%B4%88%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>2조 483억 9026만</t>
+  </si>
+  <si>
+    <t>판별식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%90%EB%B3%84%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>1조 9179억 5132만</t>
+  </si>
+  <si>
+    <t>옹야미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>1조 7780억 9419만</t>
+  </si>
+  <si>
+    <t>루맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 7147억 7486만</t>
+  </si>
+  <si>
+    <t>츄쁜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
+  </si>
+  <si>
+    <t>1조 3109억 723만</t>
+  </si>
+  <si>
+    <t>박마리아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1조 712억 9669만</t>
+  </si>
+  <si>
+    <t>한닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
+  </si>
+  <si>
+    <t>1조 287억 7641만</t>
+  </si>
+  <si>
+    <t>뮴뮴뮴뮴뮴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4</t>
+  </si>
+  <si>
+    <t>8454억 6860만</t>
+  </si>
+  <si>
+    <t>놀면머하니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%86%80%EB%A9%B4%EB%A8%B8%ED%95%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>5460억 7097만</t>
+  </si>
+  <si>
+    <t>키워봄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%8C%EB%B4%84</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>4045억 7587만</t>
+  </si>
+  <si>
+    <t>량용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%89%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>73조 2343억 4360만</t>
+  </si>
+  <si>
+    <t>달봉e</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%B4%89e</t>
+  </si>
+  <si>
+    <t>57조 7060억 6252만</t>
+  </si>
+  <si>
+    <t>가나디도둑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%82%98%EB%94%94%EB%8F%84%EB%91%91</t>
+  </si>
+  <si>
+    <t>12조 4866억 1802만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%86%ED%94%84</t>
+  </si>
+  <si>
+    <t>10조 9487억 7914만</t>
+  </si>
+  <si>
+    <t>조영현2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%98%81%ED%98%842</t>
+  </si>
+  <si>
+    <t>7조 9593억 2402만</t>
+  </si>
+  <si>
+    <t>정신못차림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>7조 8060억 2000만</t>
+  </si>
+  <si>
+    <t>핫딜패스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%ED%8C%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>4조 6737억 2415만</t>
+  </si>
+  <si>
+    <t>캔터베리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%ED%84%B0%EB%B2%A0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>4조 5801억 8016만</t>
+  </si>
+  <si>
+    <t>안경나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EA%B2%BD%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>4조 5024억 3431만</t>
+  </si>
+  <si>
+    <t>빅밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>4조 925억 4982만</t>
+  </si>
+  <si>
+    <t>햐밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%90%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>3조 9463억 1177만</t>
+  </si>
+  <si>
+    <t>템플스테이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%ED%94%8C%EC%8A%A4%ED%85%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 8133억 8999만</t>
+  </si>
+  <si>
+    <t>하콩치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%BD%A9%EC%B9%98</t>
+  </si>
+  <si>
+    <t>3조 7615억 6767만</t>
+  </si>
+  <si>
+    <t>아무렇게할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AC%B4%EB%A0%87%EA%B2%8C%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>3조 4448억 837만</t>
+  </si>
+  <si>
+    <t>유쥬아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A5%AC%EC%95%84</t>
+  </si>
+  <si>
+    <t>3조 2349억 3054만</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Scope</t>
+  </si>
+  <si>
+    <t>3조 587억 9625만</t>
+  </si>
+  <si>
+    <t>별잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%9E%87</t>
+  </si>
+  <si>
+    <t>2조 5461억 1188만</t>
+  </si>
+  <si>
+    <t>리디엘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%94%94%EC%97%98</t>
+  </si>
+  <si>
+    <t>2조 3632억 6531만</t>
+  </si>
+  <si>
+    <t>산로지노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 3212억 9041만</t>
+  </si>
+  <si>
+    <t>부울가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%9A%B8%EA%B0%80</t>
+  </si>
+  <si>
+    <t>1조 9067억 4086만</t>
+  </si>
+  <si>
+    <t>Azham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Azham</t>
+  </si>
+  <si>
+    <t>1조 8855억 771만</t>
+  </si>
+  <si>
+    <t>흙심이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 8326억 1914만</t>
+  </si>
+  <si>
+    <t>떠하야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%ED%95%98%EC%95%BC</t>
+  </si>
+  <si>
+    <t>1조 7780억 4761만</t>
+  </si>
+  <si>
+    <t>이즈뤼얼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A6%88%EB%A4%BC%EC%96%BC</t>
+  </si>
+  <si>
+    <t>1조 5617억 1646만</t>
+  </si>
+  <si>
+    <t>Porto</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Porto</t>
+  </si>
+  <si>
+    <t>1조 4619억 7338만</t>
+  </si>
+  <si>
+    <t>비라비스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%9D%BC%EB%B9%84%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1조 3316억 488만</t>
+  </si>
+  <si>
+    <t>쥐이에이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8899억 9716만</t>
+  </si>
+  <si>
+    <t>후려까기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%A0%A4%EA%B9%8C%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>8636억 9674만</t>
+  </si>
+  <si>
+    <t>뽀미l</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
+  </si>
+  <si>
+    <t>7614억 9229만</t>
+  </si>
+  <si>
+    <t>짜뇨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%87%A8</t>
+  </si>
+  <si>
+    <t>6827억 3813만</t>
+  </si>
+  <si>
+    <t>동띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>140조 6792억 5418만</t>
+  </si>
+  <si>
+    <t>나무키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%AC%B4%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>40조 9279억 2449만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EB%8C%80</t>
+  </si>
+  <si>
+    <t>20조 9250억 1712만</t>
+  </si>
+  <si>
+    <t>원남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
+  </si>
+  <si>
+    <t>6조 5912억 796만</t>
+  </si>
+  <si>
+    <t>숍솝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%8D%EC%86%9D</t>
+  </si>
+  <si>
+    <t>4조 3745억 1323만</t>
+  </si>
+  <si>
+    <t>동동띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%8F%99%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>3조 6018억 487만</t>
+  </si>
+  <si>
+    <t>정뽀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%BD%80</t>
+  </si>
+  <si>
+    <t>3조 5848억 1463만</t>
+  </si>
+  <si>
+    <t>단정이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 233억 1344만</t>
+  </si>
+  <si>
+    <t>지구뿌셔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
+  </si>
+  <si>
+    <t>1조 9159억 821만</t>
+  </si>
+  <si>
+    <t>꼬햄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%ED%96%84</t>
+  </si>
+  <si>
+    <t>1조 5958억 681만</t>
+  </si>
+  <si>
+    <t>사맛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%9B</t>
+  </si>
+  <si>
+    <t>1조 2778억 1504만</t>
+  </si>
+  <si>
+    <t>훈다띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>9421억 6228만</t>
+  </si>
+  <si>
+    <t>자쿰키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%BF%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>8961억 7322만</t>
+  </si>
+  <si>
+    <t>갓굴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
+  </si>
+  <si>
+    <t>7666억 8200만</t>
+  </si>
+  <si>
+    <t>다릿골</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%A6%BF%EA%B3%A8</t>
+  </si>
+  <si>
+    <t>7653억 8853만</t>
+  </si>
+  <si>
+    <t>귀쮸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
+  </si>
+  <si>
+    <t>6330억 9543만</t>
+  </si>
+  <si>
+    <t>당겨쏴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B2%A8%EC%8F%B4</t>
+  </si>
+  <si>
+    <t>5927억 513만</t>
+  </si>
+  <si>
+    <t>알뺘노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%BA%98%EB%85%B8</t>
+  </si>
+  <si>
+    <t>5827억 5044만</t>
+  </si>
+  <si>
+    <t>은단월</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
+  </si>
+  <si>
+    <t>5724억 593만</t>
+  </si>
+  <si>
+    <t>Viceversa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
+  </si>
+  <si>
+    <t>5249억 8907만</t>
+  </si>
+  <si>
+    <t>투냉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
+  </si>
+  <si>
+    <t>5028억 335만</t>
+  </si>
+  <si>
+    <t>비비다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>4455억 4351만</t>
+  </si>
+  <si>
+    <t>진1용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%841%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>4214억 4816만</t>
+  </si>
+  <si>
+    <t>사과클럽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
+  </si>
+  <si>
+    <t>3761억 6030만</t>
+  </si>
+  <si>
+    <t>차눅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
+  </si>
+  <si>
+    <t>3396억 5369만</t>
+  </si>
+  <si>
+    <t>팔나무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%82%98%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>2966억 3542만</t>
+  </si>
+  <si>
+    <t>53다2329</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=53%EB%8B%A42329</t>
+  </si>
+  <si>
+    <t>2599억 2443만</t>
+  </si>
+  <si>
+    <t>강진현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%A7%84%ED%98%84</t>
+  </si>
+  <si>
     <t>91</t>
   </si>
   <si>
-    <t>1362억 8894만</t>
-  </si>
-  <si>
-    <t>상현별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
-  </si>
-  <si>
-    <t>68조 1997억 2808만</t>
-  </si>
-  <si>
-    <t>말랑콩닥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
-  </si>
-  <si>
-    <t>23조 6316억 3798만</t>
-  </si>
-  <si>
-    <t>안루핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A3%A8%ED%95%91</t>
-  </si>
-  <si>
-    <t>18조 1491억 4830만</t>
-  </si>
-  <si>
-    <t>귀심</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>16조 1454억 9024만</t>
-  </si>
-  <si>
-    <t>찌율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>8조 1843억 9177만</t>
-  </si>
-  <si>
-    <t>루나스틱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
-  </si>
-  <si>
-    <t>7조 7509억 5317만</t>
-  </si>
-  <si>
-    <t>메키현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%ED%98%84</t>
-  </si>
-  <si>
-    <t>7조 1964억 4196만</t>
-  </si>
-  <si>
-    <t>최상급조준경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%83%81%EA%B8%89%EC%A1%B0%EC%A4%80%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>6조 6585억 6602만</t>
-  </si>
-  <si>
-    <t>감자도리유지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%EC%9E%90%EB%8F%84%EB%A6%AC%EC%9C%A0%EC%A7%80</t>
-  </si>
-  <si>
-    <t>6조 624억 3694만</t>
-  </si>
-  <si>
-    <t>도맘가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A7%98%EA%B0%80</t>
-  </si>
-  <si>
-    <t>5조 8941억 4679만</t>
-  </si>
-  <si>
-    <t>엠비피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EB%B9%84%ED%94%BC</t>
-  </si>
-  <si>
-    <t>5조 8472억 3465만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>4조 2760억 6894만</t>
-  </si>
-  <si>
-    <t>브로큰애로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>4조 1678억 7437만</t>
-  </si>
-  <si>
-    <t>용감한순대국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>3조 1034억 1903만</t>
-  </si>
-  <si>
-    <t>별밖에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
-  </si>
-  <si>
-    <t>2조 8458억 4628만</t>
-  </si>
-  <si>
-    <t>곱션이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EC%85%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2조 5899억 3096만</t>
-  </si>
-  <si>
-    <t>양념반탈리반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%85%90%EB%B0%98%ED%83%88%EB%A6%AC%EB%B0%98</t>
-  </si>
-  <si>
-    <t>2조 4904억 6746만</t>
-  </si>
-  <si>
-    <t>딸둘아범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EB%91%98%EC%95%84%EB%B2%94</t>
-  </si>
-  <si>
-    <t>2조 3756억 8523만</t>
-  </si>
-  <si>
-    <t>박예쁜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
-  </si>
-  <si>
-    <t>2조 1139억 4649만</t>
-  </si>
-  <si>
-    <t>쿰척쿰쳑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
-  </si>
-  <si>
-    <t>2조 972억 4800만</t>
-  </si>
-  <si>
-    <t>신궁초보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%B4%88%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>2조 483억 9026만</t>
-  </si>
-  <si>
-    <t>판별식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%90%EB%B3%84%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>1조 9179억 5132만</t>
-  </si>
-  <si>
-    <t>옹야미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1조 7700억 2940만</t>
-  </si>
-  <si>
-    <t>루맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 6759억 7300만</t>
-  </si>
-  <si>
-    <t>츄쁜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
-  </si>
-  <si>
-    <t>1조 1335억 4299만</t>
-  </si>
-  <si>
-    <t>박마리아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 645억 5505만</t>
-  </si>
-  <si>
-    <t>한닝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
-  </si>
-  <si>
-    <t>9945억 8723만</t>
-  </si>
-  <si>
-    <t>뮴뮴뮴뮴뮴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4%EB%AE%B4</t>
-  </si>
-  <si>
-    <t>8061억 1941만</t>
-  </si>
-  <si>
-    <t>놀면머하니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%86%80%EB%A9%B4%EB%A8%B8%ED%95%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>5456억 6511만</t>
-  </si>
-  <si>
-    <t>키워봄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%8C%EB%B4%84</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>4043억 1390만</t>
-  </si>
-  <si>
-    <t>량용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%89%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>68조 4417억 7851만</t>
-  </si>
-  <si>
-    <t>달봉e</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%B4%89e</t>
-  </si>
-  <si>
-    <t>54조 6397억 8672만</t>
-  </si>
-  <si>
-    <t>가나디도둑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%82%98%EB%94%94%EB%8F%84%EB%91%91</t>
-  </si>
-  <si>
-    <t>12조 875억 7214만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%86%ED%94%84</t>
-  </si>
-  <si>
-    <t>10조 9487억 7914만</t>
-  </si>
-  <si>
-    <t>조영현2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%98%81%ED%98%842</t>
-  </si>
-  <si>
-    <t>7조 9593억 2402만</t>
-  </si>
-  <si>
-    <t>정신못차림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>6조 4753억 1198만</t>
-  </si>
-  <si>
-    <t>핫딜패스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%ED%8C%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>4조 6737억 2415만</t>
-  </si>
-  <si>
-    <t>캔터베리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%ED%84%B0%EB%B2%A0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>4조 5801억 8016만</t>
-  </si>
-  <si>
-    <t>안경나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EA%B2%BD%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>4조 3133억 5612만</t>
-  </si>
-  <si>
-    <t>빅밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>3조 8230억 4635만</t>
-  </si>
-  <si>
-    <t>하콩치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%BD%A9%EC%B9%98</t>
-  </si>
-  <si>
-    <t>3조 7615억 6767만</t>
-  </si>
-  <si>
-    <t>햐밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%90%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>3조 7517억 4264만</t>
-  </si>
-  <si>
-    <t>템플스테이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%ED%94%8C%EC%8A%A4%ED%85%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3조 7511억 4873만</t>
-  </si>
-  <si>
-    <t>아무렇게할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AC%B4%EB%A0%87%EA%B2%8C%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>3조 2335억 9930만</t>
-  </si>
-  <si>
-    <t>유쥬아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%A5%AC%EC%95%84</t>
-  </si>
-  <si>
-    <t>2조 8014억 6559만</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Scope</t>
-  </si>
-  <si>
-    <t>2조 7096억 2142만</t>
-  </si>
-  <si>
-    <t>산로지노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 3212억 9041만</t>
-  </si>
-  <si>
-    <t>리디엘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%94%94%EC%97%98</t>
-  </si>
-  <si>
-    <t>2조 2974억 3159만</t>
-  </si>
-  <si>
-    <t>별잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%9E%87</t>
-  </si>
-  <si>
-    <t>2조 2286억 8898만</t>
-  </si>
-  <si>
-    <t>부울가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%9A%B8%EA%B0%80</t>
-  </si>
-  <si>
-    <t>1조 9067억 4086만</t>
-  </si>
-  <si>
-    <t>흙심이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 8326억 1914만</t>
-  </si>
-  <si>
-    <t>Azham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Azham</t>
-  </si>
-  <si>
-    <t>1조 7844억 564만</t>
-  </si>
-  <si>
-    <t>떠하야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%ED%95%98%EC%95%BC</t>
-  </si>
-  <si>
-    <t>1조 7727억 9821만</t>
-  </si>
-  <si>
-    <t>Porto</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Porto</t>
-  </si>
-  <si>
-    <t>1조 4619억 7338만</t>
-  </si>
-  <si>
-    <t>이즈뤼얼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A6%88%EB%A4%BC%EC%96%BC</t>
-  </si>
-  <si>
-    <t>1조 4582억 1847만</t>
-  </si>
-  <si>
-    <t>비라비스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%9D%BC%EB%B9%84%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1조 3316억 488만</t>
-  </si>
-  <si>
-    <t>쥐이에이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8780억 2867만</t>
-  </si>
-  <si>
-    <t>후려까기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%A0%A4%EA%B9%8C%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>8636억 9674만</t>
-  </si>
-  <si>
-    <t>뽀미l</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
-  </si>
-  <si>
-    <t>7614억 9229만</t>
-  </si>
-  <si>
-    <t>짜뇨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EB%87%A8</t>
-  </si>
-  <si>
-    <t>6391억 6462만</t>
-  </si>
-  <si>
-    <t>동띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>131조 4547억 6897만</t>
-  </si>
-  <si>
-    <t>나무키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%AC%B4%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>34조 9382억 3297만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EB%8C%80</t>
-  </si>
-  <si>
-    <t>20조 9250억 1712만</t>
-  </si>
-  <si>
-    <t>원남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
-  </si>
-  <si>
-    <t>6조 3121억 6486만</t>
-  </si>
-  <si>
-    <t>숍솝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%8D%EC%86%9D</t>
-  </si>
-  <si>
-    <t>4조 3745억 1323만</t>
-  </si>
-  <si>
-    <t>동동띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%8F%99%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>3조 5398억 5386만</t>
-  </si>
-  <si>
-    <t>정뽀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%BD%80</t>
-  </si>
-  <si>
-    <t>3조 5086억 4014만</t>
-  </si>
-  <si>
-    <t>단정이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 9459억 5450만</t>
-  </si>
-  <si>
-    <t>지구뿌셔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
-  </si>
-  <si>
-    <t>1조 7949억 2734만</t>
-  </si>
-  <si>
-    <t>꼬햄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%ED%96%84</t>
-  </si>
-  <si>
-    <t>1조 4985억 8369만</t>
-  </si>
-  <si>
-    <t>사맛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%A7%9B</t>
-  </si>
-  <si>
-    <t>1조 1560억 3647만</t>
-  </si>
-  <si>
-    <t>훈다띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>9421억 6228만</t>
-  </si>
-  <si>
-    <t>자쿰키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%BF%B0%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>8961억 7322만</t>
-  </si>
-  <si>
-    <t>다릿골</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%A6%BF%EA%B3%A8</t>
-  </si>
-  <si>
-    <t>7522억 3055만</t>
-  </si>
-  <si>
-    <t>갓굴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
-  </si>
-  <si>
-    <t>7372억 158만</t>
-  </si>
-  <si>
-    <t>귀쮸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
-  </si>
-  <si>
-    <t>6330억 9543만</t>
-  </si>
-  <si>
-    <t>당겨쏴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B2%A8%EC%8F%B4</t>
-  </si>
-  <si>
-    <t>5840억 6560만</t>
-  </si>
-  <si>
-    <t>은단월</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
-  </si>
-  <si>
-    <t>5473억 8620만</t>
-  </si>
-  <si>
-    <t>Viceversa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
-  </si>
-  <si>
-    <t>5093억 3264만</t>
-  </si>
-  <si>
-    <t>알뺘노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%BA%98%EB%85%B8</t>
-  </si>
-  <si>
-    <t>4920억 9616만</t>
-  </si>
-  <si>
-    <t>투냉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
-  </si>
-  <si>
-    <t>4586억 7349만</t>
-  </si>
-  <si>
-    <t>비비다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>4455억 4351만</t>
-  </si>
-  <si>
-    <t>진1용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%841%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>3832억 2080만</t>
-  </si>
-  <si>
-    <t>사과클럽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
-  </si>
-  <si>
-    <t>3754억 2462만</t>
-  </si>
-  <si>
-    <t>차눅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
-  </si>
-  <si>
-    <t>3380억 8111만</t>
-  </si>
-  <si>
-    <t>팔나무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%82%98%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>2966억 3542만</t>
-  </si>
-  <si>
-    <t>53다2329</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=53%EB%8B%A42329</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>2465억 5851만</t>
+    <t>1632억 2685만</t>
   </si>
   <si>
     <t>나루토토</t>
@@ -2013,16 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%A3%A8%ED%86%A0%ED%86%A0</t>
   </si>
   <si>
-    <t>1590억 6119만</t>
-  </si>
-  <si>
-    <t>강진현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%A7%84%ED%98%84</t>
-  </si>
-  <si>
-    <t>1558억 3839만</t>
+    <t>1630억 5864만</t>
   </si>
   <si>
     <t>길지녁</t>
@@ -2046,7 +2046,7 @@
     <t>https://mgf.gg/contents/character.php?n=86%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>3조 1058억 738만</t>
+    <t>3조 1103억 5726만</t>
   </si>
   <si>
     <t>다있다하노</t>
@@ -2055,7 +2055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 4069억 8692만</t>
+    <t>2조 6623억 5909만</t>
   </si>
   <si>
     <t>델타시그마</t>
@@ -2064,7 +2064,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>2조 2706억 9400만</t>
+    <t>2조 4331억 9460만</t>
+  </si>
+  <si>
+    <t>끽스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>2조 3537억 5133만</t>
   </si>
   <si>
     <t>꿍물</t>
@@ -2082,16 +2091,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>2조 1279억 8468만</t>
-  </si>
-  <si>
-    <t>끽스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>2조 1219억 3007만</t>
+    <t>2조 1699억 9260만</t>
   </si>
   <si>
     <t>흑인드록바</t>
@@ -2109,7 +2109,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
   </si>
   <si>
-    <t>1조 9550억 7808만</t>
+    <t>1조 9572억 7982만</t>
+  </si>
+  <si>
+    <t>한콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>1조 8643억 7838만</t>
   </si>
   <si>
     <t>전팡</t>
@@ -2121,22 +2130,13 @@
     <t>1조 8307억 4393만</t>
   </si>
   <si>
-    <t>한콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>1조 8123억 1510만</t>
-  </si>
-  <si>
     <t>밀가루죽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EA%B0%80%EB%A3%A8%EC%A3%BD</t>
   </si>
   <si>
-    <t>1조 7994억 3437만</t>
+    <t>1조 8169억 4544만</t>
   </si>
   <si>
     <t>야로야옹</t>
@@ -2145,7 +2145,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
   </si>
   <si>
-    <t>1조 5975억 8791만</t>
+    <t>1조 7321억 443만</t>
   </si>
   <si>
     <t>또유유</t>
@@ -2154,7 +2154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%9C%A0%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 5245억 986만</t>
+    <t>1조 5257억 5441만</t>
   </si>
   <si>
     <t>웅잉당</t>
@@ -2163,7 +2163,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>1조 3968억 6957만</t>
+    <t>1조 4029억 4630만</t>
   </si>
   <si>
     <t>사람님아</t>
@@ -2172,7 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
   </si>
   <si>
-    <t>1조 3126억 2740만</t>
+    <t>1조 3138억 3895만</t>
   </si>
   <si>
     <t>흑인햄찌</t>
@@ -2181,7 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
   </si>
   <si>
-    <t>1조 1836억 4670만</t>
+    <t>1조 2572억 8714만</t>
   </si>
   <si>
     <t>비숍마로밍</t>
@@ -2190,7 +2190,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%A7%88%EB%A1%9C%EB%B0%8D</t>
   </si>
   <si>
-    <t>1조 1488억 5053만</t>
+    <t>1조 2437억 6182만</t>
+  </si>
+  <si>
+    <t>에머슨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
+  </si>
+  <si>
+    <t>1조 2295억 490만</t>
   </si>
   <si>
     <t>은둔형오덕후</t>
@@ -2199,16 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%91%94%ED%98%95%EC%98%A4%EB%8D%95%ED%9B%84</t>
   </si>
   <si>
-    <t>1조 1113억 6681만</t>
-  </si>
-  <si>
-    <t>에머슨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
-  </si>
-  <si>
-    <t>9697억 2044만</t>
+    <t>1조 1219억 8727만</t>
   </si>
   <si>
     <t>하랸</t>
@@ -2217,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
   </si>
   <si>
-    <t>9395억 8417만</t>
+    <t>1조 605억 7563만</t>
   </si>
   <si>
     <t>존못에겐남짱</t>
@@ -2226,7 +2226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
   </si>
   <si>
-    <t>8763억 6277만</t>
+    <t>9944억 3565만</t>
   </si>
   <si>
     <t>섀레기</t>
@@ -2235,7 +2235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
   </si>
   <si>
-    <t>8512억 8487만</t>
+    <t>8714억 9440만</t>
   </si>
   <si>
     <t>민초양갱</t>
@@ -2262,7 +2262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
   </si>
   <si>
-    <t>7128억 1218만</t>
+    <t>7220억 5577만</t>
   </si>
   <si>
     <t>뉴비i</t>
@@ -2274,6 +2274,15 @@
     <t>7075억 5483만</t>
   </si>
   <si>
+    <t>두부장구니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B6%80%EC%9E%A5%EA%B5%AC%EB%8B%88</t>
+  </si>
+  <si>
+    <t>4959억 980만</t>
+  </si>
+  <si>
     <t>아임몽순</t>
   </si>
   <si>
@@ -2283,22 +2292,13 @@
     <t>4816억 386만</t>
   </si>
   <si>
-    <t>두부장구니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B6%80%EC%9E%A5%EA%B5%AC%EB%8B%88</t>
-  </si>
-  <si>
-    <t>4812억 8494만</t>
-  </si>
-  <si>
     <t>오리박사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B0%95%EC%82%AC</t>
   </si>
   <si>
-    <t>3720억 5724만</t>
+    <t>3774억 8222만</t>
   </si>
 </sst>
 </file>
@@ -2859,20 +2859,20 @@
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2880,25 +2880,25 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2907,13 +2907,13 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2921,40 +2921,40 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>24</v>
@@ -2962,25 +2962,25 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>68</v>
@@ -3213,7 +3213,7 @@
         <v>108</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>109</v>
@@ -3242,10 +3242,10 @@
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>113</v>
@@ -3402,7 +3402,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>126</v>
@@ -3434,7 +3434,7 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>126</v>
@@ -3466,10 +3466,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>144</v>
@@ -3498,13 +3498,13 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3515,25 +3515,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>153</v>
@@ -3562,13 +3562,13 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3579,25 +3579,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>162</v>
@@ -3626,10 +3626,10 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>166</v>
@@ -3658,10 +3658,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>170</v>
@@ -3757,7 +3757,7 @@
         <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>182</v>
@@ -3789,7 +3789,7 @@
         <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>186</v>
@@ -3818,10 +3818,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>190</v>
@@ -3850,10 +3850,10 @@
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>194</v>
@@ -3917,7 +3917,7 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>202</v>
@@ -3949,7 +3949,7 @@
         <v>206</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>207</v>
@@ -3981,7 +3981,7 @@
         <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>211</v>
@@ -4010,7 +4010,7 @@
         <v>89</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>126</v>
@@ -4130,7 +4130,7 @@
         <v>206</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>218</v>
@@ -4162,7 +4162,7 @@
         <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>221</v>
@@ -4194,7 +4194,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>224</v>
@@ -4287,7 +4287,7 @@
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>103</v>
@@ -4386,7 +4386,7 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>241</v>
@@ -4418,7 +4418,7 @@
         <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>244</v>
@@ -4447,7 +4447,7 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>126</v>
@@ -4482,7 +4482,7 @@
         <v>131</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>250</v>
@@ -4511,10 +4511,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>253</v>
@@ -4543,10 +4543,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>256</v>
@@ -4560,7 +4560,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>257</v>
@@ -4578,7 +4578,7 @@
         <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>259</v>
@@ -4607,10 +4607,10 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>262</v>
@@ -4624,7 +4624,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>263</v>
@@ -4639,10 +4639,10 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>265</v>
@@ -4674,7 +4674,7 @@
         <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>268</v>
@@ -4735,10 +4735,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>274</v>
@@ -4767,10 +4767,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>277</v>
@@ -4799,10 +4799,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>280</v>
@@ -4834,7 +4834,7 @@
         <v>131</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>283</v>
@@ -4866,7 +4866,7 @@
         <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>286</v>
@@ -4898,7 +4898,7 @@
         <v>206</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>289</v>
@@ -4962,7 +4962,7 @@
         <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>296</v>
@@ -5026,7 +5026,7 @@
         <v>131</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>302</v>
@@ -5206,7 +5206,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>311</v>
@@ -5267,10 +5267,10 @@
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>317</v>
@@ -5331,10 +5331,10 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5363,7 +5363,7 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>103</v>
@@ -5398,7 +5398,7 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>329</v>
@@ -5427,10 +5427,10 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>332</v>
@@ -5459,10 +5459,10 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>335</v>
@@ -5491,10 +5491,10 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>338</v>
@@ -5523,10 +5523,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>341</v>
@@ -5555,10 +5555,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>344</v>
@@ -5572,7 +5572,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>345</v>
@@ -5587,10 +5587,10 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>347</v>
@@ -5619,10 +5619,10 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>350</v>
@@ -5636,7 +5636,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>351</v>
@@ -5651,10 +5651,10 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>353</v>
@@ -5683,10 +5683,10 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>356</v>
@@ -5715,7 +5715,7 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
@@ -5747,10 +5747,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>362</v>
@@ -5782,7 +5782,7 @@
         <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>365</v>
@@ -5811,10 +5811,10 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>368</v>
@@ -5843,10 +5843,10 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>371</v>
@@ -5875,10 +5875,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>374</v>
@@ -5910,7 +5910,7 @@
         <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>377</v>
@@ -5939,10 +5939,10 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>380</v>
@@ -5971,10 +5971,10 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>383</v>
@@ -6006,7 +6006,7 @@
         <v>131</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>386</v>
@@ -6067,7 +6067,7 @@
         <v>89</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>392</v>
@@ -6216,10 +6216,10 @@
         <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>399</v>
@@ -6280,10 +6280,10 @@
         <v>89</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>405</v>
@@ -6344,10 +6344,10 @@
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>411</v>
@@ -6376,7 +6376,7 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>126</v>
@@ -6472,7 +6472,7 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>103</v>
@@ -6504,10 +6504,10 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>426</v>
@@ -6524,10 +6524,10 @@
         <v>137</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>427</v>
@@ -6571,7 +6571,7 @@
         <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>431</v>
@@ -6600,10 +6600,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>434</v>
@@ -6617,7 +6617,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>435</v>
@@ -6635,7 +6635,7 @@
         <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>437</v>
@@ -6667,7 +6667,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>440</v>
@@ -6681,7 +6681,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>441</v>
@@ -6696,10 +6696,10 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>443</v>
@@ -6728,10 +6728,10 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>304</v>
+        <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>446</v>
@@ -6760,10 +6760,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>449</v>
@@ -6795,7 +6795,7 @@
         <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>452</v>
@@ -6824,10 +6824,10 @@
         <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>455</v>
@@ -6859,7 +6859,7 @@
         <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>458</v>
@@ -6888,7 +6888,7 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>292</v>
@@ -6952,10 +6952,10 @@
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>467</v>
@@ -6984,7 +6984,7 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>470</v>
@@ -7211,7 +7211,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>80</v>
@@ -7243,7 +7243,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
@@ -7307,16 +7307,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>497</v>
@@ -7328,7 +7328,7 @@
         <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>498</v>
@@ -7339,7 +7339,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>105</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
@@ -7424,7 +7424,7 @@
         <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>507</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>128</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
@@ -7549,10 +7549,10 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>519</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
@@ -7581,10 +7581,10 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>522</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
@@ -7613,10 +7613,10 @@
         <v>89</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>525</v>
@@ -7627,7 +7627,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>145</v>
@@ -7648,7 +7648,7 @@
         <v>131</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>528</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>529</v>
@@ -7691,7 +7691,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
@@ -7709,10 +7709,10 @@
         <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>534</v>
@@ -7723,10 +7723,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>535</v>
@@ -7741,10 +7741,10 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>537</v>
@@ -7755,7 +7755,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>163</v>
@@ -7776,7 +7776,7 @@
         <v>131</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>540</v>
@@ -7787,7 +7787,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
@@ -7805,10 +7805,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>543</v>
@@ -7819,7 +7819,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
@@ -7837,10 +7837,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>546</v>
@@ -7851,7 +7851,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
@@ -7872,7 +7872,7 @@
         <v>304</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>549</v>
@@ -7883,7 +7883,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
@@ -7904,7 +7904,7 @@
         <v>304</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>552</v>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>183</v>
@@ -7933,10 +7933,10 @@
         <v>89</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>555</v>
@@ -7947,7 +7947,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>187</v>
@@ -7965,10 +7965,10 @@
         <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>292</v>
+        <v>152</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>558</v>
@@ -7979,7 +7979,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>191</v>
@@ -7997,10 +7997,10 @@
         <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>561</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>195</v>
@@ -8032,7 +8032,7 @@
         <v>304</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>564</v>
@@ -8043,7 +8043,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>199</v>
@@ -8061,10 +8061,10 @@
         <v>89</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>567</v>
@@ -8075,7 +8075,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>203</v>
@@ -8093,7 +8093,7 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>470</v>
@@ -8107,7 +8107,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>208</v>
@@ -8125,7 +8125,7 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>470</v>
@@ -8139,7 +8139,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>212</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>80</v>
@@ -8288,7 +8288,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -8306,10 +8306,10 @@
         <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>582</v>
@@ -8320,16 +8320,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>583</v>
@@ -8341,7 +8341,7 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>584</v>
@@ -8352,7 +8352,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
@@ -8384,7 +8384,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>105</v>
@@ -8416,7 +8416,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
@@ -8437,7 +8437,7 @@
         <v>484</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>593</v>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
@@ -8501,7 +8501,7 @@
         <v>131</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>599</v>
@@ -8512,7 +8512,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
@@ -8533,7 +8533,7 @@
         <v>131</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>602</v>
@@ -8544,7 +8544,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>128</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
@@ -8597,7 +8597,7 @@
         <v>304</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>608</v>
@@ -8608,7 +8608,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
@@ -8626,7 +8626,7 @@
         <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>292</v>
@@ -8640,7 +8640,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
@@ -8672,7 +8672,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>145</v>
@@ -8690,10 +8690,10 @@
         <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>485</v>
+        <v>292</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>617</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>618</v>
@@ -8722,10 +8722,10 @@
         <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>292</v>
+        <v>485</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>620</v>
@@ -8736,7 +8736,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
@@ -8768,10 +8768,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>624</v>
@@ -8786,7 +8786,7 @@
         <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>480</v>
@@ -8800,7 +8800,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>163</v>
@@ -8818,7 +8818,7 @@
         <v>89</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>304</v>
+        <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>470</v>
@@ -8832,7 +8832,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
@@ -8864,7 +8864,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
@@ -8882,7 +8882,7 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>304</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>470</v>
@@ -8896,7 +8896,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
@@ -8917,7 +8917,7 @@
         <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>470</v>
+        <v>292</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>638</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>183</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>187</v>
@@ -9024,7 +9024,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>191</v>
@@ -9056,7 +9056,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>195</v>
@@ -9088,7 +9088,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>199</v>
@@ -9109,10 +9109,10 @@
         <v>484</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9120,28 +9120,28 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>660</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>208</v>
@@ -9170,10 +9170,10 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>392</v>
+        <v>659</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>663</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>212</v>
@@ -9301,7 +9301,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>80</v>
@@ -9322,7 +9322,7 @@
         <v>484</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>669</v>
@@ -9333,7 +9333,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>86</v>
@@ -9351,10 +9351,10 @@
         <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>671</v>
@@ -9365,7 +9365,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>93</v>
@@ -9386,7 +9386,7 @@
         <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>674</v>
@@ -9397,7 +9397,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>99</v>
@@ -9418,7 +9418,7 @@
         <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>677</v>
@@ -9429,7 +9429,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>105</v>
@@ -9447,10 +9447,10 @@
         <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>304</v>
+        <v>131</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>292</v>
+        <v>152</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>680</v>
@@ -9461,7 +9461,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>110</v>
@@ -9479,10 +9479,10 @@
         <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>304</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>157</v>
+        <v>292</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>683</v>
@@ -9493,7 +9493,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>114</v>
@@ -9511,10 +9511,10 @@
         <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>686</v>
@@ -9525,7 +9525,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
@@ -9543,10 +9543,10 @@
         <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>292</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>689</v>
@@ -9557,7 +9557,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>122</v>
@@ -9578,7 +9578,7 @@
         <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>692</v>
@@ -9589,7 +9589,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>128</v>
@@ -9607,10 +9607,10 @@
         <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>292</v>
+        <v>470</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>695</v>
@@ -9621,7 +9621,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>133</v>
@@ -9639,10 +9639,10 @@
         <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>470</v>
+        <v>292</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>698</v>
@@ -9653,7 +9653,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
@@ -9674,7 +9674,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>292</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>701</v>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>141</v>
@@ -9706,7 +9706,7 @@
         <v>484</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>704</v>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>145</v>
@@ -9749,10 +9749,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>708</v>
@@ -9781,7 +9781,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>154</v>
@@ -9802,7 +9802,7 @@
         <v>304</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>713</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>714</v>
@@ -9834,7 +9834,7 @@
         <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>716</v>
@@ -9845,7 +9845,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>163</v>
@@ -9877,7 +9877,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>167</v>
@@ -9895,10 +9895,10 @@
         <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>470</v>
+        <v>292</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>722</v>
@@ -9909,7 +9909,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>171</v>
@@ -9927,10 +9927,10 @@
         <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>292</v>
+        <v>470</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>725</v>
@@ -9941,7 +9941,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>175</v>
@@ -9973,7 +9973,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>179</v>
@@ -10005,7 +10005,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>183</v>
@@ -10037,7 +10037,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>187</v>
@@ -10069,7 +10069,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>191</v>
@@ -10101,7 +10101,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>195</v>
@@ -10119,7 +10119,7 @@
         <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>480</v>
@@ -10133,7 +10133,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>199</v>
@@ -10154,7 +10154,7 @@
         <v>304</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>746</v>
@@ -10165,7 +10165,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>203</v>
@@ -10183,10 +10183,10 @@
         <v>89</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>749</v>
@@ -10197,7 +10197,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>208</v>
@@ -10215,10 +10215,10 @@
         <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>752</v>
@@ -10229,7 +10229,7 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>212</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -84,10 +84,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>14위</t>
+    <t>353</t>
+  </si>
+  <si>
+    <t>11위</t>
   </si>
   <si>
     <t>Lv.8</t>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>227조 2799억 3680만</t>
+    <t>272조 1350억 3602만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,7 +105,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.28</t>
+    <t>2026.04.29</t>
   </si>
   <si>
     <t>블랙소울</t>
@@ -117,7 +117,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>337</t>
+    <t>325</t>
   </si>
   <si>
     <t>8위</t>
@@ -129,7 +129,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>300조 5896억 2875만</t>
+    <t>329조 4645억 204만</t>
   </si>
   <si>
     <t>보심</t>
@@ -144,13 +144,13 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>338</t>
+    <t>324</t>
   </si>
   <si>
     <t>7위</t>
   </si>
   <si>
-    <t>294조 9718억 5464만</t>
+    <t>330조 6705억 3079만</t>
   </si>
   <si>
     <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 2조 이상 재밌게 소통하면서 게임하실 분 공대애봉이/뒁글 문의 주세요</t>
@@ -168,10 +168,10 @@
     <t>Scania 18</t>
   </si>
   <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>211조 5466억 8150만</t>
+    <t>399</t>
+  </si>
+  <si>
+    <t>214조 3889억 9049만</t>
   </si>
   <si>
     <t>초코남</t>
@@ -186,13 +186,13 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>31위</t>
-  </si>
-  <si>
-    <t>234조 9198억 2286만</t>
+    <t>378</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>235조 8911억 5476만</t>
   </si>
   <si>
     <t>비련길드 모집조건 : 투력 9000억 이상 일일기부 300+ 길컨 참여자</t>
@@ -207,13 +207,13 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>686</t>
-  </si>
-  <si>
-    <t>51위</t>
-  </si>
-  <si>
-    <t>78조 3187억 322만</t>
+    <t>696</t>
+  </si>
+  <si>
+    <t>50위</t>
+  </si>
+  <si>
+    <t>78조 9317억 699만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요</t>
@@ -231,13 +231,13 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>978</t>
+    <t>984</t>
   </si>
   <si>
     <t>Lv.6</t>
   </si>
   <si>
-    <t>47조 9504억 6228만</t>
+    <t>48조 8283억 3875만</t>
   </si>
   <si>
     <t>*투력 3조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
@@ -273,6 +273,27 @@
     <t>1</t>
   </si>
   <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>46조 8814억 2450만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
@@ -282,13 +303,10 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>33조 6514억 3727만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>33조 9446억 6489만</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -297,9 +315,6 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>다크나이트</t>
   </si>
   <si>
@@ -309,7 +324,7 @@
     <t>22조 7632억 1918만</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>큐샤프</t>
@@ -324,7 +339,7 @@
     <t>20조 8772억 7416만</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -339,10 +354,10 @@
     <t>101</t>
   </si>
   <si>
-    <t>14조 8623억 2147만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>15조 4304억 3522만</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>야가다</t>
@@ -360,7 +375,7 @@
     <t>13조 2229억 5022만</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -369,10 +384,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>12조 6451억 9325만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>12조 7144억 1150만</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -384,7 +399,7 @@
     <t>8조 3818억 1066만</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>양정팔</t>
@@ -393,10 +408,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 8622억 22만</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>7조 8716억 4430만</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>반도</t>
@@ -411,10 +426,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>7조 1219억 6098만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>7조 1271억 2840만</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>포스코퓨처엠</t>
@@ -423,10 +438,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>6조 8249억 4902만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>6조 9200억 704만</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -435,13 +450,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6조 7155억 1566만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>6조 7222억 597만</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>우후</t>
@@ -450,10 +462,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>6조 6454억 425만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>6조 6544억 7794만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>5조 3631억 9121만</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>므고</t>
@@ -465,7 +489,7 @@
     <t>5조 2326억 4158만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -474,22 +498,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>5조 1150억 4755만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>5조 582억 6768만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>5조 2009억 8901만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 9510억 5146만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -498,25 +525,10 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>4조 8881억 6806만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>4조 8235억 7398만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>4조 9299억 7891만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -531,7 +543,7 @@
     <t>4조 7975억 1419만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -540,10 +552,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>4조 1571억 2932만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>4조 1586억 2443만</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -552,19 +564,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>3조 9882억 292만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>3조 6838억 5909만</t>
+    <t>4조 16억 1372만</t>
   </si>
   <si>
     <t>22</t>
@@ -588,7 +588,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>3조 477억 3365만</t>
+    <t>3조 488억 9661만</t>
   </si>
   <si>
     <t>24</t>
@@ -675,7 +675,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 317억 2232만</t>
+    <t>2조 570억 4078만</t>
   </si>
   <si>
     <t>상현별</t>
@@ -684,7 +684,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
   </si>
   <si>
-    <t>68조 9721억 9475만</t>
+    <t>105</t>
+  </si>
+  <si>
+    <t>101조 2855억 9955만</t>
   </si>
   <si>
     <t>머니파파</t>
@@ -693,7 +696,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EB%8B%88%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>45조 1626억 8223만</t>
+    <t>45조 2448억 4064만</t>
   </si>
   <si>
     <t>뚜까랜덤</t>
@@ -711,7 +714,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
   </si>
   <si>
-    <t>25조 2390억 5937만</t>
+    <t>25조 5823억 9783만</t>
   </si>
   <si>
     <t>귀심</t>
@@ -732,6 +735,24 @@
     <t>9조 9880억 3047만</t>
   </si>
   <si>
+    <t>루나스틱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
+  </si>
+  <si>
+    <t>8조 7404억 8408만</t>
+  </si>
+  <si>
+    <t>찌율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>8조 6728억 846만</t>
+  </si>
+  <si>
     <t>난다이</t>
   </si>
   <si>
@@ -741,24 +762,6 @@
     <t>8조 5324억 5472만</t>
   </si>
   <si>
-    <t>찌율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>8조 4962억 4957만</t>
-  </si>
-  <si>
-    <t>루나스틱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
-  </si>
-  <si>
-    <t>8조 4116억 7331만</t>
-  </si>
-  <si>
     <t>킴보리파파</t>
   </si>
   <si>
@@ -768,15 +771,6 @@
     <t>7조 2596억 5172만</t>
   </si>
   <si>
-    <t>메키현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%ED%98%84</t>
-  </si>
-  <si>
-    <t>7조 1964억 4196만</t>
-  </si>
-  <si>
     <t>엠비피</t>
   </si>
   <si>
@@ -804,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%EC%9E%90%EB%8F%84%EB%A6%AC%EC%9C%A0%EC%A7%80</t>
   </si>
   <si>
-    <t>6조 624억 3694만</t>
+    <t>6조 1878억 6641만</t>
   </si>
   <si>
     <t>도맘가</t>
@@ -816,19 +810,28 @@
     <t>5조 9946억 8247만</t>
   </si>
   <si>
+    <t>브로큰애로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>5조 4947억 7139만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
   </si>
   <si>
     <t>5조 302억 9374만</t>
   </si>
   <si>
-    <t>브로큰애로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>4조 7765억 1191만</t>
+    <t>박예쁜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
+  </si>
+  <si>
+    <t>3조 7667억 1231만</t>
   </si>
   <si>
     <t>용감한순대국</t>
@@ -837,16 +840,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
   </si>
   <si>
-    <t>3조 3980억 7619만</t>
-  </si>
-  <si>
-    <t>박예쁜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
-  </si>
-  <si>
-    <t>3조 2486억 2256만</t>
+    <t>3조 4552억 4622만</t>
   </si>
   <si>
     <t>별밖에</t>
@@ -882,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
   </si>
   <si>
-    <t>2조 2787억 9266만</t>
+    <t>2조 3192억 6960만</t>
   </si>
   <si>
     <t>김군파파</t>
@@ -903,7 +897,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>1조 9053억 9527만</t>
+    <t>1조 9078억 2171만</t>
   </si>
   <si>
     <t>루맹이</t>
@@ -924,175 +918,202 @@
     <t>1조 3109억 723만</t>
   </si>
   <si>
+    <t>서브장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%B8%8C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>1조 2740억 9092만</t>
+  </si>
+  <si>
     <t>박마리아</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
   </si>
   <si>
+    <t>1조 1749억 1399만</t>
+  </si>
+  <si>
+    <t>한닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
+  </si>
+  <si>
+    <t>1조 917억 4459만</t>
+  </si>
+  <si>
+    <t>눈꽃물망초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
+  </si>
+  <si>
+    <t>94조 358억 5237만</t>
+  </si>
+  <si>
+    <t>포르쉐718</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
+  </si>
+  <si>
+    <t>67조 2879억 2679만</t>
+  </si>
+  <si>
+    <t>초보자시프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
+  </si>
+  <si>
+    <t>44조 3090억 2166만</t>
+  </si>
+  <si>
+    <t>A수라A</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=A%EC%88%98%EB%9D%BCA</t>
+  </si>
+  <si>
+    <t>16조 9092억 4197만</t>
+  </si>
+  <si>
+    <t>뒁글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
+  </si>
+  <si>
+    <t>12조 2523억 4090만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
+  </si>
+  <si>
+    <t>12조 408억 5948만</t>
+  </si>
+  <si>
+    <t>나윤v파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>9조 4655억 697만</t>
+  </si>
+  <si>
+    <t>공대애봉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8조 1162억 7516만</t>
+  </si>
+  <si>
+    <t>언기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>5조 8317억 2691만</t>
+  </si>
+  <si>
+    <t>우타이테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
+  </si>
+  <si>
+    <t>4조 8579억 2804만</t>
+  </si>
+  <si>
+    <t>원투아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>4조 880억 7151만</t>
+  </si>
+  <si>
+    <t>따뜻한배추</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
+  </si>
+  <si>
+    <t>4조 209억 3004만</t>
+  </si>
+  <si>
+    <t>범지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
+  </si>
+  <si>
+    <t>4조 46억 7508만</t>
+  </si>
+  <si>
+    <t>JAEYA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
+  </si>
+  <si>
+    <t>3조 9679억 8772만</t>
+  </si>
+  <si>
+    <t>묘목키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>3조 9486억 7828만</t>
+  </si>
+  <si>
+    <t>토르릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>3조 6432억 2966만</t>
+  </si>
+  <si>
+    <t>옵션키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>3조 5498억 548만</t>
+  </si>
+  <si>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>3조 4469억 2648만</t>
+  </si>
+  <si>
+    <t>까부네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%B6%80%EB%84%A4</t>
+  </si>
+  <si>
     <t>96</t>
   </si>
   <si>
-    <t>1조 1467억 8127만</t>
-  </si>
-  <si>
-    <t>한닝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
-  </si>
-  <si>
-    <t>1조 287억 7641만</t>
-  </si>
-  <si>
-    <t>눈꽃물망초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
-  </si>
-  <si>
-    <t>94조 358억 5237만</t>
-  </si>
-  <si>
-    <t>포르쉐718</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
-  </si>
-  <si>
-    <t>41조 5370억 1359만</t>
-  </si>
-  <si>
-    <t>초보자시프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B3%B4%EC%9E%90%EC%8B%9C%ED%94%84</t>
-  </si>
-  <si>
-    <t>40조 9007억 2111만</t>
-  </si>
-  <si>
-    <t>A수라A</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=A%EC%88%98%EB%9D%BCA</t>
-  </si>
-  <si>
-    <t>16조 8563억 9841만</t>
-  </si>
-  <si>
-    <t>뒁글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
-  </si>
-  <si>
-    <t>12조 105억 3693만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
-  </si>
-  <si>
-    <t>11조 6224억 4250만</t>
-  </si>
-  <si>
-    <t>나윤v파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>9조 3185억 6116만</t>
-  </si>
-  <si>
-    <t>공대애봉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7조 4796억 9261만</t>
-  </si>
-  <si>
-    <t>언기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 8317억 2691만</t>
-  </si>
-  <si>
-    <t>우타이테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
-  </si>
-  <si>
-    <t>4조 7010억 7830만</t>
-  </si>
-  <si>
-    <t>묘목키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>3조 8961억 1813만</t>
-  </si>
-  <si>
-    <t>따뜻한배추</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%EB%9C%BB%ED%95%9C%EB%B0%B0%EC%B6%94</t>
-  </si>
-  <si>
-    <t>3조 8367억 2418만</t>
-  </si>
-  <si>
-    <t>JAEYA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
-  </si>
-  <si>
-    <t>3조 7985억 8217만</t>
-  </si>
-  <si>
-    <t>토르릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>3조 6432억 2966만</t>
-  </si>
-  <si>
-    <t>원투아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>3조 6264억 1558만</t>
-  </si>
-  <si>
-    <t>옵션키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>3조 4973억 4530만</t>
-  </si>
-  <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>3조 4469억 2648만</t>
+    <t>3조 2964억 2379만</t>
   </si>
   <si>
     <t>웅쟈쓰</t>
@@ -1104,22 +1125,13 @@
     <t>3조 839억 9560만</t>
   </si>
   <si>
-    <t>범지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
-  </si>
-  <si>
-    <t>3조 308억 2909만</t>
-  </si>
-  <si>
     <t>밍고스틴</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
   </si>
   <si>
-    <t>2조 6944억 3951만</t>
+    <t>2조 8430억 1732만</t>
   </si>
   <si>
     <t>김주왕</t>
@@ -1128,7 +1140,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
   </si>
   <si>
-    <t>2조 2280억 9412만</t>
+    <t>2조 4517억 3557만</t>
   </si>
   <si>
     <t>맛닭꼬시멘토</t>
@@ -1137,7 +1149,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9B%EB%8B%AD%EA%BC%AC%EC%8B%9C%EB%A9%98%ED%86%A0</t>
   </si>
   <si>
-    <t>2조 1614억 5837만</t>
+    <t>2조 3059억 9107만</t>
+  </si>
+  <si>
+    <t>아쿠마불독</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
+  </si>
+  <si>
+    <t>2조 1285억 9288만</t>
   </si>
   <si>
     <t>l우주아이l</t>
@@ -1149,22 +1170,13 @@
     <t>2조 24억 4824만</t>
   </si>
   <si>
-    <t>아쿠마불독</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
-  </si>
-  <si>
-    <t>1조 9490억 4958만</t>
-  </si>
-  <si>
     <t>지짓수</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A7%93%EC%88%98</t>
   </si>
   <si>
-    <t>1조 7414억 8838만</t>
+    <t>1조 7746억 322만</t>
   </si>
   <si>
     <t>몽실망실토실</t>
@@ -1173,7 +1185,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
   </si>
   <si>
-    <t>1조 5696억 5134만</t>
+    <t>1조 5955억 6471만</t>
   </si>
   <si>
     <t>타락파워스님</t>
@@ -1185,22 +1197,13 @@
     <t>1조 5525억 1242만</t>
   </si>
   <si>
-    <t>2D파트장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2D%ED%8C%8C%ED%8A%B8%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>1조 1301억 5672만</t>
-  </si>
-  <si>
     <t>체시어</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
   </si>
   <si>
-    <t>9895억 4110만</t>
+    <t>1조 261억 6970만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -1209,13 +1212,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
   </si>
   <si>
-    <t>7988억 2463만</t>
+    <t>8324억 9163만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
   </si>
   <si>
-    <t>67조 5448억 5994만</t>
+    <t>67조 7289억 9326만</t>
   </si>
   <si>
     <t>멈디</t>
@@ -1233,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
   </si>
   <si>
-    <t>10조 699억 8945만</t>
+    <t>10조 1216억 3522만</t>
   </si>
   <si>
     <t>사숩</t>
@@ -1251,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
   </si>
   <si>
-    <t>7조 1524억 3820만</t>
+    <t>7조 7580억 6296만</t>
   </si>
   <si>
     <t>포도맛맥플</t>
@@ -1260,7 +1263,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
   </si>
   <si>
-    <t>6조 9686억 1816만</t>
+    <t>7조 858억 2199만</t>
+  </si>
+  <si>
+    <t>단비둘기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>6조 5624억 6390만</t>
   </si>
   <si>
     <t>또긔</t>
@@ -1269,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
   </si>
   <si>
-    <t>6조 3322억 9186만</t>
+    <t>6조 5488억 7448만</t>
   </si>
   <si>
     <t>썬콜법사도희</t>
@@ -1281,13 +1293,13 @@
     <t>6조 2037억 5385만</t>
   </si>
   <si>
-    <t>단비둘기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 9440억 3661만</t>
+    <t>김롸아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
+  </si>
+  <si>
+    <t>6조 1127억 3454만</t>
   </si>
   <si>
     <t>우치앵</t>
@@ -1305,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
   </si>
   <si>
-    <t>5조 7536억 447만</t>
+    <t>5조 7765억 9583만</t>
   </si>
   <si>
     <t>린샹판</t>
@@ -1317,15 +1329,6 @@
     <t>5조 7296억 6765만</t>
   </si>
   <si>
-    <t>김롸아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
-  </si>
-  <si>
-    <t>5조 6993억 2936만</t>
-  </si>
-  <si>
     <t>A7R4</t>
   </si>
   <si>
@@ -1335,6 +1338,15 @@
     <t>5조 3425억 1165만</t>
   </si>
   <si>
+    <t>limno</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=limno</t>
+  </si>
+  <si>
+    <t>5조 3184억 5603만</t>
+  </si>
+  <si>
     <t>까만색양갱</t>
   </si>
   <si>
@@ -1344,22 +1356,13 @@
     <t>4조 9594억 755만</t>
   </si>
   <si>
-    <t>limno</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=limno</t>
-  </si>
-  <si>
-    <t>4조 9037억 6342만</t>
-  </si>
-  <si>
     <t>도윤파덜</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%9C%A4%ED%8C%8C%EB%8D%9C</t>
   </si>
   <si>
-    <t>4조 865억 4637만</t>
+    <t>4조 1315억 4555만</t>
   </si>
   <si>
     <t>불곰파워</t>
@@ -1389,6 +1392,15 @@
     <t>3조 7546억 9317만</t>
   </si>
   <si>
+    <t>히어로경원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
+  </si>
+  <si>
+    <t>3조 7370억 885만</t>
+  </si>
+  <si>
     <t>무쿠미</t>
   </si>
   <si>
@@ -1398,13 +1410,13 @@
     <t>3조 7352억 6496만</t>
   </si>
   <si>
-    <t>히어로경원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
-  </si>
-  <si>
-    <t>3조 7189억 9950만</t>
+    <t>구파발메타몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>3조 6402억 7971만</t>
   </si>
   <si>
     <t>투둠</t>
@@ -1413,16 +1425,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%91%A0</t>
   </si>
   <si>
-    <t>3조 6104억 1512만</t>
-  </si>
-  <si>
-    <t>구파발메타몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>3조 6040억 7226만</t>
+    <t>3조 6143억 7610만</t>
   </si>
   <si>
     <t>zl지존썬콜lz</t>
@@ -1431,7 +1434,7 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
   </si>
   <si>
-    <t>3조 4971억 6620만</t>
+    <t>3조 5705억 528만</t>
   </si>
   <si>
     <t>구파발고양이</t>
@@ -1458,7 +1461,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 9467억 2817만</t>
+    <t>1조 9493억 6695만</t>
   </si>
   <si>
     <t>토리파더</t>
@@ -1479,7 +1482,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>1453억 7012만</t>
+    <t>1658억 7652만</t>
   </si>
   <si>
     <t>량용</t>
@@ -1488,10 +1491,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%89%EC%9A%A9</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>73조 4619억 2480만</t>
+    <t>73조 7039억 7143만</t>
   </si>
   <si>
     <t>달봉e</t>
@@ -1509,13 +1509,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%82%98%EB%94%94%EB%8F%84%EB%91%91</t>
   </si>
   <si>
-    <t>13조 459억 5525만</t>
+    <t>13조 2818억 687만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%86%ED%94%84</t>
   </si>
   <si>
-    <t>11조 1195억 6741만</t>
+    <t>11조 2534억 8195만</t>
   </si>
   <si>
     <t>조영현2</t>
@@ -1536,7 +1536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>7조 8320억 5093만</t>
+    <t>7조 9456억 8010만</t>
   </si>
   <si>
     <t>캔터베리</t>
@@ -1545,7 +1545,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%ED%84%B0%EB%B2%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>5조 7635억 642만</t>
+    <t>5조 7798억 2668만</t>
   </si>
   <si>
     <t>안경나라</t>
@@ -1572,7 +1572,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%85%EB%B0%A5</t>
   </si>
   <si>
-    <t>4조 925억 4982만</t>
+    <t>4조 1859억 69만</t>
   </si>
   <si>
     <t>햐밍</t>
@@ -1629,6 +1629,15 @@
     <t>3조 953억 891만</t>
   </si>
   <si>
+    <t>별잇</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%9E%87</t>
+  </si>
+  <si>
+    <t>2조 6405억 3405만</t>
+  </si>
+  <si>
     <t>리디엘</t>
   </si>
   <si>
@@ -1638,22 +1647,13 @@
     <t>2조 5833억 6655만</t>
   </si>
   <si>
-    <t>별잇</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EC%9E%87</t>
-  </si>
-  <si>
-    <t>2조 5818억 7789만</t>
-  </si>
-  <si>
     <t>산로지노</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%EB%A1%9C%EC%A7%80%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 4325억 6626만</t>
+    <t>2조 4384억 9680만</t>
   </si>
   <si>
     <t>Azham</t>
@@ -1680,7 +1680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%99%EC%8B%AC%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 8326억 1914만</t>
+    <t>1조 8390억 1488만</t>
   </si>
   <si>
     <t>떠하야</t>
@@ -1689,7 +1689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%ED%95%98%EC%95%BC</t>
   </si>
   <si>
-    <t>1조 8059억 8479만</t>
+    <t>1조 8209억 8251만</t>
   </si>
   <si>
     <t>이즈뤼얼</t>
@@ -1707,7 +1707,7 @@
     <t>https://mgf.gg/contents/character.php?n=Porto</t>
   </si>
   <si>
-    <t>1조 4619억 7338만</t>
+    <t>1조 4715억 7757만</t>
   </si>
   <si>
     <t>비라비스</t>
@@ -1725,7 +1725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>8949억 1218만</t>
+    <t>9355억 4664만</t>
   </si>
   <si>
     <t>후려까기</t>
@@ -1770,7 +1770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
   </si>
   <si>
-    <t>6조 6018억 1964만</t>
+    <t>6조 6202억 1570만</t>
   </si>
   <si>
     <t>숍솝</t>
@@ -1803,7 +1803,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EC%A0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 717억 5837만</t>
+    <t>2조 4323억 3883만</t>
   </si>
   <si>
     <t>지구뿌셔</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>1조 9227억 2332만</t>
+    <t>1조 9280억 3672만</t>
   </si>
   <si>
     <t>꼬햄</t>
@@ -1839,7 +1839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EC%82%90%EB%A7%A8</t>
   </si>
   <si>
-    <t>1조 627억 9891만</t>
+    <t>1조 1441억 5673만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1848,7 +1848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
   </si>
   <si>
-    <t>9421억 6228만</t>
+    <t>1조 816억 6177만</t>
   </si>
   <si>
     <t>다릿골</t>
@@ -1860,7 +1860,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>8087억 1343만</t>
+    <t>8398억 362만</t>
   </si>
   <si>
     <t>갓굴</t>
@@ -1869,7 +1869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EA%B5%B4</t>
   </si>
   <si>
-    <t>7789억 6373만</t>
+    <t>8134억 144만</t>
   </si>
   <si>
     <t>귀쮸</t>
@@ -1878,7 +1878,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%AE%B8</t>
   </si>
   <si>
-    <t>7216억 1422만</t>
+    <t>7393억 7168만</t>
+  </si>
+  <si>
+    <t>Viceversa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
+  </si>
+  <si>
+    <t>6154억 7095만</t>
   </si>
   <si>
     <t>당겨쏴</t>
@@ -1890,7 +1899,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>5927억 2018만</t>
+    <t>6153억 8678만</t>
   </si>
   <si>
     <t>알뺘노</t>
@@ -1902,31 +1911,13 @@
     <t>5827억 5044만</t>
   </si>
   <si>
-    <t>은단월</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%A8%EC%9B%94</t>
-  </si>
-  <si>
-    <t>5724억 593만</t>
-  </si>
-  <si>
-    <t>Viceversa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Viceversa</t>
-  </si>
-  <si>
-    <t>5548억 7550만</t>
-  </si>
-  <si>
     <t>투냉</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
   </si>
   <si>
-    <t>5056억 5251만</t>
+    <t>5211억 155만</t>
   </si>
   <si>
     <t>비비다</t>
@@ -1935,7 +1926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%8B%A4</t>
   </si>
   <si>
-    <t>4455억 4351만</t>
+    <t>4463억 3868만</t>
   </si>
   <si>
     <t>진1용</t>
@@ -1944,7 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%841%EC%9A%A9</t>
   </si>
   <si>
-    <t>4259억 9776만</t>
+    <t>4422억 5523만</t>
   </si>
   <si>
     <t>사과클럽</t>
@@ -1953,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
   </si>
   <si>
-    <t>4204억 5452만</t>
+    <t>4236억 699만</t>
   </si>
   <si>
     <t>차눅</t>
@@ -1962,7 +1953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EB%88%85</t>
   </si>
   <si>
-    <t>3710억 5118만</t>
+    <t>3717억 9532만</t>
   </si>
   <si>
     <t>팔나무</t>
@@ -1971,16 +1962,37 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%82%98%EB%AC%B4</t>
   </si>
   <si>
-    <t>3068억 2069만</t>
-  </si>
-  <si>
-    <t>53다2329</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=53%EB%8B%A42329</t>
-  </si>
-  <si>
-    <t>2599억 2443만</t>
+    <t>3306억 6021만</t>
+  </si>
+  <si>
+    <t>관현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%ED%98%84</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>2856억 3408만</t>
+  </si>
+  <si>
+    <t>양갱이유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EA%B0%B1%EC%9D%B4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>2734억 1037만</t>
+  </si>
+  <si>
+    <t>길지녁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%A7%80%EB%85%81</t>
+  </si>
+  <si>
+    <t>1999억 9827만</t>
   </si>
   <si>
     <t>쿠쇼</t>
@@ -1989,9 +2001,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%87%BC</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
     <t>1814억 9220만</t>
   </si>
   <si>
@@ -2004,7 +2013,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1655억 9678만</t>
+    <t>1661억 5982만</t>
   </si>
   <si>
     <t>강진현</t>
@@ -2013,16 +2022,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%A7%84%ED%98%84</t>
   </si>
   <si>
-    <t>1636억 818만</t>
-  </si>
-  <si>
-    <t>길지녁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B8%EC%A7%80%EB%85%81</t>
-  </si>
-  <si>
-    <t>1475억 2490만</t>
+    <t>1649억 2903만</t>
   </si>
   <si>
     <t>아포짓</t>
@@ -2046,7 +2046,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 9183억 3579만</t>
+    <t>2조 9213억 4964만</t>
+  </si>
+  <si>
+    <t>흑인드록바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%EB%93%9C%EB%A1%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>2조 5745억 4411만</t>
   </si>
   <si>
     <t>델타시그마</t>
@@ -2055,7 +2064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>2조 5324억 8776만</t>
+    <t>2조 5668억 406만</t>
   </si>
   <si>
     <t>끽스</t>
@@ -2085,22 +2094,13 @@
     <t>2조 2328억 7964만</t>
   </si>
   <si>
-    <t>흑인드록바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%EB%93%9C%EB%A1%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>2조 11억 1978만</t>
-  </si>
-  <si>
     <t>딴모</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
   </si>
   <si>
-    <t>1조 9572억 7982만</t>
+    <t>2조 138억 7582만</t>
   </si>
   <si>
     <t>밀가루죽</t>
@@ -2109,7 +2109,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%80%EA%B0%80%EB%A3%A8%EC%A3%BD</t>
   </si>
   <si>
-    <t>1조 8919억 1335만</t>
+    <t>1조 9302억 5342만</t>
   </si>
   <si>
     <t>한콩순</t>
@@ -2118,7 +2118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>1조 8643억 7838만</t>
+    <t>1조 8710억 7077만</t>
   </si>
   <si>
     <t>전팡</t>
@@ -2163,7 +2163,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>1조 4029억 4630만</t>
+    <t>1조 4074억 5435만</t>
   </si>
   <si>
     <t>사람님아</t>
@@ -2172,7 +2172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%8C%EB%8B%98%EC%95%84</t>
   </si>
   <si>
-    <t>1조 3495억 7233만</t>
+    <t>1조 3645억 6433만</t>
   </si>
   <si>
     <t>흑인햄찌</t>
@@ -2181,7 +2181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
   </si>
   <si>
-    <t>1조 2863억 886만</t>
+    <t>1조 2947억 2967만</t>
   </si>
   <si>
     <t>비숍마로밍</t>
@@ -2190,7 +2190,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%A7%88%EB%A1%9C%EB%B0%8D</t>
   </si>
   <si>
-    <t>1조 2530억 2256만</t>
+    <t>1조 2554억 3217만</t>
+  </si>
+  <si>
+    <t>은둔형오덕후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%91%94%ED%98%95%EC%98%A4%EB%8D%95%ED%9B%84</t>
+  </si>
+  <si>
+    <t>1조 1464억 7725만</t>
   </si>
   <si>
     <t>하랸</t>
@@ -2199,16 +2208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
   </si>
   <si>
-    <t>1조 1230억 4910만</t>
-  </si>
-  <si>
-    <t>은둔형오덕후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%91%94%ED%98%95%EC%98%A4%EB%8D%95%ED%9B%84</t>
-  </si>
-  <si>
-    <t>1조 1219억 8727만</t>
+    <t>1조 1236억 7320만</t>
   </si>
   <si>
     <t>존못에겐남짱</t>
@@ -2217,7 +2217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
   </si>
   <si>
-    <t>9944억 3565만</t>
+    <t>1조 220억 6242만</t>
   </si>
   <si>
     <t>민초양갱</t>
@@ -2253,7 +2253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
   </si>
   <si>
-    <t>7247억 2619만</t>
+    <t>7361억 6460만</t>
   </si>
   <si>
     <t>뉴비i</t>
@@ -2271,7 +2271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9E%84%EB%AA%BD%EC%88%9C</t>
   </si>
   <si>
-    <t>5291억 7916만</t>
+    <t>5800억 3070만</t>
   </si>
   <si>
     <t>두부장구니</t>
@@ -2280,7 +2280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EB%B6%80%EC%9E%A5%EA%B5%AC%EB%8B%88</t>
   </si>
   <si>
-    <t>4967억 7979만</t>
+    <t>5169억 1206만</t>
   </si>
   <si>
     <t>오리박사</t>
@@ -3061,25 +3061,25 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3090,13 +3090,13 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>87</v>
@@ -3108,10 +3108,10 @@
         <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3122,25 +3122,25 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>96</v>
@@ -3166,16 +3166,16 @@
         <v>99</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3186,28 +3186,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3218,28 +3218,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3250,28 +3250,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3282,28 +3282,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3314,28 +3314,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3346,28 +3346,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3378,25 +3378,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>135</v>
@@ -3422,13 +3422,13 @@
         <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>139</v>
@@ -3454,13 +3454,13 @@
         <v>142</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>143</v>
@@ -3486,13 +3486,13 @@
         <v>146</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>147</v>
@@ -3518,13 +3518,13 @@
         <v>150</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>151</v>
@@ -3550,13 +3550,13 @@
         <v>154</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>155</v>
@@ -3582,10 +3582,10 @@
         <v>158</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>159</v>
@@ -3614,16 +3614,16 @@
         <v>163</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3634,25 +3634,25 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>169</v>
@@ -3678,13 +3678,13 @@
         <v>172</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>173</v>
@@ -3710,13 +3710,13 @@
         <v>176</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>177</v>
@@ -3742,13 +3742,13 @@
         <v>180</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>181</v>
@@ -3774,13 +3774,13 @@
         <v>184</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>185</v>
@@ -3806,13 +3806,13 @@
         <v>188</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>189</v>
@@ -3838,10 +3838,10 @@
         <v>192</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>159</v>
@@ -3870,13 +3870,13 @@
         <v>196</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>197</v>
@@ -3902,10 +3902,10 @@
         <v>200</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>159</v>
@@ -3934,13 +3934,13 @@
         <v>204</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>205</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>206</v>
@@ -3966,10 +3966,10 @@
         <v>209</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>159</v>
@@ -3998,13 +3998,13 @@
         <v>213</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>214</v>
@@ -4062,7 +4062,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4115,16 +4115,16 @@
         <v>216</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4135,28 +4135,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4167,28 +4167,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4202,25 +4202,25 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4231,28 +4231,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4263,28 +4263,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4295,28 +4295,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4327,28 +4327,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4359,28 +4359,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4391,28 +4391,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4423,28 +4423,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4458,25 +4458,25 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4490,25 +4490,25 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4522,25 +4522,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4554,25 +4554,25 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4592,19 +4592,19 @@
         <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4618,25 +4618,25 @@
         <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4650,25 +4650,25 @@
         <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4679,28 +4679,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4714,25 +4714,25 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4746,25 +4746,25 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4778,25 +4778,25 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4810,25 +4810,25 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4842,25 +4842,25 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>159</v>
+        <v>287</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4874,25 +4874,25 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4906,25 +4906,25 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4938,25 +4938,25 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>159</v>
+        <v>287</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4970,22 +4970,22 @@
         <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>300</v>
@@ -5011,13 +5011,13 @@
         <v>302</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>303</v>
@@ -5127,13 +5127,13 @@
         <v>305</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>205</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>306</v>
@@ -5147,7 +5147,7 @@
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>307</v>
@@ -5159,13 +5159,13 @@
         <v>308</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>309</v>
@@ -5179,7 +5179,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>310</v>
@@ -5191,13 +5191,13 @@
         <v>311</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>312</v>
@@ -5223,13 +5223,13 @@
         <v>314</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>315</v>
@@ -5243,7 +5243,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>316</v>
@@ -5255,13 +5255,13 @@
         <v>317</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>318</v>
@@ -5275,7 +5275,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>41</v>
@@ -5287,13 +5287,13 @@
         <v>319</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>320</v>
@@ -5307,7 +5307,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>321</v>
@@ -5319,13 +5319,13 @@
         <v>322</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>323</v>
@@ -5339,7 +5339,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -5351,13 +5351,13 @@
         <v>325</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>326</v>
@@ -5371,7 +5371,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>327</v>
@@ -5383,13 +5383,13 @@
         <v>328</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>329</v>
@@ -5403,7 +5403,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>330</v>
@@ -5415,13 +5415,13 @@
         <v>331</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>332</v>
@@ -5435,7 +5435,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>333</v>
@@ -5447,13 +5447,13 @@
         <v>334</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>335</v>
@@ -5479,13 +5479,13 @@
         <v>337</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>205</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>338</v>
@@ -5511,13 +5511,13 @@
         <v>340</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>341</v>
@@ -5543,13 +5543,13 @@
         <v>343</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>344</v>
@@ -5575,13 +5575,13 @@
         <v>346</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>347</v>
@@ -5607,13 +5607,13 @@
         <v>349</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>350</v>
@@ -5639,13 +5639,13 @@
         <v>352</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>353</v>
@@ -5671,13 +5671,13 @@
         <v>355</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>356</v>
@@ -5691,7 +5691,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>357</v>
@@ -5703,16 +5703,16 @@
         <v>358</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>164</v>
+        <v>359</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5726,25 +5726,25 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5758,25 +5758,25 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5790,25 +5790,25 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5822,25 +5822,25 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5854,25 +5854,25 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5886,25 +5886,25 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5918,25 +5918,25 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5950,25 +5950,25 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5982,25 +5982,25 @@
         <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6014,16 +6014,16 @@
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>205</v>
@@ -6032,7 +6032,7 @@
         <v>159</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6046,25 +6046,25 @@
         <v>211</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6169,19 +6169,19 @@
         <v>47</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6192,28 +6192,28 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6224,28 +6224,28 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6259,25 +6259,25 @@
         <v>97</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6288,28 +6288,28 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>205</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6320,28 +6320,28 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6352,28 +6352,28 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6384,28 +6384,28 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6416,28 +6416,28 @@
         <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6448,28 +6448,28 @@
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6480,28 +6480,28 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6515,25 +6515,25 @@
         <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6547,25 +6547,25 @@
         <v>140</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6579,25 +6579,25 @@
         <v>144</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6611,25 +6611,25 @@
         <v>148</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6643,25 +6643,25 @@
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6675,25 +6675,25 @@
         <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6707,25 +6707,25 @@
         <v>161</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6736,28 +6736,28 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6771,25 +6771,25 @@
         <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6803,25 +6803,25 @@
         <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6835,25 +6835,25 @@
         <v>178</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6867,25 +6867,25 @@
         <v>182</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6899,25 +6899,25 @@
         <v>186</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6931,25 +6931,25 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6963,25 +6963,25 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6995,25 +6995,25 @@
         <v>198</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7027,25 +7027,25 @@
         <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7059,25 +7059,25 @@
         <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7091,25 +7091,25 @@
         <v>211</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -7208,22 +7208,22 @@
         <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>485</v>
+        <v>217</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>486</v>
@@ -7237,7 +7237,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>487</v>
@@ -7249,13 +7249,13 @@
         <v>488</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>489</v>
@@ -7269,7 +7269,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>490</v>
@@ -7281,13 +7281,13 @@
         <v>491</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>492</v>
@@ -7313,13 +7313,13 @@
         <v>493</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>494</v>
@@ -7333,7 +7333,7 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>495</v>
@@ -7345,13 +7345,13 @@
         <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>497</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>498</v>
@@ -7365,7 +7365,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>499</v>
@@ -7377,13 +7377,13 @@
         <v>500</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>501</v>
@@ -7397,7 +7397,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>502</v>
@@ -7409,13 +7409,13 @@
         <v>503</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>504</v>
@@ -7429,7 +7429,7 @@
         <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>505</v>
@@ -7441,13 +7441,13 @@
         <v>506</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>507</v>
@@ -7461,7 +7461,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>508</v>
@@ -7473,13 +7473,13 @@
         <v>509</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>510</v>
@@ -7493,7 +7493,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>511</v>
@@ -7505,13 +7505,13 @@
         <v>512</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>513</v>
@@ -7525,7 +7525,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>514</v>
@@ -7537,13 +7537,13 @@
         <v>515</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>516</v>
@@ -7569,13 +7569,13 @@
         <v>518</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>519</v>
@@ -7601,13 +7601,13 @@
         <v>521</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>522</v>
@@ -7633,13 +7633,13 @@
         <v>524</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>525</v>
@@ -7665,13 +7665,13 @@
         <v>527</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>528</v>
@@ -7697,13 +7697,13 @@
         <v>530</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>531</v>
@@ -7729,10 +7729,10 @@
         <v>533</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>159</v>
@@ -7761,10 +7761,10 @@
         <v>536</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>159</v>
@@ -7781,7 +7781,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>538</v>
@@ -7793,13 +7793,13 @@
         <v>539</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>540</v>
@@ -7825,10 +7825,10 @@
         <v>542</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>159</v>
@@ -7857,13 +7857,13 @@
         <v>545</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>546</v>
@@ -7889,10 +7889,10 @@
         <v>548</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>159</v>
@@ -7921,13 +7921,13 @@
         <v>551</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>552</v>
@@ -7953,10 +7953,10 @@
         <v>554</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>159</v>
@@ -7985,13 +7985,13 @@
         <v>557</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>558</v>
@@ -8017,10 +8017,10 @@
         <v>560</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>159</v>
@@ -8049,10 +8049,10 @@
         <v>563</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>159</v>
@@ -8081,13 +8081,13 @@
         <v>566</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>567</v>
@@ -8113,13 +8113,13 @@
         <v>569</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>570</v>
@@ -8145,13 +8145,13 @@
         <v>572</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>573</v>
@@ -8262,13 +8262,13 @@
         <v>575</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>576</v>
@@ -8282,7 +8282,7 @@
         <v>56</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>577</v>
@@ -8294,13 +8294,13 @@
         <v>578</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>579</v>
@@ -8314,7 +8314,7 @@
         <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>580</v>
@@ -8326,13 +8326,13 @@
         <v>581</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>582</v>
@@ -8358,13 +8358,13 @@
         <v>584</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>497</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>585</v>
@@ -8378,7 +8378,7 @@
         <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>62</v>
@@ -8390,13 +8390,13 @@
         <v>586</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>587</v>
@@ -8410,7 +8410,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>588</v>
@@ -8422,13 +8422,13 @@
         <v>589</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>590</v>
@@ -8442,7 +8442,7 @@
         <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>591</v>
@@ -8454,10 +8454,10 @@
         <v>592</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>159</v>
@@ -8474,7 +8474,7 @@
         <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>594</v>
@@ -8486,13 +8486,13 @@
         <v>595</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>596</v>
@@ -8506,7 +8506,7 @@
         <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>597</v>
@@ -8518,10 +8518,10 @@
         <v>598</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>159</v>
@@ -8538,7 +8538,7 @@
         <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>600</v>
@@ -8550,13 +8550,13 @@
         <v>601</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>602</v>
@@ -8570,7 +8570,7 @@
         <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>603</v>
@@ -8582,10 +8582,10 @@
         <v>604</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>159</v>
@@ -8614,10 +8614,10 @@
         <v>607</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>608</v>
@@ -8646,13 +8646,13 @@
         <v>611</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>612</v>
@@ -8678,13 +8678,13 @@
         <v>614</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>615</v>
@@ -8710,16 +8710,16 @@
         <v>617</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>251</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -8733,22 +8733,22 @@
         <v>152</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>622</v>
@@ -8774,13 +8774,13 @@
         <v>624</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>253</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>625</v>
@@ -8806,13 +8806,13 @@
         <v>627</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>628</v>
@@ -8826,7 +8826,7 @@
         <v>56</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>629</v>
@@ -8838,13 +8838,13 @@
         <v>630</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>289</v>
+        <v>621</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>631</v>
@@ -8870,13 +8870,13 @@
         <v>633</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>618</v>
+        <v>359</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>634</v>
@@ -8902,13 +8902,13 @@
         <v>636</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>299</v>
+        <v>608</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>637</v>
@@ -8934,13 +8934,13 @@
         <v>639</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>640</v>
@@ -8966,13 +8966,13 @@
         <v>642</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>643</v>
@@ -8998,16 +8998,16 @@
         <v>645</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -9021,25 +9021,25 @@
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>497</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>481</v>
+        <v>646</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -9053,22 +9053,22 @@
         <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>652</v>
+        <v>482</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>653</v>
@@ -9094,16 +9094,16 @@
         <v>655</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -9117,22 +9117,22 @@
         <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>660</v>
@@ -9158,13 +9158,13 @@
         <v>662</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>481</v>
+        <v>659</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>663</v>
@@ -9274,13 +9274,13 @@
         <v>665</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>497</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>666</v>
@@ -9294,7 +9294,7 @@
         <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>70</v>
@@ -9306,10 +9306,10 @@
         <v>667</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>159</v>
@@ -9326,7 +9326,7 @@
         <v>63</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>669</v>
@@ -9338,10 +9338,10 @@
         <v>670</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>159</v>
@@ -9370,10 +9370,10 @@
         <v>673</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>159</v>
@@ -9390,7 +9390,7 @@
         <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>675</v>
@@ -9402,13 +9402,13 @@
         <v>676</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>677</v>
@@ -9422,7 +9422,7 @@
         <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>678</v>
@@ -9434,10 +9434,10 @@
         <v>679</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>159</v>
@@ -9454,7 +9454,7 @@
         <v>63</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>681</v>
@@ -9466,10 +9466,10 @@
         <v>682</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>95</v>
+        <v>251</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>159</v>
@@ -9486,7 +9486,7 @@
         <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>684</v>
@@ -9498,10 +9498,10 @@
         <v>685</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>159</v>
@@ -9518,7 +9518,7 @@
         <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>687</v>
@@ -9530,10 +9530,10 @@
         <v>688</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>159</v>
@@ -9550,7 +9550,7 @@
         <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>690</v>
@@ -9562,10 +9562,10 @@
         <v>691</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>159</v>
@@ -9582,7 +9582,7 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>693</v>
@@ -9594,13 +9594,13 @@
         <v>694</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>695</v>
@@ -9626,13 +9626,13 @@
         <v>697</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>698</v>
@@ -9658,7 +9658,7 @@
         <v>700</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>497</v>
@@ -9690,13 +9690,13 @@
         <v>703</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>704</v>
@@ -9722,13 +9722,13 @@
         <v>706</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>289</v>
+        <v>159</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>707</v>
@@ -9754,13 +9754,13 @@
         <v>709</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>497</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>710</v>
@@ -9786,10 +9786,10 @@
         <v>712</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>159</v>
@@ -9818,10 +9818,10 @@
         <v>715</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>159</v>
@@ -9838,7 +9838,7 @@
         <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>717</v>
@@ -9850,13 +9850,13 @@
         <v>718</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>719</v>
@@ -9882,13 +9882,13 @@
         <v>721</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>722</v>
@@ -9914,13 +9914,13 @@
         <v>724</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>725</v>
@@ -9946,13 +9946,13 @@
         <v>727</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>728</v>
@@ -9978,13 +9978,13 @@
         <v>730</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>731</v>
@@ -10010,13 +10010,13 @@
         <v>733</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>734</v>
@@ -10042,13 +10042,13 @@
         <v>736</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>497</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>737</v>
@@ -10074,13 +10074,13 @@
         <v>739</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>618</v>
+        <v>359</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>740</v>
@@ -10106,10 +10106,10 @@
         <v>742</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>159</v>
@@ -10138,10 +10138,10 @@
         <v>745</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>608</v>
@@ -10170,13 +10170,13 @@
         <v>748</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>749</v>
@@ -10202,10 +10202,10 @@
         <v>751</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>608</v>

--- a/reports/빅딜/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_training_mgf_report.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="다다익선" sheetId="3" r:id="rId3"/>
-    <sheet name="블랙소울" sheetId="4" r:id="rId4"/>
+    <sheet name="블랙소울" sheetId="3" r:id="rId3"/>
+    <sheet name="다다익선" sheetId="4" r:id="rId4"/>
     <sheet name="초코나라" sheetId="5" r:id="rId5"/>
     <sheet name="비련" sheetId="6" r:id="rId6"/>
     <sheet name="밀크런" sheetId="7" r:id="rId7"/>
@@ -18,20 +18,20 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">다다익선!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">다다익선!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">밀크런!$A$1:$J$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">블랙소울!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">블랙소울!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">초코나라!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">털미녀!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">털미녀!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="758">
   <si>
     <t>guild_name</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>355</t>
+    <t>353</t>
   </si>
   <si>
     <t>10위</t>
@@ -96,7 +96,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>381조 9031억 5417만</t>
+    <t>401조 2467억 9148만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -105,7 +105,31 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.05.03</t>
+    <t>2026.05.04</t>
+  </si>
+  <si>
+    <t>블랙소울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>709조 373억 7984만</t>
+  </si>
+  <si>
+    <t>보심</t>
   </si>
   <si>
     <t>다다익선</t>
@@ -117,13 +141,13 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>285</t>
+    <t>277</t>
   </si>
   <si>
     <t>6위</t>
   </si>
   <si>
-    <t>640조 6750억 5937만</t>
+    <t>723조 2918억 8487만</t>
   </si>
   <si>
     <t>2일 미접 여부 확인 길드컨텐츠 갱신 여부 확인,전투력 2조 이상 재밌게 소통하면서 게임하실 분 공대애봉이/뒁글 문의 주세요</t>
@@ -132,124 +156,100 @@
     <t>Pakistan</t>
   </si>
   <si>
-    <t>블랙소울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%9E%99%EC%86%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>309</t>
+    <t>초코나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>459조 9694억 8423만</t>
+  </si>
+  <si>
+    <t>초코남</t>
+  </si>
+  <si>
+    <t>비련</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>388조 6421억 4264만</t>
+  </si>
+  <si>
+    <t>비련길드 모집조건 : 투력 9000억 이상 일일기부 300+ 길컨 참여자</t>
+  </si>
+  <si>
+    <t>렆프</t>
+  </si>
+  <si>
+    <t>밀크런</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
+  </si>
+  <si>
+    <t>596</t>
+  </si>
+  <si>
+    <t>46위</t>
+  </si>
+  <si>
+    <t>137조 3369억 5891만</t>
+  </si>
+  <si>
+    <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요 길갑문의 : 정뽀</t>
+  </si>
+  <si>
+    <t>정뽀</t>
+  </si>
+  <si>
+    <t>털미녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%84%B8%EB%AF%B8%EB%85%80</t>
+  </si>
+  <si>
+    <t>Scania 33</t>
+  </si>
+  <si>
+    <t>926</t>
   </si>
   <si>
     <t>8위</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>536조 7920억 1493만</t>
-  </si>
-  <si>
-    <t>보심</t>
-  </si>
-  <si>
-    <t>초코나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B4%88%EC%BD%94%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>348</t>
-  </si>
-  <si>
-    <t>7위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>402조 7161억 316만</t>
-  </si>
-  <si>
-    <t>초코남</t>
-  </si>
-  <si>
-    <t>비련</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%84%EB%A0%A8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>32위</t>
-  </si>
-  <si>
-    <t>354조 7680억 3416만</t>
-  </si>
-  <si>
-    <t>비련길드 모집조건 : 투력 9000억 이상 일일기부 300+ 길컨 참여자</t>
-  </si>
-  <si>
-    <t>렆프</t>
-  </si>
-  <si>
-    <t>밀크런</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
-  </si>
-  <si>
-    <t>589</t>
-  </si>
-  <si>
-    <t>45위</t>
-  </si>
-  <si>
-    <t>132조 5685억 1968만</t>
-  </si>
-  <si>
-    <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요</t>
-  </si>
-  <si>
-    <t>정뽀</t>
-  </si>
-  <si>
-    <t>털미녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%84%B8%EB%AF%B8%EB%85%80</t>
-  </si>
-  <si>
-    <t>Scania 33</t>
-  </si>
-  <si>
-    <t>905</t>
-  </si>
-  <si>
     <t>Lv.6</t>
   </si>
   <si>
-    <t>67조 7356억 4202만</t>
+    <t>68조 8047억 5766만</t>
   </si>
   <si>
     <t>*투력 3조이상* *길컨필수* *미접1일추방* *공헌도체크* 조건많아서 미안해 사랑</t>
   </si>
   <si>
-    <t>86미녀</t>
+    <t>야로야옹</t>
   </si>
   <si>
     <t>member_rank_in_guild</t>
@@ -294,7 +294,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>69조 2475억 454만</t>
+    <t>77조 6482억 4541만</t>
   </si>
   <si>
     <t>2</t>
@@ -360,12 +360,27 @@
     <t>102</t>
   </si>
   <si>
-    <t>22조 1991억 4843만</t>
+    <t>22조 7424억 8669만</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>15조 9331억 5952만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>단풍카우</t>
   </si>
   <si>
@@ -375,21 +390,6 @@
     <t>15조 1609억 687만</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>13조 2229억 5022만</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -399,7 +399,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>10조 4842억 7700만</t>
+    <t>13조 4210억 4260만</t>
   </si>
   <si>
     <t>9</t>
@@ -435,16 +435,31 @@
     <t>11</t>
   </si>
   <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>8조 9186억 3216만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>우후</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>8조 2972억 3433만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>8조 5687억 2721만</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>반도</t>
@@ -459,10 +474,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>7조 8230억 2060만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>8조 601억 9446만</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -471,22 +486,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>7조 6231억 8496만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>7조 5148억 1235만</t>
+    <t>7조 8295억 868만</t>
   </si>
   <si>
     <t>15</t>
@@ -498,7 +498,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>6조 1489억 7925만</t>
+    <t>6조 3249억 5172만</t>
   </si>
   <si>
     <t>16</t>
@@ -522,7 +522,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>5조 5412억 1354만</t>
+    <t>5조 5808억 4621만</t>
   </si>
   <si>
     <t>18</t>
@@ -540,6 +540,18 @@
     <t>19</t>
   </si>
   <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>5조 393억 3442만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
@@ -552,7 +564,7 @@
     <t>4조 9725억 1519만</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>여븨</t>
@@ -564,7 +576,7 @@
     <t>4조 8791억 7843만</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -573,10 +585,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>4조 8132억 8816만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>4조 8619억 4165만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -591,21 +603,21 @@
     <t>4조 7975억 1419만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>4조 5572억 5348만</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>3조 4127억 6119만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>불보독지</t>
   </si>
   <si>
@@ -615,10 +627,10 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>3조 3228억 3964만</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>3조 3575억 6204만</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -630,18 +642,6 @@
     <t>3조 488억 9661만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>3조 265억 4028만</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -690,13 +690,286 @@
     <t>2조 3292억 507만</t>
   </si>
   <si>
+    <t>상현별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>261조 7712억 3734만</t>
+  </si>
+  <si>
+    <t>머니파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EB%8B%88%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>88조 4978억 6146만</t>
+  </si>
+  <si>
+    <t>말랑콩닥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
+  </si>
+  <si>
+    <t>79조 1064억 4654만</t>
+  </si>
+  <si>
+    <t>뚜까랜덤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B9%8C%EB%9E%9C%EB%8D%A4</t>
+  </si>
+  <si>
+    <t>56조 6828억 4581만</t>
+  </si>
+  <si>
+    <t>한박자느리게</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%95%EC%9E%90%EB%8A%90%EB%A6%AC%EA%B2%8C</t>
+  </si>
+  <si>
+    <t>22조 7377억 1998만</t>
+  </si>
+  <si>
+    <t>귀심</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>21조 2871억 8916만</t>
+  </si>
+  <si>
+    <t>난다이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%8B%A4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>17조 1314억 2626만</t>
+  </si>
+  <si>
+    <t>시눈재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%88%88%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>15조 7902억 7493만</t>
+  </si>
+  <si>
+    <t>루나스틱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
+  </si>
+  <si>
+    <t>15조 6010억 3840만</t>
+  </si>
+  <si>
+    <t>킴보리파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B3%B4%EB%A6%AC%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>13조 2651억 2665만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>13조 2571억 1105만</t>
+  </si>
+  <si>
+    <t>최상급조준경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%83%81%EA%B8%89%EC%A1%B0%EC%A4%80%EA%B2%BD</t>
+  </si>
+  <si>
+    <t>13조 2069억 2594만</t>
+  </si>
+  <si>
+    <t>도맘가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A7%98%EA%B0%80</t>
+  </si>
+  <si>
+    <t>12조 6104억 9618만</t>
+  </si>
+  <si>
+    <t>으넝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%84%9D</t>
+  </si>
+  <si>
+    <t>10조 2762억 1167만</t>
+  </si>
+  <si>
+    <t>엠비피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EB%B9%84%ED%94%BC</t>
+  </si>
+  <si>
+    <t>8조 2462억 5403만</t>
+  </si>
+  <si>
+    <t>브로큰애로우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>7조 3382억 6192만</t>
+  </si>
+  <si>
+    <t>곱션이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EC%85%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7조 552억 7360만</t>
+  </si>
+  <si>
+    <t>감자도리유지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%EC%9E%90%EB%8F%84%EB%A6%AC%EC%9C%A0%EC%A7%80</t>
+  </si>
+  <si>
+    <t>6조 1878억 6641만</t>
+  </si>
+  <si>
+    <t>용감한순대국</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
+  </si>
+  <si>
+    <t>5조 8005억 319만</t>
+  </si>
+  <si>
+    <t>곱동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 5587억 6389만</t>
+  </si>
+  <si>
+    <t>박예쁜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
+  </si>
+  <si>
+    <t>4조 7032억 6017만</t>
+  </si>
+  <si>
+    <t>별밖에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
+  </si>
+  <si>
+    <t>3조 4957억 4623만</t>
+  </si>
+  <si>
+    <t>김군파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B5%B0%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>3조 4934억 4191만</t>
+  </si>
+  <si>
+    <t>쿰척쿰쳑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
+  </si>
+  <si>
+    <t>3조 2919억 705만</t>
+  </si>
+  <si>
+    <t>딸둘아범</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EB%91%98%EC%95%84%EB%B2%94</t>
+  </si>
+  <si>
+    <t>2조 9884억 9757만</t>
+  </si>
+  <si>
+    <t>루맹이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 5976억 5729만</t>
+  </si>
+  <si>
+    <t>박마리아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2조 1194억 6179만</t>
+  </si>
+  <si>
+    <t>츄쁜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
+  </si>
+  <si>
+    <t>1조 9244억 279만</t>
+  </si>
+  <si>
+    <t>한닝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
+  </si>
+  <si>
+    <t>1조 7327억 3192만</t>
+  </si>
+  <si>
+    <t>서브장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%B8%8C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>1조 4830억 2205만</t>
+  </si>
+  <si>
     <t>눈꽃물망초</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EB%AC%BC%EB%A7%9D%EC%B4%88</t>
   </si>
   <si>
-    <t>167조 1389억 8967만</t>
+    <t>200조 7381억 9631만</t>
   </si>
   <si>
     <t>비숍이된시프</t>
@@ -705,7 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EC%9D%B4%EB%90%9C%EC%8B%9C%ED%94%84</t>
   </si>
   <si>
-    <t>143조 2531억 9499만</t>
+    <t>153조 7896억 5692만</t>
   </si>
   <si>
     <t>포르쉐718</t>
@@ -714,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%A5%B4%EC%89%90718</t>
   </si>
   <si>
-    <t>131조 9501억 201만</t>
+    <t>147조 5615억 6342만</t>
   </si>
   <si>
     <t>A수라A</t>
@@ -723,13 +996,13 @@
     <t>https://mgf.gg/contents/character.php?n=A%EC%88%98%EB%9D%BCA</t>
   </si>
   <si>
-    <t>23조 1226억 4542만</t>
+    <t>31조 5119억 8985만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Pakistan</t>
   </si>
   <si>
-    <t>20조 5778억 3351만</t>
+    <t>23조 1864억 2354만</t>
   </si>
   <si>
     <t>공대애봉이</t>
@@ -738,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%8C%80%EC%95%A0%EB%B4%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>20조 4480억 6908만</t>
+    <t>21조 3058억 364만</t>
   </si>
   <si>
     <t>뒁글</t>
@@ -747,7 +1020,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%92%81%EA%B8%80</t>
   </si>
   <si>
-    <t>17조 7101억 5191만</t>
+    <t>18조 3847억 2608만</t>
   </si>
   <si>
     <t>나윤v파파</t>
@@ -756,7 +1029,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EC%9C%A4v%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>12조 8997억 3930만</t>
+    <t>13조 9482억 2970만</t>
+  </si>
+  <si>
+    <t>까부네</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%B6%80%EB%84%A4</t>
+  </si>
+  <si>
+    <t>10조 1631억 661만</t>
   </si>
   <si>
     <t>우타이테</t>
@@ -765,7 +1047,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%83%80%EC%9D%B4%ED%85%8C</t>
   </si>
   <si>
-    <t>8조 7969억 4133만</t>
+    <t>9조 6069억 1128만</t>
   </si>
   <si>
     <t>진리총</t>
@@ -774,16 +1056,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EB%A6%AC%EC%B4%9D</t>
   </si>
   <si>
-    <t>8조 6240억 8559만</t>
-  </si>
-  <si>
-    <t>까부네</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%B6%80%EB%84%A4</t>
-  </si>
-  <si>
-    <t>8조 2993억 6105만</t>
+    <t>8조 7782억 591만</t>
+  </si>
+  <si>
+    <t>웅쟈쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
+  </si>
+  <si>
+    <t>7조 2200억 1049만</t>
+  </si>
+  <si>
+    <t>샤생니임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
+  </si>
+  <si>
+    <t>7조 269억 5270만</t>
   </si>
   <si>
     <t>언기</t>
@@ -792,7 +1083,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B8%EA%B8%B0</t>
   </si>
   <si>
-    <t>5조 9781억 28만</t>
+    <t>6조 5787억 5428만</t>
+  </si>
+  <si>
+    <t>옵션키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>6조 2377억 555만</t>
+  </si>
+  <si>
+    <t>원투아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>5조 9123억 5906만</t>
   </si>
   <si>
     <t>따뜻한배추</t>
@@ -804,49 +1113,49 @@
     <t>5조 8681억 3383만</t>
   </si>
   <si>
-    <t>옵션키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B5%EC%85%98%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>5조 5601억 4756만</t>
-  </si>
-  <si>
-    <t>샤생니임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%83%9D%EB%8B%88%EC%9E%84</t>
-  </si>
-  <si>
-    <t>5조 4713억 3873만</t>
-  </si>
-  <si>
     <t>JAEYA</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=JAEYA</t>
   </si>
   <si>
-    <t>5조 4568억 4941만</t>
-  </si>
-  <si>
-    <t>웅쟈쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9F%88%EC%93%B0</t>
-  </si>
-  <si>
-    <t>5조 4102억 9698만</t>
-  </si>
-  <si>
-    <t>원투아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%ED%88%AC%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>5조 924억 6028만</t>
+    <t>5조 7163억 2520만</t>
+  </si>
+  <si>
+    <t>토르릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>4조 7085억 1761만</t>
+  </si>
+  <si>
+    <t>타락파워스님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>4조 6641억 381만</t>
+  </si>
+  <si>
+    <t>김주왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
+  </si>
+  <si>
+    <t>4조 6467억 5603만</t>
+  </si>
+  <si>
+    <t>묘목키우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>4조 6051억 3481만</t>
   </si>
   <si>
     <t>맛닭꼬시멘토</t>
@@ -858,49 +1167,22 @@
     <t>4조 5282억 9168만</t>
   </si>
   <si>
-    <t>묘목키우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%98%EB%AA%A9%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>4조 4411억 8655만</t>
-  </si>
-  <si>
-    <t>타락파워스님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EB%9D%BD%ED%8C%8C%EC%9B%8C%EC%8A%A4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>4조 3015억 6167만</t>
-  </si>
-  <si>
-    <t>토르릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A5%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>4조 2425억 8027만</t>
-  </si>
-  <si>
-    <t>김주왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%A3%BC%EC%99%95</t>
-  </si>
-  <si>
-    <t>4조 1038억 9525만</t>
-  </si>
-  <si>
     <t>아쿠마불독</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%BF%A0%EB%A7%88%EB%B6%88%EB%8F%85</t>
   </si>
   <si>
-    <t>3조 7308억 3217만</t>
+    <t>3조 8011억 3843만</t>
+  </si>
+  <si>
+    <t>지짓수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A7%93%EC%88%98</t>
+  </si>
+  <si>
+    <t>3조 417억 9823만</t>
   </si>
   <si>
     <t>밍고스틴</t>
@@ -909,16 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EA%B3%A0%EC%8A%A4%ED%8B%B4</t>
   </si>
   <si>
-    <t>2조 9273억 6356만</t>
-  </si>
-  <si>
-    <t>지짓수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A7%93%EC%88%98</t>
-  </si>
-  <si>
-    <t>2조 5568억 8661만</t>
+    <t>2조 9718억 6264만</t>
   </si>
   <si>
     <t>몽실망실토실</t>
@@ -927,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%8B%A4%EB%A7%9D%EC%8B%A4%ED%86%A0%EC%8B%A4</t>
   </si>
   <si>
-    <t>2조 1030억 2891만</t>
+    <t>2조 1204억 706만</t>
   </si>
   <si>
     <t>l우주아이l</t>
@@ -936,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=l%EC%9A%B0%EC%A3%BC%EC%95%84%EC%9D%B4l</t>
   </si>
   <si>
-    <t>2조 24억 4824만</t>
+    <t>2조 869억 4116만</t>
   </si>
   <si>
     <t>체시어</t>
@@ -945,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EC%8B%9C%EC%96%B4</t>
   </si>
   <si>
-    <t>1조 4135억 2772만</t>
+    <t>1조 4668억 6682만</t>
   </si>
   <si>
     <t>주니이옹</t>
@@ -954,286 +1227,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%8B%88%EC%9D%B4%EC%98%B9</t>
   </si>
   <si>
-    <t>1조 758억 4538만</t>
-  </si>
-  <si>
-    <t>상현별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%98%84%EB%B3%84</t>
-  </si>
-  <si>
-    <t>160조 5172억 4862만</t>
-  </si>
-  <si>
-    <t>머니파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EB%8B%88%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>72조 5448억 9309만</t>
-  </si>
-  <si>
-    <t>말랑콩닥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%9E%91%EC%BD%A9%EB%8B%A5</t>
-  </si>
-  <si>
-    <t>68조 4115억 646만</t>
-  </si>
-  <si>
-    <t>뚜까랜덤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%9C%EA%B9%8C%EB%9E%9C%EB%8D%A4</t>
-  </si>
-  <si>
-    <t>50조 9201억 118만</t>
-  </si>
-  <si>
-    <t>귀심</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>16조 1454억 9024만</t>
-  </si>
-  <si>
-    <t>시눈재</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%88%88%EC%9E%AC</t>
-  </si>
-  <si>
-    <t>15조 7387억 3626만</t>
-  </si>
-  <si>
-    <t>난다이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%8B%A4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>14조 9042억 313만</t>
-  </si>
-  <si>
-    <t>루나스틱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%82%98%EC%8A%A4%ED%8B%B1</t>
-  </si>
-  <si>
-    <t>13조 3245억 9057만</t>
-  </si>
-  <si>
-    <t>킴보리파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%B3%B4%EB%A6%AC%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>13조 2651억 2665만</t>
-  </si>
-  <si>
-    <t>최상급조준경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%83%81%EA%B8%89%EC%A1%B0%EC%A4%80%EA%B2%BD</t>
-  </si>
-  <si>
-    <t>12조 3616억 5359만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>11조 1019억 6605만</t>
-  </si>
-  <si>
-    <t>도맘가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A7%98%EA%B0%80</t>
-  </si>
-  <si>
-    <t>10조 9634억 6892만</t>
-  </si>
-  <si>
-    <t>으넝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%84%9D</t>
-  </si>
-  <si>
-    <t>8조 3388억 1631만</t>
-  </si>
-  <si>
-    <t>엠비피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EB%B9%84%ED%94%BC</t>
-  </si>
-  <si>
-    <t>8조 2384억 1648만</t>
-  </si>
-  <si>
-    <t>브로큰애로우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EB%A1%9C%ED%81%B0%EC%95%A0%EB%A1%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>6조 6252억 7758만</t>
-  </si>
-  <si>
-    <t>감자도리유지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%EC%9E%90%EB%8F%84%EB%A6%AC%EC%9C%A0%EC%A7%80</t>
-  </si>
-  <si>
-    <t>6조 1878억 6641만</t>
-  </si>
-  <si>
-    <t>곱동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 5587억 6389만</t>
-  </si>
-  <si>
-    <t>용감한순대국</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B0%90%ED%95%9C%EC%88%9C%EB%8C%80%EA%B5%AD</t>
-  </si>
-  <si>
-    <t>5조 3214억 9814만</t>
-  </si>
-  <si>
-    <t>곱션이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B1%EC%85%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 2972억 2548만</t>
-  </si>
-  <si>
-    <t>박예쁜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%88%EC%81%9C</t>
-  </si>
-  <si>
-    <t>4조 3707억 7387만</t>
-  </si>
-  <si>
-    <t>별밖에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B0%96%EC%97%90</t>
-  </si>
-  <si>
-    <t>3조 4472억 766만</t>
-  </si>
-  <si>
-    <t>쿰척쿰쳑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EC%B2%99%EC%BF%B0%EC%B3%91</t>
-  </si>
-  <si>
-    <t>3조 2919억 705만</t>
-  </si>
-  <si>
-    <t>딸둘아범</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B8%EB%91%98%EC%95%84%EB%B2%94</t>
-  </si>
-  <si>
-    <t>2조 9213억 3422만</t>
-  </si>
-  <si>
-    <t>김군파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B5%B0%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 5212억 3383만</t>
-  </si>
-  <si>
-    <t>옹야미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%95%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2조 926억 9665만</t>
-  </si>
-  <si>
-    <t>루맹이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%A7%B9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2조 217억 4779만</t>
-  </si>
-  <si>
-    <t>박마리아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%A7%88%EB%A6%AC%EC%95%84</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>2조 155억 9101만</t>
-  </si>
-  <si>
-    <t>한닝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8B%9D</t>
-  </si>
-  <si>
-    <t>1조 7327억 3192만</t>
-  </si>
-  <si>
-    <t>츄쁜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EC%81%9C</t>
-  </si>
-  <si>
-    <t>1조 6750억 6817만</t>
-  </si>
-  <si>
-    <t>서브장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%B8%8C%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>1조 4830억 2205만</t>
+    <t>1조 1150억 1207만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%82%A8</t>
   </si>
   <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>200조 8877억 112만</t>
+    <t>219조 8990억 6214만</t>
   </si>
   <si>
     <t>멈디</t>
@@ -1242,7 +1242,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%88%EB%94%94</t>
   </si>
   <si>
-    <t>29조 3800억 4519만</t>
+    <t>34조 6754억 4546만</t>
+  </si>
+  <si>
+    <t>표창도적도아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%8F%84%EC%A0%81%EB%8F%84%EC%95%84</t>
+  </si>
+  <si>
+    <t>18조 1369억 7023만</t>
   </si>
   <si>
     <t>유랑민</t>
@@ -1251,7 +1260,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%9E%91%EB%AF%BC</t>
   </si>
   <si>
-    <t>12조 6493억 4151만</t>
+    <t>15조 2835억 2970만</t>
   </si>
   <si>
     <t>단비둘기</t>
@@ -1260,7 +1269,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%EB%B9%84%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>10조 7140억 2340만</t>
+    <t>12조 1522억 4701만</t>
+  </si>
+  <si>
+    <t>연바기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>12조 164억 6190만</t>
+  </si>
+  <si>
+    <t>썬콜법사도희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>11조 8378억 7044만</t>
   </si>
   <si>
     <t>스라차차소스</t>
@@ -1269,7 +1296,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EB%9D%BC%EC%B0%A8%EC%B0%A8%EC%86%8C%EC%8A%A4</t>
   </si>
   <si>
-    <t>10조 4316억 5155만</t>
+    <t>10조 8787억 8473만</t>
+  </si>
+  <si>
+    <t>포도맛맥플</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
+  </si>
+  <si>
+    <t>10조 5258억 714만</t>
   </si>
   <si>
     <t>사숩</t>
@@ -1278,34 +1314,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%88%A9</t>
   </si>
   <si>
-    <t>10조 3602억 635만</t>
-  </si>
-  <si>
-    <t>썬콜법사도희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>10조 376억 6682만</t>
-  </si>
-  <si>
-    <t>연바기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>9조 7262억 2731만</t>
-  </si>
-  <si>
-    <t>포도맛맥플</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%8F%84%EB%A7%9B%EB%A7%A5%ED%94%8C</t>
-  </si>
-  <si>
-    <t>9조 3321억 5719만</t>
+    <t>10조 4477억 1164만</t>
   </si>
   <si>
     <t>또긔</t>
@@ -1314,7 +1323,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EA%B8%94</t>
   </si>
   <si>
-    <t>9조 2990억 4856만</t>
+    <t>9조 8117억 2826만</t>
   </si>
   <si>
     <t>김롸아</t>
@@ -1323,7 +1332,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%B8%EC%95%84</t>
   </si>
   <si>
-    <t>8조 3443억 8839만</t>
+    <t>8조 9210억 9249만</t>
+  </si>
+  <si>
+    <t>limno</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=limno</t>
+  </si>
+  <si>
+    <t>7조 8295억 8744만</t>
   </si>
   <si>
     <t>린샹판</t>
@@ -1332,16 +1350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%B0%EC%83%B9%ED%8C%90</t>
   </si>
   <si>
-    <t>7조 6905억 619만</t>
-  </si>
-  <si>
-    <t>limno</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=limno</t>
-  </si>
-  <si>
-    <t>7조 1717억 3885만</t>
+    <t>7조 7561억 7566만</t>
   </si>
   <si>
     <t>우치앵</t>
@@ -1350,7 +1359,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
   </si>
   <si>
-    <t>6조 4888억 4332만</t>
+    <t>7조 2039억 1907만</t>
   </si>
   <si>
     <t>A7R4</t>
@@ -1359,7 +1368,7 @@
     <t>https://mgf.gg/contents/character.php?n=A7R4</t>
   </si>
   <si>
-    <t>6조 2349억 2625만</t>
+    <t>6조 7355억 3550만</t>
   </si>
   <si>
     <t>까만색양갱</t>
@@ -1368,7 +1377,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%8C%EB%A7%8C%EC%83%89%EC%96%91%EA%B0%B1</t>
   </si>
   <si>
-    <t>5조 7923억 986만</t>
+    <t>6조 1408억 4475만</t>
   </si>
   <si>
     <t>썹웨피망빼</t>
@@ -1377,7 +1386,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%B9%EC%9B%A8%ED%94%BC%EB%A7%9D%EB%B9%BC</t>
   </si>
   <si>
-    <t>5조 1626억 3500만</t>
+    <t>5조 4028억 5113만</t>
   </si>
   <si>
     <t>불곰파워</t>
@@ -1386,7 +1395,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
   </si>
   <si>
-    <t>4조 9903억 9077만</t>
+    <t>5조 2423억 5357만</t>
   </si>
   <si>
     <t>히어로경원</t>
@@ -1395,7 +1404,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%EA%B2%BD%EC%9B%90</t>
   </si>
   <si>
-    <t>4조 9416억 3177만</t>
+    <t>5조 525억 1199만</t>
   </si>
   <si>
     <t>구파발메타몽</t>
@@ -1404,7 +1413,43 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EB%A9%94%ED%83%80%EB%AA%BD</t>
   </si>
   <si>
-    <t>4조 7396억 9365만</t>
+    <t>5조 429억 7149만</t>
+  </si>
+  <si>
+    <t>무쿠미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>4조 9241억 7052만</t>
+  </si>
+  <si>
+    <t>zl지존썬콜lz</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
+  </si>
+  <si>
+    <t>4조 7005억 4123만</t>
+  </si>
+  <si>
+    <t>낮잠중</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
+  </si>
+  <si>
+    <t>4조 6711억 2987만</t>
+  </si>
+  <si>
+    <t>구파발고양이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 6458억 283만</t>
   </si>
   <si>
     <t>투둠</t>
@@ -1416,42 +1461,6 @@
     <t>4조 6130억 4469만</t>
   </si>
   <si>
-    <t>무쿠미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>4조 5258억 1454만</t>
-  </si>
-  <si>
-    <t>구파발고양이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 2537억 3502만</t>
-  </si>
-  <si>
-    <t>낮잠중</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AE%EC%9E%A0%EC%A4%91</t>
-  </si>
-  <si>
-    <t>4조 1552억 4961만</t>
-  </si>
-  <si>
-    <t>zl지존썬콜lz</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
-  </si>
-  <si>
-    <t>4조 1512억 8022만</t>
-  </si>
-  <si>
     <t>용날라가유</t>
   </si>
   <si>
@@ -1467,16 +1476,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B9%EC%AA%BD%EC%9D%B4</t>
   </si>
   <si>
-    <t>2조 5616억 1518만</t>
-  </si>
-  <si>
-    <t>토리파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>1조 247억 2358만</t>
+    <t>2조 5752억 1048만</t>
   </si>
   <si>
     <t>닼나왕</t>
@@ -1488,7 +1488,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>1834억 3344만</t>
+    <t>1972억 8631만</t>
   </si>
   <si>
     <t>량용</t>
@@ -1497,7 +1497,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%89%EC%9A%A9</t>
   </si>
   <si>
-    <t>107조 6329억 4370만</t>
+    <t>126조 2969억 4650만</t>
   </si>
   <si>
     <t>달봉e</t>
@@ -1515,7 +1515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EB%82%98%EB%94%94%EB%8F%84%EB%91%91</t>
   </si>
   <si>
-    <t>24조 7853억 4851만</t>
+    <t>28조 5321억 3247만</t>
   </si>
   <si>
     <t>조영현2</t>
@@ -1524,13 +1524,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%98%81%ED%98%842</t>
   </si>
   <si>
-    <t>16조 8037억 7912만</t>
+    <t>22조 1080억 4513만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%86%ED%94%84</t>
   </si>
   <si>
-    <t>13조 1945억 3597만</t>
+    <t>13조 1954억 2276만</t>
   </si>
   <si>
     <t>정신못차림</t>
@@ -1539,7 +1539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%8B%A0%EB%AA%BB%EC%B0%A8%EB%A6%BC</t>
   </si>
   <si>
-    <t>9조 4650억 6351만</t>
+    <t>10조 3224억 6758만</t>
   </si>
   <si>
     <t>핫딜패스</t>
@@ -1548,7 +1548,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%AB%EB%94%9C%ED%8C%A8%EC%8A%A4</t>
   </si>
   <si>
-    <t>8조 6570억 8234만</t>
+    <t>9조 6193억 3715만</t>
+  </si>
+  <si>
+    <t>안경나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EA%B2%BD%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>9조 285억 5410만</t>
   </si>
   <si>
     <t>캔터베리</t>
@@ -1557,16 +1566,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%ED%84%B0%EB%B2%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>7조 8216억 662만</t>
-  </si>
-  <si>
-    <t>안경나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EA%B2%BD%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>7조 5968억 5172만</t>
+    <t>8조 253억 1476만</t>
   </si>
   <si>
     <t>햐밍</t>
@@ -1575,7 +1575,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%90%EB%B0%8D</t>
   </si>
   <si>
-    <t>4조 9475억 3243만</t>
+    <t>5조 2367억 5161만</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Scope</t>
+  </si>
+  <si>
+    <t>4조 9233억 2936만</t>
   </si>
   <si>
     <t>빅밥</t>
@@ -1587,15 +1596,6 @@
     <t>4조 2007억 9565만</t>
   </si>
   <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Scope</t>
-  </si>
-  <si>
-    <t>4조 589억 7815만</t>
-  </si>
-  <si>
     <t>아무렇게할래</t>
   </si>
   <si>
@@ -1683,7 +1683,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A6%88%EB%A4%BC%EC%96%BC</t>
   </si>
   <si>
-    <t>2조 1131억 2478만</t>
+    <t>2조 1354억 7842만</t>
   </si>
   <si>
     <t>Azham</t>
@@ -1719,7 +1719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%90%EC%9D%B4%EC%97%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 3318억 3388만</t>
+    <t>1조 3622억 7892만</t>
   </si>
   <si>
     <t>비라비스</t>
@@ -1758,7 +1758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%AC%B4%ED%82%A4%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>81조 4589억 2821만</t>
+    <t>82조 6589억 1302만</t>
   </si>
   <si>
     <t>원남</t>
@@ -1767,7 +1767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%82%A8</t>
   </si>
   <si>
-    <t>12조 2142억 4416만</t>
+    <t>14조 2132억 8971만</t>
   </si>
   <si>
     <t>숍솝</t>
@@ -1794,7 +1794,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4조 8359억 6222만</t>
+    <t>4조 9032억 2882만</t>
   </si>
   <si>
     <t>단정이</t>
@@ -1812,7 +1812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>2조 1272억 7513만</t>
+    <t>2조 6981억 5162만</t>
   </si>
   <si>
     <t>꼬햄</t>
@@ -1824,6 +1824,15 @@
     <t>1조 6448억 4247만</t>
   </si>
   <si>
+    <t>훈다띠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>1조 3535억 5138만</t>
+  </si>
+  <si>
     <t>사맛</t>
   </si>
   <si>
@@ -1842,15 +1851,6 @@
     <t>1조 1441억 5673만</t>
   </si>
   <si>
-    <t>훈다띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%88%EB%8B%A4%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>1조 1067억 1505만</t>
-  </si>
-  <si>
     <t>다릿골</t>
   </si>
   <si>
@@ -1872,6 +1872,24 @@
     <t>8134억 144만</t>
   </si>
   <si>
+    <t>알뺘노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%BA%98%EB%85%B8</t>
+  </si>
+  <si>
+    <t>7903억 1401만</t>
+  </si>
+  <si>
+    <t>투냉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
+  </si>
+  <si>
+    <t>7603억 4630만</t>
+  </si>
+  <si>
     <t>귀쮸</t>
   </si>
   <si>
@@ -1881,15 +1899,6 @@
     <t>7393억 7168만</t>
   </si>
   <si>
-    <t>알뺘노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%8C%EB%BA%98%EB%85%B8</t>
-  </si>
-  <si>
-    <t>6248억 4025만</t>
-  </si>
-  <si>
     <t>당겨쏴</t>
   </si>
   <si>
@@ -1911,13 +1920,13 @@
     <t>6154억 7095만</t>
   </si>
   <si>
-    <t>투냉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
-  </si>
-  <si>
-    <t>5420억 4964만</t>
+    <t>싸다만눈물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%8B%A4%EB%A7%8C%EB%88%88%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>5320억 9869만</t>
   </si>
   <si>
     <t>사과클럽</t>
@@ -1926,16 +1935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%ED%81%B4%EB%9F%BD</t>
   </si>
   <si>
-    <t>5142억 4600만</t>
-  </si>
-  <si>
-    <t>싸다만눈물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%8B%A4%EB%A7%8C%EB%88%88%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>4918억 8363만</t>
+    <t>5269억 2511만</t>
   </si>
   <si>
     <t>비비다</t>
@@ -2043,10 +2043,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EC%8B%B8</t>
   </si>
   <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>745만</t>
+    <t>60</t>
+  </si>
+  <si>
+    <t>2848만</t>
   </si>
   <si>
     <t>아포짓</t>
@@ -2055,16 +2055,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%ED%8F%AC%EC%A7%93</t>
   </si>
   <si>
-    <t>5조 7819억 2331만</t>
-  </si>
-  <si>
-    <t>야로야옹</t>
+    <t>5조 8639억 2704만</t>
+  </si>
+  <si>
+    <t>부산형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>4조 2447억 5669만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EB%A1%9C%EC%95%BC%EC%98%B9</t>
   </si>
   <si>
-    <t>4조 107억 1872만</t>
+    <t>4조 286억 2701만</t>
+  </si>
+  <si>
+    <t>딴모</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
+  </si>
+  <si>
+    <t>3조 9603억 9560만</t>
+  </si>
+  <si>
+    <t>끽스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3조 9321억 6807만</t>
+  </si>
+  <si>
+    <t>다있다하노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
+  </si>
+  <si>
+    <t>3조 8885억 5405만</t>
   </si>
   <si>
     <t>꿍물</t>
@@ -2076,55 +2109,13 @@
     <t>3조 7289억 9111만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=86%EB%AF%B8%EB%85%80</t>
-  </si>
-  <si>
-    <t>3조 4880억 7153만</t>
-  </si>
-  <si>
-    <t>딴모</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B4%EB%AA%A8</t>
-  </si>
-  <si>
-    <t>3조 4414억 3039만</t>
-  </si>
-  <si>
-    <t>다있다하노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9E%88%EB%8B%A4%ED%95%98%EB%85%B8</t>
-  </si>
-  <si>
-    <t>3조 4121억 3606만</t>
-  </si>
-  <si>
     <t>델타시그마</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>3조 3341억 9006만</t>
-  </si>
-  <si>
-    <t>끽스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3조 2479억 2338만</t>
-  </si>
-  <si>
-    <t>부산형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>3조 2412억 4239만</t>
+    <t>3조 7253억 5014만</t>
   </si>
   <si>
     <t>흑인드록바</t>
@@ -2142,7 +2133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
   </si>
   <si>
-    <t>2조 5391억 9178만</t>
+    <t>2조 9382억 5186만</t>
   </si>
   <si>
     <t>밀가루죽</t>
@@ -2160,7 +2151,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EA%B0%90</t>
   </si>
   <si>
-    <t>2조 2621억 9868만</t>
+    <t>2조 2666억 6138만</t>
   </si>
   <si>
     <t>전팡</t>
@@ -2178,7 +2169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EC%9C%A0%EC%9C%A0</t>
   </si>
   <si>
-    <t>2조 170억 6694만</t>
+    <t>2조 1556억 9854만</t>
   </si>
   <si>
     <t>사람님아</t>
@@ -2196,7 +2187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A8%B8%EC%8A%A8</t>
   </si>
   <si>
-    <t>1조 8383억 9597만</t>
+    <t>1조 9368억 357만</t>
   </si>
   <si>
     <t>하랸</t>
@@ -2214,7 +2205,34 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EC%9D%B8%ED%96%84%EC%B0%8C</t>
   </si>
   <si>
-    <t>1조 6091억 7509만</t>
+    <t>1조 7222억 6978만</t>
+  </si>
+  <si>
+    <t>뉴비i</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
+  </si>
+  <si>
+    <t>1조 6782억 3112만</t>
+  </si>
+  <si>
+    <t>섀레기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1조 3897억 7402만</t>
+  </si>
+  <si>
+    <t>민초양갱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%B4%88%EC%96%91%EA%B0%B1</t>
+  </si>
+  <si>
+    <t>1조 3860억 2488만</t>
   </si>
   <si>
     <t>비숍마로밍</t>
@@ -2235,40 +2253,13 @@
     <t>1조 3403억 9189만</t>
   </si>
   <si>
-    <t>민초양갱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%B4%88%EC%96%91%EA%B0%B1</t>
-  </si>
-  <si>
-    <t>1조 3245억 6465만</t>
-  </si>
-  <si>
-    <t>뉴비i</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
-  </si>
-  <si>
-    <t>1조 3242억 6599만</t>
-  </si>
-  <si>
-    <t>섀레기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%80%EB%A0%88%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1조 3032억 218만</t>
-  </si>
-  <si>
     <t>스피드노멘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%94%BC%EB%93%9C%EB%85%B8%EB%A9%98</t>
   </si>
   <si>
-    <t>1조 1973억 2360만</t>
+    <t>1조 2906억 2803만</t>
   </si>
   <si>
     <t>존못에겐남짱</t>
@@ -2277,7 +2268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EB%AA%BB%EC%97%90%EA%B2%90%EB%82%A8%EC%A7%B1</t>
   </si>
   <si>
-    <t>1조 1128억 7938만</t>
+    <t>1조 1366억 4584만</t>
   </si>
   <si>
     <t>두부장구니</t>
@@ -2304,7 +2295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9E%84%EB%AA%BD%EC%88%9C</t>
   </si>
   <si>
-    <t>6990억 7457만</t>
+    <t>7260억 9388만</t>
   </si>
   <si>
     <t>오리박사</t>
@@ -2313,7 +2304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A6%AC%EB%B0%95%EC%82%AC</t>
   </si>
   <si>
-    <t>5097억 9699만</t>
+    <t>5438억 1157만</t>
   </si>
 </sst>
 </file>
@@ -2797,17 +2788,15 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
@@ -2838,15 +2827,17 @@
         <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>40</v>
       </c>
@@ -2874,20 +2865,20 @@
         <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2895,25 +2886,25 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2922,13 +2913,13 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2936,40 +2927,40 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>24</v>
@@ -2977,31 +2968,31 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>70</v>
@@ -3257,13 +3248,13 @@
         <v>84</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3274,25 +3265,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>118</v>
@@ -3417,13 +3408,13 @@
         <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3434,28 +3425,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3466,25 +3457,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>147</v>
@@ -3513,7 +3504,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>127</v>
@@ -3580,7 +3571,7 @@
         <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>159</v>
@@ -3673,13 +3664,13 @@
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3690,25 +3681,25 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>176</v>
@@ -3737,7 +3728,7 @@
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>127</v>
@@ -3769,13 +3760,13 @@
         <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3786,25 +3777,25 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>189</v>
@@ -3833,13 +3824,13 @@
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3850,25 +3841,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>198</v>
@@ -3897,10 +3888,10 @@
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>202</v>
@@ -3932,7 +3923,7 @@
         <v>102</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>206</v>
@@ -3964,7 +3955,7 @@
         <v>102</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>210</v>
@@ -3996,7 +3987,7 @@
         <v>126</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>214</v>
@@ -4028,7 +4019,7 @@
         <v>126</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>218</v>
@@ -4142,13 +4133,13 @@
         <v>84</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>86</v>
+        <v>221</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4162,13 +4153,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -4177,10 +4168,10 @@
         <v>85</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4194,25 +4185,25 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4226,13 +4217,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -4241,10 +4232,10 @@
         <v>126</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4258,25 +4249,25 @@
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>126</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4290,25 +4281,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4319,28 +4310,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4354,25 +4345,25 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4386,25 +4377,25 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4418,13 +4409,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -4433,10 +4424,10 @@
         <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4450,25 +4441,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>248</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>248</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4479,28 +4470,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4511,28 +4502,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4546,25 +4537,25 @@
         <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4578,25 +4569,25 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4610,25 +4601,25 @@
         <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4642,13 +4633,13 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -4657,10 +4648,10 @@
         <v>126</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4674,25 +4665,25 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4706,13 +4697,13 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -4721,10 +4712,10 @@
         <v>126</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4735,28 +4726,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4770,25 +4761,25 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4802,25 +4793,25 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4831,28 +4822,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4866,25 +4857,25 @@
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4895,28 +4886,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4930,25 +4921,25 @@
         <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4962,25 +4953,25 @@
         <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>141</v>
+        <v>299</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4994,25 +4985,25 @@
         <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5026,25 +5017,25 @@
         <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5058,25 +5049,25 @@
         <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>141</v>
+        <v>299</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5175,25 +5166,25 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5207,13 +5198,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -5222,10 +5213,10 @@
         <v>85</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5239,25 +5230,25 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5271,13 +5262,13 @@
         <v>99</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -5286,10 +5277,10 @@
         <v>126</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5303,25 +5294,25 @@
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5335,25 +5326,25 @@
         <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5364,28 +5355,28 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5399,25 +5390,25 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5431,25 +5422,25 @@
         <v>123</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5463,25 +5454,25 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5495,25 +5486,25 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5524,28 +5515,28 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5556,28 +5547,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5591,13 +5582,13 @@
         <v>148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -5609,7 +5600,7 @@
         <v>127</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5623,25 +5614,25 @@
         <v>152</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5655,25 +5646,25 @@
         <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5687,25 +5678,25 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5719,25 +5710,25 @@
         <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5751,25 +5742,25 @@
         <v>168</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5780,28 +5771,28 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5815,25 +5806,25 @@
         <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5847,13 +5838,13 @@
         <v>181</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -5862,10 +5853,10 @@
         <v>126</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5876,28 +5867,28 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5911,25 +5902,25 @@
         <v>190</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5940,28 +5931,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5975,25 +5966,25 @@
         <v>199</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6007,25 +5998,25 @@
         <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>387</v>
+        <v>146</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6039,25 +6030,25 @@
         <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6071,25 +6062,25 @@
         <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6103,25 +6094,25 @@
         <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>387</v>
+        <v>146</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6176,7 +6167,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6220,13 +6211,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>96</v>
@@ -6235,7 +6226,7 @@
         <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>399</v>
+        <v>221</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>400</v>
@@ -6264,7 +6255,7 @@
         <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>127</v>
@@ -6296,7 +6287,7 @@
         <v>84</v>
       </c>
       <c r="G4" s="2" t="s">